--- a/data/portfolio.xlsx
+++ b/data/portfolio.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="194">
   <si>
     <t>Self/Other Remarks</t>
   </si>
@@ -46,90 +46,78 @@
     <t>Remarks</t>
   </si>
   <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>3MINDIA</t>
+  </si>
+  <si>
+    <t>3,94,247.35</t>
+  </si>
+  <si>
+    <t>3,93,360.00</t>
+  </si>
+  <si>
+    <t>2.Mar'26 Must buy</t>
+  </si>
+  <si>
+    <t>MUSTBUY</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
-    <t>NH</t>
-  </si>
-  <si>
-    <t>1,83,396.90</t>
-  </si>
-  <si>
-    <t>7,00,989</t>
-  </si>
-  <si>
-    <t>5,17,592.40</t>
+    <t>HCG</t>
+  </si>
+  <si>
+    <t>1,91,353.60</t>
+  </si>
+  <si>
+    <t>3,91,161</t>
+  </si>
+  <si>
+    <t>1,99,807.10</t>
   </si>
   <si>
     <t>Self</t>
   </si>
   <si>
+    <t>AEROFLEX</t>
+  </si>
+  <si>
+    <t>1,79,710.57</t>
+  </si>
+  <si>
+    <t>3,90,048.00</t>
+  </si>
+  <si>
+    <t>2,10,337.43</t>
+  </si>
+  <si>
+    <t>SONACOMS</t>
+  </si>
+  <si>
+    <t>3,08,749.05</t>
+  </si>
+  <si>
+    <t>3,40,800.00</t>
+  </si>
+  <si>
+    <t>SYRMA</t>
+  </si>
+  <si>
+    <t>1,24,501.80</t>
+  </si>
+  <si>
+    <t>3,31,310</t>
+  </si>
+  <si>
+    <t>2,06,807.80</t>
+  </si>
+  <si>
     <t>Others</t>
   </si>
   <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>3MINDIA</t>
-  </si>
-  <si>
-    <t>3,94,247.35</t>
-  </si>
-  <si>
-    <t>3,93,360.00</t>
-  </si>
-  <si>
-    <t>2.Mar'26 Must buy</t>
-  </si>
-  <si>
-    <t>MUSTBUY</t>
-  </si>
-  <si>
-    <t>HCG</t>
-  </si>
-  <si>
-    <t>1,91,353.60</t>
-  </si>
-  <si>
-    <t>3,91,161</t>
-  </si>
-  <si>
-    <t>1,99,807.10</t>
-  </si>
-  <si>
-    <t>AEROFLEX</t>
-  </si>
-  <si>
-    <t>1,79,710.57</t>
-  </si>
-  <si>
-    <t>3,90,048.00</t>
-  </si>
-  <si>
-    <t>2,10,337.43</t>
-  </si>
-  <si>
-    <t>SONACOMS</t>
-  </si>
-  <si>
-    <t>3,08,749.05</t>
-  </si>
-  <si>
-    <t>3,40,800.00</t>
-  </si>
-  <si>
-    <t>SYRMA</t>
-  </si>
-  <si>
-    <t>1,24,501.80</t>
-  </si>
-  <si>
-    <t>3,31,310</t>
-  </si>
-  <si>
-    <t>2,06,807.80</t>
-  </si>
-  <si>
     <t>PARKHOSPS</t>
   </si>
   <si>
@@ -605,9 +593,6 @@
   </si>
   <si>
     <t>SUVEN</t>
-  </si>
-  <si>
-    <t>MAFANG</t>
   </si>
 </sst>
 </file>
@@ -931,72 +916,72 @@
         <v>12</v>
       </c>
       <c r="C2" s="1">
-        <v>369.0</v>
-      </c>
-      <c r="D2" s="1">
-        <v>497.01</v>
+        <v>12.0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>32853.95</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="2">
-        <v>1899.7</v>
+        <v>32780.0</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="1">
+        <v>-887.35</v>
+      </c>
+      <c r="I2" s="3">
+        <v>-0.0023</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="3">
-        <v>2.8223</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1">
+        <v>609.0</v>
+      </c>
+      <c r="D3" s="1">
+        <v>314.21</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>32853.95</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1">
+        <v>642.3</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="2">
-        <v>32780.0</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="1">
-        <v>-887.35</v>
-      </c>
       <c r="I3" s="3">
-        <v>-0.0023</v>
+        <v>1.0442</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -1004,113 +989,113 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="1">
+        <v>960.0</v>
+      </c>
+      <c r="D4" s="1">
+        <v>187.2</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="1">
-        <v>609.0</v>
-      </c>
-      <c r="D4" s="1">
-        <v>314.21</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1">
+        <v>406.3</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="1">
-        <v>642.3</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="I4" s="3">
-        <v>1.0442</v>
+        <v>1.1704</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1">
+        <v>568.0</v>
+      </c>
+      <c r="D5" s="1">
+        <v>543.57</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="1">
-        <v>960.0</v>
-      </c>
-      <c r="D5" s="1">
-        <v>187.2</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1">
+        <v>600.0</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="1">
-        <v>406.3</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>31</v>
+      <c r="H5" s="2">
+        <v>32050.95</v>
       </c>
       <c r="I5" s="3">
-        <v>1.1704</v>
+        <v>0.1038</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="1">
+        <v>289.0</v>
+      </c>
+      <c r="D6" s="1">
+        <v>430.8</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1146.4</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="1">
-        <v>568.0</v>
-      </c>
-      <c r="D6" s="1">
-        <v>543.57</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="1">
-        <v>600.0</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" s="2">
-        <v>32050.95</v>
-      </c>
       <c r="I6" s="3">
-        <v>0.1038</v>
+        <v>1.6611</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -1121,16 +1106,16 @@
         <v>35</v>
       </c>
       <c r="C7" s="1">
-        <v>289.0</v>
+        <v>896.0</v>
       </c>
       <c r="D7" s="1">
-        <v>430.8</v>
+        <v>158.81</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="2">
-        <v>1146.4</v>
+      <c r="F7" s="1">
+        <v>279.9</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>37</v>
@@ -1139,36 +1124,36 @@
         <v>38</v>
       </c>
       <c r="I7" s="3">
-        <v>1.6611</v>
+        <v>0.7625</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" s="1">
-        <v>896.0</v>
-      </c>
-      <c r="D8" s="1">
-        <v>158.81</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="1">
-        <v>279.9</v>
+        <v>26.0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1514.93</v>
+      </c>
+      <c r="E8" s="2">
+        <v>39388.3</v>
+      </c>
+      <c r="F8" s="2">
+        <v>7107.0</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>41</v>
@@ -1177,16 +1162,16 @@
         <v>42</v>
       </c>
       <c r="I8" s="3">
-        <v>0.7625</v>
+        <v>3.6913</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
@@ -1194,265 +1179,265 @@
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="1">
+        <v>255.0</v>
+      </c>
+      <c r="D9" s="1">
+        <v>261.86</v>
+      </c>
+      <c r="E9" s="2">
+        <v>66773.95</v>
+      </c>
+      <c r="F9" s="1">
+        <v>636.0</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="1">
-        <v>26.0</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1514.93</v>
-      </c>
-      <c r="E9" s="2">
-        <v>39388.3</v>
-      </c>
-      <c r="F9" s="2">
-        <v>7107.0</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>46</v>
+      <c r="H9" s="2">
+        <v>95406.05</v>
       </c>
       <c r="I9" s="3">
-        <v>3.6913</v>
+        <v>1.4288</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1">
-        <v>255.0</v>
-      </c>
-      <c r="D10" s="1">
-        <v>261.86</v>
+        <v>56.0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1524.46</v>
       </c>
       <c r="E10" s="2">
-        <v>66773.95</v>
-      </c>
-      <c r="F10" s="1">
-        <v>636.0</v>
+        <v>85369.7</v>
+      </c>
+      <c r="F10" s="2">
+        <v>2892.7</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2">
-        <v>95406.05</v>
+        <v>76621.5</v>
       </c>
       <c r="I10" s="3">
-        <v>1.4288</v>
+        <v>0.8975</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="1">
+        <v>230.0</v>
+      </c>
+      <c r="D11" s="1">
+        <v>551.14</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="1">
+        <v>680.35</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="1">
-        <v>56.0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1524.46</v>
-      </c>
-      <c r="E11" s="2">
-        <v>85369.7</v>
-      </c>
-      <c r="F11" s="2">
-        <v>2892.7</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="H11" s="2">
-        <v>76621.5</v>
+        <v>29717.35</v>
       </c>
       <c r="I11" s="3">
-        <v>0.8975</v>
+        <v>0.2344</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>4430.55</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="1">
-        <v>230.0</v>
-      </c>
-      <c r="D12" s="1">
-        <v>551.14</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="2">
+        <v>4868.0</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="1">
-        <v>680.35</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="H12" s="2">
-        <v>29717.35</v>
+        <v>13123.5</v>
       </c>
       <c r="I12" s="3">
-        <v>0.2344</v>
+        <v>0.0987</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="1">
+        <v>245.0</v>
+      </c>
+      <c r="D13" s="1">
+        <v>552.93</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>4430.55</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1">
+        <v>579.5</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="2">
-        <v>4868.0</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="H13" s="2">
-        <v>13123.5</v>
+        <v>6509.6</v>
       </c>
       <c r="I13" s="3">
-        <v>0.0987</v>
+        <v>0.0481</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>2195.91</v>
+      </c>
+      <c r="E14" s="2">
+        <v>8783.65</v>
+      </c>
+      <c r="F14" s="2">
+        <v>35450.0</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="1">
-        <v>245.0</v>
-      </c>
-      <c r="D14" s="1">
-        <v>552.93</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="1">
-        <v>579.5</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H14" s="2">
-        <v>6509.6</v>
-      </c>
       <c r="I14" s="3">
-        <v>0.0481</v>
+        <v>15.1436</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="1">
+        <v>101.0</v>
+      </c>
+      <c r="D15" s="1">
+        <v>224.73</v>
+      </c>
+      <c r="E15" s="2">
+        <v>22697.7</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1355.8</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="D15" s="2">
-        <v>2195.91</v>
-      </c>
-      <c r="E15" s="2">
-        <v>8783.65</v>
-      </c>
-      <c r="F15" s="2">
-        <v>35450.0</v>
-      </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="I15" s="3">
-        <v>15.1436</v>
+        <v>5.033</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -1460,75 +1445,75 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>4330.32</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="1">
-        <v>101.0</v>
-      </c>
-      <c r="D16" s="1">
-        <v>224.73</v>
-      </c>
-      <c r="E16" s="2">
-        <v>22697.7</v>
-      </c>
       <c r="F16" s="2">
-        <v>1355.8</v>
+        <v>3732.0</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>65</v>
+      <c r="H16" s="2">
+        <v>-21539.7</v>
       </c>
       <c r="I16" s="3">
-        <v>5.033</v>
+        <v>-0.1382</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L16" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="1">
+        <v>183.0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>283.78</v>
+      </c>
+      <c r="E17" s="2">
+        <v>51931.5</v>
+      </c>
+      <c r="F17" s="1">
+        <v>729.0</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="1">
-        <v>36.0</v>
-      </c>
-      <c r="D17" s="2">
-        <v>4330.32</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F17" s="2">
-        <v>3732.0</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="H17" s="2">
-        <v>-21539.7</v>
+        <v>81475.5</v>
       </c>
       <c r="I17" s="3">
-        <v>-0.1382</v>
+        <v>1.5689</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
@@ -1536,113 +1521,113 @@
         <v>11</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1465.0</v>
+      </c>
+      <c r="D18" s="1">
+        <v>74.72</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" s="1">
+        <v>72.32</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="1">
-        <v>183.0</v>
-      </c>
-      <c r="D18" s="1">
-        <v>283.78</v>
-      </c>
-      <c r="E18" s="2">
-        <v>51931.5</v>
-      </c>
-      <c r="F18" s="1">
-        <v>729.0</v>
-      </c>
-      <c r="G18" s="1" t="s">
+      <c r="H18" s="2">
+        <v>-3513.75</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-0.0321</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H18" s="2">
-        <v>81475.5</v>
-      </c>
-      <c r="I18" s="3">
-        <v>1.5689</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K18" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="4">
-        <v>1465.0</v>
+      <c r="C19" s="1">
+        <v>164.0</v>
       </c>
       <c r="D19" s="1">
-        <v>74.72</v>
-      </c>
-      <c r="E19" s="1" t="s">
+        <v>606.55</v>
+      </c>
+      <c r="E19" s="2">
+        <v>99474.25</v>
+      </c>
+      <c r="F19" s="1">
+        <v>636.7</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F19" s="1">
-        <v>72.32</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="H19" s="2">
-        <v>-3513.75</v>
+        <v>4944.55</v>
       </c>
       <c r="I19" s="3">
-        <v>-0.0321</v>
+        <v>0.0497</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C20" s="1">
-        <v>164.0</v>
-      </c>
-      <c r="D20" s="1">
-        <v>606.55</v>
+        <v>6.0</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1031.85</v>
       </c>
       <c r="E20" s="2">
-        <v>99474.25</v>
-      </c>
-      <c r="F20" s="1">
-        <v>636.7</v>
+        <v>6191.1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>16836.05</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H20" s="2">
-        <v>4944.55</v>
+        <v>94825.2</v>
       </c>
       <c r="I20" s="3">
-        <v>0.0497</v>
+        <v>15.3164</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
@@ -1650,75 +1635,75 @@
         <v>11</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C21" s="1">
-        <v>6.0</v>
+        <v>68.0</v>
       </c>
       <c r="D21" s="2">
-        <v>1031.85</v>
+        <v>1182.81</v>
       </c>
       <c r="E21" s="2">
-        <v>6191.1</v>
+        <v>80431.2</v>
       </c>
       <c r="F21" s="2">
-        <v>16836.05</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>78</v>
+        <v>1453.0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>98804.0</v>
       </c>
       <c r="H21" s="2">
-        <v>94825.2</v>
+        <v>18372.8</v>
       </c>
       <c r="I21" s="3">
-        <v>15.3164</v>
+        <v>0.2284</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L21" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C22" s="1">
-        <v>68.0</v>
-      </c>
-      <c r="D22" s="2">
-        <v>1182.81</v>
+        <v>540.0</v>
+      </c>
+      <c r="D22" s="1">
+        <v>13.39</v>
       </c>
       <c r="E22" s="2">
-        <v>80431.2</v>
-      </c>
-      <c r="F22" s="2">
-        <v>1453.0</v>
-      </c>
-      <c r="G22" s="2">
-        <v>98804.0</v>
+        <v>7229.6</v>
+      </c>
+      <c r="F22" s="1">
+        <v>176.0</v>
+      </c>
+      <c r="G22" s="4">
+        <v>95040.0</v>
       </c>
       <c r="H22" s="2">
-        <v>18372.8</v>
+        <v>87810.4</v>
       </c>
       <c r="I22" s="3">
-        <v>0.2284</v>
+        <v>12.146</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -1726,341 +1711,341 @@
         <v>11</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C23" s="1">
-        <v>540.0</v>
+        <v>350.0</v>
       </c>
       <c r="D23" s="1">
-        <v>13.39</v>
+        <v>165.99</v>
       </c>
       <c r="E23" s="2">
-        <v>7229.6</v>
+        <v>58095.38</v>
       </c>
       <c r="F23" s="1">
-        <v>176.0</v>
-      </c>
-      <c r="G23" s="4">
-        <v>95040.0</v>
+        <v>266.7</v>
+      </c>
+      <c r="G23" s="2">
+        <v>93345.0</v>
       </c>
       <c r="H23" s="2">
-        <v>87810.4</v>
+        <v>35249.62</v>
       </c>
       <c r="I23" s="3">
-        <v>12.146</v>
+        <v>0.6068</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C24" s="1">
-        <v>350.0</v>
+        <v>190.0</v>
       </c>
       <c r="D24" s="1">
-        <v>165.99</v>
+        <v>480.82</v>
       </c>
       <c r="E24" s="2">
-        <v>58095.38</v>
+        <v>91356.6</v>
       </c>
       <c r="F24" s="1">
-        <v>266.7</v>
+        <v>477.1</v>
       </c>
       <c r="G24" s="2">
-        <v>93345.0</v>
-      </c>
-      <c r="H24" s="2">
-        <v>35249.62</v>
+        <v>90649.0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>-707.6</v>
       </c>
       <c r="I24" s="3">
-        <v>0.6068</v>
+        <v>-0.0077</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C25" s="1">
-        <v>190.0</v>
+        <v>246.0</v>
       </c>
       <c r="D25" s="1">
-        <v>480.82</v>
+        <v>384.17</v>
       </c>
       <c r="E25" s="2">
-        <v>91356.6</v>
+        <v>94506.1</v>
       </c>
       <c r="F25" s="1">
-        <v>477.1</v>
+        <v>363.15</v>
       </c>
       <c r="G25" s="2">
-        <v>90649.0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>-707.6</v>
+        <v>89334.9</v>
+      </c>
+      <c r="H25" s="2">
+        <v>-5171.2</v>
       </c>
       <c r="I25" s="3">
-        <v>-0.0077</v>
+        <v>-0.0547</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C26" s="1">
-        <v>246.0</v>
+        <v>97.0</v>
       </c>
       <c r="D26" s="1">
-        <v>384.17</v>
+        <v>768.77</v>
       </c>
       <c r="E26" s="2">
-        <v>94506.1</v>
+        <v>74571.2</v>
       </c>
       <c r="F26" s="1">
-        <v>363.15</v>
+        <v>903.1</v>
       </c>
       <c r="G26" s="2">
-        <v>89334.9</v>
+        <v>87600.7</v>
       </c>
       <c r="H26" s="2">
-        <v>-5171.2</v>
+        <v>13029.5</v>
       </c>
       <c r="I26" s="3">
-        <v>-0.0547</v>
+        <v>0.1747</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C27" s="1">
         <v>97.0</v>
       </c>
-      <c r="D27" s="1">
-        <v>768.77</v>
-      </c>
-      <c r="E27" s="2">
-        <v>74571.2</v>
+      <c r="D27" s="2">
+        <v>1054.87</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="F27" s="1">
-        <v>903.1</v>
+        <v>902.3</v>
       </c>
       <c r="G27" s="2">
-        <v>87600.7</v>
+        <v>87523.1</v>
       </c>
       <c r="H27" s="2">
-        <v>13029.5</v>
+        <v>-14799.45</v>
       </c>
       <c r="I27" s="3">
-        <v>0.1747</v>
+        <v>-0.1446</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C28" s="1">
-        <v>97.0</v>
-      </c>
-      <c r="D28" s="2">
-        <v>1054.87</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>86</v>
+        <v>269.0</v>
+      </c>
+      <c r="D28" s="1">
+        <v>171.27</v>
+      </c>
+      <c r="E28" s="2">
+        <v>46072.27</v>
       </c>
       <c r="F28" s="1">
-        <v>902.3</v>
+        <v>313.7</v>
       </c>
       <c r="G28" s="2">
-        <v>87523.1</v>
+        <v>84385.3</v>
       </c>
       <c r="H28" s="2">
-        <v>-14799.45</v>
+        <v>38313.03</v>
       </c>
       <c r="I28" s="3">
-        <v>-0.1446</v>
+        <v>0.8316</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C29" s="1">
-        <v>269.0</v>
-      </c>
-      <c r="D29" s="1">
-        <v>171.27</v>
+        <v>59.0</v>
+      </c>
+      <c r="D29" s="2">
+        <v>1056.13</v>
       </c>
       <c r="E29" s="2">
-        <v>46072.27</v>
-      </c>
-      <c r="F29" s="1">
-        <v>313.7</v>
+        <v>62311.85</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1418.0</v>
       </c>
       <c r="G29" s="2">
-        <v>84385.3</v>
+        <v>83662.0</v>
       </c>
       <c r="H29" s="2">
-        <v>38313.03</v>
+        <v>21350.15</v>
       </c>
       <c r="I29" s="3">
-        <v>0.8316</v>
+        <v>0.3426</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C30" s="1">
-        <v>59.0</v>
+        <v>69.0</v>
       </c>
       <c r="D30" s="2">
-        <v>1056.13</v>
+        <v>1213.45</v>
       </c>
       <c r="E30" s="2">
-        <v>62311.85</v>
+        <v>83728.4</v>
       </c>
       <c r="F30" s="2">
-        <v>1418.0</v>
+        <v>1165.95</v>
       </c>
       <c r="G30" s="2">
-        <v>83662.0</v>
+        <v>80450.55</v>
       </c>
       <c r="H30" s="2">
-        <v>21350.15</v>
+        <v>-3277.85</v>
       </c>
       <c r="I30" s="3">
-        <v>0.3426</v>
+        <v>-0.0391</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C31" s="1">
-        <v>69.0</v>
-      </c>
-      <c r="D31" s="2">
-        <v>1213.45</v>
+        <v>300.0</v>
+      </c>
+      <c r="D31" s="1">
+        <v>220.39</v>
       </c>
       <c r="E31" s="2">
-        <v>83728.4</v>
-      </c>
-      <c r="F31" s="2">
-        <v>1165.95</v>
-      </c>
-      <c r="G31" s="2">
-        <v>80450.55</v>
+        <v>66117.0</v>
+      </c>
+      <c r="F31" s="1">
+        <v>265.09</v>
+      </c>
+      <c r="G31" s="4">
+        <v>79527.0</v>
       </c>
       <c r="H31" s="2">
-        <v>-3277.85</v>
+        <v>13410.0</v>
       </c>
       <c r="I31" s="3">
-        <v>-0.0391</v>
+        <v>0.2028</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32">
@@ -2068,417 +2053,417 @@
         <v>11</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C32" s="1">
-        <v>300.0</v>
+        <v>100.0</v>
       </c>
       <c r="D32" s="1">
-        <v>220.39</v>
+        <v>290.95</v>
       </c>
       <c r="E32" s="2">
-        <v>66117.0</v>
+        <v>29095.0</v>
       </c>
       <c r="F32" s="1">
-        <v>265.09</v>
-      </c>
-      <c r="G32" s="4">
-        <v>79527.0</v>
+        <v>789.0</v>
+      </c>
+      <c r="G32" s="2">
+        <v>78900.0</v>
       </c>
       <c r="H32" s="2">
-        <v>13410.0</v>
+        <v>49805.0</v>
       </c>
       <c r="I32" s="3">
-        <v>0.2028</v>
+        <v>1.7118</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C33" s="1">
-        <v>100.0</v>
-      </c>
-      <c r="D33" s="1">
-        <v>290.95</v>
+        <v>33.0</v>
+      </c>
+      <c r="D33" s="2">
+        <v>1504.07</v>
       </c>
       <c r="E33" s="2">
-        <v>29095.0</v>
-      </c>
-      <c r="F33" s="1">
-        <v>789.0</v>
+        <v>49634.3</v>
+      </c>
+      <c r="F33" s="2">
+        <v>2344.0</v>
       </c>
       <c r="G33" s="2">
-        <v>78900.0</v>
+        <v>77352.0</v>
       </c>
       <c r="H33" s="2">
-        <v>49805.0</v>
+        <v>27717.7</v>
       </c>
       <c r="I33" s="3">
-        <v>1.7118</v>
+        <v>0.5584</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C34" s="1">
-        <v>33.0</v>
-      </c>
-      <c r="D34" s="2">
-        <v>1504.07</v>
+        <v>184.0</v>
+      </c>
+      <c r="D34" s="1">
+        <v>431.44</v>
       </c>
       <c r="E34" s="2">
-        <v>49634.3</v>
-      </c>
-      <c r="F34" s="2">
-        <v>2344.0</v>
+        <v>79384.9</v>
+      </c>
+      <c r="F34" s="1">
+        <v>414.85</v>
       </c>
       <c r="G34" s="2">
-        <v>77352.0</v>
+        <v>76332.4</v>
       </c>
       <c r="H34" s="2">
-        <v>27717.7</v>
+        <v>-3052.5</v>
       </c>
       <c r="I34" s="3">
-        <v>0.5584</v>
+        <v>-0.0385</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C35" s="1">
-        <v>184.0</v>
-      </c>
-      <c r="D35" s="1">
-        <v>431.44</v>
+        <v>21.0</v>
+      </c>
+      <c r="D35" s="2">
+        <v>3292.31</v>
       </c>
       <c r="E35" s="2">
-        <v>79384.9</v>
-      </c>
-      <c r="F35" s="1">
-        <v>414.85</v>
+        <v>69138.6</v>
+      </c>
+      <c r="F35" s="2">
+        <v>3620.7</v>
       </c>
       <c r="G35" s="2">
-        <v>76332.4</v>
+        <v>76034.7</v>
       </c>
       <c r="H35" s="2">
-        <v>-3052.5</v>
+        <v>6896.1</v>
       </c>
       <c r="I35" s="3">
-        <v>-0.0385</v>
+        <v>0.0997</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C36" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="D36" s="2">
-        <v>3292.31</v>
+        <v>87.0</v>
+      </c>
+      <c r="D36" s="1">
+        <v>903.4</v>
       </c>
       <c r="E36" s="2">
-        <v>69138.6</v>
-      </c>
-      <c r="F36" s="2">
-        <v>3620.7</v>
+        <v>78595.7</v>
+      </c>
+      <c r="F36" s="1">
+        <v>858.0</v>
       </c>
       <c r="G36" s="2">
-        <v>76034.7</v>
+        <v>74646.0</v>
       </c>
       <c r="H36" s="2">
-        <v>6896.1</v>
+        <v>-3949.7</v>
       </c>
       <c r="I36" s="3">
-        <v>0.0997</v>
+        <v>-0.0503</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C37" s="1">
-        <v>87.0</v>
+        <v>205.0</v>
       </c>
       <c r="D37" s="1">
-        <v>903.4</v>
+        <v>283.62</v>
       </c>
       <c r="E37" s="2">
-        <v>78595.7</v>
+        <v>58141.81</v>
       </c>
       <c r="F37" s="1">
-        <v>858.0</v>
+        <v>362.05</v>
       </c>
       <c r="G37" s="2">
-        <v>74646.0</v>
+        <v>74220.25</v>
       </c>
       <c r="H37" s="2">
-        <v>-3949.7</v>
+        <v>16078.44</v>
       </c>
       <c r="I37" s="3">
-        <v>-0.0503</v>
+        <v>0.2765</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C38" s="1">
-        <v>205.0</v>
-      </c>
-      <c r="D38" s="1">
-        <v>283.62</v>
+        <v>26.0</v>
+      </c>
+      <c r="D38" s="2">
+        <v>2476.12</v>
       </c>
       <c r="E38" s="2">
-        <v>58141.81</v>
-      </c>
-      <c r="F38" s="1">
-        <v>362.05</v>
+        <v>64379.15</v>
+      </c>
+      <c r="F38" s="2">
+        <v>2850.7</v>
       </c>
       <c r="G38" s="2">
-        <v>74220.25</v>
+        <v>74118.2</v>
       </c>
       <c r="H38" s="2">
-        <v>16078.44</v>
+        <v>9739.05</v>
       </c>
       <c r="I38" s="3">
-        <v>0.2765</v>
+        <v>0.1513</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C39" s="1">
-        <v>26.0</v>
-      </c>
-      <c r="D39" s="2">
-        <v>2476.12</v>
+        <v>215.0</v>
+      </c>
+      <c r="D39" s="1">
+        <v>255.12</v>
       </c>
       <c r="E39" s="2">
-        <v>64379.15</v>
-      </c>
-      <c r="F39" s="2">
-        <v>2850.7</v>
+        <v>54850.65</v>
+      </c>
+      <c r="F39" s="1">
+        <v>342.9</v>
       </c>
       <c r="G39" s="2">
-        <v>74118.2</v>
+        <v>73723.5</v>
       </c>
       <c r="H39" s="2">
-        <v>9739.05</v>
+        <v>18872.85</v>
       </c>
       <c r="I39" s="3">
-        <v>0.1513</v>
+        <v>0.3441</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C40" s="1">
-        <v>215.0</v>
+        <v>171.0</v>
       </c>
       <c r="D40" s="1">
-        <v>255.12</v>
+        <v>402.08</v>
       </c>
       <c r="E40" s="2">
-        <v>54850.65</v>
+        <v>68755.95</v>
       </c>
       <c r="F40" s="1">
-        <v>342.9</v>
+        <v>427.15</v>
       </c>
       <c r="G40" s="2">
-        <v>73723.5</v>
+        <v>73042.65</v>
       </c>
       <c r="H40" s="2">
-        <v>18872.85</v>
+        <v>4286.7</v>
       </c>
       <c r="I40" s="3">
-        <v>0.3441</v>
+        <v>0.0623</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C41" s="1">
-        <v>171.0</v>
+        <v>139.0</v>
       </c>
       <c r="D41" s="1">
-        <v>402.08</v>
+        <v>545.81</v>
       </c>
       <c r="E41" s="2">
-        <v>68755.95</v>
+        <v>75867.25</v>
       </c>
       <c r="F41" s="1">
-        <v>427.15</v>
+        <v>511.9</v>
       </c>
       <c r="G41" s="2">
-        <v>73042.65</v>
+        <v>71154.1</v>
       </c>
       <c r="H41" s="2">
-        <v>4286.7</v>
+        <v>-4713.15</v>
       </c>
       <c r="I41" s="3">
-        <v>0.0623</v>
+        <v>-0.0621</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C42" s="1">
-        <v>139.0</v>
+        <v>401.0</v>
       </c>
       <c r="D42" s="1">
-        <v>545.81</v>
+        <v>91.09</v>
       </c>
       <c r="E42" s="2">
-        <v>75867.25</v>
+        <v>36527.75</v>
       </c>
       <c r="F42" s="1">
-        <v>511.9</v>
-      </c>
-      <c r="G42" s="2">
-        <v>71154.1</v>
+        <v>175.85</v>
+      </c>
+      <c r="G42" s="4">
+        <v>70516.0</v>
       </c>
       <c r="H42" s="2">
-        <v>-4713.15</v>
+        <v>33988.1</v>
       </c>
       <c r="I42" s="3">
-        <v>-0.0621</v>
+        <v>0.9305</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43">
@@ -2486,835 +2471,835 @@
         <v>11</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C43" s="1">
-        <v>401.0</v>
-      </c>
-      <c r="D43" s="1">
-        <v>91.09</v>
+        <v>51.0</v>
+      </c>
+      <c r="D43" s="2">
+        <v>1099.22</v>
       </c>
       <c r="E43" s="2">
-        <v>36527.75</v>
-      </c>
-      <c r="F43" s="1">
-        <v>175.85</v>
-      </c>
-      <c r="G43" s="4">
-        <v>70516.0</v>
+        <v>56060.4</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1368.0</v>
+      </c>
+      <c r="G43" s="2">
+        <v>69768.0</v>
       </c>
       <c r="H43" s="2">
-        <v>33988.1</v>
+        <v>13707.6</v>
       </c>
       <c r="I43" s="3">
-        <v>0.9305</v>
+        <v>0.2445</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L43" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C44" s="1">
-        <v>51.0</v>
+        <v>37.0</v>
       </c>
       <c r="D44" s="2">
-        <v>1099.22</v>
+        <v>2033.06</v>
       </c>
       <c r="E44" s="2">
-        <v>56060.4</v>
+        <v>75223.3</v>
       </c>
       <c r="F44" s="2">
-        <v>1368.0</v>
+        <v>1836.3</v>
       </c>
       <c r="G44" s="2">
-        <v>69768.0</v>
+        <v>67943.1</v>
       </c>
       <c r="H44" s="2">
-        <v>13707.6</v>
+        <v>-7280.2</v>
       </c>
       <c r="I44" s="3">
-        <v>0.2445</v>
+        <v>-0.0968</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C45" s="1">
-        <v>37.0</v>
-      </c>
-      <c r="D45" s="2">
-        <v>2033.06</v>
+        <v>546.0</v>
+      </c>
+      <c r="D45" s="1">
+        <v>135.91</v>
       </c>
       <c r="E45" s="2">
-        <v>75223.3</v>
-      </c>
-      <c r="F45" s="2">
-        <v>1836.3</v>
+        <v>74208.27</v>
+      </c>
+      <c r="F45" s="1">
+        <v>122.63</v>
       </c>
       <c r="G45" s="2">
-        <v>67943.1</v>
+        <v>66955.98</v>
       </c>
       <c r="H45" s="2">
-        <v>-7280.2</v>
+        <v>-7252.29</v>
       </c>
       <c r="I45" s="3">
-        <v>-0.0968</v>
+        <v>-0.0977</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C46" s="1">
-        <v>546.0</v>
+        <v>115.0</v>
       </c>
       <c r="D46" s="1">
-        <v>135.91</v>
+        <v>511.33</v>
       </c>
       <c r="E46" s="2">
-        <v>74208.27</v>
+        <v>58802.9</v>
       </c>
       <c r="F46" s="1">
-        <v>122.63</v>
+        <v>537.85</v>
       </c>
       <c r="G46" s="2">
-        <v>66955.98</v>
+        <v>61852.75</v>
       </c>
       <c r="H46" s="2">
-        <v>-7252.29</v>
+        <v>3049.85</v>
       </c>
       <c r="I46" s="3">
-        <v>-0.0977</v>
+        <v>0.0519</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C47" s="1">
-        <v>115.0</v>
+        <v>94.0</v>
       </c>
       <c r="D47" s="1">
-        <v>511.33</v>
+        <v>846.21</v>
       </c>
       <c r="E47" s="2">
-        <v>58802.9</v>
+        <v>79544.0</v>
       </c>
       <c r="F47" s="1">
-        <v>537.85</v>
+        <v>628.7</v>
       </c>
       <c r="G47" s="2">
-        <v>61852.75</v>
+        <v>59097.8</v>
       </c>
       <c r="H47" s="2">
-        <v>3049.85</v>
+        <v>-20446.2</v>
       </c>
       <c r="I47" s="3">
-        <v>0.0519</v>
+        <v>-0.257</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C48" s="1">
-        <v>94.0</v>
+        <v>405.0</v>
       </c>
       <c r="D48" s="1">
-        <v>846.21</v>
+        <v>147.23</v>
       </c>
       <c r="E48" s="2">
-        <v>79544.0</v>
+        <v>59627.52</v>
       </c>
       <c r="F48" s="1">
-        <v>628.7</v>
+        <v>141.95</v>
       </c>
       <c r="G48" s="2">
-        <v>59097.8</v>
+        <v>57489.75</v>
       </c>
       <c r="H48" s="2">
-        <v>-20446.2</v>
+        <v>-2137.77</v>
       </c>
       <c r="I48" s="3">
-        <v>-0.257</v>
+        <v>-0.0359</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C49" s="1">
-        <v>405.0</v>
+        <v>102.0</v>
       </c>
       <c r="D49" s="1">
-        <v>147.23</v>
+        <v>540.91</v>
       </c>
       <c r="E49" s="2">
-        <v>59627.52</v>
+        <v>55172.45</v>
       </c>
       <c r="F49" s="1">
-        <v>141.95</v>
+        <v>555.6</v>
       </c>
       <c r="G49" s="2">
-        <v>57489.75</v>
+        <v>56671.2</v>
       </c>
       <c r="H49" s="2">
-        <v>-2137.77</v>
+        <v>1498.75</v>
       </c>
       <c r="I49" s="3">
-        <v>-0.0359</v>
+        <v>0.0272</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C50" s="1">
-        <v>102.0</v>
+        <v>145.0</v>
       </c>
       <c r="D50" s="1">
-        <v>540.91</v>
+        <v>362.06</v>
       </c>
       <c r="E50" s="2">
-        <v>55172.45</v>
+        <v>52499.2</v>
       </c>
       <c r="F50" s="1">
-        <v>555.6</v>
+        <v>365.5</v>
       </c>
       <c r="G50" s="2">
-        <v>56671.2</v>
-      </c>
-      <c r="H50" s="2">
-        <v>1498.75</v>
+        <v>52997.5</v>
+      </c>
+      <c r="H50" s="1">
+        <v>498.3</v>
       </c>
       <c r="I50" s="3">
-        <v>0.0272</v>
+        <v>0.0095</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C51" s="1">
-        <v>145.0</v>
+        <v>43.0</v>
       </c>
       <c r="D51" s="1">
-        <v>362.06</v>
+        <v>722.52</v>
       </c>
       <c r="E51" s="2">
-        <v>52499.2</v>
-      </c>
-      <c r="F51" s="1">
-        <v>365.5</v>
+        <v>31068.3</v>
+      </c>
+      <c r="F51" s="2">
+        <v>1222.0</v>
       </c>
       <c r="G51" s="2">
-        <v>52997.5</v>
-      </c>
-      <c r="H51" s="1">
-        <v>498.3</v>
+        <v>52546.0</v>
+      </c>
+      <c r="H51" s="2">
+        <v>21477.7</v>
       </c>
       <c r="I51" s="3">
-        <v>0.0095</v>
+        <v>0.6913</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C52" s="1">
-        <v>43.0</v>
+        <v>58.0</v>
       </c>
       <c r="D52" s="1">
-        <v>722.52</v>
+        <v>953.02</v>
       </c>
       <c r="E52" s="2">
-        <v>31068.3</v>
-      </c>
-      <c r="F52" s="2">
-        <v>1222.0</v>
+        <v>55275.15</v>
+      </c>
+      <c r="F52" s="1">
+        <v>894.15</v>
       </c>
       <c r="G52" s="2">
-        <v>52546.0</v>
+        <v>51860.7</v>
       </c>
       <c r="H52" s="2">
-        <v>21477.7</v>
+        <v>-3414.45</v>
       </c>
       <c r="I52" s="3">
-        <v>0.6913</v>
+        <v>-0.0618</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C53" s="1">
-        <v>58.0</v>
+        <v>516.0</v>
       </c>
       <c r="D53" s="1">
-        <v>953.02</v>
+        <v>97.49</v>
       </c>
       <c r="E53" s="2">
-        <v>55275.15</v>
+        <v>50306.12</v>
       </c>
       <c r="F53" s="1">
-        <v>894.15</v>
+        <v>100.36</v>
       </c>
       <c r="G53" s="2">
-        <v>51860.7</v>
+        <v>51785.76</v>
       </c>
       <c r="H53" s="2">
-        <v>-3414.45</v>
+        <v>1479.64</v>
       </c>
       <c r="I53" s="3">
-        <v>-0.0618</v>
+        <v>0.0294</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C54" s="1">
-        <v>516.0</v>
+        <v>172.0</v>
       </c>
       <c r="D54" s="1">
-        <v>97.49</v>
+        <v>302.02</v>
       </c>
       <c r="E54" s="2">
-        <v>50306.12</v>
+        <v>51947.55</v>
       </c>
       <c r="F54" s="1">
-        <v>100.36</v>
+        <v>292.95</v>
       </c>
       <c r="G54" s="2">
-        <v>51785.76</v>
+        <v>50387.4</v>
       </c>
       <c r="H54" s="2">
-        <v>1479.64</v>
+        <v>-1560.15</v>
       </c>
       <c r="I54" s="3">
-        <v>0.0294</v>
+        <v>-0.03</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C55" s="1">
-        <v>172.0</v>
+        <v>63.0</v>
       </c>
       <c r="D55" s="1">
-        <v>302.02</v>
+        <v>724.23</v>
       </c>
       <c r="E55" s="2">
-        <v>51947.55</v>
+        <v>45626.35</v>
       </c>
       <c r="F55" s="1">
-        <v>292.95</v>
+        <v>777.9</v>
       </c>
       <c r="G55" s="2">
-        <v>50387.4</v>
+        <v>49007.7</v>
       </c>
       <c r="H55" s="2">
-        <v>-1560.15</v>
+        <v>3381.35</v>
       </c>
       <c r="I55" s="3">
-        <v>-0.03</v>
+        <v>0.0741</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C56" s="1">
-        <v>63.0</v>
+        <v>72.0</v>
       </c>
       <c r="D56" s="1">
-        <v>724.23</v>
+        <v>529.68</v>
       </c>
       <c r="E56" s="2">
-        <v>45626.35</v>
+        <v>38136.95</v>
       </c>
       <c r="F56" s="1">
-        <v>777.9</v>
+        <v>671.75</v>
       </c>
       <c r="G56" s="2">
-        <v>49007.7</v>
+        <v>48366.0</v>
       </c>
       <c r="H56" s="2">
-        <v>3381.35</v>
+        <v>10229.05</v>
       </c>
       <c r="I56" s="3">
-        <v>0.0741</v>
+        <v>0.2682</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C57" s="1">
-        <v>72.0</v>
+        <v>112</v>
+      </c>
+      <c r="C57" s="4">
+        <v>1891.0</v>
       </c>
       <c r="D57" s="1">
-        <v>529.68</v>
+        <v>26.43</v>
       </c>
       <c r="E57" s="2">
-        <v>38136.95</v>
+        <v>49985.02</v>
       </c>
       <c r="F57" s="1">
-        <v>671.75</v>
+        <v>24.77</v>
       </c>
       <c r="G57" s="2">
-        <v>48366.0</v>
+        <v>46840.07</v>
       </c>
       <c r="H57" s="2">
-        <v>10229.05</v>
+        <v>-3144.95</v>
       </c>
       <c r="I57" s="3">
-        <v>0.2682</v>
+        <v>-0.0629</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C58" s="4">
-        <v>1891.0</v>
-      </c>
-      <c r="D58" s="1">
-        <v>26.43</v>
+        <v>113</v>
+      </c>
+      <c r="C58" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="D58" s="2">
+        <v>1823.31</v>
       </c>
       <c r="E58" s="2">
-        <v>49985.02</v>
-      </c>
-      <c r="F58" s="1">
-        <v>24.77</v>
+        <v>54699.2</v>
+      </c>
+      <c r="F58" s="2">
+        <v>1545.0</v>
       </c>
       <c r="G58" s="2">
-        <v>46840.07</v>
+        <v>46350.0</v>
       </c>
       <c r="H58" s="2">
-        <v>-3144.95</v>
+        <v>-8349.2</v>
       </c>
       <c r="I58" s="3">
-        <v>-0.0629</v>
+        <v>-0.1526</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C59" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="D59" s="2">
-        <v>1823.31</v>
+        <v>102.0</v>
+      </c>
+      <c r="D59" s="1">
+        <v>550.05</v>
       </c>
       <c r="E59" s="2">
-        <v>54699.2</v>
-      </c>
-      <c r="F59" s="2">
-        <v>1545.0</v>
+        <v>56105.6</v>
+      </c>
+      <c r="F59" s="1">
+        <v>438.9</v>
       </c>
       <c r="G59" s="2">
-        <v>46350.0</v>
+        <v>44767.8</v>
       </c>
       <c r="H59" s="2">
-        <v>-8349.2</v>
+        <v>-11337.8</v>
       </c>
       <c r="I59" s="3">
-        <v>-0.1526</v>
+        <v>-0.2021</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C60" s="1">
-        <v>102.0</v>
+        <v>134.0</v>
       </c>
       <c r="D60" s="1">
-        <v>550.05</v>
+        <v>448.98</v>
       </c>
       <c r="E60" s="2">
-        <v>56105.6</v>
+        <v>60163.55</v>
       </c>
       <c r="F60" s="1">
-        <v>438.9</v>
+        <v>332.2</v>
       </c>
       <c r="G60" s="2">
-        <v>44767.8</v>
+        <v>44514.8</v>
       </c>
       <c r="H60" s="2">
-        <v>-11337.8</v>
+        <v>-15648.75</v>
       </c>
       <c r="I60" s="3">
-        <v>-0.2021</v>
+        <v>-0.2601</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C61" s="1">
-        <v>134.0</v>
-      </c>
-      <c r="D61" s="1">
-        <v>448.98</v>
+        <v>43.0</v>
+      </c>
+      <c r="D61" s="2">
+        <v>1097.89</v>
       </c>
       <c r="E61" s="2">
-        <v>60163.55</v>
-      </c>
-      <c r="F61" s="1">
-        <v>332.2</v>
+        <v>47209.5</v>
+      </c>
+      <c r="F61" s="2">
+        <v>1013.6</v>
       </c>
       <c r="G61" s="2">
-        <v>44514.8</v>
+        <v>43584.8</v>
       </c>
       <c r="H61" s="2">
-        <v>-15648.75</v>
+        <v>-3624.7</v>
       </c>
       <c r="I61" s="3">
-        <v>-0.2601</v>
+        <v>-0.0768</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C62" s="1">
-        <v>43.0</v>
-      </c>
-      <c r="D62" s="2">
-        <v>1097.89</v>
+        <v>94.0</v>
+      </c>
+      <c r="D62" s="1">
+        <v>267.98</v>
       </c>
       <c r="E62" s="2">
-        <v>47209.5</v>
-      </c>
-      <c r="F62" s="2">
-        <v>1013.6</v>
+        <v>25190.12</v>
+      </c>
+      <c r="F62" s="1">
+        <v>460.3</v>
       </c>
       <c r="G62" s="2">
-        <v>43584.8</v>
+        <v>43268.2</v>
       </c>
       <c r="H62" s="2">
-        <v>-3624.7</v>
+        <v>18078.08</v>
       </c>
       <c r="I62" s="3">
-        <v>-0.0768</v>
+        <v>0.7177</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C63" s="1">
-        <v>94.0</v>
-      </c>
-      <c r="D63" s="1">
-        <v>267.98</v>
+        <v>38.0</v>
+      </c>
+      <c r="D63" s="2">
+        <v>1111.19</v>
       </c>
       <c r="E63" s="2">
-        <v>25190.12</v>
-      </c>
-      <c r="F63" s="1">
-        <v>460.3</v>
+        <v>42225.2</v>
+      </c>
+      <c r="F63" s="2">
+        <v>1116.9</v>
       </c>
       <c r="G63" s="2">
-        <v>43268.2</v>
-      </c>
-      <c r="H63" s="2">
-        <v>18078.08</v>
+        <v>42442.2</v>
+      </c>
+      <c r="H63" s="1">
+        <v>217.0</v>
       </c>
       <c r="I63" s="3">
-        <v>0.7177</v>
+        <v>0.0051</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C64" s="1">
-        <v>38.0</v>
+        <v>9.0</v>
       </c>
       <c r="D64" s="2">
-        <v>1111.19</v>
+        <v>3066.43</v>
       </c>
       <c r="E64" s="2">
-        <v>42225.2</v>
+        <v>27597.85</v>
       </c>
       <c r="F64" s="2">
-        <v>1116.9</v>
-      </c>
-      <c r="G64" s="2">
-        <v>42442.2</v>
-      </c>
-      <c r="H64" s="1">
-        <v>217.0</v>
+        <v>4705.5</v>
+      </c>
+      <c r="G64" s="4">
+        <v>42350.0</v>
+      </c>
+      <c r="H64" s="2">
+        <v>14751.65</v>
       </c>
       <c r="I64" s="3">
-        <v>0.0051</v>
+        <v>0.5345</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="65">
@@ -3322,1329 +3307,1329 @@
         <v>11</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C65" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="D65" s="2">
-        <v>3066.43</v>
+        <v>86.0</v>
+      </c>
+      <c r="D65" s="1">
+        <v>458.8</v>
       </c>
       <c r="E65" s="2">
-        <v>27597.85</v>
-      </c>
-      <c r="F65" s="2">
-        <v>4705.5</v>
-      </c>
-      <c r="G65" s="4">
-        <v>42350.0</v>
+        <v>39456.85</v>
+      </c>
+      <c r="F65" s="1">
+        <v>470.7</v>
+      </c>
+      <c r="G65" s="2">
+        <v>40480.2</v>
       </c>
       <c r="H65" s="2">
-        <v>14751.65</v>
+        <v>1023.35</v>
       </c>
       <c r="I65" s="3">
-        <v>0.5345</v>
+        <v>0.0259</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C66" s="1">
-        <v>86.0</v>
+        <v>218.0</v>
       </c>
       <c r="D66" s="1">
-        <v>458.8</v>
+        <v>182.99</v>
       </c>
       <c r="E66" s="2">
-        <v>39456.85</v>
+        <v>39890.84</v>
       </c>
       <c r="F66" s="1">
-        <v>470.7</v>
+        <v>181.03</v>
       </c>
       <c r="G66" s="2">
-        <v>40480.2</v>
-      </c>
-      <c r="H66" s="2">
-        <v>1023.35</v>
+        <v>39464.54</v>
+      </c>
+      <c r="H66" s="1">
+        <v>-426.3</v>
       </c>
       <c r="I66" s="3">
-        <v>0.0259</v>
+        <v>-0.0107</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C67" s="1">
-        <v>218.0</v>
+        <v>70.0</v>
       </c>
       <c r="D67" s="1">
-        <v>182.99</v>
+        <v>331.82</v>
       </c>
       <c r="E67" s="2">
-        <v>39890.84</v>
+        <v>23227.6</v>
       </c>
       <c r="F67" s="1">
-        <v>181.03</v>
+        <v>555.15</v>
       </c>
       <c r="G67" s="2">
-        <v>39464.54</v>
-      </c>
-      <c r="H67" s="1">
-        <v>-426.3</v>
+        <v>38860.5</v>
+      </c>
+      <c r="H67" s="2">
+        <v>15632.9</v>
       </c>
       <c r="I67" s="3">
-        <v>-0.0107</v>
+        <v>0.673</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C68" s="1">
-        <v>70.0</v>
+        <v>132.0</v>
       </c>
       <c r="D68" s="1">
-        <v>331.82</v>
+        <v>264.23</v>
       </c>
       <c r="E68" s="2">
-        <v>23227.6</v>
+        <v>34878.4</v>
       </c>
       <c r="F68" s="1">
-        <v>555.15</v>
+        <v>282.35</v>
       </c>
       <c r="G68" s="2">
-        <v>38860.5</v>
+        <v>37270.2</v>
       </c>
       <c r="H68" s="2">
-        <v>15632.9</v>
+        <v>2391.8</v>
       </c>
       <c r="I68" s="3">
-        <v>0.673</v>
+        <v>0.0686</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C69" s="1">
-        <v>132.0</v>
-      </c>
-      <c r="D69" s="1">
-        <v>264.23</v>
+        <v>10.0</v>
+      </c>
+      <c r="D69" s="2">
+        <v>3807.82</v>
       </c>
       <c r="E69" s="2">
-        <v>34878.4</v>
-      </c>
-      <c r="F69" s="1">
-        <v>282.35</v>
+        <v>38078.2</v>
+      </c>
+      <c r="F69" s="2">
+        <v>3694.0</v>
       </c>
       <c r="G69" s="2">
-        <v>37270.2</v>
+        <v>66000.0</v>
       </c>
       <c r="H69" s="2">
-        <v>2391.8</v>
+        <v>-1138.2</v>
       </c>
       <c r="I69" s="3">
-        <v>0.0686</v>
+        <v>-0.0299</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C70" s="1">
-        <v>10.0</v>
+        <v>40.0</v>
       </c>
       <c r="D70" s="2">
-        <v>3807.82</v>
+        <v>1008.5</v>
       </c>
       <c r="E70" s="2">
-        <v>38078.2</v>
-      </c>
-      <c r="F70" s="2">
-        <v>3694.0</v>
+        <v>40340.0</v>
+      </c>
+      <c r="F70" s="1">
+        <v>922.0</v>
       </c>
       <c r="G70" s="2">
-        <v>66000.0</v>
+        <v>36880.0</v>
       </c>
       <c r="H70" s="2">
-        <v>-1138.2</v>
+        <v>-3460.0</v>
       </c>
       <c r="I70" s="3">
-        <v>-0.0299</v>
+        <v>-0.0858</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C71" s="1">
-        <v>40.0</v>
+        <v>1.0</v>
       </c>
       <c r="D71" s="2">
-        <v>1008.5</v>
+        <v>35975.0</v>
       </c>
       <c r="E71" s="2">
-        <v>40340.0</v>
-      </c>
-      <c r="F71" s="1">
-        <v>922.0</v>
+        <v>35975.0</v>
+      </c>
+      <c r="F71" s="2">
+        <v>35425.1</v>
       </c>
       <c r="G71" s="2">
-        <v>36880.0</v>
-      </c>
-      <c r="H71" s="2">
-        <v>-3460.0</v>
+        <v>35425.1</v>
+      </c>
+      <c r="H71" s="1">
+        <v>-549.9</v>
       </c>
       <c r="I71" s="3">
-        <v>-0.0858</v>
+        <v>-0.0153</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C72" s="1">
-        <v>1.0</v>
+        <v>19.0</v>
       </c>
       <c r="D72" s="2">
-        <v>35975.0</v>
+        <v>1886.49</v>
       </c>
       <c r="E72" s="2">
-        <v>35975.0</v>
+        <v>35843.4</v>
       </c>
       <c r="F72" s="2">
-        <v>35425.1</v>
+        <v>1855.4</v>
       </c>
       <c r="G72" s="2">
-        <v>35425.1</v>
+        <v>35252.6</v>
       </c>
       <c r="H72" s="1">
-        <v>-549.9</v>
+        <v>-590.8</v>
       </c>
       <c r="I72" s="3">
-        <v>-0.0153</v>
+        <v>-0.0165</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C73" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="D73" s="2">
-        <v>1886.49</v>
+        <v>222.0</v>
+      </c>
+      <c r="D73" s="1">
+        <v>137.08</v>
       </c>
       <c r="E73" s="2">
-        <v>35843.4</v>
-      </c>
-      <c r="F73" s="2">
-        <v>1855.4</v>
+        <v>30430.92</v>
+      </c>
+      <c r="F73" s="1">
+        <v>153.5</v>
       </c>
       <c r="G73" s="2">
-        <v>35252.6</v>
-      </c>
-      <c r="H73" s="1">
-        <v>-590.8</v>
+        <v>34077.0</v>
+      </c>
+      <c r="H73" s="2">
+        <v>3646.08</v>
       </c>
       <c r="I73" s="3">
-        <v>-0.0165</v>
+        <v>0.1198</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C74" s="1">
-        <v>222.0</v>
-      </c>
-      <c r="D74" s="1">
-        <v>137.08</v>
+        <v>43.0</v>
+      </c>
+      <c r="D74" s="2">
+        <v>1096.25</v>
       </c>
       <c r="E74" s="2">
-        <v>30430.92</v>
+        <v>47138.65</v>
       </c>
       <c r="F74" s="1">
-        <v>153.5</v>
-      </c>
-      <c r="G74" s="2">
-        <v>34077.0</v>
+        <v>772.8</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0.0</v>
       </c>
       <c r="H74" s="2">
-        <v>3646.08</v>
+        <v>-13908.25</v>
       </c>
       <c r="I74" s="3">
-        <v>0.1198</v>
+        <v>-0.295</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C75" s="1">
-        <v>43.0</v>
+        <v>39.0</v>
       </c>
       <c r="D75" s="2">
-        <v>1096.25</v>
+        <v>1165.79</v>
       </c>
       <c r="E75" s="2">
-        <v>47138.65</v>
+        <v>45465.85</v>
       </c>
       <c r="F75" s="1">
-        <v>772.8</v>
-      </c>
-      <c r="G75" s="1">
-        <v>0.0</v>
+        <v>847.2</v>
+      </c>
+      <c r="G75" s="2">
+        <v>33040.8</v>
       </c>
       <c r="H75" s="2">
-        <v>-13908.25</v>
+        <v>-12425.05</v>
       </c>
       <c r="I75" s="3">
-        <v>-0.295</v>
+        <v>-0.2733</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C76" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="D76" s="2">
-        <v>1165.79</v>
+        <v>42.0</v>
+      </c>
+      <c r="D76" s="1">
+        <v>820.32</v>
       </c>
       <c r="E76" s="2">
-        <v>45465.85</v>
+        <v>34453.5</v>
       </c>
       <c r="F76" s="1">
-        <v>847.2</v>
+        <v>785.95</v>
       </c>
       <c r="G76" s="2">
-        <v>33040.8</v>
+        <v>33009.9</v>
       </c>
       <c r="H76" s="2">
-        <v>-12425.05</v>
+        <v>-1443.6</v>
       </c>
       <c r="I76" s="3">
-        <v>-0.2733</v>
+        <v>-0.0419</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C77" s="1">
-        <v>42.0</v>
+        <v>132</v>
+      </c>
+      <c r="C77" s="4">
+        <v>1006.0</v>
       </c>
       <c r="D77" s="1">
-        <v>820.32</v>
+        <v>65.92</v>
       </c>
       <c r="E77" s="2">
-        <v>34453.5</v>
+        <v>66314.59</v>
       </c>
       <c r="F77" s="1">
-        <v>785.95</v>
+        <v>32.76</v>
       </c>
       <c r="G77" s="2">
-        <v>33009.9</v>
+        <v>32956.56</v>
       </c>
       <c r="H77" s="2">
-        <v>-1443.6</v>
+        <v>-33358.03</v>
       </c>
       <c r="I77" s="3">
-        <v>-0.0419</v>
+        <v>-0.503</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C78" s="4">
-        <v>1006.0</v>
+        <v>133</v>
+      </c>
+      <c r="C78" s="1">
+        <v>32.0</v>
       </c>
       <c r="D78" s="1">
-        <v>65.92</v>
+        <v>934.45</v>
       </c>
       <c r="E78" s="2">
-        <v>66314.59</v>
-      </c>
-      <c r="F78" s="1">
-        <v>32.76</v>
+        <v>29902.4</v>
+      </c>
+      <c r="F78" s="2">
+        <v>1026.1</v>
       </c>
       <c r="G78" s="2">
-        <v>32956.56</v>
+        <v>32835.2</v>
       </c>
       <c r="H78" s="2">
-        <v>-33358.03</v>
+        <v>2932.8</v>
       </c>
       <c r="I78" s="3">
-        <v>-0.503</v>
+        <v>0.0981</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C79" s="1">
-        <v>32.0</v>
+        <v>53.0</v>
       </c>
       <c r="D79" s="1">
-        <v>934.45</v>
+        <v>729.68</v>
       </c>
       <c r="E79" s="2">
-        <v>29902.4</v>
-      </c>
-      <c r="F79" s="2">
-        <v>1026.1</v>
+        <v>38672.9</v>
+      </c>
+      <c r="F79" s="1">
+        <v>611.95</v>
       </c>
       <c r="G79" s="2">
-        <v>32835.2</v>
+        <v>32433.35</v>
       </c>
       <c r="H79" s="2">
-        <v>2932.8</v>
+        <v>-6239.55</v>
       </c>
       <c r="I79" s="3">
-        <v>0.0981</v>
+        <v>-0.1613</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C80" s="1">
-        <v>53.0</v>
+        <v>28.0</v>
       </c>
       <c r="D80" s="1">
-        <v>729.68</v>
+        <v>702.63</v>
       </c>
       <c r="E80" s="2">
-        <v>38672.9</v>
-      </c>
-      <c r="F80" s="1">
-        <v>611.95</v>
+        <v>19673.6</v>
+      </c>
+      <c r="F80" s="2">
+        <v>1133.4</v>
       </c>
       <c r="G80" s="2">
-        <v>32433.35</v>
+        <v>31735.2</v>
       </c>
       <c r="H80" s="2">
-        <v>-6239.55</v>
+        <v>12061.6</v>
       </c>
       <c r="I80" s="3">
-        <v>-0.1613</v>
+        <v>0.6131</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C81" s="1">
-        <v>28.0</v>
+        <v>60.0</v>
       </c>
       <c r="D81" s="1">
-        <v>702.63</v>
+        <v>527.58</v>
       </c>
       <c r="E81" s="2">
-        <v>19673.6</v>
-      </c>
-      <c r="F81" s="2">
-        <v>1133.4</v>
+        <v>31655.0</v>
+      </c>
+      <c r="F81" s="1">
+        <v>525.35</v>
       </c>
       <c r="G81" s="2">
-        <v>31735.2</v>
-      </c>
-      <c r="H81" s="2">
-        <v>12061.6</v>
+        <v>31521.0</v>
+      </c>
+      <c r="H81" s="1">
+        <v>-134.0</v>
       </c>
       <c r="I81" s="3">
-        <v>0.6131</v>
+        <v>-0.0042</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C82" s="1">
-        <v>60.0</v>
+        <v>43.0</v>
       </c>
       <c r="D82" s="1">
-        <v>527.58</v>
+        <v>579.24</v>
       </c>
       <c r="E82" s="2">
-        <v>31655.0</v>
+        <v>24907.3</v>
       </c>
       <c r="F82" s="1">
-        <v>525.35</v>
+        <v>721.5</v>
       </c>
       <c r="G82" s="2">
-        <v>31521.0</v>
-      </c>
-      <c r="H82" s="1">
-        <v>-134.0</v>
+        <v>31024.5</v>
+      </c>
+      <c r="H82" s="2">
+        <v>6117.2</v>
       </c>
       <c r="I82" s="3">
-        <v>-0.0042</v>
+        <v>0.2456</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C83" s="1">
-        <v>43.0</v>
+        <v>249.0</v>
       </c>
       <c r="D83" s="1">
-        <v>579.24</v>
+        <v>134.11</v>
       </c>
       <c r="E83" s="2">
-        <v>24907.3</v>
+        <v>33392.27</v>
       </c>
       <c r="F83" s="1">
-        <v>721.5</v>
+        <v>123.0</v>
       </c>
       <c r="G83" s="2">
-        <v>31024.5</v>
+        <v>30627.0</v>
       </c>
       <c r="H83" s="2">
-        <v>6117.2</v>
+        <v>-2765.27</v>
       </c>
       <c r="I83" s="3">
-        <v>0.2456</v>
+        <v>-0.0828</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C84" s="1">
-        <v>249.0</v>
+        <v>307.0</v>
       </c>
       <c r="D84" s="1">
-        <v>134.11</v>
+        <v>97.19</v>
       </c>
       <c r="E84" s="2">
-        <v>33392.27</v>
+        <v>29837.24</v>
       </c>
       <c r="F84" s="1">
-        <v>123.0</v>
+        <v>98.15</v>
       </c>
       <c r="G84" s="2">
-        <v>30627.0</v>
-      </c>
-      <c r="H84" s="2">
-        <v>-2765.27</v>
+        <v>30132.05</v>
+      </c>
+      <c r="H84" s="1">
+        <v>294.81</v>
       </c>
       <c r="I84" s="3">
-        <v>-0.0828</v>
+        <v>0.0099</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C85" s="1">
-        <v>307.0</v>
-      </c>
-      <c r="D85" s="1">
-        <v>97.19</v>
+        <v>20.0</v>
+      </c>
+      <c r="D85" s="2">
+        <v>1040.96</v>
       </c>
       <c r="E85" s="2">
-        <v>29837.24</v>
-      </c>
-      <c r="F85" s="1">
-        <v>98.15</v>
+        <v>20819.2</v>
+      </c>
+      <c r="F85" s="2">
+        <v>1496.2</v>
       </c>
       <c r="G85" s="2">
-        <v>30132.05</v>
-      </c>
-      <c r="H85" s="1">
-        <v>294.81</v>
+        <v>29924.0</v>
+      </c>
+      <c r="H85" s="2">
+        <v>9104.8</v>
       </c>
       <c r="I85" s="3">
-        <v>0.0099</v>
+        <v>0.4373</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C86" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="D86" s="2">
-        <v>1040.96</v>
+        <v>127.0</v>
+      </c>
+      <c r="D86" s="1">
+        <v>209.26</v>
       </c>
       <c r="E86" s="2">
-        <v>20819.2</v>
-      </c>
-      <c r="F86" s="2">
-        <v>1496.2</v>
+        <v>26575.63</v>
+      </c>
+      <c r="F86" s="1">
+        <v>235.26</v>
       </c>
       <c r="G86" s="2">
-        <v>29924.0</v>
+        <v>29878.02</v>
       </c>
       <c r="H86" s="2">
-        <v>9104.8</v>
+        <v>3302.39</v>
       </c>
       <c r="I86" s="3">
-        <v>0.4373</v>
+        <v>0.1243</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C87" s="1">
-        <v>127.0</v>
+        <v>66.0</v>
       </c>
       <c r="D87" s="1">
-        <v>209.26</v>
+        <v>387.23</v>
       </c>
       <c r="E87" s="2">
-        <v>26575.63</v>
+        <v>25557.45</v>
       </c>
       <c r="F87" s="1">
-        <v>235.26</v>
+        <v>419.65</v>
       </c>
       <c r="G87" s="2">
-        <v>29878.02</v>
+        <v>27696.9</v>
       </c>
       <c r="H87" s="2">
-        <v>3302.39</v>
+        <v>2139.45</v>
       </c>
       <c r="I87" s="3">
-        <v>0.1243</v>
+        <v>0.0837</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C88" s="1">
-        <v>66.0</v>
-      </c>
-      <c r="D88" s="1">
-        <v>387.23</v>
+        <v>20.0</v>
+      </c>
+      <c r="D88" s="2">
+        <v>1099.4</v>
       </c>
       <c r="E88" s="2">
-        <v>25557.45</v>
-      </c>
-      <c r="F88" s="1">
-        <v>419.65</v>
+        <v>21988.0</v>
+      </c>
+      <c r="F88" s="2">
+        <v>1323.7</v>
       </c>
       <c r="G88" s="2">
-        <v>27696.9</v>
+        <v>26474.0</v>
       </c>
       <c r="H88" s="2">
-        <v>2139.45</v>
+        <v>4486.0</v>
       </c>
       <c r="I88" s="3">
-        <v>0.0837</v>
+        <v>0.204</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C89" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="D89" s="2">
-        <v>1099.4</v>
+        <v>226.0</v>
+      </c>
+      <c r="D89" s="1">
+        <v>136.74</v>
       </c>
       <c r="E89" s="2">
-        <v>21988.0</v>
-      </c>
-      <c r="F89" s="2">
-        <v>1323.7</v>
+        <v>30902.6</v>
+      </c>
+      <c r="F89" s="1">
+        <v>116.23</v>
       </c>
       <c r="G89" s="2">
-        <v>26474.0</v>
+        <v>26267.98</v>
       </c>
       <c r="H89" s="2">
-        <v>4486.0</v>
+        <v>-4634.62</v>
       </c>
       <c r="I89" s="3">
-        <v>0.204</v>
+        <v>-0.15</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C90" s="1">
-        <v>226.0</v>
+        <v>298.0</v>
       </c>
       <c r="D90" s="1">
-        <v>136.74</v>
+        <v>41.79</v>
       </c>
       <c r="E90" s="2">
-        <v>30902.6</v>
+        <v>12454.04</v>
       </c>
       <c r="F90" s="1">
-        <v>116.23</v>
+        <v>88.0</v>
       </c>
       <c r="G90" s="2">
-        <v>26267.98</v>
+        <v>26224.0</v>
       </c>
       <c r="H90" s="2">
-        <v>-4634.62</v>
+        <v>13769.96</v>
       </c>
       <c r="I90" s="3">
-        <v>-0.15</v>
+        <v>1.1057</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C91" s="1">
-        <v>298.0</v>
+        <v>49.0</v>
       </c>
       <c r="D91" s="1">
-        <v>41.79</v>
+        <v>333.15</v>
       </c>
       <c r="E91" s="2">
-        <v>12454.04</v>
+        <v>16324.5</v>
       </c>
       <c r="F91" s="1">
-        <v>88.0</v>
+        <v>516.4</v>
       </c>
       <c r="G91" s="2">
-        <v>26224.0</v>
+        <v>25303.6</v>
       </c>
       <c r="H91" s="2">
-        <v>13769.96</v>
+        <v>8979.1</v>
       </c>
       <c r="I91" s="3">
-        <v>1.1057</v>
+        <v>0.55</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C92" s="1">
-        <v>49.0</v>
+        <v>186.0</v>
       </c>
       <c r="D92" s="1">
-        <v>333.15</v>
+        <v>139.03</v>
       </c>
       <c r="E92" s="2">
-        <v>16324.5</v>
+        <v>25859.79</v>
       </c>
       <c r="F92" s="1">
-        <v>516.4</v>
+        <v>128.55</v>
       </c>
       <c r="G92" s="2">
-        <v>25303.6</v>
+        <v>23910.3</v>
       </c>
       <c r="H92" s="2">
-        <v>8979.1</v>
+        <v>-1949.49</v>
       </c>
       <c r="I92" s="3">
-        <v>0.55</v>
+        <v>-0.0754</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C93" s="1">
-        <v>186.0</v>
-      </c>
-      <c r="D93" s="1">
-        <v>139.03</v>
+        <v>15.0</v>
+      </c>
+      <c r="D93" s="2">
+        <v>1526.68</v>
       </c>
       <c r="E93" s="2">
-        <v>25859.79</v>
-      </c>
-      <c r="F93" s="1">
-        <v>128.55</v>
+        <v>22900.2</v>
+      </c>
+      <c r="F93" s="2">
+        <v>1559.2</v>
       </c>
       <c r="G93" s="2">
-        <v>23910.3</v>
-      </c>
-      <c r="H93" s="2">
-        <v>-1949.49</v>
+        <v>23388.0</v>
+      </c>
+      <c r="H93" s="1">
+        <v>487.8</v>
       </c>
       <c r="I93" s="3">
-        <v>-0.0754</v>
+        <v>0.0213</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C94" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="D94" s="2">
-        <v>1526.68</v>
+        <v>124.0</v>
+      </c>
+      <c r="D94" s="1">
+        <v>160.5</v>
       </c>
       <c r="E94" s="2">
-        <v>22900.2</v>
-      </c>
-      <c r="F94" s="2">
-        <v>1559.2</v>
+        <v>19902.66</v>
+      </c>
+      <c r="F94" s="1">
+        <v>185.98</v>
       </c>
       <c r="G94" s="2">
-        <v>23388.0</v>
-      </c>
-      <c r="H94" s="1">
-        <v>487.8</v>
+        <v>23061.52</v>
+      </c>
+      <c r="H94" s="2">
+        <v>3158.86</v>
       </c>
       <c r="I94" s="3">
-        <v>0.0213</v>
+        <v>0.1587</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C95" s="1">
-        <v>124.0</v>
+        <v>59.0</v>
       </c>
       <c r="D95" s="1">
-        <v>160.5</v>
+        <v>576.82</v>
       </c>
       <c r="E95" s="2">
-        <v>19902.66</v>
+        <v>34032.35</v>
       </c>
       <c r="F95" s="1">
-        <v>185.98</v>
+        <v>373.35</v>
       </c>
       <c r="G95" s="2">
-        <v>23061.52</v>
+        <v>22027.65</v>
       </c>
       <c r="H95" s="2">
-        <v>3158.86</v>
+        <v>-12004.7</v>
       </c>
       <c r="I95" s="3">
-        <v>0.1587</v>
+        <v>-0.3527</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C96" s="1">
-        <v>59.0</v>
-      </c>
-      <c r="D96" s="1">
-        <v>576.82</v>
+        <v>9.0</v>
+      </c>
+      <c r="D96" s="2">
+        <v>1395.0</v>
       </c>
       <c r="E96" s="2">
-        <v>34032.35</v>
-      </c>
-      <c r="F96" s="1">
-        <v>373.35</v>
+        <v>12555.0</v>
+      </c>
+      <c r="F96" s="2">
+        <v>2345.0</v>
       </c>
       <c r="G96" s="2">
-        <v>22027.65</v>
+        <v>21105.0</v>
       </c>
       <c r="H96" s="2">
-        <v>-12004.7</v>
+        <v>8550.0</v>
       </c>
       <c r="I96" s="3">
-        <v>-0.3527</v>
+        <v>0.681</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C97" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="D97" s="2">
-        <v>1395.0</v>
+        <v>67.0</v>
+      </c>
+      <c r="D97" s="1">
+        <v>374.48</v>
       </c>
       <c r="E97" s="2">
-        <v>12555.0</v>
-      </c>
-      <c r="F97" s="2">
-        <v>2345.0</v>
+        <v>25090.1</v>
+      </c>
+      <c r="F97" s="1">
+        <v>307.0</v>
       </c>
       <c r="G97" s="2">
-        <v>21105.0</v>
+        <v>20569.0</v>
       </c>
       <c r="H97" s="2">
-        <v>8550.0</v>
+        <v>-4521.1</v>
       </c>
       <c r="I97" s="3">
-        <v>0.681</v>
+        <v>-0.1802</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C98" s="1">
-        <v>67.0</v>
+        <v>63.0</v>
       </c>
       <c r="D98" s="1">
-        <v>374.48</v>
+        <v>311.35</v>
       </c>
       <c r="E98" s="2">
-        <v>25090.1</v>
+        <v>19614.9</v>
       </c>
       <c r="F98" s="1">
-        <v>307.0</v>
+        <v>323.85</v>
       </c>
       <c r="G98" s="2">
-        <v>20569.0</v>
-      </c>
-      <c r="H98" s="2">
-        <v>-4521.1</v>
+        <v>20402.55</v>
+      </c>
+      <c r="H98" s="1">
+        <v>787.65</v>
       </c>
       <c r="I98" s="3">
-        <v>-0.1802</v>
+        <v>0.0402</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C99" s="1">
-        <v>63.0</v>
+        <v>91.0</v>
       </c>
       <c r="D99" s="1">
-        <v>311.35</v>
+        <v>173.53</v>
       </c>
       <c r="E99" s="2">
-        <v>19614.9</v>
+        <v>15791.45</v>
       </c>
       <c r="F99" s="1">
-        <v>323.85</v>
-      </c>
-      <c r="G99" s="2">
-        <v>20402.55</v>
-      </c>
-      <c r="H99" s="1">
-        <v>787.65</v>
+        <v>217.4</v>
+      </c>
+      <c r="G99" s="4">
+        <v>19783.0</v>
+      </c>
+      <c r="H99" s="2">
+        <v>3991.95</v>
       </c>
       <c r="I99" s="3">
-        <v>0.0402</v>
+        <v>0.2528</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="100">
@@ -4652,75 +4637,75 @@
         <v>11</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C100" s="1">
-        <v>91.0</v>
-      </c>
-      <c r="D100" s="1">
-        <v>173.53</v>
+        <v>21.0</v>
+      </c>
+      <c r="D100" s="2">
+        <v>1220.91</v>
       </c>
       <c r="E100" s="2">
-        <v>15791.45</v>
+        <v>25639.1</v>
       </c>
       <c r="F100" s="1">
-        <v>217.4</v>
-      </c>
-      <c r="G100" s="4">
-        <v>19783.0</v>
+        <v>932.25</v>
+      </c>
+      <c r="G100" s="2">
+        <v>19577.25</v>
       </c>
       <c r="H100" s="2">
-        <v>3991.95</v>
+        <v>-6061.85</v>
       </c>
       <c r="I100" s="3">
-        <v>0.2528</v>
+        <v>-0.2364</v>
       </c>
       <c r="J100" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C101" s="1">
-        <v>21.0</v>
+        <v>5.0</v>
       </c>
       <c r="D101" s="2">
-        <v>1220.91</v>
+        <v>2134.6</v>
       </c>
       <c r="E101" s="2">
-        <v>25639.1</v>
-      </c>
-      <c r="F101" s="1">
-        <v>932.25</v>
-      </c>
-      <c r="G101" s="2">
-        <v>19577.25</v>
+        <v>10673.0</v>
+      </c>
+      <c r="F101" s="2">
+        <v>3914.45</v>
+      </c>
+      <c r="G101" s="4">
+        <v>19572.0</v>
       </c>
       <c r="H101" s="2">
-        <v>-6061.85</v>
+        <v>8899.25</v>
       </c>
       <c r="I101" s="3">
-        <v>-0.2364</v>
+        <v>0.8338</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="102">
@@ -4728,721 +4713,721 @@
         <v>11</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C102" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="D102" s="2">
-        <v>2134.6</v>
+        <v>125.0</v>
+      </c>
+      <c r="D102" s="1">
+        <v>194.63</v>
       </c>
       <c r="E102" s="2">
-        <v>10673.0</v>
-      </c>
-      <c r="F102" s="2">
-        <v>3914.45</v>
-      </c>
-      <c r="G102" s="4">
-        <v>19572.0</v>
+        <v>24328.3</v>
+      </c>
+      <c r="F102" s="1">
+        <v>156.25</v>
+      </c>
+      <c r="G102" s="2">
+        <v>19531.25</v>
       </c>
       <c r="H102" s="2">
-        <v>8899.25</v>
+        <v>-4797.05</v>
       </c>
       <c r="I102" s="3">
-        <v>0.8338</v>
+        <v>-0.1972</v>
       </c>
       <c r="J102" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C103" s="1">
-        <v>125.0</v>
+        <v>44.0</v>
       </c>
       <c r="D103" s="1">
-        <v>194.63</v>
+        <v>451.6</v>
       </c>
       <c r="E103" s="2">
-        <v>24328.3</v>
+        <v>19870.25</v>
       </c>
       <c r="F103" s="1">
-        <v>156.25</v>
+        <v>442.4</v>
       </c>
       <c r="G103" s="2">
-        <v>19531.25</v>
-      </c>
-      <c r="H103" s="2">
-        <v>-4797.05</v>
+        <v>19465.6</v>
+      </c>
+      <c r="H103" s="1">
+        <v>-404.65</v>
       </c>
       <c r="I103" s="3">
-        <v>-0.1972</v>
+        <v>-0.0204</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C104" s="1">
-        <v>44.0</v>
+        <v>72.0</v>
       </c>
       <c r="D104" s="1">
-        <v>451.6</v>
+        <v>275.75</v>
       </c>
       <c r="E104" s="2">
-        <v>19870.25</v>
+        <v>19853.65</v>
       </c>
       <c r="F104" s="1">
-        <v>442.4</v>
+        <v>268.7</v>
       </c>
       <c r="G104" s="2">
-        <v>19465.6</v>
+        <v>19346.4</v>
       </c>
       <c r="H104" s="1">
-        <v>-404.65</v>
+        <v>-507.25</v>
       </c>
       <c r="I104" s="3">
-        <v>-0.0204</v>
+        <v>-0.0255</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C105" s="1">
-        <v>72.0</v>
-      </c>
-      <c r="D105" s="1">
-        <v>275.75</v>
+        <v>7.0</v>
+      </c>
+      <c r="D105" s="2">
+        <v>3125.67</v>
       </c>
       <c r="E105" s="2">
-        <v>19853.65</v>
-      </c>
-      <c r="F105" s="1">
-        <v>268.7</v>
+        <v>21879.7</v>
+      </c>
+      <c r="F105" s="2">
+        <v>2761.25</v>
       </c>
       <c r="G105" s="2">
-        <v>19346.4</v>
-      </c>
-      <c r="H105" s="1">
-        <v>-507.25</v>
+        <v>19328.75</v>
+      </c>
+      <c r="H105" s="2">
+        <v>-2550.95</v>
       </c>
       <c r="I105" s="3">
-        <v>-0.0255</v>
+        <v>-0.1166</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C106" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="D106" s="2">
-        <v>3125.67</v>
+        <v>110.0</v>
+      </c>
+      <c r="D106" s="1">
+        <v>181.04</v>
       </c>
       <c r="E106" s="2">
-        <v>21879.7</v>
-      </c>
-      <c r="F106" s="2">
-        <v>2761.25</v>
+        <v>19914.4</v>
+      </c>
+      <c r="F106" s="1">
+        <v>175.44</v>
       </c>
       <c r="G106" s="2">
-        <v>19328.75</v>
-      </c>
-      <c r="H106" s="2">
-        <v>-2550.95</v>
+        <v>19298.4</v>
+      </c>
+      <c r="H106" s="1">
+        <v>-616.0</v>
       </c>
       <c r="I106" s="3">
-        <v>-0.1166</v>
+        <v>-0.0309</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C107" s="1">
-        <v>110.0</v>
+        <v>221.0</v>
       </c>
       <c r="D107" s="1">
-        <v>181.04</v>
+        <v>126.22</v>
       </c>
       <c r="E107" s="2">
-        <v>19914.4</v>
+        <v>27894.4</v>
       </c>
       <c r="F107" s="1">
-        <v>175.44</v>
+        <v>87.06</v>
       </c>
       <c r="G107" s="2">
-        <v>19298.4</v>
-      </c>
-      <c r="H107" s="1">
-        <v>-616.0</v>
+        <v>19240.26</v>
+      </c>
+      <c r="H107" s="2">
+        <v>-8654.14</v>
       </c>
       <c r="I107" s="3">
-        <v>-0.0309</v>
+        <v>-0.3102</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C108" s="1">
-        <v>221.0</v>
-      </c>
-      <c r="D108" s="1">
-        <v>126.22</v>
+        <v>9.0</v>
+      </c>
+      <c r="D108" s="2">
+        <v>2147.0</v>
       </c>
       <c r="E108" s="2">
-        <v>27894.4</v>
-      </c>
-      <c r="F108" s="1">
-        <v>87.06</v>
+        <v>19323.0</v>
+      </c>
+      <c r="F108" s="2">
+        <v>2116.45</v>
       </c>
       <c r="G108" s="2">
-        <v>19240.26</v>
-      </c>
-      <c r="H108" s="2">
-        <v>-8654.14</v>
+        <v>19048.05</v>
+      </c>
+      <c r="H108" s="1">
+        <v>-274.95</v>
       </c>
       <c r="I108" s="3">
-        <v>-0.3102</v>
+        <v>-0.0142</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C109" s="1">
-        <v>9.0</v>
+        <v>23.0</v>
       </c>
       <c r="D109" s="2">
-        <v>2147.0</v>
+        <v>1205.77</v>
       </c>
       <c r="E109" s="2">
-        <v>19323.0</v>
-      </c>
-      <c r="F109" s="2">
-        <v>2116.45</v>
+        <v>27732.8</v>
+      </c>
+      <c r="F109" s="1">
+        <v>826.05</v>
       </c>
       <c r="G109" s="2">
-        <v>19048.05</v>
-      </c>
-      <c r="H109" s="1">
-        <v>-274.95</v>
+        <v>18999.15</v>
+      </c>
+      <c r="H109" s="2">
+        <v>-8733.65</v>
       </c>
       <c r="I109" s="3">
-        <v>-0.0142</v>
+        <v>-0.3149</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C110" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="D110" s="2">
-        <v>1205.77</v>
+        <v>20.0</v>
+      </c>
+      <c r="D110" s="1">
+        <v>988.13</v>
       </c>
       <c r="E110" s="2">
-        <v>27732.8</v>
+        <v>19762.5</v>
       </c>
       <c r="F110" s="1">
-        <v>826.05</v>
+        <v>932.35</v>
       </c>
       <c r="G110" s="2">
-        <v>18999.15</v>
+        <v>18647.0</v>
       </c>
       <c r="H110" s="2">
-        <v>-8733.65</v>
+        <v>-1115.5</v>
       </c>
       <c r="I110" s="3">
-        <v>-0.3149</v>
+        <v>-0.0564</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C111" s="1">
-        <v>20.0</v>
+        <v>32.0</v>
       </c>
       <c r="D111" s="1">
-        <v>988.13</v>
+        <v>619.5</v>
       </c>
       <c r="E111" s="2">
-        <v>19762.5</v>
+        <v>19824.0</v>
       </c>
       <c r="F111" s="1">
-        <v>932.35</v>
+        <v>580.5</v>
       </c>
       <c r="G111" s="2">
-        <v>18647.0</v>
+        <v>18576.0</v>
       </c>
       <c r="H111" s="2">
-        <v>-1115.5</v>
+        <v>-1248.0</v>
       </c>
       <c r="I111" s="3">
-        <v>-0.0564</v>
+        <v>-0.063</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C112" s="1">
-        <v>32.0</v>
+        <v>228.0</v>
       </c>
       <c r="D112" s="1">
-        <v>619.5</v>
+        <v>94.74</v>
       </c>
       <c r="E112" s="2">
-        <v>19824.0</v>
+        <v>21599.94</v>
       </c>
       <c r="F112" s="1">
-        <v>580.5</v>
+        <v>80.83</v>
       </c>
       <c r="G112" s="2">
-        <v>18576.0</v>
+        <v>18429.24</v>
       </c>
       <c r="H112" s="2">
-        <v>-1248.0</v>
+        <v>-3170.7</v>
       </c>
       <c r="I112" s="3">
-        <v>-0.063</v>
+        <v>-0.1468</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C113" s="1">
-        <v>228.0</v>
+        <v>456.0</v>
       </c>
       <c r="D113" s="1">
-        <v>94.74</v>
+        <v>43.8</v>
       </c>
       <c r="E113" s="2">
-        <v>21599.94</v>
+        <v>19972.8</v>
       </c>
       <c r="F113" s="1">
-        <v>80.83</v>
+        <v>40.16</v>
       </c>
       <c r="G113" s="2">
-        <v>18429.24</v>
+        <v>18312.96</v>
       </c>
       <c r="H113" s="2">
-        <v>-3170.7</v>
+        <v>-1659.84</v>
       </c>
       <c r="I113" s="3">
-        <v>-0.1468</v>
+        <v>-0.0831</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C114" s="1">
-        <v>456.0</v>
+        <v>46.0</v>
       </c>
       <c r="D114" s="1">
-        <v>43.8</v>
+        <v>430.98</v>
       </c>
       <c r="E114" s="2">
-        <v>19972.8</v>
+        <v>19824.9</v>
       </c>
       <c r="F114" s="1">
-        <v>40.16</v>
+        <v>394.8</v>
       </c>
       <c r="G114" s="2">
-        <v>18312.96</v>
+        <v>18160.8</v>
       </c>
       <c r="H114" s="2">
-        <v>-1659.84</v>
+        <v>-1664.1</v>
       </c>
       <c r="I114" s="3">
-        <v>-0.0831</v>
+        <v>-0.0839</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C115" s="1">
-        <v>46.0</v>
-      </c>
-      <c r="D115" s="1">
-        <v>430.98</v>
+        <v>10.0</v>
+      </c>
+      <c r="D115" s="2">
+        <v>1963.23</v>
       </c>
       <c r="E115" s="2">
-        <v>19824.9</v>
-      </c>
-      <c r="F115" s="1">
-        <v>394.8</v>
+        <v>19632.3</v>
+      </c>
+      <c r="F115" s="2">
+        <v>1713.9</v>
       </c>
       <c r="G115" s="2">
-        <v>18160.8</v>
+        <v>17139.0</v>
       </c>
       <c r="H115" s="2">
-        <v>-1664.1</v>
+        <v>-2493.3</v>
       </c>
       <c r="I115" s="3">
-        <v>-0.0839</v>
+        <v>-0.127</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C116" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D116" s="2">
-        <v>1963.23</v>
+        <v>40.0</v>
+      </c>
+      <c r="D116" s="1">
+        <v>498.93</v>
       </c>
       <c r="E116" s="2">
-        <v>19632.3</v>
-      </c>
-      <c r="F116" s="2">
-        <v>1713.9</v>
+        <v>19957.2</v>
+      </c>
+      <c r="F116" s="1">
+        <v>426.1</v>
       </c>
       <c r="G116" s="2">
-        <v>17139.0</v>
+        <v>17044.0</v>
       </c>
       <c r="H116" s="2">
-        <v>-2493.3</v>
+        <v>-2913.2</v>
       </c>
       <c r="I116" s="3">
-        <v>-0.127</v>
+        <v>-0.146</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C117" s="1">
-        <v>40.0</v>
+        <v>72.0</v>
       </c>
       <c r="D117" s="1">
-        <v>498.93</v>
+        <v>278.55</v>
       </c>
       <c r="E117" s="2">
-        <v>19957.2</v>
+        <v>20055.6</v>
       </c>
       <c r="F117" s="1">
-        <v>426.1</v>
+        <v>225.0</v>
       </c>
       <c r="G117" s="2">
-        <v>17044.0</v>
+        <v>16200.0</v>
       </c>
       <c r="H117" s="2">
-        <v>-2913.2</v>
+        <v>-3855.6</v>
       </c>
       <c r="I117" s="3">
-        <v>-0.146</v>
+        <v>-0.1922</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C118" s="1">
-        <v>72.0</v>
+        <v>50.0</v>
       </c>
       <c r="D118" s="1">
-        <v>278.55</v>
+        <v>292.7</v>
       </c>
       <c r="E118" s="2">
-        <v>20055.6</v>
+        <v>14635.0</v>
       </c>
       <c r="F118" s="1">
-        <v>225.0</v>
+        <v>311.0</v>
       </c>
       <c r="G118" s="2">
-        <v>16200.0</v>
-      </c>
-      <c r="H118" s="2">
-        <v>-3855.6</v>
+        <v>15550.0</v>
+      </c>
+      <c r="H118" s="1">
+        <v>915.0</v>
       </c>
       <c r="I118" s="3">
-        <v>-0.1922</v>
+        <v>0.0625</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C119" s="1">
-        <v>50.0</v>
+        <v>10.0</v>
       </c>
       <c r="D119" s="1">
-        <v>292.7</v>
+        <v>975.8</v>
       </c>
       <c r="E119" s="2">
-        <v>14635.0</v>
-      </c>
-      <c r="F119" s="1">
-        <v>311.0</v>
-      </c>
-      <c r="G119" s="2">
-        <v>15550.0</v>
-      </c>
-      <c r="H119" s="1">
-        <v>915.0</v>
+        <v>9758.0</v>
+      </c>
+      <c r="F119" s="2">
+        <v>1491.9</v>
+      </c>
+      <c r="G119" s="4">
+        <v>14919.0</v>
+      </c>
+      <c r="H119" s="2">
+        <v>5161.0</v>
       </c>
       <c r="I119" s="3">
-        <v>0.0625</v>
+        <v>0.5289</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C120" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D120" s="1">
-        <v>975.8</v>
+        <v>9.0</v>
+      </c>
+      <c r="D120" s="2">
+        <v>1722.96</v>
       </c>
       <c r="E120" s="2">
-        <v>9758.0</v>
+        <v>15506.6</v>
       </c>
       <c r="F120" s="2">
-        <v>1491.9</v>
+        <v>1606.1</v>
       </c>
       <c r="G120" s="4">
-        <v>14919.0</v>
+        <v>14455.0</v>
       </c>
       <c r="H120" s="2">
-        <v>5161.0</v>
+        <v>-1051.7</v>
       </c>
       <c r="I120" s="3">
-        <v>0.5289</v>
+        <v>-0.0678</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="121">
@@ -5450,417 +5435,417 @@
         <v>11</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C121" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="D121" s="2">
-        <v>1722.96</v>
+        <v>27.0</v>
+      </c>
+      <c r="D121" s="1">
+        <v>369.7</v>
       </c>
       <c r="E121" s="2">
-        <v>15506.6</v>
-      </c>
-      <c r="F121" s="2">
-        <v>1606.1</v>
-      </c>
-      <c r="G121" s="4">
-        <v>14455.0</v>
+        <v>9981.9</v>
+      </c>
+      <c r="F121" s="1">
+        <v>532.45</v>
+      </c>
+      <c r="G121" s="2">
+        <v>14376.15</v>
       </c>
       <c r="H121" s="2">
-        <v>-1051.7</v>
+        <v>4394.25</v>
       </c>
       <c r="I121" s="3">
-        <v>-0.0678</v>
+        <v>0.4402</v>
       </c>
       <c r="J121" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C122" s="1">
-        <v>27.0</v>
-      </c>
-      <c r="D122" s="1">
-        <v>369.7</v>
+        <v>3.0</v>
+      </c>
+      <c r="D122" s="2">
+        <v>5480.0</v>
       </c>
       <c r="E122" s="2">
-        <v>9981.9</v>
-      </c>
-      <c r="F122" s="1">
-        <v>532.45</v>
+        <v>16440.0</v>
+      </c>
+      <c r="F122" s="2">
+        <v>4611.7</v>
       </c>
       <c r="G122" s="2">
-        <v>14376.15</v>
+        <v>13835.1</v>
       </c>
       <c r="H122" s="2">
-        <v>4394.25</v>
+        <v>-2604.9</v>
       </c>
       <c r="I122" s="3">
-        <v>0.4402</v>
+        <v>-0.1584</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C123" s="1">
-        <v>3.0</v>
+        <v>15.0</v>
       </c>
       <c r="D123" s="2">
-        <v>5480.0</v>
+        <v>1023.34</v>
       </c>
       <c r="E123" s="2">
-        <v>16440.0</v>
-      </c>
-      <c r="F123" s="2">
-        <v>4611.7</v>
+        <v>15350.15</v>
+      </c>
+      <c r="F123" s="1">
+        <v>846.25</v>
       </c>
       <c r="G123" s="2">
-        <v>13835.1</v>
+        <v>12693.75</v>
       </c>
       <c r="H123" s="2">
-        <v>-2604.9</v>
+        <v>-2656.4</v>
       </c>
       <c r="I123" s="3">
-        <v>-0.1584</v>
+        <v>-0.1731</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C124" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="D124" s="2">
-        <v>1023.34</v>
+        <v>68.0</v>
+      </c>
+      <c r="D124" s="1">
+        <v>174.16</v>
       </c>
       <c r="E124" s="2">
-        <v>15350.15</v>
+        <v>11842.88</v>
       </c>
       <c r="F124" s="1">
-        <v>846.25</v>
+        <v>180.5</v>
       </c>
       <c r="G124" s="2">
-        <v>12693.75</v>
-      </c>
-      <c r="H124" s="2">
-        <v>-2656.4</v>
+        <v>12274.0</v>
+      </c>
+      <c r="H124" s="1">
+        <v>431.12</v>
       </c>
       <c r="I124" s="3">
-        <v>-0.1731</v>
+        <v>0.0364</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C125" s="1">
-        <v>68.0</v>
-      </c>
-      <c r="D125" s="1">
-        <v>174.16</v>
+        <v>13.0</v>
+      </c>
+      <c r="D125" s="2">
+        <v>1105.88</v>
       </c>
       <c r="E125" s="2">
-        <v>11842.88</v>
+        <v>14376.5</v>
       </c>
       <c r="F125" s="1">
-        <v>180.5</v>
+        <v>871.0</v>
       </c>
       <c r="G125" s="2">
-        <v>12274.0</v>
-      </c>
-      <c r="H125" s="1">
-        <v>431.12</v>
+        <v>11323.0</v>
+      </c>
+      <c r="H125" s="2">
+        <v>-3053.5</v>
       </c>
       <c r="I125" s="3">
-        <v>0.0364</v>
+        <v>-0.2124</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C126" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="D126" s="2">
-        <v>1105.88</v>
+        <v>14.0</v>
+      </c>
+      <c r="D126" s="1">
+        <v>855.63</v>
       </c>
       <c r="E126" s="2">
-        <v>14376.5</v>
+        <v>11978.75</v>
       </c>
       <c r="F126" s="1">
-        <v>871.0</v>
+        <v>790.0</v>
       </c>
       <c r="G126" s="2">
-        <v>11323.0</v>
-      </c>
-      <c r="H126" s="2">
-        <v>-3053.5</v>
+        <v>11060.0</v>
+      </c>
+      <c r="H126" s="1">
+        <v>-918.75</v>
       </c>
       <c r="I126" s="3">
-        <v>-0.2124</v>
+        <v>-0.0767</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C127" s="1">
-        <v>14.0</v>
+        <v>95.0</v>
       </c>
       <c r="D127" s="1">
-        <v>855.63</v>
+        <v>158.81</v>
       </c>
       <c r="E127" s="2">
-        <v>11978.75</v>
+        <v>15087.3</v>
       </c>
       <c r="F127" s="1">
-        <v>790.0</v>
+        <v>115.35</v>
       </c>
       <c r="G127" s="2">
-        <v>11060.0</v>
-      </c>
-      <c r="H127" s="1">
-        <v>-918.75</v>
+        <v>10958.25</v>
+      </c>
+      <c r="H127" s="2">
+        <v>-4129.05</v>
       </c>
       <c r="I127" s="3">
-        <v>-0.0767</v>
+        <v>-0.2737</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C128" s="1">
-        <v>95.0</v>
+        <v>50.0</v>
       </c>
       <c r="D128" s="1">
-        <v>158.81</v>
+        <v>238.76</v>
       </c>
       <c r="E128" s="2">
-        <v>15087.3</v>
+        <v>11938.1</v>
       </c>
       <c r="F128" s="1">
-        <v>115.35</v>
+        <v>210.7</v>
       </c>
       <c r="G128" s="2">
-        <v>10958.25</v>
+        <v>10535.0</v>
       </c>
       <c r="H128" s="2">
-        <v>-4129.05</v>
+        <v>-1403.1</v>
       </c>
       <c r="I128" s="3">
-        <v>-0.2737</v>
+        <v>-0.1175</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C129" s="1">
-        <v>50.0</v>
-      </c>
-      <c r="D129" s="1">
-        <v>238.76</v>
+        <v>7.0</v>
+      </c>
+      <c r="D129" s="2">
+        <v>1395.0</v>
       </c>
       <c r="E129" s="2">
-        <v>11938.1</v>
-      </c>
-      <c r="F129" s="1">
-        <v>210.7</v>
+        <v>9765.0</v>
+      </c>
+      <c r="F129" s="2">
+        <v>1463.8</v>
       </c>
       <c r="G129" s="2">
-        <v>10535.0</v>
-      </c>
-      <c r="H129" s="2">
-        <v>-1403.1</v>
+        <v>10246.6</v>
+      </c>
+      <c r="H129" s="1">
+        <v>481.6</v>
       </c>
       <c r="I129" s="3">
-        <v>-0.1175</v>
+        <v>0.0493</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C130" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="D130" s="2">
-        <v>1395.0</v>
+        <v>59.0</v>
+      </c>
+      <c r="D130" s="1">
+        <v>166.1</v>
       </c>
       <c r="E130" s="2">
-        <v>9765.0</v>
-      </c>
-      <c r="F130" s="2">
-        <v>1463.8</v>
+        <v>9799.73</v>
+      </c>
+      <c r="F130" s="1">
+        <v>171.0</v>
       </c>
       <c r="G130" s="2">
-        <v>10246.6</v>
+        <v>10089.0</v>
       </c>
       <c r="H130" s="1">
-        <v>481.6</v>
+        <v>289.27</v>
       </c>
       <c r="I130" s="3">
-        <v>0.0493</v>
+        <v>0.0295</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C131" s="1">
-        <v>59.0</v>
+        <v>20.0</v>
       </c>
       <c r="D131" s="1">
-        <v>166.1</v>
+        <v>369.45</v>
       </c>
       <c r="E131" s="2">
-        <v>9799.73</v>
+        <v>7389.0</v>
       </c>
       <c r="F131" s="1">
-        <v>171.0</v>
-      </c>
-      <c r="G131" s="2">
-        <v>10089.0</v>
-      </c>
-      <c r="H131" s="1">
-        <v>289.27</v>
+        <v>492.45</v>
+      </c>
+      <c r="G131" s="4">
+        <v>9849.0</v>
+      </c>
+      <c r="H131" s="2">
+        <v>2460.0</v>
       </c>
       <c r="I131" s="3">
-        <v>0.0295</v>
+        <v>0.3329</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K131" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="132">
@@ -5868,151 +5853,151 @@
         <v>11</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C132" s="1">
-        <v>20.0</v>
+        <v>92.0</v>
       </c>
       <c r="D132" s="1">
-        <v>369.45</v>
+        <v>108.55</v>
       </c>
       <c r="E132" s="2">
-        <v>7389.0</v>
+        <v>9986.6</v>
       </c>
       <c r="F132" s="1">
-        <v>492.45</v>
-      </c>
-      <c r="G132" s="4">
-        <v>9849.0</v>
+        <v>95.92</v>
+      </c>
+      <c r="G132" s="2">
+        <v>8824.64</v>
       </c>
       <c r="H132" s="2">
-        <v>2460.0</v>
+        <v>-1161.96</v>
       </c>
       <c r="I132" s="3">
-        <v>0.3329</v>
+        <v>-0.1164</v>
       </c>
       <c r="J132" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C133" s="1">
-        <v>92.0</v>
+        <v>148.0</v>
       </c>
       <c r="D133" s="1">
-        <v>108.55</v>
+        <v>67.59</v>
       </c>
       <c r="E133" s="2">
-        <v>9986.6</v>
+        <v>10003.56</v>
       </c>
       <c r="F133" s="1">
-        <v>95.92</v>
+        <v>57.11</v>
       </c>
       <c r="G133" s="2">
-        <v>8824.64</v>
+        <v>8452.28</v>
       </c>
       <c r="H133" s="2">
-        <v>-1161.96</v>
+        <v>-1551.28</v>
       </c>
       <c r="I133" s="3">
-        <v>-0.1164</v>
+        <v>-0.1551</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C134" s="1">
-        <v>148.0</v>
-      </c>
-      <c r="D134" s="1">
-        <v>67.59</v>
+        <v>8.0</v>
+      </c>
+      <c r="D134" s="2">
+        <v>1486.09</v>
       </c>
       <c r="E134" s="2">
-        <v>10003.56</v>
+        <v>11888.7</v>
       </c>
       <c r="F134" s="1">
-        <v>57.11</v>
-      </c>
-      <c r="G134" s="2">
-        <v>8452.28</v>
+        <v>790.5</v>
+      </c>
+      <c r="G134" s="4">
+        <v>6324.0</v>
       </c>
       <c r="H134" s="2">
-        <v>-1551.28</v>
+        <v>-5564.7</v>
       </c>
       <c r="I134" s="3">
-        <v>-0.1551</v>
+        <v>-0.4681</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C135" s="1">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="D135" s="2">
-        <v>1486.09</v>
+        <v>1154.83</v>
       </c>
       <c r="E135" s="2">
-        <v>11888.7</v>
-      </c>
-      <c r="F135" s="1">
-        <v>790.5</v>
-      </c>
-      <c r="G135" s="4">
-        <v>6324.0</v>
+        <v>3464.5</v>
+      </c>
+      <c r="F135" s="2">
+        <v>1925.3</v>
+      </c>
+      <c r="G135" s="2">
+        <v>5775.9</v>
       </c>
       <c r="H135" s="2">
-        <v>-5564.7</v>
+        <v>2311.4</v>
       </c>
       <c r="I135" s="3">
-        <v>-0.4681</v>
+        <v>0.6672</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K135" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="136">
@@ -6020,190 +6005,128 @@
         <v>11</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C136" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="D136" s="2">
-        <v>1154.83</v>
+        <v>39.0</v>
+      </c>
+      <c r="D136" s="1">
+        <v>379.94</v>
       </c>
       <c r="E136" s="2">
-        <v>3464.5</v>
-      </c>
-      <c r="F136" s="2">
-        <v>1925.3</v>
+        <v>14817.69</v>
+      </c>
+      <c r="F136" s="1">
+        <v>86.49</v>
       </c>
       <c r="G136" s="2">
-        <v>5775.9</v>
+        <v>3373.11</v>
       </c>
       <c r="H136" s="2">
-        <v>2311.4</v>
+        <v>-11444.58</v>
       </c>
       <c r="I136" s="3">
-        <v>0.6672</v>
+        <v>-0.7724</v>
       </c>
       <c r="J136" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C137" s="1">
-        <v>39.0</v>
+        <v>26.0</v>
       </c>
       <c r="D137" s="1">
-        <v>379.94</v>
+        <v>205.31</v>
       </c>
       <c r="E137" s="2">
-        <v>14817.69</v>
+        <v>5338.0</v>
       </c>
       <c r="F137" s="1">
-        <v>86.49</v>
-      </c>
-      <c r="G137" s="2">
-        <v>3373.11</v>
+        <v>127.89</v>
+      </c>
+      <c r="G137" s="4">
+        <v>3325.0</v>
       </c>
       <c r="H137" s="2">
-        <v>-11444.58</v>
+        <v>-2012.86</v>
       </c>
       <c r="I137" s="3">
-        <v>-0.7724</v>
+        <v>-0.3771</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K137" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C138" s="1">
-        <v>26.0</v>
+        <v>11.0</v>
       </c>
       <c r="D138" s="1">
-        <v>205.31</v>
-      </c>
-      <c r="E138" s="2">
-        <v>5338.0</v>
+        <v>80.54</v>
+      </c>
+      <c r="E138" s="1">
+        <v>885.9</v>
       </c>
       <c r="F138" s="1">
-        <v>127.89</v>
+        <v>272.25</v>
       </c>
       <c r="G138" s="4">
-        <v>3325.0</v>
+        <v>2995.0</v>
       </c>
       <c r="H138" s="2">
-        <v>-2012.86</v>
+        <v>2108.85</v>
       </c>
       <c r="I138" s="3">
-        <v>-0.3771</v>
+        <v>2.3805</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K138" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C139" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="D139" s="1">
-        <v>80.54</v>
-      </c>
-      <c r="E139" s="1">
-        <v>885.9</v>
-      </c>
-      <c r="F139" s="1">
-        <v>272.25</v>
-      </c>
-      <c r="G139" s="4">
-        <v>2995.0</v>
-      </c>
-      <c r="H139" s="2">
-        <v>2108.85</v>
-      </c>
-      <c r="I139" s="3">
-        <v>2.3805</v>
-      </c>
-      <c r="J139" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K139" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L139" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B140" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C140" s="6">
-        <v>6123.0</v>
-      </c>
-      <c r="D140" s="6">
-        <v>50.33</v>
-      </c>
-      <c r="E140" s="6">
-        <v>308166.8</v>
-      </c>
-      <c r="F140" s="6">
-        <v>206.62</v>
-      </c>
-      <c r="G140" s="6">
-        <v>1265134.0</v>
-      </c>
-      <c r="H140" s="6">
-        <v>956967.5</v>
-      </c>
-      <c r="I140" s="6">
-        <v>3.1054</v>
-      </c>
-      <c r="J140" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="K140" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L140" s="5" t="s">
-        <v>17</v>
-      </c>
+      <c r="A139" s="5"/>
+      <c r="B139" s="5"/>
+      <c r="C139" s="6"/>
+      <c r="D139" s="6"/>
+      <c r="E139" s="6"/>
+      <c r="F139" s="6"/>
+      <c r="G139" s="6"/>
+      <c r="H139" s="6"/>
+      <c r="I139" s="6"/>
+      <c r="J139" s="5"/>
+      <c r="K139" s="5"/>
+      <c r="L139" s="5"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/data/portfolio.xlsx
+++ b/data/portfolio.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="202">
   <si>
     <t>Self/Other Remarks</t>
   </si>
@@ -46,9 +46,567 @@
     <t>Remarks</t>
   </si>
   <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>3MINDIA</t>
+  </si>
+  <si>
+    <t>3,94,247.35</t>
+  </si>
+  <si>
+    <t>3,93,360.00</t>
+  </si>
+  <si>
+    <t>2.Mar'26 Must buy</t>
+  </si>
+  <si>
+    <t>MUSTBUY</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
+    <t>HCG</t>
+  </si>
+  <si>
+    <t>1,91,353.60</t>
+  </si>
+  <si>
+    <t>3,91,161</t>
+  </si>
+  <si>
+    <t>1,99,807.10</t>
+  </si>
+  <si>
+    <t>Self</t>
+  </si>
+  <si>
+    <t>AEROFLEX</t>
+  </si>
+  <si>
+    <t>1,79,710.57</t>
+  </si>
+  <si>
+    <t>3,90,048.00</t>
+  </si>
+  <si>
+    <t>2,10,337.43</t>
+  </si>
+  <si>
+    <t>SONACOMS</t>
+  </si>
+  <si>
+    <t>3,08,749.05</t>
+  </si>
+  <si>
+    <t>3,40,800.00</t>
+  </si>
+  <si>
+    <t>SYRMA</t>
+  </si>
+  <si>
+    <t>1,24,501.80</t>
+  </si>
+  <si>
+    <t>3,31,310</t>
+  </si>
+  <si>
+    <t>2,06,807.80</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>PARKHOSPS</t>
+  </si>
+  <si>
+    <t>1,42,295.53</t>
+  </si>
+  <si>
+    <t>2,50,790.40</t>
+  </si>
+  <si>
+    <t>1,08,494.87</t>
+  </si>
+  <si>
+    <t>1. Oct'25 Must buy</t>
+  </si>
+  <si>
+    <t>MTARTECH</t>
+  </si>
+  <si>
+    <t>1,84,782</t>
+  </si>
+  <si>
+    <t>1,45,393.70</t>
+  </si>
+  <si>
+    <t>DEEDEV</t>
+  </si>
+  <si>
+    <t>1,62,180.00</t>
+  </si>
+  <si>
+    <t>SANSERA</t>
+  </si>
+  <si>
+    <t>1,61,991.20</t>
+  </si>
+  <si>
+    <t>TRITURBINE</t>
+  </si>
+  <si>
+    <t>1,26,763.15</t>
+  </si>
+  <si>
+    <t>1,56,480.50</t>
+  </si>
+  <si>
+    <t>THERMAX</t>
+  </si>
+  <si>
+    <t>1,32,916.50</t>
+  </si>
+  <si>
+    <t>1,46,040.00</t>
+  </si>
+  <si>
+    <t>ELGIEQUIP</t>
+  </si>
+  <si>
+    <t>1,35,467.90</t>
+  </si>
+  <si>
+    <t>1,41,977.50</t>
+  </si>
+  <si>
+    <t>POWERINDIA</t>
+  </si>
+  <si>
+    <t>1,41,800</t>
+  </si>
+  <si>
+    <t>1,33,016.35</t>
+  </si>
+  <si>
+    <t>ASTRAMICRO</t>
+  </si>
+  <si>
+    <t>1,36,936</t>
+  </si>
+  <si>
+    <t>1,14,238.10</t>
+  </si>
+  <si>
+    <t>INGERRAND</t>
+  </si>
+  <si>
+    <t>1,55,891.70</t>
+  </si>
+  <si>
+    <t>1,34,352.00</t>
+  </si>
+  <si>
+    <t>ASTERDM</t>
+  </si>
+  <si>
+    <t>1,33,407</t>
+  </si>
+  <si>
+    <t>SJVN</t>
+  </si>
+  <si>
+    <t>1,09,462.55</t>
+  </si>
+  <si>
+    <t>1,05,948.80</t>
+  </si>
+  <si>
+    <t>3.May'26 Must buy</t>
+  </si>
+  <si>
+    <t>NEPHROPLUS</t>
+  </si>
+  <si>
+    <t>1,04,418.80</t>
+  </si>
+  <si>
+    <t>NEULANDLAB</t>
+  </si>
+  <si>
+    <t>1,01,016</t>
+  </si>
+  <si>
+    <t>INOXINDIA</t>
+  </si>
+  <si>
+    <t>AVANTEL</t>
+  </si>
+  <si>
+    <t>SOUTHWEST</t>
+  </si>
+  <si>
+    <t>DLINKINDIA</t>
+  </si>
+  <si>
+    <t>TRIVENI</t>
+  </si>
+  <si>
+    <t>GALAPREC</t>
+  </si>
+  <si>
+    <t>ISGEC</t>
+  </si>
+  <si>
+    <t>1,02,322.55</t>
+  </si>
+  <si>
+    <t>MODISONLTD</t>
+  </si>
+  <si>
+    <t>HAPPYFORGE</t>
+  </si>
+  <si>
+    <t>NESCO</t>
+  </si>
+  <si>
+    <t>NIFTYBEES</t>
+  </si>
+  <si>
+    <t>HBLENGINE</t>
+  </si>
+  <si>
+    <t>SASKEN</t>
+  </si>
+  <si>
+    <t>PFC</t>
+  </si>
+  <si>
+    <t>ENRIN</t>
+  </si>
+  <si>
+    <t>ARE&amp;M</t>
+  </si>
+  <si>
+    <t>JNKINDIA</t>
+  </si>
+  <si>
+    <t>KENNAMET</t>
+  </si>
+  <si>
+    <t>NLCINDIA</t>
+  </si>
+  <si>
+    <t>INDUSTOWER</t>
+  </si>
+  <si>
+    <t>INDGN</t>
+  </si>
+  <si>
+    <t>RIR</t>
+  </si>
+  <si>
+    <t>WELCORP</t>
+  </si>
+  <si>
+    <t>TEGA</t>
+  </si>
+  <si>
+    <t>SCODATUBES</t>
+  </si>
+  <si>
+    <t>POWERICA</t>
+  </si>
+  <si>
+    <t>SALZERELEC</t>
+  </si>
+  <si>
+    <t>MENONBE</t>
+  </si>
+  <si>
+    <t>HEG</t>
+  </si>
+  <si>
+    <t>ASHIANA</t>
+  </si>
+  <si>
+    <t>RUBICON</t>
+  </si>
+  <si>
+    <t>INDNIPPON</t>
+  </si>
+  <si>
+    <t>RKSWAMY</t>
+  </si>
+  <si>
+    <t>SCI</t>
+  </si>
+  <si>
+    <t>RATEGAIN</t>
+  </si>
+  <si>
+    <t>GMDCLTD</t>
+  </si>
+  <si>
+    <t>TREL</t>
+  </si>
+  <si>
+    <t>EIMCOELECO</t>
+  </si>
+  <si>
+    <t>BLUEJET</t>
+  </si>
+  <si>
+    <t>LATENTVIEW</t>
+  </si>
+  <si>
+    <t>CARBORUNIV</t>
+  </si>
+  <si>
+    <t>SHREEJISPG</t>
+  </si>
+  <si>
+    <t>ENTERO</t>
+  </si>
+  <si>
+    <t>NETWEB</t>
+  </si>
+  <si>
+    <t>RAMCOSYS</t>
+  </si>
+  <si>
+    <t>STALLION</t>
+  </si>
+  <si>
+    <t>RPTECH</t>
+  </si>
+  <si>
+    <t>SIGNPOST</t>
+  </si>
+  <si>
+    <t>SIEMENS</t>
+  </si>
+  <si>
+    <t>EXPLEOSOL</t>
+  </si>
+  <si>
+    <t>HONAUT</t>
+  </si>
+  <si>
+    <t>GRINDWELL</t>
+  </si>
+  <si>
+    <t>BOROSCI</t>
+  </si>
+  <si>
+    <t>GMMPFAUDLR</t>
+  </si>
+  <si>
+    <t>MAPMYINDIA</t>
+  </si>
+  <si>
+    <t>YATHARTH</t>
+  </si>
+  <si>
+    <t>VASCONEQ</t>
+  </si>
+  <si>
+    <t>FRACTAL</t>
+  </si>
+  <si>
+    <t>PROTEAN</t>
+  </si>
+  <si>
+    <t>UNIVCABLES</t>
+  </si>
+  <si>
+    <t>RAYMOND</t>
+  </si>
+  <si>
+    <t>GRAPHITE</t>
+  </si>
+  <si>
+    <t>URBANCO</t>
+  </si>
+  <si>
+    <t>GMRAIRPORT</t>
+  </si>
+  <si>
+    <t>GESHIP</t>
+  </si>
+  <si>
+    <t>LAXMIDENTL</t>
+  </si>
+  <si>
+    <t>BIOCON</t>
+  </si>
+  <si>
+    <t>ANURAS</t>
+  </si>
+  <si>
+    <t>SHANKARA</t>
+  </si>
+  <si>
+    <t>INCAP</t>
+  </si>
+  <si>
+    <t>SHILPAMED</t>
+  </si>
+  <si>
+    <t>ECOSMOBLTY</t>
+  </si>
+  <si>
+    <t>KIRLPNU</t>
+  </si>
+  <si>
+    <t>PTC</t>
+  </si>
+  <si>
+    <t>LANDMARK</t>
+  </si>
+  <si>
+    <t>FREDUN</t>
+  </si>
+  <si>
+    <t>CMSINFO</t>
+  </si>
+  <si>
+    <t>DIFFNKG</t>
+  </si>
+  <si>
+    <t>MOSCHIP</t>
+  </si>
+  <si>
+    <t>GULFOILLUB</t>
+  </si>
+  <si>
+    <t>DATAPATTNS</t>
+  </si>
+  <si>
+    <t>TOTEM</t>
+  </si>
+  <si>
+    <t>CYIENTDLM</t>
+  </si>
+  <si>
+    <t>MMP</t>
+  </si>
+  <si>
+    <t>BBL</t>
+  </si>
+  <si>
+    <t>CESC</t>
+  </si>
+  <si>
+    <t>OMINFRAL</t>
+  </si>
+  <si>
+    <t>SKFINDUS</t>
+  </si>
+  <si>
+    <t>WHIRLPOOL</t>
+  </si>
+  <si>
+    <t>PITTIENG</t>
+  </si>
+  <si>
+    <t>RAYMONDREL</t>
+  </si>
+  <si>
+    <t>NIITLTD</t>
+  </si>
+  <si>
+    <t>ORIENTCER</t>
+  </si>
+  <si>
+    <t>RUSTOMJEE</t>
+  </si>
+  <si>
+    <t>INTERARCH</t>
+  </si>
+  <si>
+    <t>FMGOETZE</t>
+  </si>
+  <si>
+    <t>CAPACITE</t>
+  </si>
+  <si>
+    <t>RAILTEL</t>
+  </si>
+  <si>
+    <t>AFFLE</t>
+  </si>
+  <si>
+    <t>SKFINDIA</t>
+  </si>
+  <si>
+    <t>TEJASNET</t>
+  </si>
+  <si>
+    <t>VSTTILLERS</t>
+  </si>
+  <si>
+    <t>ASALCBR</t>
+  </si>
+  <si>
+    <t>GREAVESCOT</t>
+  </si>
+  <si>
+    <t>GLOBUSSPR</t>
+  </si>
+  <si>
+    <t>ELDEHSG</t>
+  </si>
+  <si>
+    <t>ARIS</t>
+  </si>
+  <si>
+    <t>QUESS</t>
+  </si>
+  <si>
+    <t>AVALON</t>
+  </si>
+  <si>
+    <t>GIPCL</t>
+  </si>
+  <si>
+    <t>TVSELECT</t>
+  </si>
+  <si>
+    <t>AEROENTER</t>
+  </si>
+  <si>
+    <t>EMBDL</t>
+  </si>
+  <si>
+    <t>LAKSELEC</t>
+  </si>
+  <si>
+    <t>TATACOMM</t>
+  </si>
+  <si>
+    <t>UNIECOM</t>
+  </si>
+  <si>
+    <t>SHK</t>
+  </si>
+  <si>
+    <t>SUVEN</t>
+  </si>
+  <si>
+    <t>MAFANG</t>
+  </si>
+  <si>
+    <t>3,08,166.76</t>
+  </si>
+  <si>
+    <t>12,65,134</t>
+  </si>
+  <si>
+    <t>9,56,967.50</t>
+  </si>
+  <si>
     <t>NH</t>
   </si>
   <si>
@@ -59,562 +617,13 @@
   </si>
   <si>
     <t>5,17,592.40</t>
-  </si>
-  <si>
-    <t>Self</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>3MINDIA</t>
-  </si>
-  <si>
-    <t>3,94,247.35</t>
-  </si>
-  <si>
-    <t>3,93,360.00</t>
-  </si>
-  <si>
-    <t>2.Mar'26 Must buy</t>
-  </si>
-  <si>
-    <t>MUSTBUY</t>
-  </si>
-  <si>
-    <t>HCG</t>
-  </si>
-  <si>
-    <t>1,91,353.60</t>
-  </si>
-  <si>
-    <t>3,91,161</t>
-  </si>
-  <si>
-    <t>1,99,807.10</t>
-  </si>
-  <si>
-    <t>AEROFLEX</t>
-  </si>
-  <si>
-    <t>1,79,710.57</t>
-  </si>
-  <si>
-    <t>3,90,048.00</t>
-  </si>
-  <si>
-    <t>2,10,337.43</t>
-  </si>
-  <si>
-    <t>SONACOMS</t>
-  </si>
-  <si>
-    <t>3,08,749.05</t>
-  </si>
-  <si>
-    <t>3,40,800.00</t>
-  </si>
-  <si>
-    <t>SYRMA</t>
-  </si>
-  <si>
-    <t>1,24,501.80</t>
-  </si>
-  <si>
-    <t>3,31,310</t>
-  </si>
-  <si>
-    <t>2,06,807.80</t>
-  </si>
-  <si>
-    <t>PARKHOSPS</t>
-  </si>
-  <si>
-    <t>1,42,295.53</t>
-  </si>
-  <si>
-    <t>2,50,790.40</t>
-  </si>
-  <si>
-    <t>1,08,494.87</t>
-  </si>
-  <si>
-    <t>1. Oct'25 Must buy</t>
-  </si>
-  <si>
-    <t>MTARTECH</t>
-  </si>
-  <si>
-    <t>1,84,782</t>
-  </si>
-  <si>
-    <t>1,45,393.70</t>
-  </si>
-  <si>
-    <t>DEEDEV</t>
-  </si>
-  <si>
-    <t>1,62,180.00</t>
-  </si>
-  <si>
-    <t>SANSERA</t>
-  </si>
-  <si>
-    <t>1,61,991.20</t>
-  </si>
-  <si>
-    <t>TRITURBINE</t>
-  </si>
-  <si>
-    <t>1,26,763.15</t>
-  </si>
-  <si>
-    <t>1,56,480.50</t>
-  </si>
-  <si>
-    <t>THERMAX</t>
-  </si>
-  <si>
-    <t>1,32,916.50</t>
-  </si>
-  <si>
-    <t>1,46,040.00</t>
-  </si>
-  <si>
-    <t>ELGIEQUIP</t>
-  </si>
-  <si>
-    <t>1,35,467.90</t>
-  </si>
-  <si>
-    <t>1,41,977.50</t>
-  </si>
-  <si>
-    <t>POWERINDIA</t>
-  </si>
-  <si>
-    <t>1,41,800</t>
-  </si>
-  <si>
-    <t>1,33,016.35</t>
-  </si>
-  <si>
-    <t>ASTRAMICRO</t>
-  </si>
-  <si>
-    <t>1,36,936</t>
-  </si>
-  <si>
-    <t>1,14,238.10</t>
-  </si>
-  <si>
-    <t>INGERRAND</t>
-  </si>
-  <si>
-    <t>1,55,891.70</t>
-  </si>
-  <si>
-    <t>1,34,352.00</t>
-  </si>
-  <si>
-    <t>ASTERDM</t>
-  </si>
-  <si>
-    <t>1,33,407</t>
-  </si>
-  <si>
-    <t>SJVN</t>
-  </si>
-  <si>
-    <t>1,09,462.55</t>
-  </si>
-  <si>
-    <t>1,05,948.80</t>
-  </si>
-  <si>
-    <t>3.May'26 Must buy</t>
-  </si>
-  <si>
-    <t>NEPHROPLUS</t>
-  </si>
-  <si>
-    <t>1,04,418.80</t>
-  </si>
-  <si>
-    <t>NEULANDLAB</t>
-  </si>
-  <si>
-    <t>1,01,016</t>
-  </si>
-  <si>
-    <t>INOXINDIA</t>
-  </si>
-  <si>
-    <t>AVANTEL</t>
-  </si>
-  <si>
-    <t>SOUTHWEST</t>
-  </si>
-  <si>
-    <t>DLINKINDIA</t>
-  </si>
-  <si>
-    <t>TRIVENI</t>
-  </si>
-  <si>
-    <t>GALAPREC</t>
-  </si>
-  <si>
-    <t>ISGEC</t>
-  </si>
-  <si>
-    <t>1,02,322.55</t>
-  </si>
-  <si>
-    <t>MODISONLTD</t>
-  </si>
-  <si>
-    <t>HAPPYFORGE</t>
-  </si>
-  <si>
-    <t>NESCO</t>
-  </si>
-  <si>
-    <t>NIFTYBEES</t>
-  </si>
-  <si>
-    <t>HBLENGINE</t>
-  </si>
-  <si>
-    <t>SASKEN</t>
-  </si>
-  <si>
-    <t>PFC</t>
-  </si>
-  <si>
-    <t>ENRIN</t>
-  </si>
-  <si>
-    <t>ARE&amp;M</t>
-  </si>
-  <si>
-    <t>JNKINDIA</t>
-  </si>
-  <si>
-    <t>KENNAMET</t>
-  </si>
-  <si>
-    <t>NLCINDIA</t>
-  </si>
-  <si>
-    <t>INDUSTOWER</t>
-  </si>
-  <si>
-    <t>INDGN</t>
-  </si>
-  <si>
-    <t>RIR</t>
-  </si>
-  <si>
-    <t>WELCORP</t>
-  </si>
-  <si>
-    <t>TEGA</t>
-  </si>
-  <si>
-    <t>SCODATUBES</t>
-  </si>
-  <si>
-    <t>POWERICA</t>
-  </si>
-  <si>
-    <t>SALZERELEC</t>
-  </si>
-  <si>
-    <t>MENONBE</t>
-  </si>
-  <si>
-    <t>HEG</t>
-  </si>
-  <si>
-    <t>ASHIANA</t>
-  </si>
-  <si>
-    <t>RUBICON</t>
-  </si>
-  <si>
-    <t>INDNIPPON</t>
-  </si>
-  <si>
-    <t>RKSWAMY</t>
-  </si>
-  <si>
-    <t>SCI</t>
-  </si>
-  <si>
-    <t>RATEGAIN</t>
-  </si>
-  <si>
-    <t>GMDCLTD</t>
-  </si>
-  <si>
-    <t>TREL</t>
-  </si>
-  <si>
-    <t>EIMCOELECO</t>
-  </si>
-  <si>
-    <t>BLUEJET</t>
-  </si>
-  <si>
-    <t>LATENTVIEW</t>
-  </si>
-  <si>
-    <t>CARBORUNIV</t>
-  </si>
-  <si>
-    <t>SHREEJISPG</t>
-  </si>
-  <si>
-    <t>ENTERO</t>
-  </si>
-  <si>
-    <t>NETWEB</t>
-  </si>
-  <si>
-    <t>RAMCOSYS</t>
-  </si>
-  <si>
-    <t>STALLION</t>
-  </si>
-  <si>
-    <t>RPTECH</t>
-  </si>
-  <si>
-    <t>SIGNPOST</t>
-  </si>
-  <si>
-    <t>SIEMENS</t>
-  </si>
-  <si>
-    <t>EXPLEOSOL</t>
-  </si>
-  <si>
-    <t>HONAUT</t>
-  </si>
-  <si>
-    <t>GRINDWELL</t>
-  </si>
-  <si>
-    <t>BOROSCI</t>
-  </si>
-  <si>
-    <t>GMMPFAUDLR</t>
-  </si>
-  <si>
-    <t>MAPMYINDIA</t>
-  </si>
-  <si>
-    <t>YATHARTH</t>
-  </si>
-  <si>
-    <t>VASCONEQ</t>
-  </si>
-  <si>
-    <t>FRACTAL</t>
-  </si>
-  <si>
-    <t>PROTEAN</t>
-  </si>
-  <si>
-    <t>UNIVCABLES</t>
-  </si>
-  <si>
-    <t>RAYMOND</t>
-  </si>
-  <si>
-    <t>GRAPHITE</t>
-  </si>
-  <si>
-    <t>URBANCO</t>
-  </si>
-  <si>
-    <t>GMRAIRPORT</t>
-  </si>
-  <si>
-    <t>GESHIP</t>
-  </si>
-  <si>
-    <t>LAXMIDENTL</t>
-  </si>
-  <si>
-    <t>BIOCON</t>
-  </si>
-  <si>
-    <t>ANURAS</t>
-  </si>
-  <si>
-    <t>SHANKARA</t>
-  </si>
-  <si>
-    <t>INCAP</t>
-  </si>
-  <si>
-    <t>SHILPAMED</t>
-  </si>
-  <si>
-    <t>ECOSMOBLTY</t>
-  </si>
-  <si>
-    <t>KIRLPNU</t>
-  </si>
-  <si>
-    <t>PTC</t>
-  </si>
-  <si>
-    <t>LANDMARK</t>
-  </si>
-  <si>
-    <t>FREDUN</t>
-  </si>
-  <si>
-    <t>CMSINFO</t>
-  </si>
-  <si>
-    <t>DIFFNKG</t>
-  </si>
-  <si>
-    <t>MOSCHIP</t>
-  </si>
-  <si>
-    <t>GULFOILLUB</t>
-  </si>
-  <si>
-    <t>DATAPATTNS</t>
-  </si>
-  <si>
-    <t>TOTEM</t>
-  </si>
-  <si>
-    <t>CYIENTDLM</t>
-  </si>
-  <si>
-    <t>MMP</t>
-  </si>
-  <si>
-    <t>BBL</t>
-  </si>
-  <si>
-    <t>CESC</t>
-  </si>
-  <si>
-    <t>OMINFRAL</t>
-  </si>
-  <si>
-    <t>SKFINDUS</t>
-  </si>
-  <si>
-    <t>WHIRLPOOL</t>
-  </si>
-  <si>
-    <t>PITTIENG</t>
-  </si>
-  <si>
-    <t>RAYMONDREL</t>
-  </si>
-  <si>
-    <t>NIITLTD</t>
-  </si>
-  <si>
-    <t>ORIENTCER</t>
-  </si>
-  <si>
-    <t>RUSTOMJEE</t>
-  </si>
-  <si>
-    <t>INTERARCH</t>
-  </si>
-  <si>
-    <t>FMGOETZE</t>
-  </si>
-  <si>
-    <t>CAPACITE</t>
-  </si>
-  <si>
-    <t>RAILTEL</t>
-  </si>
-  <si>
-    <t>AFFLE</t>
-  </si>
-  <si>
-    <t>SKFINDIA</t>
-  </si>
-  <si>
-    <t>TEJASNET</t>
-  </si>
-  <si>
-    <t>VSTTILLERS</t>
-  </si>
-  <si>
-    <t>ASALCBR</t>
-  </si>
-  <si>
-    <t>GREAVESCOT</t>
-  </si>
-  <si>
-    <t>GLOBUSSPR</t>
-  </si>
-  <si>
-    <t>ELDEHSG</t>
-  </si>
-  <si>
-    <t>ARIS</t>
-  </si>
-  <si>
-    <t>QUESS</t>
-  </si>
-  <si>
-    <t>AVALON</t>
-  </si>
-  <si>
-    <t>GIPCL</t>
-  </si>
-  <si>
-    <t>TVSELECT</t>
-  </si>
-  <si>
-    <t>AEROENTER</t>
-  </si>
-  <si>
-    <t>EMBDL</t>
-  </si>
-  <si>
-    <t>LAKSELEC</t>
-  </si>
-  <si>
-    <t>TATACOMM</t>
-  </si>
-  <si>
-    <t>UNIECOM</t>
-  </si>
-  <si>
-    <t>SHK</t>
-  </si>
-  <si>
-    <t>SUVEN</t>
-  </si>
-  <si>
-    <t>MAFANG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -631,22 +640,58 @@
       <color rgb="FF000000"/>
       <name val="&quot;Aptos Narrow&quot;"/>
     </font>
+    <font>
+      <sz val="7.0"/>
+      <color rgb="FF444444"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="7.0"/>
+      <color rgb="FF10B983"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFAFB"/>
+        <bgColor rgb="FFFAFAFB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -662,11 +707,32 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -931,72 +997,72 @@
         <v>12</v>
       </c>
       <c r="C2" s="1">
-        <v>369.0</v>
-      </c>
-      <c r="D2" s="1">
-        <v>497.01</v>
+        <v>12.0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>32853.95</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="2">
-        <v>1899.7</v>
+        <v>32780.0</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="1">
+        <v>-887.35</v>
+      </c>
+      <c r="I2" s="3">
+        <v>-0.0023</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="3">
-        <v>2.8223</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1">
+        <v>609.0</v>
+      </c>
+      <c r="D3" s="1">
+        <v>314.21</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>32853.95</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1">
+        <v>642.3</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="2">
-        <v>32780.0</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="1">
-        <v>-887.35</v>
-      </c>
       <c r="I3" s="3">
-        <v>-0.0023</v>
+        <v>1.0442</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -1004,113 +1070,113 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="1">
+        <v>960.0</v>
+      </c>
+      <c r="D4" s="1">
+        <v>187.2</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="1">
-        <v>609.0</v>
-      </c>
-      <c r="D4" s="1">
-        <v>314.21</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1">
+        <v>406.3</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="1">
-        <v>642.3</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="I4" s="3">
-        <v>1.0442</v>
+        <v>1.1704</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1">
+        <v>568.0</v>
+      </c>
+      <c r="D5" s="1">
+        <v>543.57</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="1">
-        <v>960.0</v>
-      </c>
-      <c r="D5" s="1">
-        <v>187.2</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1">
+        <v>600.0</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="1">
-        <v>406.3</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>31</v>
+      <c r="H5" s="2">
+        <v>32050.95</v>
       </c>
       <c r="I5" s="3">
-        <v>1.1704</v>
+        <v>0.1038</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="1">
+        <v>289.0</v>
+      </c>
+      <c r="D6" s="1">
+        <v>430.8</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1146.4</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="1">
-        <v>568.0</v>
-      </c>
-      <c r="D6" s="1">
-        <v>543.57</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="1">
-        <v>600.0</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" s="2">
-        <v>32050.95</v>
-      </c>
       <c r="I6" s="3">
-        <v>0.1038</v>
+        <v>1.6611</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -1121,16 +1187,16 @@
         <v>35</v>
       </c>
       <c r="C7" s="1">
-        <v>289.0</v>
+        <v>896.0</v>
       </c>
       <c r="D7" s="1">
-        <v>430.8</v>
+        <v>158.81</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="2">
-        <v>1146.4</v>
+      <c r="F7" s="1">
+        <v>279.9</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>37</v>
@@ -1139,36 +1205,36 @@
         <v>38</v>
       </c>
       <c r="I7" s="3">
-        <v>1.6611</v>
+        <v>0.7625</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" s="1">
-        <v>896.0</v>
-      </c>
-      <c r="D8" s="1">
-        <v>158.81</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="1">
-        <v>279.9</v>
+        <v>26.0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1514.93</v>
+      </c>
+      <c r="E8" s="2">
+        <v>39388.3</v>
+      </c>
+      <c r="F8" s="2">
+        <v>7107.0</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>41</v>
@@ -1177,16 +1243,16 @@
         <v>42</v>
       </c>
       <c r="I8" s="3">
-        <v>0.7625</v>
+        <v>3.6913</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
@@ -1194,265 +1260,265 @@
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="1">
+        <v>255.0</v>
+      </c>
+      <c r="D9" s="1">
+        <v>261.86</v>
+      </c>
+      <c r="E9" s="2">
+        <v>66773.95</v>
+      </c>
+      <c r="F9" s="1">
+        <v>636.0</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="1">
-        <v>26.0</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1514.93</v>
-      </c>
-      <c r="E9" s="2">
-        <v>39388.3</v>
-      </c>
-      <c r="F9" s="2">
-        <v>7107.0</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>46</v>
+      <c r="H9" s="2">
+        <v>95406.05</v>
       </c>
       <c r="I9" s="3">
-        <v>3.6913</v>
+        <v>1.4288</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1">
-        <v>255.0</v>
-      </c>
-      <c r="D10" s="1">
-        <v>261.86</v>
+        <v>56.0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1524.46</v>
       </c>
       <c r="E10" s="2">
-        <v>66773.95</v>
-      </c>
-      <c r="F10" s="1">
-        <v>636.0</v>
+        <v>85369.7</v>
+      </c>
+      <c r="F10" s="2">
+        <v>2892.7</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2">
-        <v>95406.05</v>
+        <v>76621.5</v>
       </c>
       <c r="I10" s="3">
-        <v>1.4288</v>
+        <v>0.8975</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="1">
+        <v>230.0</v>
+      </c>
+      <c r="D11" s="1">
+        <v>551.14</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="1">
+        <v>680.35</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="1">
-        <v>56.0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1524.46</v>
-      </c>
-      <c r="E11" s="2">
-        <v>85369.7</v>
-      </c>
-      <c r="F11" s="2">
-        <v>2892.7</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="H11" s="2">
-        <v>76621.5</v>
+        <v>29717.35</v>
       </c>
       <c r="I11" s="3">
-        <v>0.8975</v>
+        <v>0.2344</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>4430.55</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="1">
-        <v>230.0</v>
-      </c>
-      <c r="D12" s="1">
-        <v>551.14</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="2">
+        <v>4868.0</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="1">
-        <v>680.35</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="H12" s="2">
-        <v>29717.35</v>
+        <v>13123.5</v>
       </c>
       <c r="I12" s="3">
-        <v>0.2344</v>
+        <v>0.0987</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="1">
+        <v>245.0</v>
+      </c>
+      <c r="D13" s="1">
+        <v>552.93</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>4430.55</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1">
+        <v>579.5</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="2">
-        <v>4868.0</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="H13" s="2">
-        <v>13123.5</v>
+        <v>6509.6</v>
       </c>
       <c r="I13" s="3">
-        <v>0.0987</v>
+        <v>0.0481</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>2195.91</v>
+      </c>
+      <c r="E14" s="2">
+        <v>8783.65</v>
+      </c>
+      <c r="F14" s="2">
+        <v>35450.0</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="1">
-        <v>245.0</v>
-      </c>
-      <c r="D14" s="1">
-        <v>552.93</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="1">
-        <v>579.5</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H14" s="2">
-        <v>6509.6</v>
-      </c>
       <c r="I14" s="3">
-        <v>0.0481</v>
+        <v>15.1436</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="1">
+        <v>101.0</v>
+      </c>
+      <c r="D15" s="1">
+        <v>224.73</v>
+      </c>
+      <c r="E15" s="2">
+        <v>22697.7</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1355.8</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="D15" s="2">
-        <v>2195.91</v>
-      </c>
-      <c r="E15" s="2">
-        <v>8783.65</v>
-      </c>
-      <c r="F15" s="2">
-        <v>35450.0</v>
-      </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="I15" s="3">
-        <v>15.1436</v>
+        <v>5.033</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -1460,75 +1526,75 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>4330.32</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="1">
-        <v>101.0</v>
-      </c>
-      <c r="D16" s="1">
-        <v>224.73</v>
-      </c>
-      <c r="E16" s="2">
-        <v>22697.7</v>
-      </c>
       <c r="F16" s="2">
-        <v>1355.8</v>
+        <v>3732.0</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>65</v>
+      <c r="H16" s="2">
+        <v>-21539.7</v>
       </c>
       <c r="I16" s="3">
-        <v>5.033</v>
+        <v>-0.1382</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L16" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="1">
+        <v>183.0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>283.78</v>
+      </c>
+      <c r="E17" s="2">
+        <v>51931.5</v>
+      </c>
+      <c r="F17" s="1">
+        <v>729.0</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="1">
-        <v>36.0</v>
-      </c>
-      <c r="D17" s="2">
-        <v>4330.32</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F17" s="2">
-        <v>3732.0</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="H17" s="2">
-        <v>-21539.7</v>
+        <v>81475.5</v>
       </c>
       <c r="I17" s="3">
-        <v>-0.1382</v>
+        <v>1.5689</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
@@ -1536,113 +1602,113 @@
         <v>11</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1465.0</v>
+      </c>
+      <c r="D18" s="1">
+        <v>74.72</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" s="1">
+        <v>72.32</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="1">
-        <v>183.0</v>
-      </c>
-      <c r="D18" s="1">
-        <v>283.78</v>
-      </c>
-      <c r="E18" s="2">
-        <v>51931.5</v>
-      </c>
-      <c r="F18" s="1">
-        <v>729.0</v>
-      </c>
-      <c r="G18" s="1" t="s">
+      <c r="H18" s="2">
+        <v>-3513.75</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-0.0321</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H18" s="2">
-        <v>81475.5</v>
-      </c>
-      <c r="I18" s="3">
-        <v>1.5689</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K18" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="4">
-        <v>1465.0</v>
+      <c r="C19" s="1">
+        <v>164.0</v>
       </c>
       <c r="D19" s="1">
-        <v>74.72</v>
-      </c>
-      <c r="E19" s="1" t="s">
+        <v>606.55</v>
+      </c>
+      <c r="E19" s="2">
+        <v>99474.25</v>
+      </c>
+      <c r="F19" s="1">
+        <v>636.7</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F19" s="1">
-        <v>72.32</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="H19" s="2">
-        <v>-3513.75</v>
+        <v>4944.55</v>
       </c>
       <c r="I19" s="3">
-        <v>-0.0321</v>
+        <v>0.0497</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C20" s="1">
-        <v>164.0</v>
-      </c>
-      <c r="D20" s="1">
-        <v>606.55</v>
+        <v>6.0</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1031.85</v>
       </c>
       <c r="E20" s="2">
-        <v>99474.25</v>
-      </c>
-      <c r="F20" s="1">
-        <v>636.7</v>
+        <v>6191.1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>16836.05</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H20" s="2">
-        <v>4944.55</v>
+        <v>94825.2</v>
       </c>
       <c r="I20" s="3">
-        <v>0.0497</v>
+        <v>15.3164</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
@@ -1650,75 +1716,75 @@
         <v>11</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C21" s="1">
-        <v>6.0</v>
+        <v>68.0</v>
       </c>
       <c r="D21" s="2">
-        <v>1031.85</v>
+        <v>1182.81</v>
       </c>
       <c r="E21" s="2">
-        <v>6191.1</v>
+        <v>80431.2</v>
       </c>
       <c r="F21" s="2">
-        <v>16836.05</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>78</v>
+        <v>1453.0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>98804.0</v>
       </c>
       <c r="H21" s="2">
-        <v>94825.2</v>
+        <v>18372.8</v>
       </c>
       <c r="I21" s="3">
-        <v>15.3164</v>
+        <v>0.2284</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L21" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C22" s="1">
-        <v>68.0</v>
-      </c>
-      <c r="D22" s="2">
-        <v>1182.81</v>
+        <v>540.0</v>
+      </c>
+      <c r="D22" s="1">
+        <v>13.39</v>
       </c>
       <c r="E22" s="2">
-        <v>80431.2</v>
-      </c>
-      <c r="F22" s="2">
-        <v>1453.0</v>
-      </c>
-      <c r="G22" s="2">
-        <v>98804.0</v>
+        <v>7229.6</v>
+      </c>
+      <c r="F22" s="1">
+        <v>176.0</v>
+      </c>
+      <c r="G22" s="4">
+        <v>95040.0</v>
       </c>
       <c r="H22" s="2">
-        <v>18372.8</v>
+        <v>87810.4</v>
       </c>
       <c r="I22" s="3">
-        <v>0.2284</v>
+        <v>12.146</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -1726,341 +1792,341 @@
         <v>11</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C23" s="1">
-        <v>540.0</v>
+        <v>350.0</v>
       </c>
       <c r="D23" s="1">
-        <v>13.39</v>
+        <v>165.99</v>
       </c>
       <c r="E23" s="2">
-        <v>7229.6</v>
+        <v>58095.38</v>
       </c>
       <c r="F23" s="1">
-        <v>176.0</v>
-      </c>
-      <c r="G23" s="4">
-        <v>95040.0</v>
+        <v>266.7</v>
+      </c>
+      <c r="G23" s="2">
+        <v>93345.0</v>
       </c>
       <c r="H23" s="2">
-        <v>87810.4</v>
+        <v>35249.62</v>
       </c>
       <c r="I23" s="3">
-        <v>12.146</v>
+        <v>0.6068</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C24" s="1">
-        <v>350.0</v>
+        <v>190.0</v>
       </c>
       <c r="D24" s="1">
-        <v>165.99</v>
+        <v>480.82</v>
       </c>
       <c r="E24" s="2">
-        <v>58095.38</v>
+        <v>91356.6</v>
       </c>
       <c r="F24" s="1">
-        <v>266.7</v>
+        <v>477.1</v>
       </c>
       <c r="G24" s="2">
-        <v>93345.0</v>
-      </c>
-      <c r="H24" s="2">
-        <v>35249.62</v>
+        <v>90649.0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>-707.6</v>
       </c>
       <c r="I24" s="3">
-        <v>0.6068</v>
+        <v>-0.0077</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C25" s="1">
-        <v>190.0</v>
+        <v>246.0</v>
       </c>
       <c r="D25" s="1">
-        <v>480.82</v>
+        <v>384.17</v>
       </c>
       <c r="E25" s="2">
-        <v>91356.6</v>
+        <v>94506.1</v>
       </c>
       <c r="F25" s="1">
-        <v>477.1</v>
+        <v>363.15</v>
       </c>
       <c r="G25" s="2">
-        <v>90649.0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>-707.6</v>
+        <v>89334.9</v>
+      </c>
+      <c r="H25" s="2">
+        <v>-5171.2</v>
       </c>
       <c r="I25" s="3">
-        <v>-0.0077</v>
+        <v>-0.0547</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C26" s="1">
-        <v>246.0</v>
+        <v>97.0</v>
       </c>
       <c r="D26" s="1">
-        <v>384.17</v>
+        <v>768.77</v>
       </c>
       <c r="E26" s="2">
-        <v>94506.1</v>
+        <v>74571.2</v>
       </c>
       <c r="F26" s="1">
-        <v>363.15</v>
+        <v>903.1</v>
       </c>
       <c r="G26" s="2">
-        <v>89334.9</v>
+        <v>87600.7</v>
       </c>
       <c r="H26" s="2">
-        <v>-5171.2</v>
+        <v>13029.5</v>
       </c>
       <c r="I26" s="3">
-        <v>-0.0547</v>
+        <v>0.1747</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C27" s="1">
         <v>97.0</v>
       </c>
-      <c r="D27" s="1">
-        <v>768.77</v>
-      </c>
-      <c r="E27" s="2">
-        <v>74571.2</v>
+      <c r="D27" s="2">
+        <v>1054.87</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="F27" s="1">
-        <v>903.1</v>
+        <v>902.3</v>
       </c>
       <c r="G27" s="2">
-        <v>87600.7</v>
+        <v>87523.1</v>
       </c>
       <c r="H27" s="2">
-        <v>13029.5</v>
+        <v>-14799.45</v>
       </c>
       <c r="I27" s="3">
-        <v>0.1747</v>
+        <v>-0.1446</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C28" s="1">
-        <v>97.0</v>
-      </c>
-      <c r="D28" s="2">
-        <v>1054.87</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>86</v>
+        <v>269.0</v>
+      </c>
+      <c r="D28" s="1">
+        <v>171.27</v>
+      </c>
+      <c r="E28" s="2">
+        <v>46072.27</v>
       </c>
       <c r="F28" s="1">
-        <v>902.3</v>
+        <v>313.7</v>
       </c>
       <c r="G28" s="2">
-        <v>87523.1</v>
+        <v>84385.3</v>
       </c>
       <c r="H28" s="2">
-        <v>-14799.45</v>
+        <v>38313.03</v>
       </c>
       <c r="I28" s="3">
-        <v>-0.1446</v>
+        <v>0.8316</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C29" s="1">
-        <v>269.0</v>
-      </c>
-      <c r="D29" s="1">
-        <v>171.27</v>
+        <v>59.0</v>
+      </c>
+      <c r="D29" s="2">
+        <v>1056.13</v>
       </c>
       <c r="E29" s="2">
-        <v>46072.27</v>
-      </c>
-      <c r="F29" s="1">
-        <v>313.7</v>
+        <v>62311.85</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1418.0</v>
       </c>
       <c r="G29" s="2">
-        <v>84385.3</v>
+        <v>83662.0</v>
       </c>
       <c r="H29" s="2">
-        <v>38313.03</v>
+        <v>21350.15</v>
       </c>
       <c r="I29" s="3">
-        <v>0.8316</v>
+        <v>0.3426</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C30" s="1">
-        <v>59.0</v>
+        <v>69.0</v>
       </c>
       <c r="D30" s="2">
-        <v>1056.13</v>
+        <v>1213.45</v>
       </c>
       <c r="E30" s="2">
-        <v>62311.85</v>
+        <v>83728.4</v>
       </c>
       <c r="F30" s="2">
-        <v>1418.0</v>
+        <v>1165.95</v>
       </c>
       <c r="G30" s="2">
-        <v>83662.0</v>
+        <v>80450.55</v>
       </c>
       <c r="H30" s="2">
-        <v>21350.15</v>
+        <v>-3277.85</v>
       </c>
       <c r="I30" s="3">
-        <v>0.3426</v>
+        <v>-0.0391</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C31" s="1">
-        <v>69.0</v>
-      </c>
-      <c r="D31" s="2">
-        <v>1213.45</v>
+        <v>300.0</v>
+      </c>
+      <c r="D31" s="1">
+        <v>220.39</v>
       </c>
       <c r="E31" s="2">
-        <v>83728.4</v>
-      </c>
-      <c r="F31" s="2">
-        <v>1165.95</v>
-      </c>
-      <c r="G31" s="2">
-        <v>80450.55</v>
+        <v>66117.0</v>
+      </c>
+      <c r="F31" s="1">
+        <v>265.09</v>
+      </c>
+      <c r="G31" s="4">
+        <v>79527.0</v>
       </c>
       <c r="H31" s="2">
-        <v>-3277.85</v>
+        <v>13410.0</v>
       </c>
       <c r="I31" s="3">
-        <v>-0.0391</v>
+        <v>0.2028</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32">
@@ -2068,417 +2134,417 @@
         <v>11</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C32" s="1">
-        <v>300.0</v>
+        <v>100.0</v>
       </c>
       <c r="D32" s="1">
-        <v>220.39</v>
+        <v>290.95</v>
       </c>
       <c r="E32" s="2">
-        <v>66117.0</v>
+        <v>29095.0</v>
       </c>
       <c r="F32" s="1">
-        <v>265.09</v>
-      </c>
-      <c r="G32" s="4">
-        <v>79527.0</v>
+        <v>789.0</v>
+      </c>
+      <c r="G32" s="2">
+        <v>78900.0</v>
       </c>
       <c r="H32" s="2">
-        <v>13410.0</v>
+        <v>49805.0</v>
       </c>
       <c r="I32" s="3">
-        <v>0.2028</v>
+        <v>1.7118</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C33" s="1">
-        <v>100.0</v>
-      </c>
-      <c r="D33" s="1">
-        <v>290.95</v>
+        <v>33.0</v>
+      </c>
+      <c r="D33" s="2">
+        <v>1504.07</v>
       </c>
       <c r="E33" s="2">
-        <v>29095.0</v>
-      </c>
-      <c r="F33" s="1">
-        <v>789.0</v>
+        <v>49634.3</v>
+      </c>
+      <c r="F33" s="2">
+        <v>2344.0</v>
       </c>
       <c r="G33" s="2">
-        <v>78900.0</v>
+        <v>77352.0</v>
       </c>
       <c r="H33" s="2">
-        <v>49805.0</v>
+        <v>27717.7</v>
       </c>
       <c r="I33" s="3">
-        <v>1.7118</v>
+        <v>0.5584</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C34" s="1">
-        <v>33.0</v>
-      </c>
-      <c r="D34" s="2">
-        <v>1504.07</v>
+        <v>184.0</v>
+      </c>
+      <c r="D34" s="1">
+        <v>431.44</v>
       </c>
       <c r="E34" s="2">
-        <v>49634.3</v>
-      </c>
-      <c r="F34" s="2">
-        <v>2344.0</v>
+        <v>79384.9</v>
+      </c>
+      <c r="F34" s="1">
+        <v>414.85</v>
       </c>
       <c r="G34" s="2">
-        <v>77352.0</v>
+        <v>76332.4</v>
       </c>
       <c r="H34" s="2">
-        <v>27717.7</v>
+        <v>-3052.5</v>
       </c>
       <c r="I34" s="3">
-        <v>0.5584</v>
+        <v>-0.0385</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C35" s="1">
-        <v>184.0</v>
-      </c>
-      <c r="D35" s="1">
-        <v>431.44</v>
+        <v>21.0</v>
+      </c>
+      <c r="D35" s="2">
+        <v>3292.31</v>
       </c>
       <c r="E35" s="2">
-        <v>79384.9</v>
-      </c>
-      <c r="F35" s="1">
-        <v>414.85</v>
+        <v>69138.6</v>
+      </c>
+      <c r="F35" s="2">
+        <v>3620.7</v>
       </c>
       <c r="G35" s="2">
-        <v>76332.4</v>
+        <v>76034.7</v>
       </c>
       <c r="H35" s="2">
-        <v>-3052.5</v>
+        <v>6896.1</v>
       </c>
       <c r="I35" s="3">
-        <v>-0.0385</v>
+        <v>0.0997</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C36" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="D36" s="2">
-        <v>3292.31</v>
+        <v>87.0</v>
+      </c>
+      <c r="D36" s="1">
+        <v>903.4</v>
       </c>
       <c r="E36" s="2">
-        <v>69138.6</v>
-      </c>
-      <c r="F36" s="2">
-        <v>3620.7</v>
+        <v>78595.7</v>
+      </c>
+      <c r="F36" s="1">
+        <v>858.0</v>
       </c>
       <c r="G36" s="2">
-        <v>76034.7</v>
+        <v>74646.0</v>
       </c>
       <c r="H36" s="2">
-        <v>6896.1</v>
+        <v>-3949.7</v>
       </c>
       <c r="I36" s="3">
-        <v>0.0997</v>
+        <v>-0.0503</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C37" s="1">
-        <v>87.0</v>
+        <v>205.0</v>
       </c>
       <c r="D37" s="1">
-        <v>903.4</v>
+        <v>283.62</v>
       </c>
       <c r="E37" s="2">
-        <v>78595.7</v>
+        <v>58141.81</v>
       </c>
       <c r="F37" s="1">
-        <v>858.0</v>
+        <v>362.05</v>
       </c>
       <c r="G37" s="2">
-        <v>74646.0</v>
+        <v>74220.25</v>
       </c>
       <c r="H37" s="2">
-        <v>-3949.7</v>
+        <v>16078.44</v>
       </c>
       <c r="I37" s="3">
-        <v>-0.0503</v>
+        <v>0.2765</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C38" s="1">
-        <v>205.0</v>
-      </c>
-      <c r="D38" s="1">
-        <v>283.62</v>
+        <v>26.0</v>
+      </c>
+      <c r="D38" s="2">
+        <v>2476.12</v>
       </c>
       <c r="E38" s="2">
-        <v>58141.81</v>
-      </c>
-      <c r="F38" s="1">
-        <v>362.05</v>
+        <v>64379.15</v>
+      </c>
+      <c r="F38" s="2">
+        <v>2850.7</v>
       </c>
       <c r="G38" s="2">
-        <v>74220.25</v>
+        <v>74118.2</v>
       </c>
       <c r="H38" s="2">
-        <v>16078.44</v>
+        <v>9739.05</v>
       </c>
       <c r="I38" s="3">
-        <v>0.2765</v>
+        <v>0.1513</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C39" s="1">
-        <v>26.0</v>
-      </c>
-      <c r="D39" s="2">
-        <v>2476.12</v>
+        <v>215.0</v>
+      </c>
+      <c r="D39" s="1">
+        <v>255.12</v>
       </c>
       <c r="E39" s="2">
-        <v>64379.15</v>
-      </c>
-      <c r="F39" s="2">
-        <v>2850.7</v>
+        <v>54850.65</v>
+      </c>
+      <c r="F39" s="1">
+        <v>342.9</v>
       </c>
       <c r="G39" s="2">
-        <v>74118.2</v>
+        <v>73723.5</v>
       </c>
       <c r="H39" s="2">
-        <v>9739.05</v>
+        <v>18872.85</v>
       </c>
       <c r="I39" s="3">
-        <v>0.1513</v>
+        <v>0.3441</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C40" s="1">
-        <v>215.0</v>
+        <v>171.0</v>
       </c>
       <c r="D40" s="1">
-        <v>255.12</v>
+        <v>402.08</v>
       </c>
       <c r="E40" s="2">
-        <v>54850.65</v>
+        <v>68755.95</v>
       </c>
       <c r="F40" s="1">
-        <v>342.9</v>
+        <v>427.15</v>
       </c>
       <c r="G40" s="2">
-        <v>73723.5</v>
+        <v>73042.65</v>
       </c>
       <c r="H40" s="2">
-        <v>18872.85</v>
+        <v>4286.7</v>
       </c>
       <c r="I40" s="3">
-        <v>0.3441</v>
+        <v>0.0623</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C41" s="1">
-        <v>171.0</v>
+        <v>139.0</v>
       </c>
       <c r="D41" s="1">
-        <v>402.08</v>
+        <v>545.81</v>
       </c>
       <c r="E41" s="2">
-        <v>68755.95</v>
+        <v>75867.25</v>
       </c>
       <c r="F41" s="1">
-        <v>427.15</v>
+        <v>511.9</v>
       </c>
       <c r="G41" s="2">
-        <v>73042.65</v>
+        <v>71154.1</v>
       </c>
       <c r="H41" s="2">
-        <v>4286.7</v>
+        <v>-4713.15</v>
       </c>
       <c r="I41" s="3">
-        <v>0.0623</v>
+        <v>-0.0621</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C42" s="1">
-        <v>139.0</v>
+        <v>401.0</v>
       </c>
       <c r="D42" s="1">
-        <v>545.81</v>
+        <v>91.09</v>
       </c>
       <c r="E42" s="2">
-        <v>75867.25</v>
+        <v>36527.75</v>
       </c>
       <c r="F42" s="1">
-        <v>511.9</v>
-      </c>
-      <c r="G42" s="2">
-        <v>71154.1</v>
+        <v>175.85</v>
+      </c>
+      <c r="G42" s="4">
+        <v>70516.0</v>
       </c>
       <c r="H42" s="2">
-        <v>-4713.15</v>
+        <v>33988.1</v>
       </c>
       <c r="I42" s="3">
-        <v>-0.0621</v>
+        <v>0.9305</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43">
@@ -2486,835 +2552,835 @@
         <v>11</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C43" s="1">
-        <v>401.0</v>
-      </c>
-      <c r="D43" s="1">
-        <v>91.09</v>
+        <v>51.0</v>
+      </c>
+      <c r="D43" s="2">
+        <v>1099.22</v>
       </c>
       <c r="E43" s="2">
-        <v>36527.75</v>
-      </c>
-      <c r="F43" s="1">
-        <v>175.85</v>
-      </c>
-      <c r="G43" s="4">
-        <v>70516.0</v>
+        <v>56060.4</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1368.0</v>
+      </c>
+      <c r="G43" s="2">
+        <v>69768.0</v>
       </c>
       <c r="H43" s="2">
-        <v>33988.1</v>
+        <v>13707.6</v>
       </c>
       <c r="I43" s="3">
-        <v>0.9305</v>
+        <v>0.2445</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L43" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C44" s="1">
-        <v>51.0</v>
+        <v>37.0</v>
       </c>
       <c r="D44" s="2">
-        <v>1099.22</v>
+        <v>2033.06</v>
       </c>
       <c r="E44" s="2">
-        <v>56060.4</v>
+        <v>75223.3</v>
       </c>
       <c r="F44" s="2">
-        <v>1368.0</v>
+        <v>1836.3</v>
       </c>
       <c r="G44" s="2">
-        <v>69768.0</v>
+        <v>67943.1</v>
       </c>
       <c r="H44" s="2">
-        <v>13707.6</v>
+        <v>-7280.2</v>
       </c>
       <c r="I44" s="3">
-        <v>0.2445</v>
+        <v>-0.0968</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C45" s="1">
-        <v>37.0</v>
-      </c>
-      <c r="D45" s="2">
-        <v>2033.06</v>
+        <v>546.0</v>
+      </c>
+      <c r="D45" s="1">
+        <v>135.91</v>
       </c>
       <c r="E45" s="2">
-        <v>75223.3</v>
-      </c>
-      <c r="F45" s="2">
-        <v>1836.3</v>
+        <v>74208.27</v>
+      </c>
+      <c r="F45" s="1">
+        <v>122.63</v>
       </c>
       <c r="G45" s="2">
-        <v>67943.1</v>
+        <v>66955.98</v>
       </c>
       <c r="H45" s="2">
-        <v>-7280.2</v>
+        <v>-7252.29</v>
       </c>
       <c r="I45" s="3">
-        <v>-0.0968</v>
+        <v>-0.0977</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C46" s="1">
-        <v>546.0</v>
+        <v>115.0</v>
       </c>
       <c r="D46" s="1">
-        <v>135.91</v>
+        <v>511.33</v>
       </c>
       <c r="E46" s="2">
-        <v>74208.27</v>
+        <v>58802.9</v>
       </c>
       <c r="F46" s="1">
-        <v>122.63</v>
+        <v>537.85</v>
       </c>
       <c r="G46" s="2">
-        <v>66955.98</v>
+        <v>61852.75</v>
       </c>
       <c r="H46" s="2">
-        <v>-7252.29</v>
+        <v>3049.85</v>
       </c>
       <c r="I46" s="3">
-        <v>-0.0977</v>
+        <v>0.0519</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C47" s="1">
-        <v>115.0</v>
+        <v>94.0</v>
       </c>
       <c r="D47" s="1">
-        <v>511.33</v>
+        <v>846.21</v>
       </c>
       <c r="E47" s="2">
-        <v>58802.9</v>
+        <v>79544.0</v>
       </c>
       <c r="F47" s="1">
-        <v>537.85</v>
+        <v>628.7</v>
       </c>
       <c r="G47" s="2">
-        <v>61852.75</v>
+        <v>59097.8</v>
       </c>
       <c r="H47" s="2">
-        <v>3049.85</v>
+        <v>-20446.2</v>
       </c>
       <c r="I47" s="3">
-        <v>0.0519</v>
+        <v>-0.257</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C48" s="1">
-        <v>94.0</v>
+        <v>405.0</v>
       </c>
       <c r="D48" s="1">
-        <v>846.21</v>
+        <v>147.23</v>
       </c>
       <c r="E48" s="2">
-        <v>79544.0</v>
+        <v>59627.52</v>
       </c>
       <c r="F48" s="1">
-        <v>628.7</v>
+        <v>141.95</v>
       </c>
       <c r="G48" s="2">
-        <v>59097.8</v>
+        <v>57489.75</v>
       </c>
       <c r="H48" s="2">
-        <v>-20446.2</v>
+        <v>-2137.77</v>
       </c>
       <c r="I48" s="3">
-        <v>-0.257</v>
+        <v>-0.0359</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C49" s="1">
-        <v>405.0</v>
+        <v>102.0</v>
       </c>
       <c r="D49" s="1">
-        <v>147.23</v>
+        <v>540.91</v>
       </c>
       <c r="E49" s="2">
-        <v>59627.52</v>
+        <v>55172.45</v>
       </c>
       <c r="F49" s="1">
-        <v>141.95</v>
+        <v>555.6</v>
       </c>
       <c r="G49" s="2">
-        <v>57489.75</v>
+        <v>56671.2</v>
       </c>
       <c r="H49" s="2">
-        <v>-2137.77</v>
+        <v>1498.75</v>
       </c>
       <c r="I49" s="3">
-        <v>-0.0359</v>
+        <v>0.0272</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C50" s="1">
-        <v>102.0</v>
+        <v>145.0</v>
       </c>
       <c r="D50" s="1">
-        <v>540.91</v>
+        <v>362.06</v>
       </c>
       <c r="E50" s="2">
-        <v>55172.45</v>
+        <v>52499.2</v>
       </c>
       <c r="F50" s="1">
-        <v>555.6</v>
+        <v>365.5</v>
       </c>
       <c r="G50" s="2">
-        <v>56671.2</v>
-      </c>
-      <c r="H50" s="2">
-        <v>1498.75</v>
+        <v>52997.5</v>
+      </c>
+      <c r="H50" s="1">
+        <v>498.3</v>
       </c>
       <c r="I50" s="3">
-        <v>0.0272</v>
+        <v>0.0095</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C51" s="1">
-        <v>145.0</v>
+        <v>43.0</v>
       </c>
       <c r="D51" s="1">
-        <v>362.06</v>
+        <v>722.52</v>
       </c>
       <c r="E51" s="2">
-        <v>52499.2</v>
-      </c>
-      <c r="F51" s="1">
-        <v>365.5</v>
+        <v>31068.3</v>
+      </c>
+      <c r="F51" s="2">
+        <v>1222.0</v>
       </c>
       <c r="G51" s="2">
-        <v>52997.5</v>
-      </c>
-      <c r="H51" s="1">
-        <v>498.3</v>
+        <v>52546.0</v>
+      </c>
+      <c r="H51" s="2">
+        <v>21477.7</v>
       </c>
       <c r="I51" s="3">
-        <v>0.0095</v>
+        <v>0.6913</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C52" s="1">
-        <v>43.0</v>
+        <v>58.0</v>
       </c>
       <c r="D52" s="1">
-        <v>722.52</v>
+        <v>953.02</v>
       </c>
       <c r="E52" s="2">
-        <v>31068.3</v>
-      </c>
-      <c r="F52" s="2">
-        <v>1222.0</v>
+        <v>55275.15</v>
+      </c>
+      <c r="F52" s="1">
+        <v>894.15</v>
       </c>
       <c r="G52" s="2">
-        <v>52546.0</v>
+        <v>51860.7</v>
       </c>
       <c r="H52" s="2">
-        <v>21477.7</v>
+        <v>-3414.45</v>
       </c>
       <c r="I52" s="3">
-        <v>0.6913</v>
+        <v>-0.0618</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C53" s="1">
-        <v>58.0</v>
+        <v>516.0</v>
       </c>
       <c r="D53" s="1">
-        <v>953.02</v>
+        <v>97.49</v>
       </c>
       <c r="E53" s="2">
-        <v>55275.15</v>
+        <v>50306.12</v>
       </c>
       <c r="F53" s="1">
-        <v>894.15</v>
+        <v>100.36</v>
       </c>
       <c r="G53" s="2">
-        <v>51860.7</v>
+        <v>51785.76</v>
       </c>
       <c r="H53" s="2">
-        <v>-3414.45</v>
+        <v>1479.64</v>
       </c>
       <c r="I53" s="3">
-        <v>-0.0618</v>
+        <v>0.0294</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C54" s="1">
-        <v>516.0</v>
+        <v>172.0</v>
       </c>
       <c r="D54" s="1">
-        <v>97.49</v>
+        <v>302.02</v>
       </c>
       <c r="E54" s="2">
-        <v>50306.12</v>
+        <v>51947.55</v>
       </c>
       <c r="F54" s="1">
-        <v>100.36</v>
+        <v>292.95</v>
       </c>
       <c r="G54" s="2">
-        <v>51785.76</v>
+        <v>50387.4</v>
       </c>
       <c r="H54" s="2">
-        <v>1479.64</v>
+        <v>-1560.15</v>
       </c>
       <c r="I54" s="3">
-        <v>0.0294</v>
+        <v>-0.03</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C55" s="1">
-        <v>172.0</v>
+        <v>63.0</v>
       </c>
       <c r="D55" s="1">
-        <v>302.02</v>
+        <v>724.23</v>
       </c>
       <c r="E55" s="2">
-        <v>51947.55</v>
+        <v>45626.35</v>
       </c>
       <c r="F55" s="1">
-        <v>292.95</v>
+        <v>777.9</v>
       </c>
       <c r="G55" s="2">
-        <v>50387.4</v>
+        <v>49007.7</v>
       </c>
       <c r="H55" s="2">
-        <v>-1560.15</v>
+        <v>3381.35</v>
       </c>
       <c r="I55" s="3">
-        <v>-0.03</v>
+        <v>0.0741</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C56" s="1">
-        <v>63.0</v>
+        <v>72.0</v>
       </c>
       <c r="D56" s="1">
-        <v>724.23</v>
+        <v>529.68</v>
       </c>
       <c r="E56" s="2">
-        <v>45626.35</v>
+        <v>38136.95</v>
       </c>
       <c r="F56" s="1">
-        <v>777.9</v>
+        <v>671.75</v>
       </c>
       <c r="G56" s="2">
-        <v>49007.7</v>
+        <v>48366.0</v>
       </c>
       <c r="H56" s="2">
-        <v>3381.35</v>
+        <v>10229.05</v>
       </c>
       <c r="I56" s="3">
-        <v>0.0741</v>
+        <v>0.2682</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C57" s="1">
-        <v>72.0</v>
+        <v>112</v>
+      </c>
+      <c r="C57" s="4">
+        <v>1891.0</v>
       </c>
       <c r="D57" s="1">
-        <v>529.68</v>
+        <v>26.43</v>
       </c>
       <c r="E57" s="2">
-        <v>38136.95</v>
+        <v>49985.02</v>
       </c>
       <c r="F57" s="1">
-        <v>671.75</v>
+        <v>24.77</v>
       </c>
       <c r="G57" s="2">
-        <v>48366.0</v>
+        <v>46840.07</v>
       </c>
       <c r="H57" s="2">
-        <v>10229.05</v>
+        <v>-3144.95</v>
       </c>
       <c r="I57" s="3">
-        <v>0.2682</v>
+        <v>-0.0629</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C58" s="4">
-        <v>1891.0</v>
-      </c>
-      <c r="D58" s="1">
-        <v>26.43</v>
+        <v>113</v>
+      </c>
+      <c r="C58" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="D58" s="2">
+        <v>1823.31</v>
       </c>
       <c r="E58" s="2">
-        <v>49985.02</v>
-      </c>
-      <c r="F58" s="1">
-        <v>24.77</v>
+        <v>54699.2</v>
+      </c>
+      <c r="F58" s="2">
+        <v>1545.0</v>
       </c>
       <c r="G58" s="2">
-        <v>46840.07</v>
+        <v>46350.0</v>
       </c>
       <c r="H58" s="2">
-        <v>-3144.95</v>
+        <v>-8349.2</v>
       </c>
       <c r="I58" s="3">
-        <v>-0.0629</v>
+        <v>-0.1526</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C59" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="D59" s="2">
-        <v>1823.31</v>
+        <v>102.0</v>
+      </c>
+      <c r="D59" s="1">
+        <v>550.05</v>
       </c>
       <c r="E59" s="2">
-        <v>54699.2</v>
-      </c>
-      <c r="F59" s="2">
-        <v>1545.0</v>
+        <v>56105.6</v>
+      </c>
+      <c r="F59" s="1">
+        <v>438.9</v>
       </c>
       <c r="G59" s="2">
-        <v>46350.0</v>
+        <v>44767.8</v>
       </c>
       <c r="H59" s="2">
-        <v>-8349.2</v>
+        <v>-11337.8</v>
       </c>
       <c r="I59" s="3">
-        <v>-0.1526</v>
+        <v>-0.2021</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C60" s="1">
-        <v>102.0</v>
+        <v>134.0</v>
       </c>
       <c r="D60" s="1">
-        <v>550.05</v>
+        <v>448.98</v>
       </c>
       <c r="E60" s="2">
-        <v>56105.6</v>
+        <v>60163.55</v>
       </c>
       <c r="F60" s="1">
-        <v>438.9</v>
+        <v>332.2</v>
       </c>
       <c r="G60" s="2">
-        <v>44767.8</v>
+        <v>44514.8</v>
       </c>
       <c r="H60" s="2">
-        <v>-11337.8</v>
+        <v>-15648.75</v>
       </c>
       <c r="I60" s="3">
-        <v>-0.2021</v>
+        <v>-0.2601</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C61" s="1">
-        <v>134.0</v>
-      </c>
-      <c r="D61" s="1">
-        <v>448.98</v>
+        <v>43.0</v>
+      </c>
+      <c r="D61" s="2">
+        <v>1097.89</v>
       </c>
       <c r="E61" s="2">
-        <v>60163.55</v>
-      </c>
-      <c r="F61" s="1">
-        <v>332.2</v>
+        <v>47209.5</v>
+      </c>
+      <c r="F61" s="2">
+        <v>1013.6</v>
       </c>
       <c r="G61" s="2">
-        <v>44514.8</v>
+        <v>43584.8</v>
       </c>
       <c r="H61" s="2">
-        <v>-15648.75</v>
+        <v>-3624.7</v>
       </c>
       <c r="I61" s="3">
-        <v>-0.2601</v>
+        <v>-0.0768</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C62" s="1">
-        <v>43.0</v>
-      </c>
-      <c r="D62" s="2">
-        <v>1097.89</v>
+        <v>94.0</v>
+      </c>
+      <c r="D62" s="1">
+        <v>267.98</v>
       </c>
       <c r="E62" s="2">
-        <v>47209.5</v>
-      </c>
-      <c r="F62" s="2">
-        <v>1013.6</v>
+        <v>25190.12</v>
+      </c>
+      <c r="F62" s="1">
+        <v>460.3</v>
       </c>
       <c r="G62" s="2">
-        <v>43584.8</v>
+        <v>43268.2</v>
       </c>
       <c r="H62" s="2">
-        <v>-3624.7</v>
+        <v>18078.08</v>
       </c>
       <c r="I62" s="3">
-        <v>-0.0768</v>
+        <v>0.7177</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C63" s="1">
-        <v>94.0</v>
-      </c>
-      <c r="D63" s="1">
-        <v>267.98</v>
+        <v>38.0</v>
+      </c>
+      <c r="D63" s="2">
+        <v>1111.19</v>
       </c>
       <c r="E63" s="2">
-        <v>25190.12</v>
-      </c>
-      <c r="F63" s="1">
-        <v>460.3</v>
+        <v>42225.2</v>
+      </c>
+      <c r="F63" s="2">
+        <v>1116.9</v>
       </c>
       <c r="G63" s="2">
-        <v>43268.2</v>
-      </c>
-      <c r="H63" s="2">
-        <v>18078.08</v>
+        <v>42442.2</v>
+      </c>
+      <c r="H63" s="1">
+        <v>217.0</v>
       </c>
       <c r="I63" s="3">
-        <v>0.7177</v>
+        <v>0.0051</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C64" s="1">
-        <v>38.0</v>
+        <v>9.0</v>
       </c>
       <c r="D64" s="2">
-        <v>1111.19</v>
+        <v>3066.43</v>
       </c>
       <c r="E64" s="2">
-        <v>42225.2</v>
+        <v>27597.85</v>
       </c>
       <c r="F64" s="2">
-        <v>1116.9</v>
-      </c>
-      <c r="G64" s="2">
-        <v>42442.2</v>
-      </c>
-      <c r="H64" s="1">
-        <v>217.0</v>
+        <v>4705.5</v>
+      </c>
+      <c r="G64" s="4">
+        <v>42350.0</v>
+      </c>
+      <c r="H64" s="2">
+        <v>14751.65</v>
       </c>
       <c r="I64" s="3">
-        <v>0.0051</v>
+        <v>0.5345</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="65">
@@ -3322,1329 +3388,1329 @@
         <v>11</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C65" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="D65" s="2">
-        <v>3066.43</v>
+        <v>86.0</v>
+      </c>
+      <c r="D65" s="1">
+        <v>458.8</v>
       </c>
       <c r="E65" s="2">
-        <v>27597.85</v>
-      </c>
-      <c r="F65" s="2">
-        <v>4705.5</v>
-      </c>
-      <c r="G65" s="4">
-        <v>42350.0</v>
+        <v>39456.85</v>
+      </c>
+      <c r="F65" s="1">
+        <v>470.7</v>
+      </c>
+      <c r="G65" s="2">
+        <v>40480.2</v>
       </c>
       <c r="H65" s="2">
-        <v>14751.65</v>
+        <v>1023.35</v>
       </c>
       <c r="I65" s="3">
-        <v>0.5345</v>
+        <v>0.0259</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C66" s="1">
-        <v>86.0</v>
+        <v>218.0</v>
       </c>
       <c r="D66" s="1">
-        <v>458.8</v>
+        <v>182.99</v>
       </c>
       <c r="E66" s="2">
-        <v>39456.85</v>
+        <v>39890.84</v>
       </c>
       <c r="F66" s="1">
-        <v>470.7</v>
+        <v>181.03</v>
       </c>
       <c r="G66" s="2">
-        <v>40480.2</v>
-      </c>
-      <c r="H66" s="2">
-        <v>1023.35</v>
+        <v>39464.54</v>
+      </c>
+      <c r="H66" s="1">
+        <v>-426.3</v>
       </c>
       <c r="I66" s="3">
-        <v>0.0259</v>
+        <v>-0.0107</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C67" s="1">
-        <v>218.0</v>
+        <v>70.0</v>
       </c>
       <c r="D67" s="1">
-        <v>182.99</v>
+        <v>331.82</v>
       </c>
       <c r="E67" s="2">
-        <v>39890.84</v>
+        <v>23227.6</v>
       </c>
       <c r="F67" s="1">
-        <v>181.03</v>
+        <v>555.15</v>
       </c>
       <c r="G67" s="2">
-        <v>39464.54</v>
-      </c>
-      <c r="H67" s="1">
-        <v>-426.3</v>
+        <v>38860.5</v>
+      </c>
+      <c r="H67" s="2">
+        <v>15632.9</v>
       </c>
       <c r="I67" s="3">
-        <v>-0.0107</v>
+        <v>0.673</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C68" s="1">
-        <v>70.0</v>
+        <v>132.0</v>
       </c>
       <c r="D68" s="1">
-        <v>331.82</v>
+        <v>264.23</v>
       </c>
       <c r="E68" s="2">
-        <v>23227.6</v>
+        <v>34878.4</v>
       </c>
       <c r="F68" s="1">
-        <v>555.15</v>
+        <v>282.35</v>
       </c>
       <c r="G68" s="2">
-        <v>38860.5</v>
+        <v>37270.2</v>
       </c>
       <c r="H68" s="2">
-        <v>15632.9</v>
+        <v>2391.8</v>
       </c>
       <c r="I68" s="3">
-        <v>0.673</v>
+        <v>0.0686</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C69" s="1">
-        <v>132.0</v>
-      </c>
-      <c r="D69" s="1">
-        <v>264.23</v>
+        <v>10.0</v>
+      </c>
+      <c r="D69" s="2">
+        <v>3807.82</v>
       </c>
       <c r="E69" s="2">
-        <v>34878.4</v>
-      </c>
-      <c r="F69" s="1">
-        <v>282.35</v>
+        <v>38078.2</v>
+      </c>
+      <c r="F69" s="2">
+        <v>3694.0</v>
       </c>
       <c r="G69" s="2">
-        <v>37270.2</v>
+        <v>66000.0</v>
       </c>
       <c r="H69" s="2">
-        <v>2391.8</v>
+        <v>-1138.2</v>
       </c>
       <c r="I69" s="3">
-        <v>0.0686</v>
+        <v>-0.0299</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C70" s="1">
-        <v>10.0</v>
+        <v>40.0</v>
       </c>
       <c r="D70" s="2">
-        <v>3807.82</v>
+        <v>1008.5</v>
       </c>
       <c r="E70" s="2">
-        <v>38078.2</v>
-      </c>
-      <c r="F70" s="2">
-        <v>3694.0</v>
+        <v>40340.0</v>
+      </c>
+      <c r="F70" s="1">
+        <v>922.0</v>
       </c>
       <c r="G70" s="2">
-        <v>66000.0</v>
+        <v>36880.0</v>
       </c>
       <c r="H70" s="2">
-        <v>-1138.2</v>
+        <v>-3460.0</v>
       </c>
       <c r="I70" s="3">
-        <v>-0.0299</v>
+        <v>-0.0858</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C71" s="1">
-        <v>40.0</v>
+        <v>1.0</v>
       </c>
       <c r="D71" s="2">
-        <v>1008.5</v>
+        <v>35975.0</v>
       </c>
       <c r="E71" s="2">
-        <v>40340.0</v>
-      </c>
-      <c r="F71" s="1">
-        <v>922.0</v>
+        <v>35975.0</v>
+      </c>
+      <c r="F71" s="2">
+        <v>35425.1</v>
       </c>
       <c r="G71" s="2">
-        <v>36880.0</v>
-      </c>
-      <c r="H71" s="2">
-        <v>-3460.0</v>
+        <v>35425.1</v>
+      </c>
+      <c r="H71" s="1">
+        <v>-549.9</v>
       </c>
       <c r="I71" s="3">
-        <v>-0.0858</v>
+        <v>-0.0153</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C72" s="1">
-        <v>1.0</v>
+        <v>19.0</v>
       </c>
       <c r="D72" s="2">
-        <v>35975.0</v>
+        <v>1886.49</v>
       </c>
       <c r="E72" s="2">
-        <v>35975.0</v>
+        <v>35843.4</v>
       </c>
       <c r="F72" s="2">
-        <v>35425.1</v>
+        <v>1855.4</v>
       </c>
       <c r="G72" s="2">
-        <v>35425.1</v>
+        <v>35252.6</v>
       </c>
       <c r="H72" s="1">
-        <v>-549.9</v>
+        <v>-590.8</v>
       </c>
       <c r="I72" s="3">
-        <v>-0.0153</v>
+        <v>-0.0165</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C73" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="D73" s="2">
-        <v>1886.49</v>
+        <v>222.0</v>
+      </c>
+      <c r="D73" s="1">
+        <v>137.08</v>
       </c>
       <c r="E73" s="2">
-        <v>35843.4</v>
-      </c>
-      <c r="F73" s="2">
-        <v>1855.4</v>
+        <v>30430.92</v>
+      </c>
+      <c r="F73" s="1">
+        <v>153.5</v>
       </c>
       <c r="G73" s="2">
-        <v>35252.6</v>
-      </c>
-      <c r="H73" s="1">
-        <v>-590.8</v>
+        <v>34077.0</v>
+      </c>
+      <c r="H73" s="2">
+        <v>3646.08</v>
       </c>
       <c r="I73" s="3">
-        <v>-0.0165</v>
+        <v>0.1198</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C74" s="1">
-        <v>222.0</v>
-      </c>
-      <c r="D74" s="1">
-        <v>137.08</v>
+        <v>43.0</v>
+      </c>
+      <c r="D74" s="2">
+        <v>1096.25</v>
       </c>
       <c r="E74" s="2">
-        <v>30430.92</v>
+        <v>47138.65</v>
       </c>
       <c r="F74" s="1">
-        <v>153.5</v>
-      </c>
-      <c r="G74" s="2">
-        <v>34077.0</v>
+        <v>772.8</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0.0</v>
       </c>
       <c r="H74" s="2">
-        <v>3646.08</v>
+        <v>-13908.25</v>
       </c>
       <c r="I74" s="3">
-        <v>0.1198</v>
+        <v>-0.295</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C75" s="1">
-        <v>43.0</v>
+        <v>39.0</v>
       </c>
       <c r="D75" s="2">
-        <v>1096.25</v>
+        <v>1165.79</v>
       </c>
       <c r="E75" s="2">
-        <v>47138.65</v>
+        <v>45465.85</v>
       </c>
       <c r="F75" s="1">
-        <v>772.8</v>
-      </c>
-      <c r="G75" s="1">
-        <v>0.0</v>
+        <v>847.2</v>
+      </c>
+      <c r="G75" s="2">
+        <v>33040.8</v>
       </c>
       <c r="H75" s="2">
-        <v>-13908.25</v>
+        <v>-12425.05</v>
       </c>
       <c r="I75" s="3">
-        <v>-0.295</v>
+        <v>-0.2733</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C76" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="D76" s="2">
-        <v>1165.79</v>
+        <v>42.0</v>
+      </c>
+      <c r="D76" s="1">
+        <v>820.32</v>
       </c>
       <c r="E76" s="2">
-        <v>45465.85</v>
+        <v>34453.5</v>
       </c>
       <c r="F76" s="1">
-        <v>847.2</v>
+        <v>785.95</v>
       </c>
       <c r="G76" s="2">
-        <v>33040.8</v>
+        <v>33009.9</v>
       </c>
       <c r="H76" s="2">
-        <v>-12425.05</v>
+        <v>-1443.6</v>
       </c>
       <c r="I76" s="3">
-        <v>-0.2733</v>
+        <v>-0.0419</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C77" s="1">
-        <v>42.0</v>
+        <v>132</v>
+      </c>
+      <c r="C77" s="4">
+        <v>1006.0</v>
       </c>
       <c r="D77" s="1">
-        <v>820.32</v>
+        <v>65.92</v>
       </c>
       <c r="E77" s="2">
-        <v>34453.5</v>
+        <v>66314.59</v>
       </c>
       <c r="F77" s="1">
-        <v>785.95</v>
+        <v>32.76</v>
       </c>
       <c r="G77" s="2">
-        <v>33009.9</v>
+        <v>32956.56</v>
       </c>
       <c r="H77" s="2">
-        <v>-1443.6</v>
+        <v>-33358.03</v>
       </c>
       <c r="I77" s="3">
-        <v>-0.0419</v>
+        <v>-0.503</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C78" s="4">
-        <v>1006.0</v>
+        <v>133</v>
+      </c>
+      <c r="C78" s="1">
+        <v>32.0</v>
       </c>
       <c r="D78" s="1">
-        <v>65.92</v>
+        <v>934.45</v>
       </c>
       <c r="E78" s="2">
-        <v>66314.59</v>
-      </c>
-      <c r="F78" s="1">
-        <v>32.76</v>
+        <v>29902.4</v>
+      </c>
+      <c r="F78" s="2">
+        <v>1026.1</v>
       </c>
       <c r="G78" s="2">
-        <v>32956.56</v>
+        <v>32835.2</v>
       </c>
       <c r="H78" s="2">
-        <v>-33358.03</v>
+        <v>2932.8</v>
       </c>
       <c r="I78" s="3">
-        <v>-0.503</v>
+        <v>0.0981</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C79" s="1">
-        <v>32.0</v>
+        <v>53.0</v>
       </c>
       <c r="D79" s="1">
-        <v>934.45</v>
+        <v>729.68</v>
       </c>
       <c r="E79" s="2">
-        <v>29902.4</v>
-      </c>
-      <c r="F79" s="2">
-        <v>1026.1</v>
+        <v>38672.9</v>
+      </c>
+      <c r="F79" s="1">
+        <v>611.95</v>
       </c>
       <c r="G79" s="2">
-        <v>32835.2</v>
+        <v>32433.35</v>
       </c>
       <c r="H79" s="2">
-        <v>2932.8</v>
+        <v>-6239.55</v>
       </c>
       <c r="I79" s="3">
-        <v>0.0981</v>
+        <v>-0.1613</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C80" s="1">
-        <v>53.0</v>
+        <v>28.0</v>
       </c>
       <c r="D80" s="1">
-        <v>729.68</v>
+        <v>702.63</v>
       </c>
       <c r="E80" s="2">
-        <v>38672.9</v>
-      </c>
-      <c r="F80" s="1">
-        <v>611.95</v>
+        <v>19673.6</v>
+      </c>
+      <c r="F80" s="2">
+        <v>1133.4</v>
       </c>
       <c r="G80" s="2">
-        <v>32433.35</v>
+        <v>31735.2</v>
       </c>
       <c r="H80" s="2">
-        <v>-6239.55</v>
+        <v>12061.6</v>
       </c>
       <c r="I80" s="3">
-        <v>-0.1613</v>
+        <v>0.6131</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C81" s="1">
-        <v>28.0</v>
+        <v>60.0</v>
       </c>
       <c r="D81" s="1">
-        <v>702.63</v>
+        <v>527.58</v>
       </c>
       <c r="E81" s="2">
-        <v>19673.6</v>
-      </c>
-      <c r="F81" s="2">
-        <v>1133.4</v>
+        <v>31655.0</v>
+      </c>
+      <c r="F81" s="1">
+        <v>525.35</v>
       </c>
       <c r="G81" s="2">
-        <v>31735.2</v>
-      </c>
-      <c r="H81" s="2">
-        <v>12061.6</v>
+        <v>31521.0</v>
+      </c>
+      <c r="H81" s="1">
+        <v>-134.0</v>
       </c>
       <c r="I81" s="3">
-        <v>0.6131</v>
+        <v>-0.0042</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C82" s="1">
-        <v>60.0</v>
+        <v>43.0</v>
       </c>
       <c r="D82" s="1">
-        <v>527.58</v>
+        <v>579.24</v>
       </c>
       <c r="E82" s="2">
-        <v>31655.0</v>
+        <v>24907.3</v>
       </c>
       <c r="F82" s="1">
-        <v>525.35</v>
+        <v>721.5</v>
       </c>
       <c r="G82" s="2">
-        <v>31521.0</v>
-      </c>
-      <c r="H82" s="1">
-        <v>-134.0</v>
+        <v>31024.5</v>
+      </c>
+      <c r="H82" s="2">
+        <v>6117.2</v>
       </c>
       <c r="I82" s="3">
-        <v>-0.0042</v>
+        <v>0.2456</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C83" s="1">
-        <v>43.0</v>
+        <v>249.0</v>
       </c>
       <c r="D83" s="1">
-        <v>579.24</v>
+        <v>134.11</v>
       </c>
       <c r="E83" s="2">
-        <v>24907.3</v>
+        <v>33392.27</v>
       </c>
       <c r="F83" s="1">
-        <v>721.5</v>
+        <v>123.0</v>
       </c>
       <c r="G83" s="2">
-        <v>31024.5</v>
+        <v>30627.0</v>
       </c>
       <c r="H83" s="2">
-        <v>6117.2</v>
+        <v>-2765.27</v>
       </c>
       <c r="I83" s="3">
-        <v>0.2456</v>
+        <v>-0.0828</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C84" s="1">
-        <v>249.0</v>
+        <v>307.0</v>
       </c>
       <c r="D84" s="1">
-        <v>134.11</v>
+        <v>97.19</v>
       </c>
       <c r="E84" s="2">
-        <v>33392.27</v>
+        <v>29837.24</v>
       </c>
       <c r="F84" s="1">
-        <v>123.0</v>
+        <v>98.15</v>
       </c>
       <c r="G84" s="2">
-        <v>30627.0</v>
-      </c>
-      <c r="H84" s="2">
-        <v>-2765.27</v>
+        <v>30132.05</v>
+      </c>
+      <c r="H84" s="1">
+        <v>294.81</v>
       </c>
       <c r="I84" s="3">
-        <v>-0.0828</v>
+        <v>0.0099</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C85" s="1">
-        <v>307.0</v>
-      </c>
-      <c r="D85" s="1">
-        <v>97.19</v>
+        <v>20.0</v>
+      </c>
+      <c r="D85" s="2">
+        <v>1040.96</v>
       </c>
       <c r="E85" s="2">
-        <v>29837.24</v>
-      </c>
-      <c r="F85" s="1">
-        <v>98.15</v>
+        <v>20819.2</v>
+      </c>
+      <c r="F85" s="2">
+        <v>1496.2</v>
       </c>
       <c r="G85" s="2">
-        <v>30132.05</v>
-      </c>
-      <c r="H85" s="1">
-        <v>294.81</v>
+        <v>29924.0</v>
+      </c>
+      <c r="H85" s="2">
+        <v>9104.8</v>
       </c>
       <c r="I85" s="3">
-        <v>0.0099</v>
+        <v>0.4373</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C86" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="D86" s="2">
-        <v>1040.96</v>
+        <v>127.0</v>
+      </c>
+      <c r="D86" s="1">
+        <v>209.26</v>
       </c>
       <c r="E86" s="2">
-        <v>20819.2</v>
-      </c>
-      <c r="F86" s="2">
-        <v>1496.2</v>
+        <v>26575.63</v>
+      </c>
+      <c r="F86" s="1">
+        <v>235.26</v>
       </c>
       <c r="G86" s="2">
-        <v>29924.0</v>
+        <v>29878.02</v>
       </c>
       <c r="H86" s="2">
-        <v>9104.8</v>
+        <v>3302.39</v>
       </c>
       <c r="I86" s="3">
-        <v>0.4373</v>
+        <v>0.1243</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C87" s="1">
-        <v>127.0</v>
+        <v>66.0</v>
       </c>
       <c r="D87" s="1">
-        <v>209.26</v>
+        <v>387.23</v>
       </c>
       <c r="E87" s="2">
-        <v>26575.63</v>
+        <v>25557.45</v>
       </c>
       <c r="F87" s="1">
-        <v>235.26</v>
+        <v>419.65</v>
       </c>
       <c r="G87" s="2">
-        <v>29878.02</v>
+        <v>27696.9</v>
       </c>
       <c r="H87" s="2">
-        <v>3302.39</v>
+        <v>2139.45</v>
       </c>
       <c r="I87" s="3">
-        <v>0.1243</v>
+        <v>0.0837</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C88" s="1">
-        <v>66.0</v>
-      </c>
-      <c r="D88" s="1">
-        <v>387.23</v>
+        <v>20.0</v>
+      </c>
+      <c r="D88" s="2">
+        <v>1099.4</v>
       </c>
       <c r="E88" s="2">
-        <v>25557.45</v>
-      </c>
-      <c r="F88" s="1">
-        <v>419.65</v>
+        <v>21988.0</v>
+      </c>
+      <c r="F88" s="2">
+        <v>1323.7</v>
       </c>
       <c r="G88" s="2">
-        <v>27696.9</v>
+        <v>26474.0</v>
       </c>
       <c r="H88" s="2">
-        <v>2139.45</v>
+        <v>4486.0</v>
       </c>
       <c r="I88" s="3">
-        <v>0.0837</v>
+        <v>0.204</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C89" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="D89" s="2">
-        <v>1099.4</v>
+        <v>226.0</v>
+      </c>
+      <c r="D89" s="1">
+        <v>136.74</v>
       </c>
       <c r="E89" s="2">
-        <v>21988.0</v>
-      </c>
-      <c r="F89" s="2">
-        <v>1323.7</v>
+        <v>30902.6</v>
+      </c>
+      <c r="F89" s="1">
+        <v>116.23</v>
       </c>
       <c r="G89" s="2">
-        <v>26474.0</v>
+        <v>26267.98</v>
       </c>
       <c r="H89" s="2">
-        <v>4486.0</v>
+        <v>-4634.62</v>
       </c>
       <c r="I89" s="3">
-        <v>0.204</v>
+        <v>-0.15</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C90" s="1">
-        <v>226.0</v>
+        <v>298.0</v>
       </c>
       <c r="D90" s="1">
-        <v>136.74</v>
+        <v>41.79</v>
       </c>
       <c r="E90" s="2">
-        <v>30902.6</v>
+        <v>12454.04</v>
       </c>
       <c r="F90" s="1">
-        <v>116.23</v>
+        <v>88.0</v>
       </c>
       <c r="G90" s="2">
-        <v>26267.98</v>
+        <v>26224.0</v>
       </c>
       <c r="H90" s="2">
-        <v>-4634.62</v>
+        <v>13769.96</v>
       </c>
       <c r="I90" s="3">
-        <v>-0.15</v>
+        <v>1.1057</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C91" s="1">
-        <v>298.0</v>
+        <v>49.0</v>
       </c>
       <c r="D91" s="1">
-        <v>41.79</v>
+        <v>333.15</v>
       </c>
       <c r="E91" s="2">
-        <v>12454.04</v>
+        <v>16324.5</v>
       </c>
       <c r="F91" s="1">
-        <v>88.0</v>
+        <v>516.4</v>
       </c>
       <c r="G91" s="2">
-        <v>26224.0</v>
+        <v>25303.6</v>
       </c>
       <c r="H91" s="2">
-        <v>13769.96</v>
+        <v>8979.1</v>
       </c>
       <c r="I91" s="3">
-        <v>1.1057</v>
+        <v>0.55</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C92" s="1">
-        <v>49.0</v>
+        <v>186.0</v>
       </c>
       <c r="D92" s="1">
-        <v>333.15</v>
+        <v>139.03</v>
       </c>
       <c r="E92" s="2">
-        <v>16324.5</v>
+        <v>25859.79</v>
       </c>
       <c r="F92" s="1">
-        <v>516.4</v>
+        <v>128.55</v>
       </c>
       <c r="G92" s="2">
-        <v>25303.6</v>
+        <v>23910.3</v>
       </c>
       <c r="H92" s="2">
-        <v>8979.1</v>
+        <v>-1949.49</v>
       </c>
       <c r="I92" s="3">
-        <v>0.55</v>
+        <v>-0.0754</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C93" s="1">
-        <v>186.0</v>
-      </c>
-      <c r="D93" s="1">
-        <v>139.03</v>
+        <v>15.0</v>
+      </c>
+      <c r="D93" s="2">
+        <v>1526.68</v>
       </c>
       <c r="E93" s="2">
-        <v>25859.79</v>
-      </c>
-      <c r="F93" s="1">
-        <v>128.55</v>
+        <v>22900.2</v>
+      </c>
+      <c r="F93" s="2">
+        <v>1559.2</v>
       </c>
       <c r="G93" s="2">
-        <v>23910.3</v>
-      </c>
-      <c r="H93" s="2">
-        <v>-1949.49</v>
+        <v>23388.0</v>
+      </c>
+      <c r="H93" s="1">
+        <v>487.8</v>
       </c>
       <c r="I93" s="3">
-        <v>-0.0754</v>
+        <v>0.0213</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C94" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="D94" s="2">
-        <v>1526.68</v>
+        <v>124.0</v>
+      </c>
+      <c r="D94" s="1">
+        <v>160.5</v>
       </c>
       <c r="E94" s="2">
-        <v>22900.2</v>
-      </c>
-      <c r="F94" s="2">
-        <v>1559.2</v>
+        <v>19902.66</v>
+      </c>
+      <c r="F94" s="1">
+        <v>185.98</v>
       </c>
       <c r="G94" s="2">
-        <v>23388.0</v>
-      </c>
-      <c r="H94" s="1">
-        <v>487.8</v>
+        <v>23061.52</v>
+      </c>
+      <c r="H94" s="2">
+        <v>3158.86</v>
       </c>
       <c r="I94" s="3">
-        <v>0.0213</v>
+        <v>0.1587</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C95" s="1">
-        <v>124.0</v>
+        <v>59.0</v>
       </c>
       <c r="D95" s="1">
-        <v>160.5</v>
+        <v>576.82</v>
       </c>
       <c r="E95" s="2">
-        <v>19902.66</v>
+        <v>34032.35</v>
       </c>
       <c r="F95" s="1">
-        <v>185.98</v>
+        <v>373.35</v>
       </c>
       <c r="G95" s="2">
-        <v>23061.52</v>
+        <v>22027.65</v>
       </c>
       <c r="H95" s="2">
-        <v>3158.86</v>
+        <v>-12004.7</v>
       </c>
       <c r="I95" s="3">
-        <v>0.1587</v>
+        <v>-0.3527</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C96" s="1">
-        <v>59.0</v>
-      </c>
-      <c r="D96" s="1">
-        <v>576.82</v>
+        <v>9.0</v>
+      </c>
+      <c r="D96" s="2">
+        <v>1395.0</v>
       </c>
       <c r="E96" s="2">
-        <v>34032.35</v>
-      </c>
-      <c r="F96" s="1">
-        <v>373.35</v>
+        <v>12555.0</v>
+      </c>
+      <c r="F96" s="2">
+        <v>2345.0</v>
       </c>
       <c r="G96" s="2">
-        <v>22027.65</v>
+        <v>21105.0</v>
       </c>
       <c r="H96" s="2">
-        <v>-12004.7</v>
+        <v>8550.0</v>
       </c>
       <c r="I96" s="3">
-        <v>-0.3527</v>
+        <v>0.681</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C97" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="D97" s="2">
-        <v>1395.0</v>
+        <v>67.0</v>
+      </c>
+      <c r="D97" s="1">
+        <v>374.48</v>
       </c>
       <c r="E97" s="2">
-        <v>12555.0</v>
-      </c>
-      <c r="F97" s="2">
-        <v>2345.0</v>
+        <v>25090.1</v>
+      </c>
+      <c r="F97" s="1">
+        <v>307.0</v>
       </c>
       <c r="G97" s="2">
-        <v>21105.0</v>
+        <v>20569.0</v>
       </c>
       <c r="H97" s="2">
-        <v>8550.0</v>
+        <v>-4521.1</v>
       </c>
       <c r="I97" s="3">
-        <v>0.681</v>
+        <v>-0.1802</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C98" s="1">
-        <v>67.0</v>
+        <v>63.0</v>
       </c>
       <c r="D98" s="1">
-        <v>374.48</v>
+        <v>311.35</v>
       </c>
       <c r="E98" s="2">
-        <v>25090.1</v>
+        <v>19614.9</v>
       </c>
       <c r="F98" s="1">
-        <v>307.0</v>
+        <v>323.85</v>
       </c>
       <c r="G98" s="2">
-        <v>20569.0</v>
-      </c>
-      <c r="H98" s="2">
-        <v>-4521.1</v>
+        <v>20402.55</v>
+      </c>
+      <c r="H98" s="1">
+        <v>787.65</v>
       </c>
       <c r="I98" s="3">
-        <v>-0.1802</v>
+        <v>0.0402</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C99" s="1">
-        <v>63.0</v>
+        <v>91.0</v>
       </c>
       <c r="D99" s="1">
-        <v>311.35</v>
+        <v>173.53</v>
       </c>
       <c r="E99" s="2">
-        <v>19614.9</v>
+        <v>15791.45</v>
       </c>
       <c r="F99" s="1">
-        <v>323.85</v>
-      </c>
-      <c r="G99" s="2">
-        <v>20402.55</v>
-      </c>
-      <c r="H99" s="1">
-        <v>787.65</v>
+        <v>217.4</v>
+      </c>
+      <c r="G99" s="4">
+        <v>19783.0</v>
+      </c>
+      <c r="H99" s="2">
+        <v>3991.95</v>
       </c>
       <c r="I99" s="3">
-        <v>0.0402</v>
+        <v>0.2528</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="100">
@@ -4652,75 +4718,75 @@
         <v>11</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C100" s="1">
-        <v>91.0</v>
-      </c>
-      <c r="D100" s="1">
-        <v>173.53</v>
+        <v>21.0</v>
+      </c>
+      <c r="D100" s="2">
+        <v>1220.91</v>
       </c>
       <c r="E100" s="2">
-        <v>15791.45</v>
+        <v>25639.1</v>
       </c>
       <c r="F100" s="1">
-        <v>217.4</v>
-      </c>
-      <c r="G100" s="4">
-        <v>19783.0</v>
+        <v>932.25</v>
+      </c>
+      <c r="G100" s="2">
+        <v>19577.25</v>
       </c>
       <c r="H100" s="2">
-        <v>3991.95</v>
+        <v>-6061.85</v>
       </c>
       <c r="I100" s="3">
-        <v>0.2528</v>
+        <v>-0.2364</v>
       </c>
       <c r="J100" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C101" s="1">
-        <v>21.0</v>
+        <v>5.0</v>
       </c>
       <c r="D101" s="2">
-        <v>1220.91</v>
+        <v>2134.6</v>
       </c>
       <c r="E101" s="2">
-        <v>25639.1</v>
-      </c>
-      <c r="F101" s="1">
-        <v>932.25</v>
-      </c>
-      <c r="G101" s="2">
-        <v>19577.25</v>
+        <v>10673.0</v>
+      </c>
+      <c r="F101" s="2">
+        <v>3914.45</v>
+      </c>
+      <c r="G101" s="4">
+        <v>19572.0</v>
       </c>
       <c r="H101" s="2">
-        <v>-6061.85</v>
+        <v>8899.25</v>
       </c>
       <c r="I101" s="3">
-        <v>-0.2364</v>
+        <v>0.8338</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="102">
@@ -4728,721 +4794,721 @@
         <v>11</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C102" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="D102" s="2">
-        <v>2134.6</v>
+        <v>125.0</v>
+      </c>
+      <c r="D102" s="1">
+        <v>194.63</v>
       </c>
       <c r="E102" s="2">
-        <v>10673.0</v>
-      </c>
-      <c r="F102" s="2">
-        <v>3914.45</v>
-      </c>
-      <c r="G102" s="4">
-        <v>19572.0</v>
+        <v>24328.3</v>
+      </c>
+      <c r="F102" s="1">
+        <v>156.25</v>
+      </c>
+      <c r="G102" s="2">
+        <v>19531.25</v>
       </c>
       <c r="H102" s="2">
-        <v>8899.25</v>
+        <v>-4797.05</v>
       </c>
       <c r="I102" s="3">
-        <v>0.8338</v>
+        <v>-0.1972</v>
       </c>
       <c r="J102" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C103" s="1">
-        <v>125.0</v>
+        <v>44.0</v>
       </c>
       <c r="D103" s="1">
-        <v>194.63</v>
+        <v>451.6</v>
       </c>
       <c r="E103" s="2">
-        <v>24328.3</v>
+        <v>19870.25</v>
       </c>
       <c r="F103" s="1">
-        <v>156.25</v>
+        <v>442.4</v>
       </c>
       <c r="G103" s="2">
-        <v>19531.25</v>
-      </c>
-      <c r="H103" s="2">
-        <v>-4797.05</v>
+        <v>19465.6</v>
+      </c>
+      <c r="H103" s="1">
+        <v>-404.65</v>
       </c>
       <c r="I103" s="3">
-        <v>-0.1972</v>
+        <v>-0.0204</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C104" s="1">
-        <v>44.0</v>
+        <v>72.0</v>
       </c>
       <c r="D104" s="1">
-        <v>451.6</v>
+        <v>275.75</v>
       </c>
       <c r="E104" s="2">
-        <v>19870.25</v>
+        <v>19853.65</v>
       </c>
       <c r="F104" s="1">
-        <v>442.4</v>
+        <v>268.7</v>
       </c>
       <c r="G104" s="2">
-        <v>19465.6</v>
+        <v>19346.4</v>
       </c>
       <c r="H104" s="1">
-        <v>-404.65</v>
+        <v>-507.25</v>
       </c>
       <c r="I104" s="3">
-        <v>-0.0204</v>
+        <v>-0.0255</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C105" s="1">
-        <v>72.0</v>
-      </c>
-      <c r="D105" s="1">
-        <v>275.75</v>
+        <v>7.0</v>
+      </c>
+      <c r="D105" s="2">
+        <v>3125.67</v>
       </c>
       <c r="E105" s="2">
-        <v>19853.65</v>
-      </c>
-      <c r="F105" s="1">
-        <v>268.7</v>
+        <v>21879.7</v>
+      </c>
+      <c r="F105" s="2">
+        <v>2761.25</v>
       </c>
       <c r="G105" s="2">
-        <v>19346.4</v>
-      </c>
-      <c r="H105" s="1">
-        <v>-507.25</v>
+        <v>19328.75</v>
+      </c>
+      <c r="H105" s="2">
+        <v>-2550.95</v>
       </c>
       <c r="I105" s="3">
-        <v>-0.0255</v>
+        <v>-0.1166</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C106" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="D106" s="2">
-        <v>3125.67</v>
+        <v>110.0</v>
+      </c>
+      <c r="D106" s="1">
+        <v>181.04</v>
       </c>
       <c r="E106" s="2">
-        <v>21879.7</v>
-      </c>
-      <c r="F106" s="2">
-        <v>2761.25</v>
+        <v>19914.4</v>
+      </c>
+      <c r="F106" s="1">
+        <v>175.44</v>
       </c>
       <c r="G106" s="2">
-        <v>19328.75</v>
-      </c>
-      <c r="H106" s="2">
-        <v>-2550.95</v>
+        <v>19298.4</v>
+      </c>
+      <c r="H106" s="1">
+        <v>-616.0</v>
       </c>
       <c r="I106" s="3">
-        <v>-0.1166</v>
+        <v>-0.0309</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C107" s="1">
-        <v>110.0</v>
+        <v>221.0</v>
       </c>
       <c r="D107" s="1">
-        <v>181.04</v>
+        <v>126.22</v>
       </c>
       <c r="E107" s="2">
-        <v>19914.4</v>
+        <v>27894.4</v>
       </c>
       <c r="F107" s="1">
-        <v>175.44</v>
+        <v>87.06</v>
       </c>
       <c r="G107" s="2">
-        <v>19298.4</v>
-      </c>
-      <c r="H107" s="1">
-        <v>-616.0</v>
+        <v>19240.26</v>
+      </c>
+      <c r="H107" s="2">
+        <v>-8654.14</v>
       </c>
       <c r="I107" s="3">
-        <v>-0.0309</v>
+        <v>-0.3102</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C108" s="1">
-        <v>221.0</v>
-      </c>
-      <c r="D108" s="1">
-        <v>126.22</v>
+        <v>9.0</v>
+      </c>
+      <c r="D108" s="2">
+        <v>2147.0</v>
       </c>
       <c r="E108" s="2">
-        <v>27894.4</v>
-      </c>
-      <c r="F108" s="1">
-        <v>87.06</v>
+        <v>19323.0</v>
+      </c>
+      <c r="F108" s="2">
+        <v>2116.45</v>
       </c>
       <c r="G108" s="2">
-        <v>19240.26</v>
-      </c>
-      <c r="H108" s="2">
-        <v>-8654.14</v>
+        <v>19048.05</v>
+      </c>
+      <c r="H108" s="1">
+        <v>-274.95</v>
       </c>
       <c r="I108" s="3">
-        <v>-0.3102</v>
+        <v>-0.0142</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C109" s="1">
-        <v>9.0</v>
+        <v>23.0</v>
       </c>
       <c r="D109" s="2">
-        <v>2147.0</v>
+        <v>1205.77</v>
       </c>
       <c r="E109" s="2">
-        <v>19323.0</v>
-      </c>
-      <c r="F109" s="2">
-        <v>2116.45</v>
+        <v>27732.8</v>
+      </c>
+      <c r="F109" s="1">
+        <v>826.05</v>
       </c>
       <c r="G109" s="2">
-        <v>19048.05</v>
-      </c>
-      <c r="H109" s="1">
-        <v>-274.95</v>
+        <v>18999.15</v>
+      </c>
+      <c r="H109" s="2">
+        <v>-8733.65</v>
       </c>
       <c r="I109" s="3">
-        <v>-0.0142</v>
+        <v>-0.3149</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C110" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="D110" s="2">
-        <v>1205.77</v>
+        <v>20.0</v>
+      </c>
+      <c r="D110" s="1">
+        <v>988.13</v>
       </c>
       <c r="E110" s="2">
-        <v>27732.8</v>
+        <v>19762.5</v>
       </c>
       <c r="F110" s="1">
-        <v>826.05</v>
+        <v>932.35</v>
       </c>
       <c r="G110" s="2">
-        <v>18999.15</v>
+        <v>18647.0</v>
       </c>
       <c r="H110" s="2">
-        <v>-8733.65</v>
+        <v>-1115.5</v>
       </c>
       <c r="I110" s="3">
-        <v>-0.3149</v>
+        <v>-0.0564</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C111" s="1">
-        <v>20.0</v>
+        <v>32.0</v>
       </c>
       <c r="D111" s="1">
-        <v>988.13</v>
+        <v>619.5</v>
       </c>
       <c r="E111" s="2">
-        <v>19762.5</v>
+        <v>19824.0</v>
       </c>
       <c r="F111" s="1">
-        <v>932.35</v>
+        <v>580.5</v>
       </c>
       <c r="G111" s="2">
-        <v>18647.0</v>
+        <v>18576.0</v>
       </c>
       <c r="H111" s="2">
-        <v>-1115.5</v>
+        <v>-1248.0</v>
       </c>
       <c r="I111" s="3">
-        <v>-0.0564</v>
+        <v>-0.063</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C112" s="1">
-        <v>32.0</v>
+        <v>228.0</v>
       </c>
       <c r="D112" s="1">
-        <v>619.5</v>
+        <v>94.74</v>
       </c>
       <c r="E112" s="2">
-        <v>19824.0</v>
+        <v>21599.94</v>
       </c>
       <c r="F112" s="1">
-        <v>580.5</v>
+        <v>80.83</v>
       </c>
       <c r="G112" s="2">
-        <v>18576.0</v>
+        <v>18429.24</v>
       </c>
       <c r="H112" s="2">
-        <v>-1248.0</v>
+        <v>-3170.7</v>
       </c>
       <c r="I112" s="3">
-        <v>-0.063</v>
+        <v>-0.1468</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C113" s="1">
-        <v>228.0</v>
+        <v>456.0</v>
       </c>
       <c r="D113" s="1">
-        <v>94.74</v>
+        <v>43.8</v>
       </c>
       <c r="E113" s="2">
-        <v>21599.94</v>
+        <v>19972.8</v>
       </c>
       <c r="F113" s="1">
-        <v>80.83</v>
+        <v>40.16</v>
       </c>
       <c r="G113" s="2">
-        <v>18429.24</v>
+        <v>18312.96</v>
       </c>
       <c r="H113" s="2">
-        <v>-3170.7</v>
+        <v>-1659.84</v>
       </c>
       <c r="I113" s="3">
-        <v>-0.1468</v>
+        <v>-0.0831</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C114" s="1">
-        <v>456.0</v>
+        <v>46.0</v>
       </c>
       <c r="D114" s="1">
-        <v>43.8</v>
+        <v>430.98</v>
       </c>
       <c r="E114" s="2">
-        <v>19972.8</v>
+        <v>19824.9</v>
       </c>
       <c r="F114" s="1">
-        <v>40.16</v>
+        <v>394.8</v>
       </c>
       <c r="G114" s="2">
-        <v>18312.96</v>
+        <v>18160.8</v>
       </c>
       <c r="H114" s="2">
-        <v>-1659.84</v>
+        <v>-1664.1</v>
       </c>
       <c r="I114" s="3">
-        <v>-0.0831</v>
+        <v>-0.0839</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C115" s="1">
-        <v>46.0</v>
-      </c>
-      <c r="D115" s="1">
-        <v>430.98</v>
+        <v>10.0</v>
+      </c>
+      <c r="D115" s="2">
+        <v>1963.23</v>
       </c>
       <c r="E115" s="2">
-        <v>19824.9</v>
-      </c>
-      <c r="F115" s="1">
-        <v>394.8</v>
+        <v>19632.3</v>
+      </c>
+      <c r="F115" s="2">
+        <v>1713.9</v>
       </c>
       <c r="G115" s="2">
-        <v>18160.8</v>
+        <v>17139.0</v>
       </c>
       <c r="H115" s="2">
-        <v>-1664.1</v>
+        <v>-2493.3</v>
       </c>
       <c r="I115" s="3">
-        <v>-0.0839</v>
+        <v>-0.127</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C116" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D116" s="2">
-        <v>1963.23</v>
+        <v>40.0</v>
+      </c>
+      <c r="D116" s="1">
+        <v>498.93</v>
       </c>
       <c r="E116" s="2">
-        <v>19632.3</v>
-      </c>
-      <c r="F116" s="2">
-        <v>1713.9</v>
+        <v>19957.2</v>
+      </c>
+      <c r="F116" s="1">
+        <v>426.1</v>
       </c>
       <c r="G116" s="2">
-        <v>17139.0</v>
+        <v>17044.0</v>
       </c>
       <c r="H116" s="2">
-        <v>-2493.3</v>
+        <v>-2913.2</v>
       </c>
       <c r="I116" s="3">
-        <v>-0.127</v>
+        <v>-0.146</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C117" s="1">
-        <v>40.0</v>
+        <v>72.0</v>
       </c>
       <c r="D117" s="1">
-        <v>498.93</v>
+        <v>278.55</v>
       </c>
       <c r="E117" s="2">
-        <v>19957.2</v>
+        <v>20055.6</v>
       </c>
       <c r="F117" s="1">
-        <v>426.1</v>
+        <v>225.0</v>
       </c>
       <c r="G117" s="2">
-        <v>17044.0</v>
+        <v>16200.0</v>
       </c>
       <c r="H117" s="2">
-        <v>-2913.2</v>
+        <v>-3855.6</v>
       </c>
       <c r="I117" s="3">
-        <v>-0.146</v>
+        <v>-0.1922</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C118" s="1">
-        <v>72.0</v>
+        <v>50.0</v>
       </c>
       <c r="D118" s="1">
-        <v>278.55</v>
+        <v>292.7</v>
       </c>
       <c r="E118" s="2">
-        <v>20055.6</v>
+        <v>14635.0</v>
       </c>
       <c r="F118" s="1">
-        <v>225.0</v>
+        <v>311.0</v>
       </c>
       <c r="G118" s="2">
-        <v>16200.0</v>
-      </c>
-      <c r="H118" s="2">
-        <v>-3855.6</v>
+        <v>15550.0</v>
+      </c>
+      <c r="H118" s="1">
+        <v>915.0</v>
       </c>
       <c r="I118" s="3">
-        <v>-0.1922</v>
+        <v>0.0625</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C119" s="1">
-        <v>50.0</v>
+        <v>10.0</v>
       </c>
       <c r="D119" s="1">
-        <v>292.7</v>
+        <v>975.8</v>
       </c>
       <c r="E119" s="2">
-        <v>14635.0</v>
-      </c>
-      <c r="F119" s="1">
-        <v>311.0</v>
-      </c>
-      <c r="G119" s="2">
-        <v>15550.0</v>
-      </c>
-      <c r="H119" s="1">
-        <v>915.0</v>
+        <v>9758.0</v>
+      </c>
+      <c r="F119" s="2">
+        <v>1491.9</v>
+      </c>
+      <c r="G119" s="4">
+        <v>14919.0</v>
+      </c>
+      <c r="H119" s="2">
+        <v>5161.0</v>
       </c>
       <c r="I119" s="3">
-        <v>0.0625</v>
+        <v>0.5289</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C120" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D120" s="1">
-        <v>975.8</v>
+        <v>9.0</v>
+      </c>
+      <c r="D120" s="2">
+        <v>1722.96</v>
       </c>
       <c r="E120" s="2">
-        <v>9758.0</v>
+        <v>15506.6</v>
       </c>
       <c r="F120" s="2">
-        <v>1491.9</v>
+        <v>1606.1</v>
       </c>
       <c r="G120" s="4">
-        <v>14919.0</v>
+        <v>14455.0</v>
       </c>
       <c r="H120" s="2">
-        <v>5161.0</v>
+        <v>-1051.7</v>
       </c>
       <c r="I120" s="3">
-        <v>0.5289</v>
+        <v>-0.0678</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="121">
@@ -5450,417 +5516,417 @@
         <v>11</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C121" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="D121" s="2">
-        <v>1722.96</v>
+        <v>27.0</v>
+      </c>
+      <c r="D121" s="1">
+        <v>369.7</v>
       </c>
       <c r="E121" s="2">
-        <v>15506.6</v>
-      </c>
-      <c r="F121" s="2">
-        <v>1606.1</v>
-      </c>
-      <c r="G121" s="4">
-        <v>14455.0</v>
+        <v>9981.9</v>
+      </c>
+      <c r="F121" s="1">
+        <v>532.45</v>
+      </c>
+      <c r="G121" s="2">
+        <v>14376.15</v>
       </c>
       <c r="H121" s="2">
-        <v>-1051.7</v>
+        <v>4394.25</v>
       </c>
       <c r="I121" s="3">
-        <v>-0.0678</v>
+        <v>0.4402</v>
       </c>
       <c r="J121" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C122" s="1">
-        <v>27.0</v>
-      </c>
-      <c r="D122" s="1">
-        <v>369.7</v>
+        <v>3.0</v>
+      </c>
+      <c r="D122" s="2">
+        <v>5480.0</v>
       </c>
       <c r="E122" s="2">
-        <v>9981.9</v>
-      </c>
-      <c r="F122" s="1">
-        <v>532.45</v>
+        <v>16440.0</v>
+      </c>
+      <c r="F122" s="2">
+        <v>4611.7</v>
       </c>
       <c r="G122" s="2">
-        <v>14376.15</v>
+        <v>13835.1</v>
       </c>
       <c r="H122" s="2">
-        <v>4394.25</v>
+        <v>-2604.9</v>
       </c>
       <c r="I122" s="3">
-        <v>0.4402</v>
+        <v>-0.1584</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C123" s="1">
-        <v>3.0</v>
+        <v>15.0</v>
       </c>
       <c r="D123" s="2">
-        <v>5480.0</v>
+        <v>1023.34</v>
       </c>
       <c r="E123" s="2">
-        <v>16440.0</v>
-      </c>
-      <c r="F123" s="2">
-        <v>4611.7</v>
+        <v>15350.15</v>
+      </c>
+      <c r="F123" s="1">
+        <v>846.25</v>
       </c>
       <c r="G123" s="2">
-        <v>13835.1</v>
+        <v>12693.75</v>
       </c>
       <c r="H123" s="2">
-        <v>-2604.9</v>
+        <v>-2656.4</v>
       </c>
       <c r="I123" s="3">
-        <v>-0.1584</v>
+        <v>-0.1731</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C124" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="D124" s="2">
-        <v>1023.34</v>
+        <v>68.0</v>
+      </c>
+      <c r="D124" s="1">
+        <v>174.16</v>
       </c>
       <c r="E124" s="2">
-        <v>15350.15</v>
+        <v>11842.88</v>
       </c>
       <c r="F124" s="1">
-        <v>846.25</v>
+        <v>180.5</v>
       </c>
       <c r="G124" s="2">
-        <v>12693.75</v>
-      </c>
-      <c r="H124" s="2">
-        <v>-2656.4</v>
+        <v>12274.0</v>
+      </c>
+      <c r="H124" s="1">
+        <v>431.12</v>
       </c>
       <c r="I124" s="3">
-        <v>-0.1731</v>
+        <v>0.0364</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C125" s="1">
-        <v>68.0</v>
-      </c>
-      <c r="D125" s="1">
-        <v>174.16</v>
+        <v>13.0</v>
+      </c>
+      <c r="D125" s="2">
+        <v>1105.88</v>
       </c>
       <c r="E125" s="2">
-        <v>11842.88</v>
+        <v>14376.5</v>
       </c>
       <c r="F125" s="1">
-        <v>180.5</v>
+        <v>871.0</v>
       </c>
       <c r="G125" s="2">
-        <v>12274.0</v>
-      </c>
-      <c r="H125" s="1">
-        <v>431.12</v>
+        <v>11323.0</v>
+      </c>
+      <c r="H125" s="2">
+        <v>-3053.5</v>
       </c>
       <c r="I125" s="3">
-        <v>0.0364</v>
+        <v>-0.2124</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C126" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="D126" s="2">
-        <v>1105.88</v>
+        <v>14.0</v>
+      </c>
+      <c r="D126" s="1">
+        <v>855.63</v>
       </c>
       <c r="E126" s="2">
-        <v>14376.5</v>
+        <v>11978.75</v>
       </c>
       <c r="F126" s="1">
-        <v>871.0</v>
+        <v>790.0</v>
       </c>
       <c r="G126" s="2">
-        <v>11323.0</v>
-      </c>
-      <c r="H126" s="2">
-        <v>-3053.5</v>
+        <v>11060.0</v>
+      </c>
+      <c r="H126" s="1">
+        <v>-918.75</v>
       </c>
       <c r="I126" s="3">
-        <v>-0.2124</v>
+        <v>-0.0767</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C127" s="1">
-        <v>14.0</v>
+        <v>95.0</v>
       </c>
       <c r="D127" s="1">
-        <v>855.63</v>
+        <v>158.81</v>
       </c>
       <c r="E127" s="2">
-        <v>11978.75</v>
+        <v>15087.3</v>
       </c>
       <c r="F127" s="1">
-        <v>790.0</v>
+        <v>115.35</v>
       </c>
       <c r="G127" s="2">
-        <v>11060.0</v>
-      </c>
-      <c r="H127" s="1">
-        <v>-918.75</v>
+        <v>10958.25</v>
+      </c>
+      <c r="H127" s="2">
+        <v>-4129.05</v>
       </c>
       <c r="I127" s="3">
-        <v>-0.0767</v>
+        <v>-0.2737</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C128" s="1">
-        <v>95.0</v>
+        <v>50.0</v>
       </c>
       <c r="D128" s="1">
-        <v>158.81</v>
+        <v>238.76</v>
       </c>
       <c r="E128" s="2">
-        <v>15087.3</v>
+        <v>11938.1</v>
       </c>
       <c r="F128" s="1">
-        <v>115.35</v>
+        <v>210.7</v>
       </c>
       <c r="G128" s="2">
-        <v>10958.25</v>
+        <v>10535.0</v>
       </c>
       <c r="H128" s="2">
-        <v>-4129.05</v>
+        <v>-1403.1</v>
       </c>
       <c r="I128" s="3">
-        <v>-0.2737</v>
+        <v>-0.1175</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C129" s="1">
-        <v>50.0</v>
-      </c>
-      <c r="D129" s="1">
-        <v>238.76</v>
+        <v>7.0</v>
+      </c>
+      <c r="D129" s="2">
+        <v>1395.0</v>
       </c>
       <c r="E129" s="2">
-        <v>11938.1</v>
-      </c>
-      <c r="F129" s="1">
-        <v>210.7</v>
+        <v>9765.0</v>
+      </c>
+      <c r="F129" s="2">
+        <v>1463.8</v>
       </c>
       <c r="G129" s="2">
-        <v>10535.0</v>
-      </c>
-      <c r="H129" s="2">
-        <v>-1403.1</v>
+        <v>10246.6</v>
+      </c>
+      <c r="H129" s="1">
+        <v>481.6</v>
       </c>
       <c r="I129" s="3">
-        <v>-0.1175</v>
+        <v>0.0493</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C130" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="D130" s="2">
-        <v>1395.0</v>
+        <v>59.0</v>
+      </c>
+      <c r="D130" s="1">
+        <v>166.1</v>
       </c>
       <c r="E130" s="2">
-        <v>9765.0</v>
-      </c>
-      <c r="F130" s="2">
-        <v>1463.8</v>
+        <v>9799.73</v>
+      </c>
+      <c r="F130" s="1">
+        <v>171.0</v>
       </c>
       <c r="G130" s="2">
-        <v>10246.6</v>
+        <v>10089.0</v>
       </c>
       <c r="H130" s="1">
-        <v>481.6</v>
+        <v>289.27</v>
       </c>
       <c r="I130" s="3">
-        <v>0.0493</v>
+        <v>0.0295</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C131" s="1">
-        <v>59.0</v>
+        <v>20.0</v>
       </c>
       <c r="D131" s="1">
-        <v>166.1</v>
+        <v>369.45</v>
       </c>
       <c r="E131" s="2">
-        <v>9799.73</v>
+        <v>7389.0</v>
       </c>
       <c r="F131" s="1">
-        <v>171.0</v>
-      </c>
-      <c r="G131" s="2">
-        <v>10089.0</v>
-      </c>
-      <c r="H131" s="1">
-        <v>289.27</v>
+        <v>492.45</v>
+      </c>
+      <c r="G131" s="4">
+        <v>9849.0</v>
+      </c>
+      <c r="H131" s="2">
+        <v>2460.0</v>
       </c>
       <c r="I131" s="3">
-        <v>0.0295</v>
+        <v>0.3329</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K131" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="132">
@@ -5868,151 +5934,151 @@
         <v>11</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C132" s="1">
-        <v>20.0</v>
+        <v>92.0</v>
       </c>
       <c r="D132" s="1">
-        <v>369.45</v>
+        <v>108.55</v>
       </c>
       <c r="E132" s="2">
-        <v>7389.0</v>
+        <v>9986.6</v>
       </c>
       <c r="F132" s="1">
-        <v>492.45</v>
-      </c>
-      <c r="G132" s="4">
-        <v>9849.0</v>
+        <v>95.92</v>
+      </c>
+      <c r="G132" s="2">
+        <v>8824.64</v>
       </c>
       <c r="H132" s="2">
-        <v>2460.0</v>
+        <v>-1161.96</v>
       </c>
       <c r="I132" s="3">
-        <v>0.3329</v>
+        <v>-0.1164</v>
       </c>
       <c r="J132" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C133" s="1">
-        <v>92.0</v>
+        <v>148.0</v>
       </c>
       <c r="D133" s="1">
-        <v>108.55</v>
+        <v>67.59</v>
       </c>
       <c r="E133" s="2">
-        <v>9986.6</v>
+        <v>10003.56</v>
       </c>
       <c r="F133" s="1">
-        <v>95.92</v>
+        <v>57.11</v>
       </c>
       <c r="G133" s="2">
-        <v>8824.64</v>
+        <v>8452.28</v>
       </c>
       <c r="H133" s="2">
-        <v>-1161.96</v>
+        <v>-1551.28</v>
       </c>
       <c r="I133" s="3">
-        <v>-0.1164</v>
+        <v>-0.1551</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C134" s="1">
-        <v>148.0</v>
-      </c>
-      <c r="D134" s="1">
-        <v>67.59</v>
+        <v>8.0</v>
+      </c>
+      <c r="D134" s="2">
+        <v>1486.09</v>
       </c>
       <c r="E134" s="2">
-        <v>10003.56</v>
+        <v>11888.7</v>
       </c>
       <c r="F134" s="1">
-        <v>57.11</v>
-      </c>
-      <c r="G134" s="2">
-        <v>8452.28</v>
+        <v>790.5</v>
+      </c>
+      <c r="G134" s="4">
+        <v>6324.0</v>
       </c>
       <c r="H134" s="2">
-        <v>-1551.28</v>
+        <v>-5564.7</v>
       </c>
       <c r="I134" s="3">
-        <v>-0.1551</v>
+        <v>-0.4681</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C135" s="1">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="D135" s="2">
-        <v>1486.09</v>
+        <v>1154.83</v>
       </c>
       <c r="E135" s="2">
-        <v>11888.7</v>
-      </c>
-      <c r="F135" s="1">
-        <v>790.5</v>
-      </c>
-      <c r="G135" s="4">
-        <v>6324.0</v>
+        <v>3464.5</v>
+      </c>
+      <c r="F135" s="2">
+        <v>1925.3</v>
+      </c>
+      <c r="G135" s="2">
+        <v>5775.9</v>
       </c>
       <c r="H135" s="2">
-        <v>-5564.7</v>
+        <v>2311.4</v>
       </c>
       <c r="I135" s="3">
-        <v>-0.4681</v>
+        <v>0.6672</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K135" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="136">
@@ -6020,189 +6086,189 @@
         <v>11</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C136" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="D136" s="2">
-        <v>1154.83</v>
+        <v>39.0</v>
+      </c>
+      <c r="D136" s="1">
+        <v>379.94</v>
       </c>
       <c r="E136" s="2">
-        <v>3464.5</v>
-      </c>
-      <c r="F136" s="2">
-        <v>1925.3</v>
+        <v>14817.69</v>
+      </c>
+      <c r="F136" s="1">
+        <v>86.49</v>
       </c>
       <c r="G136" s="2">
-        <v>5775.9</v>
+        <v>3373.11</v>
       </c>
       <c r="H136" s="2">
-        <v>2311.4</v>
+        <v>-11444.58</v>
       </c>
       <c r="I136" s="3">
-        <v>0.6672</v>
+        <v>-0.7724</v>
       </c>
       <c r="J136" s="1" t="s">
         <v>11</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C137" s="1">
-        <v>39.0</v>
+        <v>26.0</v>
       </c>
       <c r="D137" s="1">
-        <v>379.94</v>
+        <v>205.31</v>
       </c>
       <c r="E137" s="2">
-        <v>14817.69</v>
+        <v>5338.0</v>
       </c>
       <c r="F137" s="1">
-        <v>86.49</v>
-      </c>
-      <c r="G137" s="2">
-        <v>3373.11</v>
+        <v>127.89</v>
+      </c>
+      <c r="G137" s="4">
+        <v>3325.0</v>
       </c>
       <c r="H137" s="2">
-        <v>-11444.58</v>
+        <v>-2012.86</v>
       </c>
       <c r="I137" s="3">
-        <v>-0.7724</v>
+        <v>-0.3771</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K137" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B138" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C138" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D138" s="1">
+        <v>80.54</v>
+      </c>
+      <c r="E138" s="1">
+        <v>885.9</v>
+      </c>
+      <c r="F138" s="1">
+        <v>272.25</v>
+      </c>
+      <c r="G138" s="4">
+        <v>2995.0</v>
+      </c>
+      <c r="H138" s="2">
+        <v>2108.85</v>
+      </c>
+      <c r="I138" s="3">
+        <v>2.3805</v>
+      </c>
+      <c r="J138" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K138" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L138" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C139" s="7">
+        <v>6123.0</v>
+      </c>
+      <c r="D139" s="8">
+        <v>50.33</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="F139" s="8">
+        <v>206.62</v>
+      </c>
+      <c r="G139" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="C138" s="1">
-        <v>26.0</v>
-      </c>
-      <c r="D138" s="1">
-        <v>205.31</v>
-      </c>
-      <c r="E138" s="2">
-        <v>5338.0</v>
-      </c>
-      <c r="F138" s="1">
-        <v>127.89</v>
-      </c>
-      <c r="G138" s="4">
-        <v>3325.0</v>
-      </c>
-      <c r="H138" s="2">
-        <v>-2012.86</v>
-      </c>
-      <c r="I138" s="3">
-        <v>-0.3771</v>
-      </c>
-      <c r="J138" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K138" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L138" s="1" t="s">
+      <c r="H139" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="I139" s="10">
+        <v>3.1054</v>
+      </c>
+      <c r="J139" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C139" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="D139" s="1">
-        <v>80.54</v>
-      </c>
-      <c r="E139" s="1">
-        <v>885.9</v>
-      </c>
-      <c r="F139" s="1">
-        <v>272.25</v>
-      </c>
-      <c r="G139" s="4">
-        <v>2995.0</v>
-      </c>
-      <c r="H139" s="2">
-        <v>2108.85</v>
-      </c>
-      <c r="I139" s="3">
-        <v>2.3805</v>
-      </c>
-      <c r="J139" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K139" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L139" s="1" t="s">
-        <v>17</v>
+      <c r="K139" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L139" s="11" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B140" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B140" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="C140" s="6">
-        <v>6123.0</v>
-      </c>
-      <c r="D140" s="6">
-        <v>50.33</v>
-      </c>
-      <c r="E140" s="6">
-        <v>308166.8</v>
-      </c>
-      <c r="F140" s="6">
-        <v>206.62</v>
-      </c>
-      <c r="G140" s="6">
-        <v>1265134.0</v>
-      </c>
-      <c r="H140" s="6">
-        <v>956967.5</v>
-      </c>
-      <c r="I140" s="6">
-        <v>3.1054</v>
+      <c r="C140" s="8">
+        <v>369.0</v>
+      </c>
+      <c r="D140" s="8">
+        <v>497.01</v>
+      </c>
+      <c r="E140" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="F140" s="13">
+        <v>1899.7</v>
+      </c>
+      <c r="G140" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="H140" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="I140" s="10">
+        <v>2.8223</v>
       </c>
       <c r="J140" s="5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K140" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L140" s="5" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="L140" s="11" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/data/portfolio.xlsx
+++ b/data/portfolio.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="216">
   <si>
     <t>Symbol</t>
   </si>
@@ -52,10 +52,10 @@
     <t>3,08,166.76</t>
   </si>
   <si>
-    <t>11,73,901.56</t>
-  </si>
-  <si>
-    <t>8,65,734.80</t>
+    <t>11,75,860.92</t>
+  </si>
+  <si>
+    <t>8,67,694.16</t>
   </si>
   <si>
     <t>N</t>
@@ -73,10 +73,10 @@
     <t>1,83,396.90</t>
   </si>
   <si>
-    <t>6,85,786.50</t>
-  </si>
-  <si>
-    <t>5,02,389.60</t>
+    <t>6,98,553.90</t>
+  </si>
+  <si>
+    <t>5,15,157.00</t>
   </si>
   <si>
     <t>AEROFLEX</t>
@@ -85,10 +85,10 @@
     <t>1,79,710.57</t>
   </si>
   <si>
-    <t>3,92,208.00</t>
-  </si>
-  <si>
-    <t>2,12,497.43</t>
+    <t>4,50,576.00</t>
+  </si>
+  <si>
+    <t>2,70,865.43</t>
   </si>
   <si>
     <t>G</t>
@@ -100,28 +100,55 @@
     <t>MUSTBUY</t>
   </si>
   <si>
+    <t>SYRMA</t>
+  </si>
+  <si>
+    <t>1,24,501.80</t>
+  </si>
+  <si>
+    <t>3,74,775.20</t>
+  </si>
+  <si>
+    <t>2,50,273.40</t>
+  </si>
+  <si>
     <t>HCG</t>
   </si>
   <si>
     <t>1,91,353.60</t>
   </si>
   <si>
-    <t>3,81,234.00</t>
-  </si>
-  <si>
-    <t>1,89,880.40</t>
-  </si>
-  <si>
-    <t>SYRMA</t>
-  </si>
-  <si>
-    <t>1,24,501.80</t>
-  </si>
-  <si>
-    <t>3,57,088.40</t>
-  </si>
-  <si>
-    <t>2,32,586.60</t>
+    <t>3,88,389.75</t>
+  </si>
+  <si>
+    <t>1,97,036.15</t>
+  </si>
+  <si>
+    <t>POWERINDIA</t>
+  </si>
+  <si>
+    <t>1,37,780.00</t>
+  </si>
+  <si>
+    <t>1,28,996.35</t>
+  </si>
+  <si>
+    <t>ASTRAMICRO</t>
+  </si>
+  <si>
+    <t>1,48,187.20</t>
+  </si>
+  <si>
+    <t>1,25,489.50</t>
+  </si>
+  <si>
+    <t>DEEDEV-T</t>
+  </si>
+  <si>
+    <t>1,75,822.50</t>
+  </si>
+  <si>
+    <t>1,09,048.55</t>
   </si>
   <si>
     <t>PARKHOSPS</t>
@@ -130,22 +157,265 @@
     <t>1,42,295.53</t>
   </si>
   <si>
-    <t>2,44,832.00</t>
-  </si>
-  <si>
-    <t>1,02,536.47</t>
+    <t>2,45,728.00</t>
+  </si>
+  <si>
+    <t>1,03,432.47</t>
   </si>
   <si>
     <t>1. Oct'25 Must buy</t>
   </si>
   <si>
+    <t>MTARTECH</t>
+  </si>
+  <si>
+    <t>1,27,368.00</t>
+  </si>
+  <si>
+    <t>ASTERDM</t>
+  </si>
+  <si>
+    <t>1,49,840.40</t>
+  </si>
+  <si>
+    <t>NEULANDLAB</t>
+  </si>
+  <si>
+    <t>1,02,294.00</t>
+  </si>
+  <si>
+    <t>AVANTEL</t>
+  </si>
+  <si>
+    <t>SANSERA</t>
+  </si>
+  <si>
+    <t>1,63,534.00</t>
+  </si>
+  <si>
+    <t>HBLENGINE</t>
+  </si>
+  <si>
+    <t>JNKINDIA</t>
+  </si>
+  <si>
+    <t>1,13,006.25</t>
+  </si>
+  <si>
+    <t>INOXINDIA</t>
+  </si>
+  <si>
+    <t>1,07,617.20</t>
+  </si>
+  <si>
+    <t>1,51,192.80</t>
+  </si>
+  <si>
+    <t>MODISONLTD-T</t>
+  </si>
+  <si>
+    <t>RIR</t>
+  </si>
+  <si>
+    <t>UTI NIFTY 50 INDEX FUND - DIRECT PLAN</t>
+  </si>
+  <si>
+    <t>SOUTHWEST</t>
+  </si>
+  <si>
+    <t>TRITURBINE</t>
+  </si>
+  <si>
+    <t>1,26,763.15</t>
+  </si>
+  <si>
+    <t>1,53,559.50</t>
+  </si>
+  <si>
+    <t>RUBICON</t>
+  </si>
+  <si>
+    <t>GALAPREC</t>
+  </si>
+  <si>
+    <t>SHREEJISPG</t>
+  </si>
+  <si>
+    <t>SASKEN</t>
+  </si>
+  <si>
+    <t>HAPPYFORGE</t>
+  </si>
+  <si>
+    <t>NEPHROPLUS</t>
+  </si>
+  <si>
+    <t>1,29,287.90</t>
+  </si>
+  <si>
+    <t>1,46,013.00</t>
+  </si>
+  <si>
     <t>SONACOMS</t>
   </si>
   <si>
     <t>2,26,780.25</t>
   </si>
   <si>
-    <t>2,36,965.50</t>
+    <t>2,42,736.75</t>
+  </si>
+  <si>
+    <t>WELCORP</t>
+  </si>
+  <si>
+    <t>NIFTYBEES</t>
+  </si>
+  <si>
+    <t>NETWEB</t>
+  </si>
+  <si>
+    <t>NLCINDIA</t>
+  </si>
+  <si>
+    <t>ELGIEQUIP</t>
+  </si>
+  <si>
+    <t>1,35,467.90</t>
+  </si>
+  <si>
+    <t>1,48,408.75</t>
+  </si>
+  <si>
+    <t>KENNAMET</t>
+  </si>
+  <si>
+    <t>1,02,884.40</t>
+  </si>
+  <si>
+    <t>3.May'26 Must buy</t>
+  </si>
+  <si>
+    <t>KAMDHENU</t>
+  </si>
+  <si>
+    <t>RAMCOSYS</t>
+  </si>
+  <si>
+    <t>MENONBE</t>
+  </si>
+  <si>
+    <t>THERMAX</t>
+  </si>
+  <si>
+    <t>1,32,916.50</t>
+  </si>
+  <si>
+    <t>1,40,329.50</t>
+  </si>
+  <si>
+    <t>RATEGAIN</t>
+  </si>
+  <si>
+    <t>GMDCLTD</t>
+  </si>
+  <si>
+    <t>ENRIN</t>
+  </si>
+  <si>
+    <t>SKFINDUS</t>
+  </si>
+  <si>
+    <t>INDUSTOWER</t>
+  </si>
+  <si>
+    <t>LAXMIDENTL</t>
+  </si>
+  <si>
+    <t>TRIVENI</t>
+  </si>
+  <si>
+    <t>SCI</t>
+  </si>
+  <si>
+    <t>RKSWAMY</t>
+  </si>
+  <si>
+    <t>ASHIANA</t>
+  </si>
+  <si>
+    <t>ENTERO</t>
+  </si>
+  <si>
+    <t>HEG</t>
+  </si>
+  <si>
+    <t>CYIENTDLM</t>
+  </si>
+  <si>
+    <t>1,14,647.15</t>
+  </si>
+  <si>
+    <t>1,14,004.20</t>
+  </si>
+  <si>
+    <t>PFC</t>
+  </si>
+  <si>
+    <t>CARBORUNIV</t>
+  </si>
+  <si>
+    <t>TREL</t>
+  </si>
+  <si>
+    <t>SJVN</t>
+  </si>
+  <si>
+    <t>1,09,462.55</t>
+  </si>
+  <si>
+    <t>1,07,633.55</t>
+  </si>
+  <si>
+    <t>GIPCL</t>
+  </si>
+  <si>
+    <t>SIEMENS</t>
+  </si>
+  <si>
+    <t>1,18,257.30</t>
+  </si>
+  <si>
+    <t>1,15,345.60</t>
+  </si>
+  <si>
+    <t>BLUEJET</t>
+  </si>
+  <si>
+    <t>INGERRAND</t>
+  </si>
+  <si>
+    <t>1,55,891.70</t>
+  </si>
+  <si>
+    <t>1,51,675.20</t>
+  </si>
+  <si>
+    <t>INDGN</t>
+  </si>
+  <si>
+    <t>POWERICA</t>
+  </si>
+  <si>
+    <t>ARE&amp;M</t>
+  </si>
+  <si>
+    <t>SCODATUBES</t>
+  </si>
+  <si>
+    <t>NESCO</t>
+  </si>
+  <si>
+    <t>EIMCOELECO</t>
   </si>
   <si>
     <t>3MINDIA</t>
@@ -154,157 +424,7 @@
     <t>1,99,812.35</t>
   </si>
   <si>
-    <t>1,86,990.00</t>
-  </si>
-  <si>
-    <t>MTARTECH</t>
-  </si>
-  <si>
-    <t>1,63,685.60</t>
-  </si>
-  <si>
-    <t>1,24,297.30</t>
-  </si>
-  <si>
-    <t>SANSERA</t>
-  </si>
-  <si>
-    <t>1,60,104.00</t>
-  </si>
-  <si>
-    <t>DEEDEV-T</t>
-  </si>
-  <si>
-    <t>1,59,489.75</t>
-  </si>
-  <si>
-    <t>ASTERDM</t>
-  </si>
-  <si>
-    <t>1,48,916.25</t>
-  </si>
-  <si>
-    <t>TRITURBINE</t>
-  </si>
-  <si>
-    <t>1,26,763.15</t>
-  </si>
-  <si>
-    <t>1,47,361.00</t>
-  </si>
-  <si>
-    <t>ELGIEQUIP</t>
-  </si>
-  <si>
-    <t>1,35,467.90</t>
-  </si>
-  <si>
-    <t>1,44,795.00</t>
-  </si>
-  <si>
-    <t>INGERRAND</t>
-  </si>
-  <si>
-    <t>1,55,891.70</t>
-  </si>
-  <si>
-    <t>1,44,036.00</t>
-  </si>
-  <si>
-    <t>ASTRAMICRO</t>
-  </si>
-  <si>
-    <t>1,41,026.30</t>
-  </si>
-  <si>
-    <t>1,18,328.60</t>
-  </si>
-  <si>
-    <t>THERMAX</t>
-  </si>
-  <si>
-    <t>1,32,916.50</t>
-  </si>
-  <si>
-    <t>1,37,139.00</t>
-  </si>
-  <si>
-    <t>INOXINDIA</t>
-  </si>
-  <si>
-    <t>1,34,962.40</t>
-  </si>
-  <si>
-    <t>POWERINDIA</t>
-  </si>
-  <si>
-    <t>1,33,000.00</t>
-  </si>
-  <si>
-    <t>1,24,216.35</t>
-  </si>
-  <si>
-    <t>NEPHROPLUS</t>
-  </si>
-  <si>
-    <t>1,23,213.20</t>
-  </si>
-  <si>
-    <t>SIEMENS</t>
-  </si>
-  <si>
-    <t>1,18,257.30</t>
-  </si>
-  <si>
-    <t>1,12,704.00</t>
-  </si>
-  <si>
-    <t>CYIENTDLM</t>
-  </si>
-  <si>
-    <t>1,14,647.15</t>
-  </si>
-  <si>
-    <t>1,08,319.05</t>
-  </si>
-  <si>
-    <t>JNKINDIA</t>
-  </si>
-  <si>
-    <t>1,05,750.00</t>
-  </si>
-  <si>
-    <t>SJVN</t>
-  </si>
-  <si>
-    <t>1,09,462.55</t>
-  </si>
-  <si>
-    <t>1,02,989.50</t>
-  </si>
-  <si>
-    <t>3.May'26 Must buy</t>
-  </si>
-  <si>
-    <t>NEULANDLAB</t>
-  </si>
-  <si>
-    <t>1,01,260.20</t>
-  </si>
-  <si>
-    <t>KENNAMET</t>
-  </si>
-  <si>
-    <t>TRIVENI</t>
-  </si>
-  <si>
-    <t>GALAPREC</t>
-  </si>
-  <si>
-    <t>KAMDHENU</t>
-  </si>
-  <si>
-    <t>MODISONLTD-T</t>
+    <t>1,90,212.00</t>
   </si>
   <si>
     <t>ISGEC</t>
@@ -313,358 +433,232 @@
     <t>1,02,322.55</t>
   </si>
   <si>
-    <t>AVANTEL</t>
-  </si>
-  <si>
-    <t>SOUTHWEST</t>
-  </si>
-  <si>
-    <t>SASKEN</t>
-  </si>
-  <si>
-    <t>HAPPYFORGE</t>
-  </si>
-  <si>
-    <t>NIFTYBEES</t>
-  </si>
-  <si>
-    <t>MENONBE</t>
-  </si>
-  <si>
-    <t>PFC</t>
-  </si>
-  <si>
-    <t>HBLENGINE</t>
-  </si>
-  <si>
-    <t>ENRIN</t>
-  </si>
-  <si>
-    <t>WELCORP</t>
-  </si>
-  <si>
-    <t>INDGN</t>
-  </si>
-  <si>
-    <t>ARE&amp;M</t>
-  </si>
-  <si>
-    <t>SKFINDUS</t>
+    <t>SALZERELEC</t>
+  </si>
+  <si>
+    <t>RPTECH</t>
+  </si>
+  <si>
+    <t>UNIVCABLES</t>
+  </si>
+  <si>
+    <t>INCAP-X</t>
+  </si>
+  <si>
+    <t>DATAPATTNS</t>
+  </si>
+  <si>
+    <t>SHILPAMED</t>
+  </si>
+  <si>
+    <t>FREDUN-X</t>
+  </si>
+  <si>
+    <t>GESHIP</t>
+  </si>
+  <si>
+    <t>TEJASNET</t>
+  </si>
+  <si>
+    <t>AVALON</t>
+  </si>
+  <si>
+    <t>AFFLE</t>
+  </si>
+  <si>
+    <t>RAYMOND</t>
+  </si>
+  <si>
+    <t>PTC</t>
+  </si>
+  <si>
+    <t>MOSCHIP</t>
+  </si>
+  <si>
+    <t>BOROSCI</t>
+  </si>
+  <si>
+    <t>DIFFNKG</t>
+  </si>
+  <si>
+    <t>GRAPHITE</t>
+  </si>
+  <si>
+    <t>GMRAIRPORT</t>
+  </si>
+  <si>
+    <t>ANURAS</t>
+  </si>
+  <si>
+    <t>TATACOMM</t>
+  </si>
+  <si>
+    <t>SUVEN</t>
+  </si>
+  <si>
+    <t>BIOCON</t>
+  </si>
+  <si>
+    <t>TVSELECT</t>
+  </si>
+  <si>
+    <t>KIRLPNU</t>
+  </si>
+  <si>
+    <t>GRINDWELL</t>
+  </si>
+  <si>
+    <t>WOCKPHARMA</t>
+  </si>
+  <si>
+    <t>STALLION</t>
+  </si>
+  <si>
+    <t>RAILTEL</t>
+  </si>
+  <si>
+    <t>GREAVESCOT</t>
+  </si>
+  <si>
+    <t>FRACTAL</t>
+  </si>
+  <si>
+    <t>HONAUT</t>
   </si>
   <si>
     <t>DLINKINDIA</t>
   </si>
   <si>
-    <t>NLCINDIA</t>
-  </si>
-  <si>
-    <t>RIR</t>
-  </si>
-  <si>
-    <t>SCODATUBES</t>
-  </si>
-  <si>
-    <t>NESCO</t>
-  </si>
-  <si>
-    <t>HLEGLAS</t>
-  </si>
-  <si>
-    <t>SALZERELEC</t>
-  </si>
-  <si>
-    <t>RUBICON</t>
-  </si>
-  <si>
-    <t>GIPCL</t>
-  </si>
-  <si>
-    <t>HEG</t>
-  </si>
-  <si>
-    <t>ASHIANA</t>
-  </si>
-  <si>
-    <t>BLUEJET</t>
-  </si>
-  <si>
-    <t>POWERICA</t>
-  </si>
-  <si>
-    <t>RKSWAMY</t>
-  </si>
-  <si>
-    <t>INDUSTOWER</t>
-  </si>
-  <si>
-    <t>SCI</t>
-  </si>
-  <si>
-    <t>TREL</t>
-  </si>
-  <si>
-    <t>RATEGAIN</t>
-  </si>
-  <si>
-    <t>RAMCOSYS</t>
-  </si>
-  <si>
-    <t>EIMCOELECO</t>
-  </si>
-  <si>
-    <t>CARBORUNIV</t>
-  </si>
-  <si>
-    <t>ENTERO</t>
-  </si>
-  <si>
-    <t>SHREEJISPG</t>
-  </si>
-  <si>
-    <t>GMDCLTD</t>
-  </si>
-  <si>
-    <t>TEJASNET</t>
-  </si>
-  <si>
-    <t>NETWEB</t>
-  </si>
-  <si>
-    <t>STALLION</t>
-  </si>
-  <si>
-    <t>RPTECH</t>
-  </si>
-  <si>
     <t>SIGNPOST</t>
   </si>
   <si>
-    <t>GRINDWELL</t>
-  </si>
-  <si>
-    <t>HONAUT</t>
+    <t>USHAMART</t>
+  </si>
+  <si>
+    <t>MSTCLTD</t>
+  </si>
+  <si>
+    <t>QUESS</t>
+  </si>
+  <si>
+    <t>MON100-E</t>
+  </si>
+  <si>
+    <t>LAKSELEC-X</t>
+  </si>
+  <si>
+    <t>BOROLTD</t>
+  </si>
+  <si>
+    <t>REDINGTON</t>
+  </si>
+  <si>
+    <t>VIYASH</t>
+  </si>
+  <si>
+    <t>ORIENTHOT</t>
+  </si>
+  <si>
+    <t>PITTIENG</t>
   </si>
   <si>
     <t>YATHARTH</t>
   </si>
   <si>
-    <t>BOROSCI</t>
-  </si>
-  <si>
-    <t>RAYMOND</t>
+    <t>ABLBL</t>
+  </si>
+  <si>
+    <t>GAUDIUMIVF-T</t>
+  </si>
+  <si>
+    <t>TEGA</t>
+  </si>
+  <si>
+    <t>ECOSMOBLTY-T</t>
+  </si>
+  <si>
+    <t>EIHOTEL</t>
+  </si>
+  <si>
+    <t>RAYMONDREL</t>
+  </si>
+  <si>
+    <t>ELDEHSG</t>
+  </si>
+  <si>
+    <t>KPITTECH</t>
+  </si>
+  <si>
+    <t>MMP</t>
+  </si>
+  <si>
+    <t>EMBDL</t>
+  </si>
+  <si>
+    <t>SKFINDIA</t>
+  </si>
+  <si>
+    <t>CESC</t>
+  </si>
+  <si>
+    <t>NIITLTD</t>
+  </si>
+  <si>
+    <t>INTERARCH</t>
+  </si>
+  <si>
+    <t>URBANCO</t>
+  </si>
+  <si>
+    <t>RUSTOMJEE</t>
+  </si>
+  <si>
+    <t>BBL</t>
+  </si>
+  <si>
+    <t>VSTTILLERS</t>
+  </si>
+  <si>
+    <t>ASALCBR</t>
+  </si>
+  <si>
+    <t>CAPACITE</t>
+  </si>
+  <si>
+    <t>ARIS</t>
+  </si>
+  <si>
+    <t>CMSINFO</t>
+  </si>
+  <si>
+    <t>GULFOILLUB</t>
+  </si>
+  <si>
+    <t>PROTEAN</t>
+  </si>
+  <si>
+    <t>SHANKARA-T</t>
   </si>
   <si>
     <t>MAPMYINDIA</t>
   </si>
   <si>
-    <t>UNIVCABLES</t>
+    <t>OMINFRAL</t>
+  </si>
+  <si>
+    <t>LANDMARK</t>
+  </si>
+  <si>
+    <t>WHIRLPOOL</t>
+  </si>
+  <si>
+    <t>LATENTVIEW</t>
+  </si>
+  <si>
+    <t>UNIECOM</t>
   </si>
   <si>
     <t>VASCONEQ-T</t>
-  </si>
-  <si>
-    <t>PROTEAN</t>
-  </si>
-  <si>
-    <t>GMRAIRPORT</t>
-  </si>
-  <si>
-    <t>URBANCO</t>
-  </si>
-  <si>
-    <t>FRACTAL</t>
-  </si>
-  <si>
-    <t>GESHIP</t>
-  </si>
-  <si>
-    <t>BIOCON</t>
-  </si>
-  <si>
-    <t>LAXMIDENTL</t>
-  </si>
-  <si>
-    <t>GRAPHITE</t>
-  </si>
-  <si>
-    <t>SHILPAMED</t>
-  </si>
-  <si>
-    <t>ANURAS</t>
-  </si>
-  <si>
-    <t>SHANKARA-T</t>
-  </si>
-  <si>
-    <t>LANDMARK</t>
-  </si>
-  <si>
-    <t>KIRLPNU</t>
-  </si>
-  <si>
-    <t>ECOSMOBLTY-T</t>
-  </si>
-  <si>
-    <t>DIFFNKG</t>
-  </si>
-  <si>
-    <t>INCAP-X</t>
-  </si>
-  <si>
-    <t>PTC</t>
-  </si>
-  <si>
-    <t>AVALON</t>
-  </si>
-  <si>
-    <t>DATAPATTNS</t>
-  </si>
-  <si>
-    <t>FREDUN-X</t>
-  </si>
-  <si>
-    <t>LATENTVIEW</t>
-  </si>
-  <si>
-    <t>NIITLTD</t>
-  </si>
-  <si>
-    <t>CMSINFO</t>
-  </si>
-  <si>
-    <t>KSB</t>
-  </si>
-  <si>
-    <t>CLEANMAX</t>
-  </si>
-  <si>
-    <t>GULFOILLUB</t>
-  </si>
-  <si>
-    <t>BBL</t>
-  </si>
-  <si>
-    <t>PITTIENG</t>
-  </si>
-  <si>
-    <t>CESC</t>
-  </si>
-  <si>
-    <t>MOSCHIP</t>
-  </si>
-  <si>
-    <t>MMP</t>
-  </si>
-  <si>
-    <t>RAYMONDREL</t>
-  </si>
-  <si>
-    <t>OMINFRAL</t>
-  </si>
-  <si>
-    <t>WHIRLPOOL</t>
-  </si>
-  <si>
-    <t>RUSTOMJEE</t>
-  </si>
-  <si>
-    <t>INTERARCH</t>
-  </si>
-  <si>
-    <t>CAPACITE</t>
-  </si>
-  <si>
-    <t>RAILTEL</t>
-  </si>
-  <si>
-    <t>AMBER</t>
-  </si>
-  <si>
-    <t>AFFLE</t>
-  </si>
-  <si>
-    <t>SKFINDIA</t>
-  </si>
-  <si>
-    <t>VSTTILLERS</t>
-  </si>
-  <si>
-    <t>ASALCBR</t>
-  </si>
-  <si>
-    <t>QUESS</t>
-  </si>
-  <si>
-    <t>GREAVESCOT</t>
-  </si>
-  <si>
-    <t>ELDEHSG</t>
-  </si>
-  <si>
-    <t>ARIS</t>
-  </si>
-  <si>
-    <t>AEROENTER</t>
-  </si>
-  <si>
-    <t>IFGLEXPOR</t>
-  </si>
-  <si>
-    <t>TVSELECT</t>
-  </si>
-  <si>
-    <t>EMBDL</t>
-  </si>
-  <si>
-    <t>TATACOMM</t>
-  </si>
-  <si>
-    <t>UNIECOM</t>
-  </si>
-  <si>
-    <t>SUVEN</t>
-  </si>
-  <si>
-    <t>WOCKPHARMA</t>
-  </si>
-  <si>
-    <t>TEGA</t>
-  </si>
-  <si>
-    <t>EIHOTEL</t>
-  </si>
-  <si>
-    <t>LAKSELEC-X</t>
-  </si>
-  <si>
-    <t>KPITTECH</t>
-  </si>
-  <si>
-    <t>MSTCLTD</t>
-  </si>
-  <si>
-    <t>USHAMART</t>
-  </si>
-  <si>
-    <t>MON100-E</t>
-  </si>
-  <si>
-    <t>VIYASH</t>
-  </si>
-  <si>
-    <t>REDINGTON</t>
-  </si>
-  <si>
-    <t>BOROLTD</t>
-  </si>
-  <si>
-    <t>ORIENTHOT</t>
-  </si>
-  <si>
-    <t>GAUDIUMIVF-T</t>
-  </si>
-  <si>
-    <t>ABLBL</t>
   </si>
 </sst>
 </file>
@@ -754,10 +748,10 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
@@ -786,6 +780,9 @@
     <xf borderId="1" fillId="2" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="2" fontId="5" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
@@ -793,9 +790,6 @@
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="5" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -1073,7 +1067,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="5">
-        <v>191.72</v>
+        <v>192.04</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>13</v>
@@ -1082,7 +1076,7 @@
         <v>14</v>
       </c>
       <c r="I2" s="8">
-        <v>2.8093</v>
+        <v>2.8157</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>15</v>
@@ -1108,7 +1102,7 @@
         <v>19</v>
       </c>
       <c r="F3" s="6">
-        <v>1858.5</v>
+        <v>1893.1</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>20</v>
@@ -1117,7 +1111,7 @@
         <v>21</v>
       </c>
       <c r="I3" s="8">
-        <v>2.7394</v>
+        <v>2.809</v>
       </c>
       <c r="J3" s="9" t="s">
         <v>15</v>
@@ -1143,7 +1137,7 @@
         <v>23</v>
       </c>
       <c r="F4" s="5">
-        <v>408.55</v>
+        <v>469.35</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>24</v>
@@ -1152,7 +1146,7 @@
         <v>25</v>
       </c>
       <c r="I4" s="8">
-        <v>1.1824</v>
+        <v>1.5072</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>26</v>
@@ -1169,16 +1163,16 @@
         <v>29</v>
       </c>
       <c r="C5" s="5">
-        <v>609.0</v>
+        <v>289.0</v>
       </c>
       <c r="D5" s="6">
-        <v>314.21</v>
+        <v>430.8</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>30</v>
       </c>
       <c r="F5" s="6">
-        <v>626.0</v>
+        <v>1296.8</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>31</v>
@@ -1187,7 +1181,7 @@
         <v>32</v>
       </c>
       <c r="I5" s="8">
-        <v>0.9923</v>
+        <v>2.0102</v>
       </c>
       <c r="J5" s="9" t="s">
         <v>15</v>
@@ -1204,16 +1198,16 @@
         <v>33</v>
       </c>
       <c r="C6" s="5">
-        <v>289.0</v>
+        <v>609.0</v>
       </c>
       <c r="D6" s="6">
-        <v>430.8</v>
+        <v>314.21</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
       </c>
       <c r="F6" s="6">
-        <v>1235.6</v>
+        <v>637.75</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>35</v>
@@ -1222,7 +1216,7 @@
         <v>36</v>
       </c>
       <c r="I6" s="8">
-        <v>1.8681</v>
+        <v>1.0297</v>
       </c>
       <c r="J6" s="9" t="s">
         <v>15</v>
@@ -1239,206 +1233,206 @@
         <v>37</v>
       </c>
       <c r="C7" s="5">
-        <v>896.0</v>
+        <v>4.0</v>
       </c>
       <c r="D7" s="6">
-        <v>158.81</v>
-      </c>
-      <c r="E7" s="6" t="s">
+        <v>2195.91</v>
+      </c>
+      <c r="E7" s="6">
+        <v>8783.65</v>
+      </c>
+      <c r="F7" s="6">
+        <v>34445.0</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="5">
-        <v>273.25</v>
-      </c>
-      <c r="G7" s="5" t="s">
+      <c r="H7" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="7" t="s">
-        <v>40</v>
-      </c>
       <c r="I7" s="8">
-        <v>0.7206</v>
+        <v>14.686</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="5">
+        <v>101.0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>224.73</v>
+      </c>
+      <c r="E8" s="6">
+        <v>22697.7</v>
+      </c>
+      <c r="F8" s="6">
+        <v>1467.2</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="5">
-        <v>405.0</v>
-      </c>
-      <c r="D8" s="5">
-        <v>559.95</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="6">
-        <v>585.1</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" s="11">
-        <v>10185.25</v>
-      </c>
       <c r="I8" s="8">
-        <v>0.0449</v>
+        <v>5.5287</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="5">
+        <v>255.0</v>
+      </c>
+      <c r="D9" s="6">
+        <v>261.86</v>
+      </c>
+      <c r="E9" s="6">
+        <v>66773.95</v>
+      </c>
+      <c r="F9" s="6">
+        <v>689.5</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="5">
-        <v>6.0</v>
-      </c>
-      <c r="D9" s="6">
-        <v>33302.06</v>
-      </c>
-      <c r="E9" s="6" t="s">
+      <c r="I9" s="8">
+        <v>1.6331</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="6">
-        <v>31165.0</v>
-      </c>
-      <c r="G9" s="5" t="s">
+      <c r="C10" s="5">
+        <v>896.0</v>
+      </c>
+      <c r="D10" s="6">
+        <v>158.81</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H9" s="12">
-        <v>-12822.35</v>
-      </c>
-      <c r="I9" s="13">
-        <v>-0.0642</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" s="9" t="s">
+      <c r="F10" s="6">
+        <v>274.25</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10" s="8">
+        <v>0.7269</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="L10" s="9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="5">
-        <v>26.0</v>
-      </c>
-      <c r="D10" s="6">
-        <v>1514.93</v>
-      </c>
-      <c r="E10" s="6">
-        <v>39388.3</v>
-      </c>
-      <c r="F10" s="6">
-        <v>6295.6</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="I10" s="8">
-        <v>3.1557</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
     <row r="11">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="10" t="s">
         <v>51</v>
       </c>
       <c r="C11" s="5">
-        <v>56.0</v>
+        <v>18.0</v>
       </c>
       <c r="D11" s="6">
-        <v>1524.46</v>
+        <v>1603.74</v>
       </c>
       <c r="E11" s="6">
-        <v>85369.7</v>
+        <v>28867.35</v>
       </c>
       <c r="F11" s="6">
-        <v>2859.0</v>
+        <v>7076.0</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>52</v>
       </c>
       <c r="H11" s="11">
-        <v>74734.3</v>
+        <v>98500.65</v>
       </c>
       <c r="I11" s="8">
-        <v>0.8754</v>
+        <v>3.4122</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C12" s="5">
-        <v>255.0</v>
+        <v>183.0</v>
       </c>
       <c r="D12" s="6">
-        <v>261.86</v>
+        <v>283.78</v>
       </c>
       <c r="E12" s="6">
-        <v>66773.95</v>
+        <v>51931.5</v>
       </c>
       <c r="F12" s="6">
-        <v>625.45</v>
+        <v>818.8</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>54</v>
       </c>
       <c r="H12" s="11">
-        <v>92715.8</v>
+        <v>97908.9</v>
       </c>
       <c r="I12" s="8">
-        <v>1.3885</v>
+        <v>1.8853</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L12" s="9" t="s">
         <v>17</v>
@@ -1449,25 +1443,25 @@
         <v>55</v>
       </c>
       <c r="C13" s="5">
-        <v>183.0</v>
+        <v>6.0</v>
       </c>
       <c r="D13" s="6">
-        <v>283.78</v>
+        <v>1031.85</v>
       </c>
       <c r="E13" s="6">
-        <v>51931.5</v>
+        <v>6191.1</v>
       </c>
       <c r="F13" s="6">
-        <v>813.75</v>
+        <v>17049.0</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>56</v>
       </c>
       <c r="H13" s="11">
-        <v>96984.75</v>
+        <v>96102.9</v>
       </c>
       <c r="I13" s="8">
-        <v>1.8676</v>
+        <v>15.5228</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>15</v>
@@ -1484,60 +1478,60 @@
         <v>57</v>
       </c>
       <c r="C14" s="5">
-        <v>230.0</v>
+        <v>540.0</v>
       </c>
       <c r="D14" s="5">
-        <v>551.14</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>58</v>
+        <v>13.39</v>
+      </c>
+      <c r="E14" s="6">
+        <v>7229.6</v>
       </c>
       <c r="F14" s="6">
-        <v>640.7</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>59</v>
+        <v>168.41</v>
+      </c>
+      <c r="G14" s="6">
+        <v>90941.4</v>
       </c>
       <c r="H14" s="11">
-        <v>20597.85</v>
+        <v>83711.8</v>
       </c>
       <c r="I14" s="8">
-        <v>0.1625</v>
+        <v>11.579</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C15" s="5">
-        <v>245.0</v>
-      </c>
-      <c r="D15" s="5">
-        <v>552.93</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>61</v>
+        <v>56.0</v>
+      </c>
+      <c r="D15" s="6">
+        <v>1524.46</v>
+      </c>
+      <c r="E15" s="6">
+        <v>85369.7</v>
       </c>
       <c r="F15" s="6">
-        <v>591.0</v>
+        <v>2920.25</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H15" s="11">
-        <v>9327.1</v>
+        <v>78164.3</v>
       </c>
       <c r="I15" s="8">
-        <v>0.0689</v>
+        <v>0.9156</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>26</v>
@@ -1550,99 +1544,99 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="10" t="s">
-        <v>63</v>
+      <c r="B16" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="C16" s="5">
-        <v>36.0</v>
+        <v>100.0</v>
       </c>
       <c r="D16" s="6">
-        <v>4330.32</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>64</v>
+        <v>290.95</v>
+      </c>
+      <c r="E16" s="6">
+        <v>29095.0</v>
       </c>
       <c r="F16" s="6">
-        <v>4001.0</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="H16" s="12">
-        <v>-11855.7</v>
-      </c>
-      <c r="I16" s="13">
-        <v>-0.0761</v>
+        <v>800.2</v>
+      </c>
+      <c r="G16" s="6">
+        <v>80020.0</v>
+      </c>
+      <c r="H16" s="11">
+        <v>50925.0</v>
+      </c>
+      <c r="I16" s="8">
+        <v>1.7503</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C17" s="5">
-        <v>101.0</v>
+        <v>225.0</v>
       </c>
       <c r="D17" s="6">
-        <v>224.73</v>
+        <v>300.93</v>
       </c>
       <c r="E17" s="6">
-        <v>22697.7</v>
+        <v>67709.81</v>
       </c>
       <c r="F17" s="6">
-        <v>1396.3</v>
+        <v>502.25</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="H17" s="11">
+        <v>45296.44</v>
       </c>
       <c r="I17" s="8">
-        <v>5.2132</v>
+        <v>0.669</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C18" s="5">
-        <v>30.0</v>
+        <v>83.0</v>
       </c>
       <c r="D18" s="4">
-        <v>4430.55</v>
+        <v>1296.59</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F18" s="6">
-        <v>4571.3</v>
+        <v>1821.6</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H18" s="11">
-        <v>4222.5</v>
+        <v>43575.6</v>
       </c>
       <c r="I18" s="8">
-        <v>0.0318</v>
+        <v>0.4049</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>26</v>
@@ -1656,63 +1650,63 @@
     </row>
     <row r="19">
       <c r="B19" s="3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C19" s="5">
-        <v>73.0</v>
+        <v>269.0</v>
       </c>
       <c r="D19" s="6">
-        <v>1225.03</v>
+        <v>171.27</v>
       </c>
       <c r="E19" s="6">
-        <v>89427.2</v>
+        <v>46072.27</v>
       </c>
       <c r="F19" s="6">
-        <v>1848.8</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>73</v>
+        <v>294.2</v>
+      </c>
+      <c r="G19" s="6">
+        <v>79139.8</v>
       </c>
       <c r="H19" s="11">
-        <v>45535.2</v>
+        <v>33067.53</v>
       </c>
       <c r="I19" s="8">
-        <v>0.5092</v>
+        <v>0.7177</v>
       </c>
       <c r="J19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="10" t="s">
-        <v>74</v>
+      <c r="B20" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="C20" s="5">
-        <v>4.0</v>
+        <v>401.0</v>
       </c>
       <c r="D20" s="6">
-        <v>2195.91</v>
+        <v>91.09</v>
       </c>
       <c r="E20" s="6">
-        <v>8783.65</v>
+        <v>36527.75</v>
       </c>
       <c r="F20" s="6">
-        <v>33250.0</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>76</v>
+        <v>170.5</v>
+      </c>
+      <c r="G20" s="6">
+        <v>68370.5</v>
+      </c>
+      <c r="H20" s="11">
+        <v>31842.75</v>
       </c>
       <c r="I20" s="8">
-        <v>14.1418</v>
+        <v>0.8717</v>
       </c>
       <c r="J20" s="9" t="s">
         <v>15</v>
@@ -1726,28 +1720,28 @@
     </row>
     <row r="21">
       <c r="B21" s="3" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C21" s="5">
-        <v>164.0</v>
+        <v>432.33</v>
       </c>
       <c r="D21" s="6">
-        <v>606.55</v>
+        <v>92.52</v>
       </c>
       <c r="E21" s="6">
-        <v>99474.25</v>
+        <v>39998.01</v>
       </c>
       <c r="F21" s="6">
-        <v>751.3</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>78</v>
+        <v>165.52</v>
+      </c>
+      <c r="G21" s="6">
+        <v>71559.78</v>
       </c>
       <c r="H21" s="11">
-        <v>23738.95</v>
+        <v>31561.77</v>
       </c>
       <c r="I21" s="8">
-        <v>0.2386</v>
+        <v>0.7891</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>26</v>
@@ -1761,174 +1755,174 @@
     </row>
     <row r="22">
       <c r="B22" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C22" s="5">
-        <v>32.0</v>
+        <v>350.0</v>
       </c>
       <c r="D22" s="6">
-        <v>3695.54</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>80</v>
+        <v>165.99</v>
+      </c>
+      <c r="E22" s="6">
+        <v>58095.38</v>
       </c>
       <c r="F22" s="6">
-        <v>3522.0</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="H22" s="14">
-        <v>-5553.3</v>
-      </c>
-      <c r="I22" s="13">
-        <v>-0.047</v>
+        <v>248.1</v>
+      </c>
+      <c r="G22" s="6">
+        <v>86835.0</v>
+      </c>
+      <c r="H22" s="12">
+        <v>28739.62</v>
+      </c>
+      <c r="I22" s="8">
+        <v>0.4947</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="3" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C23" s="4">
-        <v>251.0</v>
+        <v>230.0</v>
       </c>
       <c r="D23" s="6">
-        <v>456.76</v>
+        <v>551.14</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F23" s="6">
-        <v>431.55</v>
+        <v>667.65</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="H23" s="12">
-        <v>-6328.1</v>
-      </c>
-      <c r="I23" s="13">
-        <v>-0.0552</v>
+        <v>72</v>
+      </c>
+      <c r="H23" s="11">
+        <v>26796.35</v>
+      </c>
+      <c r="I23" s="8">
+        <v>0.2114</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="3" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C24" s="5">
-        <v>225.0</v>
+        <v>43.0</v>
       </c>
       <c r="D24" s="6">
-        <v>300.93</v>
+        <v>722.52</v>
       </c>
       <c r="E24" s="6">
-        <v>67709.81</v>
+        <v>31068.3</v>
       </c>
       <c r="F24" s="6">
-        <v>470.0</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>86</v>
+        <v>1277.4</v>
+      </c>
+      <c r="G24" s="6">
+        <v>54928.2</v>
       </c>
       <c r="H24" s="11">
-        <v>38040.19</v>
+        <v>23859.9</v>
       </c>
       <c r="I24" s="8">
-        <v>0.5618</v>
+        <v>0.768</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="3" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="C25" s="4">
-        <v>1465.0</v>
+        <v>520.788</v>
       </c>
       <c r="D25" s="6">
-        <v>74.72</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>88</v>
+        <v>38.4</v>
+      </c>
+      <c r="E25" s="6">
+        <v>19998.99</v>
       </c>
       <c r="F25" s="6">
-        <v>70.3</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="H25" s="12">
-        <v>-6473.05</v>
-      </c>
-      <c r="I25" s="13">
-        <v>-0.0591</v>
+        <v>83.39</v>
+      </c>
+      <c r="G25" s="6">
+        <v>43429.5</v>
+      </c>
+      <c r="H25" s="11">
+        <v>23430.51</v>
+      </c>
+      <c r="I25" s="8">
+        <v>1.1716</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="10" t="s">
-        <v>91</v>
+      <c r="B26" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="C26" s="5">
-        <v>6.0</v>
+        <v>97.0</v>
       </c>
       <c r="D26" s="6">
-        <v>1031.85</v>
+        <v>768.77</v>
       </c>
       <c r="E26" s="6">
-        <v>6191.1</v>
+        <v>74571.2</v>
       </c>
       <c r="F26" s="6">
-        <v>16876.7</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>92</v>
+        <v>1004.5</v>
+      </c>
+      <c r="G26" s="6">
+        <v>97436.5</v>
       </c>
       <c r="H26" s="11">
-        <v>95069.1</v>
+        <v>22865.3</v>
       </c>
       <c r="I26" s="8">
-        <v>15.3558</v>
+        <v>0.3066</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="L26" s="9" t="s">
         <v>17</v>
@@ -1936,63 +1930,63 @@
     </row>
     <row r="27">
       <c r="B27" s="3" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="C27" s="5">
-        <v>36.0</v>
+        <v>94.0</v>
       </c>
       <c r="D27" s="6">
-        <v>2574.11</v>
+        <v>267.98</v>
       </c>
       <c r="E27" s="6">
-        <v>92668.05</v>
+        <v>25190.12</v>
       </c>
       <c r="F27" s="6">
-        <v>2754.6</v>
+        <v>488.15</v>
       </c>
       <c r="G27" s="6">
-        <v>99165.6</v>
+        <v>45886.1</v>
       </c>
       <c r="H27" s="11">
-        <v>6497.55</v>
+        <v>20695.98</v>
       </c>
       <c r="I27" s="8">
-        <v>0.0701</v>
+        <v>0.8216</v>
       </c>
       <c r="J27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="3" t="s">
-        <v>94</v>
+      <c r="B28" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="C28" s="5">
-        <v>246.0</v>
+        <v>41.0</v>
       </c>
       <c r="D28" s="6">
-        <v>384.17</v>
+        <v>1676.93</v>
       </c>
       <c r="E28" s="6">
-        <v>94506.1</v>
+        <v>68754.3</v>
       </c>
       <c r="F28" s="6">
-        <v>382.6</v>
+        <v>2167.4</v>
       </c>
       <c r="G28" s="6">
-        <v>94119.6</v>
-      </c>
-      <c r="H28" s="12">
-        <v>-386.5</v>
-      </c>
-      <c r="I28" s="13">
-        <v>-0.0041</v>
+        <v>88863.4</v>
+      </c>
+      <c r="H28" s="11">
+        <v>20109.1</v>
+      </c>
+      <c r="I28" s="8">
+        <v>0.2925</v>
       </c>
       <c r="J28" s="9" t="s">
         <v>26</v>
@@ -2006,28 +2000,28 @@
     </row>
     <row r="29">
       <c r="B29" s="3" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="C29" s="5">
-        <v>97.0</v>
+        <v>59.0</v>
       </c>
       <c r="D29" s="6">
-        <v>768.77</v>
+        <v>1056.13</v>
       </c>
       <c r="E29" s="6">
-        <v>74571.2</v>
+        <v>62311.85</v>
       </c>
       <c r="F29" s="6">
-        <v>920.8</v>
+        <v>1359.8</v>
       </c>
       <c r="G29" s="6">
-        <v>89317.6</v>
+        <v>80228.2</v>
       </c>
       <c r="H29" s="11">
-        <v>14746.4</v>
+        <v>17916.35</v>
       </c>
       <c r="I29" s="8">
-        <v>0.1977</v>
+        <v>0.2875</v>
       </c>
       <c r="J29" s="9" t="s">
         <v>26</v>
@@ -2040,29 +2034,29 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="3" t="s">
-        <v>96</v>
+      <c r="B30" s="10" t="s">
+        <v>78</v>
       </c>
       <c r="C30" s="4">
-        <v>3161.0</v>
+        <v>204.0</v>
       </c>
       <c r="D30" s="6">
-        <v>27.17</v>
-      </c>
-      <c r="E30" s="6">
-        <v>85878.13</v>
+        <v>633.76</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="F30" s="6">
-        <v>28.2</v>
-      </c>
-      <c r="G30" s="6">
-        <v>89140.2</v>
+        <v>715.75</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="H30" s="11">
-        <v>3262.07</v>
+        <v>16725.1</v>
       </c>
       <c r="I30" s="8">
-        <v>0.038</v>
+        <v>0.1294</v>
       </c>
       <c r="J30" s="9" t="s">
         <v>26</v>
@@ -2076,98 +2070,98 @@
     </row>
     <row r="31">
       <c r="B31" s="3" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="C31" s="5">
-        <v>269.0</v>
+        <v>405.0</v>
       </c>
       <c r="D31" s="6">
-        <v>171.27</v>
-      </c>
-      <c r="E31" s="6">
-        <v>46072.27</v>
+        <v>559.95</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="F31" s="6">
-        <v>317.0</v>
-      </c>
-      <c r="G31" s="6">
-        <v>85273.0</v>
-      </c>
-      <c r="H31" s="15">
-        <v>39200.73</v>
+        <v>599.35</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H31" s="12">
+        <v>15956.5</v>
       </c>
       <c r="I31" s="8">
-        <v>0.8509</v>
+        <v>0.0704</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="3" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C32" s="5">
-        <v>97.0</v>
+        <v>51.0</v>
       </c>
       <c r="D32" s="6">
-        <v>1054.87</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>99</v>
+        <v>1099.22</v>
+      </c>
+      <c r="E32" s="6">
+        <v>56060.4</v>
       </c>
       <c r="F32" s="6">
-        <v>873.7</v>
+        <v>1409.6</v>
       </c>
       <c r="G32" s="6">
-        <v>84748.9</v>
-      </c>
-      <c r="H32" s="12">
-        <v>-17573.65</v>
-      </c>
-      <c r="I32" s="13">
-        <v>-0.1717</v>
+        <v>71889.6</v>
+      </c>
+      <c r="H32" s="11">
+        <v>15829.2</v>
+      </c>
+      <c r="I32" s="8">
+        <v>0.2824</v>
       </c>
       <c r="J32" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K32" s="9" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="L32" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="3" t="s">
-        <v>100</v>
+      <c r="B33" s="10" t="s">
+        <v>85</v>
       </c>
       <c r="C33" s="5">
-        <v>540.0</v>
+        <v>300.0</v>
       </c>
       <c r="D33" s="6">
-        <v>13.39</v>
+        <v>220.39</v>
       </c>
       <c r="E33" s="6">
-        <v>7229.6</v>
+        <v>66117.0</v>
       </c>
       <c r="F33" s="6">
-        <v>156.9</v>
+        <v>271.21</v>
       </c>
       <c r="G33" s="6">
-        <v>84726.0</v>
+        <v>81363.0</v>
       </c>
       <c r="H33" s="11">
-        <v>77496.4</v>
+        <v>15246.0</v>
       </c>
       <c r="I33" s="8">
-        <v>10.7193</v>
+        <v>0.2306</v>
       </c>
       <c r="J33" s="9" t="s">
         <v>15</v>
@@ -2181,34 +2175,34 @@
     </row>
     <row r="34">
       <c r="B34" s="3" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="C34" s="5">
-        <v>350.0</v>
+        <v>9.0</v>
       </c>
       <c r="D34" s="6">
-        <v>165.99</v>
+        <v>3066.43</v>
       </c>
       <c r="E34" s="6">
-        <v>58095.38</v>
+        <v>27597.85</v>
       </c>
       <c r="F34" s="6">
-        <v>240.15</v>
+        <v>4643.8</v>
       </c>
       <c r="G34" s="6">
-        <v>84052.5</v>
+        <v>41794.2</v>
       </c>
       <c r="H34" s="11">
-        <v>25957.12</v>
+        <v>14196.35</v>
       </c>
       <c r="I34" s="8">
-        <v>0.4468</v>
+        <v>0.5144</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L34" s="9" t="s">
         <v>17</v>
@@ -2216,308 +2210,308 @@
     </row>
     <row r="35">
       <c r="B35" s="3" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="C35" s="5">
-        <v>41.0</v>
+        <v>215.0</v>
       </c>
       <c r="D35" s="6">
-        <v>1676.93</v>
+        <v>255.12</v>
       </c>
       <c r="E35" s="6">
-        <v>68754.3</v>
+        <v>54850.65</v>
       </c>
       <c r="F35" s="6">
-        <v>2042.0</v>
+        <v>319.1</v>
       </c>
       <c r="G35" s="6">
-        <v>83722.0</v>
+        <v>68606.5</v>
       </c>
       <c r="H35" s="11">
-        <v>14967.7</v>
+        <v>13755.85</v>
       </c>
       <c r="I35" s="8">
-        <v>0.2177</v>
+        <v>0.2508</v>
       </c>
       <c r="J35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L35" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="3" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="C36" s="5">
-        <v>59.0</v>
+        <v>245.0</v>
       </c>
       <c r="D36" s="6">
-        <v>1056.13</v>
-      </c>
-      <c r="E36" s="6">
-        <v>62311.85</v>
+        <v>552.93</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="F36" s="6">
-        <v>1348.2</v>
-      </c>
-      <c r="G36" s="6">
-        <v>79543.8</v>
+        <v>605.75</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="H36" s="11">
-        <v>17231.95</v>
+        <v>12940.85</v>
       </c>
       <c r="I36" s="8">
-        <v>0.2765</v>
+        <v>0.0955</v>
       </c>
       <c r="J36" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L36" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="10" t="s">
-        <v>104</v>
+      <c r="B37" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="C37" s="5">
-        <v>300.0</v>
+        <v>36.0</v>
       </c>
       <c r="D37" s="6">
-        <v>220.39</v>
+        <v>2574.11</v>
       </c>
       <c r="E37" s="6">
-        <v>66117.0</v>
+        <v>92668.05</v>
       </c>
       <c r="F37" s="6">
-        <v>262.44</v>
-      </c>
-      <c r="G37" s="6">
-        <v>78732.0</v>
+        <v>2857.9</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="H37" s="11">
-        <v>12615.0</v>
+        <v>10216.35</v>
       </c>
       <c r="I37" s="8">
-        <v>0.1908</v>
+        <v>0.1102</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K37" s="9" t="s">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="L37" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C38" s="5">
-        <v>464.0</v>
+        <v>94</v>
+      </c>
+      <c r="C38" s="4">
+        <v>3161.0</v>
       </c>
       <c r="D38" s="6">
-        <v>149.72</v>
+        <v>27.17</v>
       </c>
       <c r="E38" s="6">
-        <v>69468.13</v>
+        <v>85878.13</v>
       </c>
       <c r="F38" s="6">
-        <v>165.85</v>
+        <v>30.3</v>
       </c>
       <c r="G38" s="6">
-        <v>76954.4</v>
+        <v>95778.3</v>
       </c>
       <c r="H38" s="11">
-        <v>7486.27</v>
+        <v>9900.17</v>
       </c>
       <c r="I38" s="8">
-        <v>0.1078</v>
+        <v>0.1153</v>
       </c>
       <c r="J38" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="L38" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="3" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C39" s="5">
-        <v>184.0</v>
+        <v>86.0</v>
       </c>
       <c r="D39" s="6">
-        <v>431.44</v>
+        <v>458.8</v>
       </c>
       <c r="E39" s="6">
-        <v>79384.9</v>
+        <v>39456.85</v>
       </c>
       <c r="F39" s="6">
-        <v>413.5</v>
+        <v>570.0</v>
       </c>
       <c r="G39" s="6">
-        <v>76084.0</v>
-      </c>
-      <c r="H39" s="12">
-        <v>-3300.9</v>
-      </c>
-      <c r="I39" s="13">
-        <v>-0.0416</v>
+        <v>49020.0</v>
+      </c>
+      <c r="H39" s="11">
+        <v>9563.15</v>
+      </c>
+      <c r="I39" s="8">
+        <v>0.2424</v>
       </c>
       <c r="J39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L39" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="3" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C40" s="5">
-        <v>100.0</v>
+        <v>464.0</v>
       </c>
       <c r="D40" s="6">
-        <v>290.95</v>
+        <v>149.72</v>
       </c>
       <c r="E40" s="6">
-        <v>29095.0</v>
+        <v>69468.13</v>
       </c>
       <c r="F40" s="6">
-        <v>746.0</v>
+        <v>169.2</v>
       </c>
       <c r="G40" s="6">
-        <v>74600.0</v>
+        <v>78508.8</v>
       </c>
       <c r="H40" s="11">
-        <v>45505.0</v>
+        <v>9040.67</v>
       </c>
       <c r="I40" s="8">
-        <v>1.564</v>
+        <v>0.1301</v>
       </c>
       <c r="J40" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="L40" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="3" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="C41" s="5">
-        <v>21.0</v>
+        <v>30.0</v>
       </c>
       <c r="D41" s="6">
-        <v>3292.31</v>
-      </c>
-      <c r="E41" s="6">
-        <v>69138.6</v>
+        <v>4430.55</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>98</v>
       </c>
       <c r="F41" s="6">
-        <v>3409.6</v>
-      </c>
-      <c r="G41" s="6">
-        <v>71601.6</v>
+        <v>4677.65</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="H41" s="11">
-        <v>2463.0</v>
+        <v>7413.0</v>
       </c>
       <c r="I41" s="8">
-        <v>0.0356</v>
+        <v>0.0558</v>
       </c>
       <c r="J41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L41" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C42" s="5">
-        <v>51.0</v>
+        <v>63.0</v>
       </c>
       <c r="D42" s="6">
-        <v>1099.22</v>
+        <v>724.23</v>
       </c>
       <c r="E42" s="6">
-        <v>56060.4</v>
+        <v>45626.35</v>
       </c>
       <c r="F42" s="6">
-        <v>1388.05</v>
+        <v>835.75</v>
       </c>
       <c r="G42" s="6">
-        <v>70790.55</v>
-      </c>
-      <c r="H42" s="15">
-        <v>14730.15</v>
+        <v>52652.25</v>
+      </c>
+      <c r="H42" s="12">
+        <v>7025.9</v>
       </c>
       <c r="I42" s="8">
-        <v>0.2628</v>
+        <v>0.154</v>
       </c>
       <c r="J42" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L42" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="10" t="s">
-        <v>110</v>
+      <c r="B43" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="C43" s="5">
-        <v>139.0</v>
+        <v>72.0</v>
       </c>
       <c r="D43" s="6">
-        <v>545.81</v>
+        <v>529.68</v>
       </c>
       <c r="E43" s="6">
-        <v>75867.25</v>
+        <v>38136.95</v>
       </c>
       <c r="F43" s="6">
-        <v>506.75</v>
+        <v>619.0</v>
       </c>
       <c r="G43" s="6">
-        <v>70438.25</v>
-      </c>
-      <c r="H43" s="12">
-        <v>-5429.0</v>
-      </c>
-      <c r="I43" s="13">
-        <v>-0.0716</v>
+        <v>44568.0</v>
+      </c>
+      <c r="H43" s="11">
+        <v>6431.05</v>
+      </c>
+      <c r="I43" s="8">
+        <v>0.1686</v>
       </c>
       <c r="J43" s="9" t="s">
         <v>26</v>
@@ -2531,28 +2525,28 @@
     </row>
     <row r="44">
       <c r="B44" s="3" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C44" s="5">
-        <v>87.0</v>
+        <v>21.0</v>
       </c>
       <c r="D44" s="6">
-        <v>903.4</v>
+        <v>3292.31</v>
       </c>
       <c r="E44" s="6">
-        <v>78595.7</v>
+        <v>69138.6</v>
       </c>
       <c r="F44" s="6">
-        <v>796.3</v>
+        <v>3589.0</v>
       </c>
       <c r="G44" s="6">
-        <v>69278.1</v>
-      </c>
-      <c r="H44" s="12">
-        <v>-9317.6</v>
-      </c>
-      <c r="I44" s="13">
-        <v>-0.1186</v>
+        <v>75369.0</v>
+      </c>
+      <c r="H44" s="11">
+        <v>6230.4</v>
+      </c>
+      <c r="I44" s="8">
+        <v>0.0901</v>
       </c>
       <c r="J44" s="9" t="s">
         <v>26</v>
@@ -2566,7 +2560,7 @@
     </row>
     <row r="45">
       <c r="B45" s="3" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C45" s="5">
         <v>29.0</v>
@@ -2578,51 +2572,51 @@
         <v>68058.7</v>
       </c>
       <c r="F45" s="6">
-        <v>2379.3</v>
+        <v>2447.0</v>
       </c>
       <c r="G45" s="6">
-        <v>68999.7</v>
+        <v>70963.0</v>
       </c>
       <c r="H45" s="11">
-        <v>941.0</v>
+        <v>2904.3</v>
       </c>
       <c r="I45" s="8">
-        <v>0.0138</v>
+        <v>0.0427</v>
       </c>
       <c r="J45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="L45" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="3" t="s">
-        <v>113</v>
+      <c r="B46" s="10" t="s">
+        <v>104</v>
       </c>
       <c r="C46" s="5">
-        <v>140.0</v>
+        <v>120.0</v>
       </c>
       <c r="D46" s="6">
-        <v>473.17</v>
+        <v>401.67</v>
       </c>
       <c r="E46" s="6">
-        <v>66244.1</v>
+        <v>48200.4</v>
       </c>
       <c r="F46" s="6">
-        <v>490.9</v>
+        <v>423.0</v>
       </c>
       <c r="G46" s="6">
-        <v>68726.0</v>
+        <v>50760.0</v>
       </c>
       <c r="H46" s="11">
-        <v>2481.9</v>
+        <v>2559.6</v>
       </c>
       <c r="I46" s="8">
-        <v>0.0375</v>
+        <v>0.0531</v>
       </c>
       <c r="J46" s="9" t="s">
         <v>26</v>
@@ -2635,70 +2629,70 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="10" t="s">
-        <v>114</v>
+      <c r="B47" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="C47" s="5">
         <v>215.0</v>
       </c>
       <c r="D47" s="6">
-        <v>255.12</v>
+        <v>216.6</v>
       </c>
       <c r="E47" s="6">
-        <v>54850.65</v>
+        <v>46569.23</v>
       </c>
       <c r="F47" s="6">
-        <v>310.05</v>
+        <v>228.3</v>
       </c>
       <c r="G47" s="6">
-        <v>66660.75</v>
+        <v>49084.5</v>
       </c>
       <c r="H47" s="11">
-        <v>11810.1</v>
+        <v>2515.27</v>
       </c>
       <c r="I47" s="8">
-        <v>0.2153</v>
+        <v>0.054</v>
       </c>
       <c r="J47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K47" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L47" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C48" s="5">
-        <v>401.0</v>
+        <v>246.0</v>
       </c>
       <c r="D48" s="6">
-        <v>91.09</v>
+        <v>384.17</v>
       </c>
       <c r="E48" s="6">
-        <v>36527.75</v>
+        <v>94506.1</v>
       </c>
       <c r="F48" s="6">
-        <v>165.3</v>
+        <v>393.05</v>
       </c>
       <c r="G48" s="6">
-        <v>66285.3</v>
+        <v>96690.3</v>
       </c>
       <c r="H48" s="11">
-        <v>29757.55</v>
+        <v>2184.2</v>
       </c>
       <c r="I48" s="8">
-        <v>0.8147</v>
+        <v>0.0231</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="L48" s="9" t="s">
         <v>17</v>
@@ -2706,203 +2700,203 @@
     </row>
     <row r="49">
       <c r="B49" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C49" s="5">
-        <v>546.0</v>
+        <v>172.0</v>
       </c>
       <c r="D49" s="6">
-        <v>135.91</v>
+        <v>302.02</v>
       </c>
       <c r="E49" s="6">
-        <v>74208.27</v>
+        <v>51947.55</v>
       </c>
       <c r="F49" s="6">
-        <v>118.3</v>
+        <v>312.45</v>
       </c>
       <c r="G49" s="6">
-        <v>64591.8</v>
-      </c>
-      <c r="H49" s="12">
-        <v>-9616.47</v>
-      </c>
-      <c r="I49" s="13">
-        <v>-0.1296</v>
+        <v>53741.4</v>
+      </c>
+      <c r="H49" s="11">
+        <v>1793.85</v>
+      </c>
+      <c r="I49" s="8">
+        <v>0.0345</v>
       </c>
       <c r="J49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K49" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="3" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C50" s="5">
-        <v>56.0</v>
+        <v>516.0</v>
       </c>
       <c r="D50" s="6">
-        <v>1229.79</v>
+        <v>97.49</v>
       </c>
       <c r="E50" s="6">
-        <v>68868.1</v>
+        <v>50306.12</v>
       </c>
       <c r="F50" s="6">
-        <v>1089.1</v>
+        <v>100.81</v>
       </c>
       <c r="G50" s="6">
-        <v>60989.6</v>
-      </c>
-      <c r="H50" s="12">
-        <v>-7878.5</v>
-      </c>
-      <c r="I50" s="13">
-        <v>-0.1144</v>
+        <v>52017.96</v>
+      </c>
+      <c r="H50" s="11">
+        <v>1711.84</v>
+      </c>
+      <c r="I50" s="8">
+        <v>0.034</v>
       </c>
       <c r="J50" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L50" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="3" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C51" s="5">
-        <v>169.0</v>
+        <v>145.0</v>
       </c>
       <c r="D51" s="6">
-        <v>353.03</v>
+        <v>362.06</v>
       </c>
       <c r="E51" s="6">
-        <v>59661.5</v>
+        <v>52499.2</v>
       </c>
       <c r="F51" s="6">
-        <v>356.35</v>
+        <v>368.1</v>
       </c>
       <c r="G51" s="6">
-        <v>60223.15</v>
+        <v>53374.5</v>
       </c>
       <c r="H51" s="11">
-        <v>561.65</v>
+        <v>875.3</v>
       </c>
       <c r="I51" s="8">
-        <v>0.0094</v>
+        <v>0.0167</v>
       </c>
       <c r="J51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="L51" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="3" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C52" s="5">
-        <v>94.0</v>
+        <v>38.0</v>
       </c>
       <c r="D52" s="6">
-        <v>846.21</v>
+        <v>1111.19</v>
       </c>
       <c r="E52" s="6">
-        <v>79544.0</v>
+        <v>42225.2</v>
       </c>
       <c r="F52" s="6">
-        <v>617.95</v>
+        <v>1128.8</v>
       </c>
       <c r="G52" s="6">
-        <v>58087.3</v>
-      </c>
-      <c r="H52" s="12">
-        <v>-21456.7</v>
-      </c>
-      <c r="I52" s="13">
-        <v>-0.2697</v>
+        <v>42894.4</v>
+      </c>
+      <c r="H52" s="11">
+        <v>669.2</v>
+      </c>
+      <c r="I52" s="8">
+        <v>0.0158</v>
       </c>
       <c r="J52" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K52" s="9" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="L52" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="3" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C53" s="5">
-        <v>43.0</v>
+        <v>102.0</v>
       </c>
       <c r="D53" s="6">
-        <v>722.52</v>
+        <v>540.91</v>
       </c>
       <c r="E53" s="6">
-        <v>31068.3</v>
+        <v>55172.45</v>
       </c>
       <c r="F53" s="6">
-        <v>1285.3</v>
+        <v>535.0</v>
       </c>
       <c r="G53" s="6">
-        <v>55267.9</v>
-      </c>
-      <c r="H53" s="11">
-        <v>24199.6</v>
-      </c>
-      <c r="I53" s="8">
-        <v>0.7789</v>
+        <v>54570.0</v>
+      </c>
+      <c r="H53" s="13">
+        <v>-602.45</v>
+      </c>
+      <c r="I53" s="14">
+        <v>-0.0109</v>
       </c>
       <c r="J53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K53" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L53" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="10" t="s">
-        <v>121</v>
+      <c r="B54" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="C54" s="5">
-        <v>349.0</v>
+        <v>251.0</v>
       </c>
       <c r="D54" s="6">
-        <v>171.34</v>
-      </c>
-      <c r="E54" s="6">
-        <v>59799.44</v>
+        <v>456.76</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="F54" s="6">
-        <v>155.55</v>
-      </c>
-      <c r="G54" s="6">
-        <v>54286.95</v>
-      </c>
-      <c r="H54" s="12">
-        <v>-5512.49</v>
-      </c>
-      <c r="I54" s="13">
-        <v>-0.0922</v>
+        <v>454.2</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H54" s="13">
+        <v>-642.95</v>
+      </c>
+      <c r="I54" s="14">
+        <v>-0.0056</v>
       </c>
       <c r="J54" s="9" t="s">
         <v>26</v>
@@ -2916,28 +2910,28 @@
     </row>
     <row r="55">
       <c r="B55" s="3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C55" s="5">
-        <v>102.0</v>
+        <v>184.0</v>
       </c>
       <c r="D55" s="6">
-        <v>540.91</v>
+        <v>431.44</v>
       </c>
       <c r="E55" s="6">
-        <v>55172.45</v>
+        <v>79384.9</v>
       </c>
       <c r="F55" s="6">
-        <v>511.6</v>
+        <v>427.4</v>
       </c>
       <c r="G55" s="6">
-        <v>52183.2</v>
-      </c>
-      <c r="H55" s="12">
-        <v>-2989.25</v>
-      </c>
-      <c r="I55" s="13">
-        <v>-0.0542</v>
+        <v>78641.6</v>
+      </c>
+      <c r="H55" s="13">
+        <v>-743.3</v>
+      </c>
+      <c r="I55" s="14">
+        <v>-0.0094</v>
       </c>
       <c r="J55" s="9" t="s">
         <v>26</v>
@@ -2951,34 +2945,34 @@
     </row>
     <row r="56">
       <c r="B56" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C56" s="5">
-        <v>145.0</v>
+        <v>43.0</v>
       </c>
       <c r="D56" s="6">
-        <v>362.06</v>
+        <v>1097.89</v>
       </c>
       <c r="E56" s="6">
-        <v>52499.2</v>
+        <v>47209.5</v>
       </c>
       <c r="F56" s="6">
-        <v>357.2</v>
+        <v>1076.5</v>
       </c>
       <c r="G56" s="6">
-        <v>51794.0</v>
-      </c>
-      <c r="H56" s="12">
-        <v>-705.2</v>
-      </c>
-      <c r="I56" s="13">
-        <v>-0.0134</v>
+        <v>46289.5</v>
+      </c>
+      <c r="H56" s="13">
+        <v>-920.0</v>
+      </c>
+      <c r="I56" s="14">
+        <v>-0.0195</v>
       </c>
       <c r="J56" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K56" s="9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="L56" s="9" t="s">
         <v>28</v>
@@ -2986,28 +2980,28 @@
     </row>
     <row r="57">
       <c r="B57" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C57" s="5">
-        <v>102.0</v>
+        <v>117</v>
+      </c>
+      <c r="C57" s="4">
+        <v>1891.0</v>
       </c>
       <c r="D57" s="4">
-        <v>550.05</v>
+        <v>26.43</v>
       </c>
       <c r="E57" s="6">
-        <v>56105.6</v>
+        <v>49985.02</v>
       </c>
       <c r="F57" s="6">
-        <v>498.45</v>
+        <v>25.76</v>
       </c>
       <c r="G57" s="6">
-        <v>50841.9</v>
-      </c>
-      <c r="H57" s="12">
-        <v>-5263.7</v>
-      </c>
-      <c r="I57" s="13">
-        <v>-0.0938</v>
+        <v>48712.16</v>
+      </c>
+      <c r="H57" s="13">
+        <v>-1272.86</v>
+      </c>
+      <c r="I57" s="14">
+        <v>-0.0255</v>
       </c>
       <c r="J57" s="9" t="s">
         <v>26</v>
@@ -3021,63 +3015,63 @@
     </row>
     <row r="58">
       <c r="B58" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C58" s="5">
-        <v>115.0</v>
+        <v>118</v>
+      </c>
+      <c r="C58" s="4">
+        <v>1465.0</v>
       </c>
       <c r="D58" s="6">
-        <v>511.33</v>
-      </c>
-      <c r="E58" s="6">
-        <v>58802.9</v>
+        <v>74.72</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="F58" s="6">
-        <v>440.95</v>
-      </c>
-      <c r="G58" s="6">
-        <v>50709.25</v>
-      </c>
-      <c r="H58" s="12">
-        <v>-8093.65</v>
-      </c>
-      <c r="I58" s="13">
-        <v>-0.1376</v>
+        <v>73.47</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H58" s="13">
+        <v>-1829.0</v>
+      </c>
+      <c r="I58" s="14">
+        <v>-0.0167</v>
       </c>
       <c r="J58" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K58" s="9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="L58" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="10" t="s">
-        <v>126</v>
+      <c r="B59" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="C59" s="5">
-        <v>516.0</v>
+        <v>349.0</v>
       </c>
       <c r="D59" s="6">
-        <v>97.49</v>
+        <v>171.34</v>
       </c>
       <c r="E59" s="6">
-        <v>50306.12</v>
+        <v>59799.44</v>
       </c>
       <c r="F59" s="6">
-        <v>98.08</v>
+        <v>164.0</v>
       </c>
       <c r="G59" s="6">
-        <v>50609.28</v>
-      </c>
-      <c r="H59" s="11">
-        <v>303.16</v>
-      </c>
-      <c r="I59" s="8">
-        <v>0.006</v>
+        <v>57236.0</v>
+      </c>
+      <c r="H59" s="13">
+        <v>-2563.44</v>
+      </c>
+      <c r="I59" s="14">
+        <v>-0.0429</v>
       </c>
       <c r="J59" s="9" t="s">
         <v>26</v>
@@ -3091,203 +3085,203 @@
     </row>
     <row r="60">
       <c r="B60" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C60" s="5">
-        <v>120.0</v>
-      </c>
-      <c r="D60" s="5">
-        <v>401.67</v>
-      </c>
-      <c r="E60" s="6">
-        <v>48200.4</v>
+        <v>32.0</v>
+      </c>
+      <c r="D60" s="6">
+        <v>3695.54</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>123</v>
       </c>
       <c r="F60" s="6">
-        <v>413.0</v>
-      </c>
-      <c r="G60" s="6">
-        <v>49560.0</v>
-      </c>
-      <c r="H60" s="11">
-        <v>1359.6</v>
-      </c>
-      <c r="I60" s="8">
-        <v>0.0282</v>
+        <v>3604.55</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H60" s="13">
+        <v>-2911.7</v>
+      </c>
+      <c r="I60" s="14">
+        <v>-0.0246</v>
       </c>
       <c r="J60" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K60" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L60" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="10" t="s">
-        <v>128</v>
+      <c r="B61" s="3" t="s">
+        <v>125</v>
       </c>
       <c r="C61" s="5">
-        <v>172.0</v>
+        <v>102.0</v>
       </c>
       <c r="D61" s="5">
-        <v>302.02</v>
+        <v>550.05</v>
       </c>
       <c r="E61" s="6">
-        <v>51947.55</v>
+        <v>56105.6</v>
       </c>
       <c r="F61" s="6">
-        <v>286.2</v>
+        <v>509.15</v>
       </c>
       <c r="G61" s="6">
-        <v>49226.4</v>
-      </c>
-      <c r="H61" s="12">
-        <v>-2721.15</v>
-      </c>
-      <c r="I61" s="13">
-        <v>-0.0524</v>
+        <v>51933.3</v>
+      </c>
+      <c r="H61" s="13">
+        <v>-4172.3</v>
+      </c>
+      <c r="I61" s="14">
+        <v>-0.0744</v>
       </c>
       <c r="J61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K61" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L61" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C62" s="4">
-        <v>1891.0</v>
-      </c>
-      <c r="D62" s="5">
-        <v>26.43</v>
-      </c>
-      <c r="E62" s="6">
-        <v>49985.02</v>
+        <v>36.0</v>
+      </c>
+      <c r="D62" s="6">
+        <v>4330.32</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>127</v>
       </c>
       <c r="F62" s="6">
-        <v>25.63</v>
-      </c>
-      <c r="G62" s="6">
-        <v>48466.33</v>
-      </c>
-      <c r="H62" s="12">
-        <v>-1518.69</v>
-      </c>
-      <c r="I62" s="13">
-        <v>-0.0304</v>
+        <v>4213.2</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H62" s="13">
+        <v>-4216.5</v>
+      </c>
+      <c r="I62" s="14">
+        <v>-0.027</v>
       </c>
       <c r="J62" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K62" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L62" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C63" s="4">
+        <v>139.0</v>
+      </c>
+      <c r="D63" s="5">
+        <v>545.81</v>
+      </c>
+      <c r="E63" s="6">
+        <v>75867.25</v>
+      </c>
+      <c r="F63" s="6">
+        <v>513.4</v>
+      </c>
+      <c r="G63" s="6">
+        <v>71362.6</v>
+      </c>
+      <c r="H63" s="13">
+        <v>-4504.65</v>
+      </c>
+      <c r="I63" s="14">
+        <v>-0.0594</v>
+      </c>
+      <c r="J63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L63" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C63" s="4">
-        <v>63.0</v>
-      </c>
-      <c r="D63" s="5">
-        <v>724.23</v>
-      </c>
-      <c r="E63" s="6">
-        <v>45626.35</v>
-      </c>
-      <c r="F63" s="6">
-        <v>765.05</v>
-      </c>
-      <c r="G63" s="6">
-        <v>48198.15</v>
-      </c>
-      <c r="H63" s="11">
-        <v>2571.8</v>
-      </c>
-      <c r="I63" s="8">
-        <v>0.0564</v>
-      </c>
-      <c r="J63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L63" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="10" t="s">
-        <v>131</v>
-      </c>
       <c r="C64" s="5">
-        <v>86.0</v>
+        <v>115.0</v>
       </c>
       <c r="D64" s="5">
-        <v>458.8</v>
+        <v>511.33</v>
       </c>
       <c r="E64" s="6">
-        <v>39456.85</v>
+        <v>58802.9</v>
       </c>
       <c r="F64" s="6">
-        <v>549.8</v>
+        <v>472.1</v>
       </c>
       <c r="G64" s="6">
-        <v>47282.8</v>
+        <v>54291.5</v>
       </c>
       <c r="H64" s="15">
-        <v>7825.95</v>
-      </c>
-      <c r="I64" s="8">
-        <v>0.1983</v>
+        <v>-4511.4</v>
+      </c>
+      <c r="I64" s="14">
+        <v>-0.0767</v>
       </c>
       <c r="J64" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K64" s="9" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="L64" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C65" s="5">
-        <v>30.0</v>
+        <v>87.0</v>
       </c>
       <c r="D65" s="6">
-        <v>1823.31</v>
+        <v>903.4</v>
       </c>
       <c r="E65" s="6">
-        <v>54699.2</v>
+        <v>78595.7</v>
       </c>
       <c r="F65" s="6">
-        <v>1527.2</v>
+        <v>845.35</v>
       </c>
       <c r="G65" s="6">
-        <v>45816.0</v>
-      </c>
-      <c r="H65" s="12">
-        <v>-8883.2</v>
-      </c>
-      <c r="I65" s="13">
-        <v>-0.1624</v>
+        <v>73545.45</v>
+      </c>
+      <c r="H65" s="13">
+        <v>-5050.25</v>
+      </c>
+      <c r="I65" s="14">
+        <v>-0.0643</v>
       </c>
       <c r="J65" s="9" t="s">
         <v>26</v>
@@ -3301,69 +3295,69 @@
     </row>
     <row r="66">
       <c r="B66" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C66" s="5">
-        <v>43.0</v>
+        <v>546.0</v>
       </c>
       <c r="D66" s="6">
-        <v>1097.89</v>
+        <v>135.91</v>
       </c>
       <c r="E66" s="6">
-        <v>47209.5</v>
+        <v>74208.27</v>
       </c>
       <c r="F66" s="6">
-        <v>997.8</v>
+        <v>126.1</v>
       </c>
       <c r="G66" s="6">
-        <v>42905.4</v>
-      </c>
-      <c r="H66" s="12">
-        <v>-4304.1</v>
-      </c>
-      <c r="I66" s="13">
-        <v>-0.0912</v>
+        <v>68850.6</v>
+      </c>
+      <c r="H66" s="13">
+        <v>-5357.67</v>
+      </c>
+      <c r="I66" s="14">
+        <v>-0.0722</v>
       </c>
       <c r="J66" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K66" s="9" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="L66" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C67" s="5">
-        <v>38.0</v>
+        <v>56.0</v>
       </c>
       <c r="D67" s="6">
-        <v>1111.19</v>
+        <v>1229.79</v>
       </c>
       <c r="E67" s="6">
-        <v>42225.2</v>
+        <v>68868.1</v>
       </c>
       <c r="F67" s="6">
-        <v>1116.3</v>
+        <v>1107.0</v>
       </c>
       <c r="G67" s="6">
-        <v>42419.4</v>
-      </c>
-      <c r="H67" s="11">
-        <v>194.2</v>
-      </c>
-      <c r="I67" s="8">
-        <v>0.0046</v>
+        <v>61992.0</v>
+      </c>
+      <c r="H67" s="13">
+        <v>-6876.1</v>
+      </c>
+      <c r="I67" s="14">
+        <v>-0.0998</v>
       </c>
       <c r="J67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K67" s="9" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="L67" s="9" t="s">
         <v>28</v>
@@ -3371,28 +3365,28 @@
     </row>
     <row r="68">
       <c r="B68" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C68" s="5">
-        <v>94.0</v>
+        <v>30.0</v>
       </c>
       <c r="D68" s="6">
-        <v>267.98</v>
+        <v>1823.31</v>
       </c>
       <c r="E68" s="6">
-        <v>25190.12</v>
+        <v>54699.2</v>
       </c>
       <c r="F68" s="6">
-        <v>451.0</v>
+        <v>1574.0</v>
       </c>
       <c r="G68" s="6">
-        <v>42394.0</v>
-      </c>
-      <c r="H68" s="11">
-        <v>17203.88</v>
-      </c>
-      <c r="I68" s="8">
-        <v>0.683</v>
+        <v>47220.0</v>
+      </c>
+      <c r="H68" s="13">
+        <v>-7479.2</v>
+      </c>
+      <c r="I68" s="14">
+        <v>-0.1367</v>
       </c>
       <c r="J68" s="9" t="s">
         <v>26</v>
@@ -3406,104 +3400,104 @@
     </row>
     <row r="69">
       <c r="B69" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C69" s="5">
+        <v>6.0</v>
+      </c>
+      <c r="D69" s="6">
+        <v>33302.06</v>
+      </c>
+      <c r="E69" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C69" s="5">
-        <v>72.0</v>
-      </c>
-      <c r="D69" s="6">
-        <v>529.68</v>
-      </c>
-      <c r="E69" s="6">
-        <v>38136.95</v>
-      </c>
       <c r="F69" s="6">
-        <v>588.5</v>
-      </c>
-      <c r="G69" s="6">
-        <v>42372.0</v>
-      </c>
-      <c r="H69" s="11">
-        <v>4235.05</v>
-      </c>
-      <c r="I69" s="8">
-        <v>0.111</v>
+        <v>31702.0</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="H69" s="13">
+        <v>-9600.35</v>
+      </c>
+      <c r="I69" s="14">
+        <v>-0.048</v>
       </c>
       <c r="J69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K69" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L69" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C70" s="5">
-        <v>67.0</v>
+        <v>97.0</v>
       </c>
       <c r="D70" s="6">
-        <v>515.75</v>
-      </c>
-      <c r="E70" s="6">
-        <v>34555.15</v>
+        <v>1054.87</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>139</v>
       </c>
       <c r="F70" s="6">
-        <v>573.3</v>
+        <v>923.6</v>
       </c>
       <c r="G70" s="6">
-        <v>38411.1</v>
-      </c>
-      <c r="H70" s="11">
-        <v>3855.95</v>
-      </c>
-      <c r="I70" s="8">
-        <v>0.1116</v>
+        <v>89589.2</v>
+      </c>
+      <c r="H70" s="13">
+        <v>-12733.35</v>
+      </c>
+      <c r="I70" s="14">
+        <v>-0.1244</v>
       </c>
       <c r="J70" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K70" s="9" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="L70" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="3" t="s">
-        <v>138</v>
+      <c r="B71" s="10" t="s">
+        <v>140</v>
       </c>
       <c r="C71" s="5">
-        <v>9.0</v>
+        <v>94.0</v>
       </c>
       <c r="D71" s="6">
-        <v>3066.43</v>
+        <v>846.21</v>
       </c>
       <c r="E71" s="6">
-        <v>27597.85</v>
+        <v>79544.0</v>
       </c>
       <c r="F71" s="6">
-        <v>4191.4</v>
+        <v>646.45</v>
       </c>
       <c r="G71" s="6">
-        <v>37722.6</v>
-      </c>
-      <c r="H71" s="11">
-        <v>10124.75</v>
-      </c>
-      <c r="I71" s="8">
-        <v>0.3669</v>
+        <v>60766.3</v>
+      </c>
+      <c r="H71" s="13">
+        <v>-18777.7</v>
+      </c>
+      <c r="I71" s="14">
+        <v>-0.2361</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K71" s="9" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="L71" s="9" t="s">
         <v>17</v>
@@ -3511,28 +3505,28 @@
     </row>
     <row r="72">
       <c r="B72" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C72" s="5">
-        <v>218.0</v>
+        <v>70.0</v>
       </c>
       <c r="D72" s="5">
-        <v>182.99</v>
+        <v>331.82</v>
       </c>
       <c r="E72" s="6">
-        <v>39890.84</v>
+        <v>23227.6</v>
       </c>
       <c r="F72" s="6">
-        <v>172.51</v>
+        <v>562.25</v>
       </c>
       <c r="G72" s="6">
-        <v>37607.18</v>
-      </c>
-      <c r="H72" s="12">
-        <v>-2283.66</v>
-      </c>
-      <c r="I72" s="13">
-        <v>-0.0572</v>
+        <v>39357.5</v>
+      </c>
+      <c r="H72" s="11">
+        <v>16129.9</v>
+      </c>
+      <c r="I72" s="8">
+        <v>0.6944</v>
       </c>
       <c r="J72" s="9" t="s">
         <v>26</v>
@@ -3545,29 +3539,29 @@
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="3" t="s">
-        <v>140</v>
+      <c r="B73" s="10" t="s">
+        <v>142</v>
       </c>
       <c r="C73" s="5">
-        <v>70.0</v>
+        <v>28.0</v>
       </c>
       <c r="D73" s="5">
-        <v>331.82</v>
+        <v>702.63</v>
       </c>
       <c r="E73" s="6">
-        <v>23227.6</v>
+        <v>19673.6</v>
       </c>
       <c r="F73" s="6">
-        <v>522.8</v>
+        <v>1159.5</v>
       </c>
       <c r="G73" s="6">
-        <v>36596.0</v>
+        <v>32466.0</v>
       </c>
       <c r="H73" s="11">
-        <v>13368.4</v>
+        <v>12792.4</v>
       </c>
       <c r="I73" s="8">
-        <v>0.5755</v>
+        <v>0.6502</v>
       </c>
       <c r="J73" s="9" t="s">
         <v>26</v>
@@ -3581,28 +3575,28 @@
     </row>
     <row r="74">
       <c r="B74" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C74" s="5">
-        <v>132.0</v>
+        <v>298.0</v>
       </c>
       <c r="D74" s="6">
-        <v>264.23</v>
+        <v>41.79</v>
       </c>
       <c r="E74" s="6">
-        <v>34878.4</v>
+        <v>12454.04</v>
       </c>
       <c r="F74" s="6">
-        <v>274.3</v>
+        <v>79.38</v>
       </c>
       <c r="G74" s="6">
-        <v>36207.6</v>
+        <v>23655.24</v>
       </c>
       <c r="H74" s="11">
-        <v>1329.2</v>
+        <v>11201.2</v>
       </c>
       <c r="I74" s="8">
-        <v>0.0381</v>
+        <v>0.8994</v>
       </c>
       <c r="J74" s="9" t="s">
         <v>26</v>
@@ -3616,98 +3610,98 @@
     </row>
     <row r="75">
       <c r="B75" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C75" s="5">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
       <c r="D75" s="6">
-        <v>1886.49</v>
+        <v>2134.6</v>
       </c>
       <c r="E75" s="6">
-        <v>35843.4</v>
+        <v>10673.0</v>
       </c>
       <c r="F75" s="6">
-        <v>1895.0</v>
+        <v>4356.2</v>
       </c>
       <c r="G75" s="6">
-        <v>36005.0</v>
+        <v>21781.0</v>
       </c>
       <c r="H75" s="11">
-        <v>161.6</v>
+        <v>11108.0</v>
       </c>
       <c r="I75" s="8">
-        <v>0.0045</v>
+        <v>1.0408</v>
       </c>
       <c r="J75" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K75" s="9" t="s">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="L75" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C76" s="5">
-        <v>1.0</v>
+        <v>49.0</v>
       </c>
       <c r="D76" s="6">
-        <v>35975.0</v>
+        <v>333.15</v>
       </c>
       <c r="E76" s="6">
-        <v>35975.0</v>
+        <v>16324.5</v>
       </c>
       <c r="F76" s="6">
-        <v>35200.0</v>
+        <v>541.0</v>
       </c>
       <c r="G76" s="6">
-        <v>35200.0</v>
-      </c>
-      <c r="H76" s="12">
-        <v>-775.0</v>
-      </c>
-      <c r="I76" s="13">
-        <v>-0.0215</v>
+        <v>26509.0</v>
+      </c>
+      <c r="H76" s="11">
+        <v>10184.5</v>
+      </c>
+      <c r="I76" s="8">
+        <v>0.6239</v>
       </c>
       <c r="J76" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K76" s="9" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="L76" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="10" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C77" s="5">
-        <v>42.0</v>
+        <v>9.0</v>
       </c>
       <c r="D77" s="4">
-        <v>820.32</v>
+        <v>1395.0</v>
       </c>
       <c r="E77" s="6">
-        <v>34453.5</v>
+        <v>12555.0</v>
       </c>
       <c r="F77" s="6">
-        <v>825.85</v>
+        <v>2353.0</v>
       </c>
       <c r="G77" s="6">
-        <v>34685.7</v>
+        <v>21177.0</v>
       </c>
       <c r="H77" s="11">
-        <v>232.2</v>
+        <v>8622.0</v>
       </c>
       <c r="I77" s="8">
-        <v>0.0067</v>
+        <v>0.6867</v>
       </c>
       <c r="J77" s="9" t="s">
         <v>26</v>
@@ -3721,63 +3715,63 @@
     </row>
     <row r="78">
       <c r="B78" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C78" s="5">
-        <v>222.0</v>
-      </c>
-      <c r="D78" s="5">
-        <v>137.08</v>
+        <v>20.0</v>
+      </c>
+      <c r="D78" s="6">
+        <v>1040.96</v>
       </c>
       <c r="E78" s="6">
-        <v>30430.92</v>
+        <v>20819.2</v>
       </c>
       <c r="F78" s="6">
-        <v>151.88</v>
+        <v>1449.0</v>
       </c>
       <c r="G78" s="6">
-        <v>33717.36</v>
+        <v>28980.0</v>
       </c>
       <c r="H78" s="11">
-        <v>3286.44</v>
+        <v>8160.8</v>
       </c>
       <c r="I78" s="8">
-        <v>0.108</v>
+        <v>0.392</v>
       </c>
       <c r="J78" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K78" s="9" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="L78" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C79" s="5">
-        <v>60.0</v>
+        <v>67.0</v>
       </c>
       <c r="D79" s="6">
-        <v>527.58</v>
+        <v>515.75</v>
       </c>
       <c r="E79" s="6">
-        <v>31655.0</v>
+        <v>34555.15</v>
       </c>
       <c r="F79" s="6">
-        <v>555.05</v>
+        <v>596.35</v>
       </c>
       <c r="G79" s="6">
-        <v>33303.0</v>
+        <v>39955.45</v>
       </c>
       <c r="H79" s="11">
-        <v>1648.0</v>
+        <v>5400.3</v>
       </c>
       <c r="I79" s="8">
-        <v>0.0521</v>
+        <v>0.1563</v>
       </c>
       <c r="J79" s="9" t="s">
         <v>26</v>
@@ -3791,28 +3785,28 @@
     </row>
     <row r="80">
       <c r="B80" s="10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C80" s="5">
-        <v>39.0</v>
+        <v>21.0</v>
       </c>
       <c r="D80" s="6">
-        <v>1165.79</v>
+        <v>1491.75</v>
       </c>
       <c r="E80" s="6">
-        <v>45465.85</v>
+        <v>31326.8</v>
       </c>
       <c r="F80" s="6">
-        <v>842.65</v>
+        <v>1740.0</v>
       </c>
       <c r="G80" s="6">
-        <v>32863.35</v>
-      </c>
-      <c r="H80" s="12">
-        <v>-12602.5</v>
-      </c>
-      <c r="I80" s="13">
-        <v>-0.2772</v>
+        <v>36540.0</v>
+      </c>
+      <c r="H80" s="11">
+        <v>5213.2</v>
+      </c>
+      <c r="I80" s="8">
+        <v>0.1664</v>
       </c>
       <c r="J80" s="9" t="s">
         <v>26</v>
@@ -3826,63 +3820,63 @@
     </row>
     <row r="81">
       <c r="B81" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C81" s="5">
-        <v>28.0</v>
+        <v>10.0</v>
       </c>
       <c r="D81" s="5">
-        <v>702.63</v>
+        <v>975.8</v>
       </c>
       <c r="E81" s="6">
-        <v>19673.6</v>
+        <v>9758.0</v>
       </c>
       <c r="F81" s="6">
-        <v>1134.3</v>
+        <v>1463.2</v>
       </c>
       <c r="G81" s="6">
-        <v>31760.4</v>
+        <v>14632.0</v>
       </c>
       <c r="H81" s="11">
-        <v>12086.8</v>
+        <v>4874.0</v>
       </c>
       <c r="I81" s="8">
-        <v>0.6144</v>
+        <v>0.4995</v>
       </c>
       <c r="J81" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K81" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L81" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="10" t="s">
-        <v>149</v>
+      <c r="B82" s="3" t="s">
+        <v>151</v>
       </c>
       <c r="C82" s="5">
-        <v>906.0</v>
+        <v>60.0</v>
       </c>
       <c r="D82" s="6">
-        <v>66.21</v>
+        <v>527.58</v>
       </c>
       <c r="E82" s="6">
-        <v>59984.41</v>
+        <v>31655.0</v>
       </c>
       <c r="F82" s="6">
-        <v>34.69</v>
+        <v>601.05</v>
       </c>
       <c r="G82" s="6">
-        <v>31429.14</v>
-      </c>
-      <c r="H82" s="12">
-        <v>-28555.27</v>
-      </c>
-      <c r="I82" s="13">
-        <v>-0.476</v>
+        <v>36063.0</v>
+      </c>
+      <c r="H82" s="11">
+        <v>4408.0</v>
+      </c>
+      <c r="I82" s="8">
+        <v>0.1393</v>
       </c>
       <c r="J82" s="9" t="s">
         <v>26</v>
@@ -3895,29 +3889,29 @@
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="3" t="s">
-        <v>150</v>
+      <c r="B83" s="10" t="s">
+        <v>152</v>
       </c>
       <c r="C83" s="5">
-        <v>53.0</v>
+        <v>124.0</v>
       </c>
       <c r="D83" s="5">
-        <v>729.68</v>
+        <v>160.5</v>
       </c>
       <c r="E83" s="6">
-        <v>38672.9</v>
+        <v>19902.66</v>
       </c>
       <c r="F83" s="6">
-        <v>587.65</v>
+        <v>192.95</v>
       </c>
       <c r="G83" s="6">
-        <v>31145.45</v>
-      </c>
-      <c r="H83" s="12">
-        <v>-7527.45</v>
-      </c>
-      <c r="I83" s="13">
-        <v>-0.1946</v>
+        <v>23925.8</v>
+      </c>
+      <c r="H83" s="11">
+        <v>4023.14</v>
+      </c>
+      <c r="I83" s="8">
+        <v>0.2021</v>
       </c>
       <c r="J83" s="9" t="s">
         <v>26</v>
@@ -3931,34 +3925,34 @@
     </row>
     <row r="84">
       <c r="B84" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C84" s="5">
-        <v>307.0</v>
+        <v>91.0</v>
       </c>
       <c r="D84" s="6">
-        <v>97.19</v>
+        <v>173.53</v>
       </c>
       <c r="E84" s="6">
-        <v>29837.24</v>
+        <v>15791.45</v>
       </c>
       <c r="F84" s="6">
-        <v>100.1</v>
+        <v>214.78</v>
       </c>
       <c r="G84" s="6">
-        <v>30730.7</v>
+        <v>19544.98</v>
       </c>
       <c r="H84" s="11">
-        <v>893.46</v>
+        <v>3753.53</v>
       </c>
       <c r="I84" s="8">
-        <v>0.0299</v>
+        <v>0.2377</v>
       </c>
       <c r="J84" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K84" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L84" s="9" t="s">
         <v>17</v>
@@ -3966,28 +3960,28 @@
     </row>
     <row r="85">
       <c r="B85" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C85" s="5">
-        <v>249.0</v>
+        <v>222.0</v>
       </c>
       <c r="D85" s="5">
-        <v>134.11</v>
+        <v>137.08</v>
       </c>
       <c r="E85" s="6">
-        <v>33392.27</v>
+        <v>30430.92</v>
       </c>
       <c r="F85" s="6">
-        <v>122.98</v>
+        <v>153.3</v>
       </c>
       <c r="G85" s="6">
-        <v>30622.02</v>
-      </c>
-      <c r="H85" s="12">
-        <v>-2770.25</v>
-      </c>
-      <c r="I85" s="13">
-        <v>-0.083</v>
+        <v>34032.6</v>
+      </c>
+      <c r="H85" s="11">
+        <v>3601.68</v>
+      </c>
+      <c r="I85" s="8">
+        <v>0.1184</v>
       </c>
       <c r="J85" s="9" t="s">
         <v>26</v>
@@ -4001,28 +3995,28 @@
     </row>
     <row r="86">
       <c r="B86" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C86" s="5">
-        <v>32.0</v>
+        <v>63.0</v>
       </c>
       <c r="D86" s="5">
-        <v>934.45</v>
+        <v>311.35</v>
       </c>
       <c r="E86" s="6">
-        <v>29902.4</v>
+        <v>19614.9</v>
       </c>
       <c r="F86" s="6">
-        <v>941.2</v>
+        <v>367.0</v>
       </c>
       <c r="G86" s="6">
-        <v>30118.4</v>
+        <v>23121.0</v>
       </c>
       <c r="H86" s="11">
-        <v>216.0</v>
+        <v>3506.1</v>
       </c>
       <c r="I86" s="8">
-        <v>0.0072</v>
+        <v>0.1787</v>
       </c>
       <c r="J86" s="9" t="s">
         <v>26</v>
@@ -4036,98 +4030,98 @@
     </row>
     <row r="87">
       <c r="B87" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C87" s="5">
+        <v>43.0</v>
+      </c>
+      <c r="D87" s="6">
+        <v>579.24</v>
+      </c>
+      <c r="E87" s="6">
+        <v>24907.3</v>
+      </c>
+      <c r="F87" s="6">
+        <v>652.35</v>
+      </c>
+      <c r="G87" s="6">
+        <v>28051.05</v>
+      </c>
+      <c r="H87" s="11">
+        <v>3143.75</v>
+      </c>
+      <c r="I87" s="8">
+        <v>0.1262</v>
+      </c>
+      <c r="J87" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K87" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L87" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C88" s="5">
+        <v>307.0</v>
+      </c>
+      <c r="D88" s="5">
+        <v>97.19</v>
+      </c>
+      <c r="E88" s="6">
+        <v>29837.24</v>
+      </c>
+      <c r="F88" s="6">
+        <v>106.35</v>
+      </c>
+      <c r="G88" s="6">
+        <v>32649.45</v>
+      </c>
+      <c r="H88" s="11">
+        <v>2812.21</v>
+      </c>
+      <c r="I88" s="8">
+        <v>0.0943</v>
+      </c>
+      <c r="J88" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K88" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L88" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C89" s="5">
         <v>20.0</v>
       </c>
-      <c r="D87" s="6">
-        <v>1040.96</v>
-      </c>
-      <c r="E87" s="6">
-        <v>20819.2</v>
-      </c>
-      <c r="F87" s="6">
-        <v>1389.35</v>
-      </c>
-      <c r="G87" s="6">
-        <v>27787.0</v>
-      </c>
-      <c r="H87" s="11">
-        <v>6967.8</v>
-      </c>
-      <c r="I87" s="8">
-        <v>0.3347</v>
-      </c>
-      <c r="J87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K87" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L87" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="C88" s="5">
-        <v>66.0</v>
-      </c>
-      <c r="D88" s="5">
-        <v>387.23</v>
-      </c>
-      <c r="E88" s="6">
-        <v>25557.45</v>
-      </c>
-      <c r="F88" s="6">
-        <v>415.95</v>
-      </c>
-      <c r="G88" s="6">
-        <v>27452.7</v>
-      </c>
-      <c r="H88" s="11">
-        <v>1895.25</v>
-      </c>
-      <c r="I88" s="8">
-        <v>0.0742</v>
-      </c>
-      <c r="J88" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K88" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L88" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C89" s="5">
-        <v>127.0</v>
-      </c>
-      <c r="D89" s="5">
-        <v>209.26</v>
+      <c r="D89" s="6">
+        <v>1099.4</v>
       </c>
       <c r="E89" s="6">
-        <v>26575.63</v>
+        <v>21988.0</v>
       </c>
       <c r="F89" s="6">
-        <v>213.2</v>
+        <v>1227.6</v>
       </c>
       <c r="G89" s="6">
-        <v>27076.4</v>
+        <v>24552.0</v>
       </c>
       <c r="H89" s="11">
-        <v>500.77</v>
+        <v>2564.0</v>
       </c>
       <c r="I89" s="8">
-        <v>0.0188</v>
+        <v>0.1166</v>
       </c>
       <c r="J89" s="9" t="s">
         <v>26</v>
@@ -4141,28 +4135,28 @@
     </row>
     <row r="90">
       <c r="B90" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C90" s="5">
-        <v>43.0</v>
+        <v>3.0</v>
       </c>
       <c r="D90" s="6">
-        <v>579.24</v>
+        <v>1154.83</v>
       </c>
       <c r="E90" s="6">
-        <v>24907.3</v>
+        <v>3464.5</v>
       </c>
       <c r="F90" s="6">
-        <v>624.1</v>
+        <v>1952.9</v>
       </c>
       <c r="G90" s="6">
-        <v>26836.3</v>
+        <v>5858.7</v>
       </c>
       <c r="H90" s="11">
-        <v>1929.0</v>
+        <v>2394.2</v>
       </c>
       <c r="I90" s="8">
-        <v>0.0774</v>
+        <v>0.6911</v>
       </c>
       <c r="J90" s="9" t="s">
         <v>26</v>
@@ -4176,63 +4170,63 @@
     </row>
     <row r="91">
       <c r="B91" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C91" s="5">
-        <v>49.0</v>
+        <v>11.0</v>
       </c>
       <c r="D91" s="5">
-        <v>333.15</v>
+        <v>80.54</v>
       </c>
       <c r="E91" s="6">
-        <v>16324.5</v>
+        <v>885.9</v>
       </c>
       <c r="F91" s="6">
-        <v>538.85</v>
+        <v>270.35</v>
       </c>
       <c r="G91" s="6">
-        <v>26403.65</v>
+        <v>2973.85</v>
       </c>
       <c r="H91" s="11">
-        <v>10079.15</v>
+        <v>2087.95</v>
       </c>
       <c r="I91" s="8">
-        <v>0.6174</v>
+        <v>2.3569</v>
       </c>
       <c r="J91" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K91" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L91" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="10" t="s">
-        <v>159</v>
+      <c r="B92" s="3" t="s">
+        <v>161</v>
       </c>
       <c r="C92" s="5">
-        <v>20.0</v>
+        <v>66.0</v>
       </c>
       <c r="D92" s="6">
-        <v>1099.4</v>
+        <v>387.23</v>
       </c>
       <c r="E92" s="6">
-        <v>21988.0</v>
+        <v>25557.45</v>
       </c>
       <c r="F92" s="6">
-        <v>1256.6</v>
+        <v>417.95</v>
       </c>
       <c r="G92" s="6">
-        <v>25132.0</v>
+        <v>27584.7</v>
       </c>
       <c r="H92" s="11">
-        <v>3144.0</v>
+        <v>2027.25</v>
       </c>
       <c r="I92" s="8">
-        <v>0.143</v>
+        <v>0.0793</v>
       </c>
       <c r="J92" s="9" t="s">
         <v>26</v>
@@ -4246,63 +4240,63 @@
     </row>
     <row r="93">
       <c r="B93" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C93" s="5">
-        <v>226.0</v>
+        <v>20.0</v>
       </c>
       <c r="D93" s="6">
-        <v>136.74</v>
+        <v>369.45</v>
       </c>
       <c r="E93" s="6">
-        <v>30902.6</v>
+        <v>7389.0</v>
       </c>
       <c r="F93" s="6">
-        <v>110.8</v>
+        <v>465.0</v>
       </c>
       <c r="G93" s="6">
-        <v>25040.8</v>
-      </c>
-      <c r="H93" s="12">
-        <v>-5861.8</v>
-      </c>
-      <c r="I93" s="13">
-        <v>-0.1897</v>
+        <v>9300.0</v>
+      </c>
+      <c r="H93" s="11">
+        <v>1911.0</v>
+      </c>
+      <c r="I93" s="8">
+        <v>0.2586</v>
       </c>
       <c r="J93" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K93" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L93" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="10" t="s">
-        <v>161</v>
+      <c r="B94" s="3" t="s">
+        <v>163</v>
       </c>
       <c r="C94" s="5">
-        <v>59.0</v>
+        <v>15.0</v>
       </c>
       <c r="D94" s="6">
-        <v>576.82</v>
+        <v>1526.68</v>
       </c>
       <c r="E94" s="6">
-        <v>34032.35</v>
+        <v>22900.2</v>
       </c>
       <c r="F94" s="6">
-        <v>411.7</v>
+        <v>1628.2</v>
       </c>
       <c r="G94" s="6">
-        <v>24290.3</v>
-      </c>
-      <c r="H94" s="12">
-        <v>-9742.05</v>
-      </c>
-      <c r="I94" s="13">
-        <v>-0.2863</v>
+        <v>24423.0</v>
+      </c>
+      <c r="H94" s="11">
+        <v>1522.8</v>
+      </c>
+      <c r="I94" s="8">
+        <v>0.0665</v>
       </c>
       <c r="J94" s="9" t="s">
         <v>26</v>
@@ -4315,70 +4309,70 @@
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="3" t="s">
-        <v>162</v>
+      <c r="B95" s="10" t="s">
+        <v>164</v>
       </c>
       <c r="C95" s="5">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="D95" s="6">
-        <v>1526.68</v>
+        <v>1886.49</v>
       </c>
       <c r="E95" s="6">
-        <v>22900.2</v>
+        <v>35843.4</v>
       </c>
       <c r="F95" s="6">
-        <v>1574.9</v>
+        <v>1965.6</v>
       </c>
       <c r="G95" s="6">
-        <v>23623.5</v>
+        <v>37346.4</v>
       </c>
       <c r="H95" s="11">
-        <v>723.3</v>
+        <v>1503.0</v>
       </c>
       <c r="I95" s="8">
-        <v>0.0316</v>
+        <v>0.0419</v>
       </c>
       <c r="J95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K95" s="9" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="L95" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="10" t="s">
-        <v>163</v>
+      <c r="B96" s="3" t="s">
+        <v>165</v>
       </c>
       <c r="C96" s="5">
-        <v>186.0</v>
+        <v>1.0</v>
       </c>
       <c r="D96" s="6">
-        <v>139.03</v>
+        <v>415.9</v>
       </c>
       <c r="E96" s="6">
-        <v>25859.79</v>
+        <v>415.9</v>
       </c>
       <c r="F96" s="6">
-        <v>123.6</v>
+        <v>1898.05</v>
       </c>
       <c r="G96" s="6">
-        <v>22989.6</v>
-      </c>
-      <c r="H96" s="12">
-        <v>-2870.19</v>
-      </c>
-      <c r="I96" s="13">
-        <v>-0.111</v>
+        <v>1898.05</v>
+      </c>
+      <c r="H96" s="11">
+        <v>1482.15</v>
+      </c>
+      <c r="I96" s="8">
+        <v>3.5637</v>
       </c>
       <c r="J96" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K96" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L96" s="9" t="s">
         <v>17</v>
@@ -4386,28 +4380,28 @@
     </row>
     <row r="97">
       <c r="B97" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C97" s="5">
-        <v>63.0</v>
+        <v>218.0</v>
       </c>
       <c r="D97" s="5">
-        <v>311.35</v>
+        <v>182.99</v>
       </c>
       <c r="E97" s="6">
-        <v>19614.9</v>
+        <v>39890.84</v>
       </c>
       <c r="F97" s="6">
-        <v>362.4</v>
+        <v>188.76</v>
       </c>
       <c r="G97" s="6">
-        <v>22831.2</v>
+        <v>41149.68</v>
       </c>
       <c r="H97" s="11">
-        <v>3216.3</v>
+        <v>1258.84</v>
       </c>
       <c r="I97" s="8">
-        <v>0.164</v>
+        <v>0.0316</v>
       </c>
       <c r="J97" s="9" t="s">
         <v>26</v>
@@ -4421,28 +4415,28 @@
     </row>
     <row r="98">
       <c r="B98" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C98" s="5">
-        <v>298.0</v>
+        <v>50.0</v>
       </c>
       <c r="D98" s="5">
-        <v>41.79</v>
+        <v>292.7</v>
       </c>
       <c r="E98" s="6">
-        <v>12454.04</v>
+        <v>14635.0</v>
       </c>
       <c r="F98" s="6">
-        <v>76.5</v>
+        <v>316.55</v>
       </c>
       <c r="G98" s="6">
-        <v>22797.0</v>
+        <v>15827.5</v>
       </c>
       <c r="H98" s="11">
-        <v>10342.96</v>
+        <v>1192.5</v>
       </c>
       <c r="I98" s="8">
-        <v>0.8305</v>
+        <v>0.0815</v>
       </c>
       <c r="J98" s="9" t="s">
         <v>26</v>
@@ -4456,28 +4450,28 @@
     </row>
     <row r="99">
       <c r="B99" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C99" s="5">
-        <v>124.0</v>
+        <v>68.0</v>
       </c>
       <c r="D99" s="6">
-        <v>160.5</v>
+        <v>174.16</v>
       </c>
       <c r="E99" s="6">
-        <v>19902.66</v>
+        <v>11842.88</v>
       </c>
       <c r="F99" s="6">
-        <v>182.6</v>
+        <v>189.54</v>
       </c>
       <c r="G99" s="6">
-        <v>22642.4</v>
-      </c>
-      <c r="H99" s="15">
-        <v>2739.74</v>
+        <v>12888.72</v>
+      </c>
+      <c r="H99" s="12">
+        <v>1045.84</v>
       </c>
       <c r="I99" s="8">
-        <v>0.1377</v>
+        <v>0.0883</v>
       </c>
       <c r="J99" s="9" t="s">
         <v>26</v>
@@ -4490,29 +4484,29 @@
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="10" t="s">
-        <v>167</v>
+      <c r="B100" s="3" t="s">
+        <v>169</v>
       </c>
       <c r="C100" s="5">
-        <v>14.0</v>
+        <v>32.0</v>
       </c>
       <c r="D100" s="6">
-        <v>1449.3</v>
+        <v>934.45</v>
       </c>
       <c r="E100" s="6">
-        <v>20290.2</v>
+        <v>29902.4</v>
       </c>
       <c r="F100" s="6">
-        <v>1568.2</v>
+        <v>956.0</v>
       </c>
       <c r="G100" s="6">
-        <v>21954.8</v>
+        <v>30592.0</v>
       </c>
       <c r="H100" s="11">
-        <v>1664.6</v>
+        <v>689.6</v>
       </c>
       <c r="I100" s="8">
-        <v>0.082</v>
+        <v>0.0231</v>
       </c>
       <c r="J100" s="9" t="s">
         <v>26</v>
@@ -4525,64 +4519,64 @@
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="3" t="s">
-        <v>168</v>
+      <c r="B101" s="10" t="s">
+        <v>170</v>
       </c>
       <c r="C101" s="5">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="D101" s="6">
-        <v>2134.6</v>
+        <v>35975.0</v>
       </c>
       <c r="E101" s="6">
-        <v>10673.0</v>
+        <v>35975.0</v>
       </c>
       <c r="F101" s="6">
-        <v>4205.0</v>
+        <v>36660.0</v>
       </c>
       <c r="G101" s="6">
-        <v>21025.0</v>
-      </c>
-      <c r="H101" s="15">
-        <v>10352.0</v>
+        <v>36660.0</v>
+      </c>
+      <c r="H101" s="12">
+        <v>685.0</v>
       </c>
       <c r="I101" s="8">
-        <v>0.9699</v>
+        <v>0.019</v>
       </c>
       <c r="J101" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K101" s="9" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="L101" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C102" s="5">
-        <v>9.0</v>
+        <v>51.0</v>
       </c>
       <c r="D102" s="6">
-        <v>1395.0</v>
+        <v>494.56</v>
       </c>
       <c r="E102" s="6">
-        <v>12555.0</v>
+        <v>25222.6</v>
       </c>
       <c r="F102" s="6">
-        <v>2249.55</v>
+        <v>506.9</v>
       </c>
       <c r="G102" s="6">
-        <v>20245.95</v>
+        <v>25851.9</v>
       </c>
       <c r="H102" s="11">
-        <v>7690.95</v>
+        <v>629.3</v>
       </c>
       <c r="I102" s="8">
-        <v>0.6126</v>
+        <v>0.0249</v>
       </c>
       <c r="J102" s="9" t="s">
         <v>26</v>
@@ -4596,69 +4590,69 @@
     </row>
     <row r="103">
       <c r="B103" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C103" s="5">
-        <v>69.0</v>
+        <v>132.0</v>
       </c>
       <c r="D103" s="6">
-        <v>463.0</v>
+        <v>264.23</v>
       </c>
       <c r="E103" s="6">
-        <v>31947.25</v>
+        <v>34878.4</v>
       </c>
       <c r="F103" s="6">
-        <v>286.0</v>
+        <v>267.75</v>
       </c>
       <c r="G103" s="6">
-        <v>19734.0</v>
-      </c>
-      <c r="H103" s="12">
-        <v>-12213.25</v>
-      </c>
-      <c r="I103" s="13">
-        <v>-0.3823</v>
+        <v>35343.0</v>
+      </c>
+      <c r="H103" s="11">
+        <v>464.6</v>
+      </c>
+      <c r="I103" s="8">
+        <v>0.0133</v>
       </c>
       <c r="J103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K103" s="9" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="L103" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="104">
-      <c r="B104" s="10" t="s">
-        <v>171</v>
+      <c r="B104" s="3" t="s">
+        <v>173</v>
       </c>
       <c r="C104" s="5">
-        <v>228.0</v>
+        <v>1.0</v>
       </c>
       <c r="D104" s="6">
-        <v>94.74</v>
+        <v>53.6</v>
       </c>
       <c r="E104" s="6">
-        <v>21599.94</v>
+        <v>53.6</v>
       </c>
       <c r="F104" s="6">
-        <v>85.05</v>
+        <v>496.8</v>
       </c>
       <c r="G104" s="6">
-        <v>19391.4</v>
-      </c>
-      <c r="H104" s="12">
-        <v>-2208.54</v>
-      </c>
-      <c r="I104" s="13">
-        <v>-0.1022</v>
+        <v>496.8</v>
+      </c>
+      <c r="H104" s="11">
+        <v>443.2</v>
+      </c>
+      <c r="I104" s="8">
+        <v>8.2687</v>
       </c>
       <c r="J104" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K104" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L104" s="9" t="s">
         <v>17</v>
@@ -4666,63 +4660,63 @@
     </row>
     <row r="105">
       <c r="B105" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C105" s="5">
-        <v>67.0</v>
+        <v>1.0</v>
       </c>
       <c r="D105" s="5">
-        <v>374.48</v>
+        <v>262.0</v>
       </c>
       <c r="E105" s="6">
-        <v>25090.1</v>
+        <v>262.0</v>
       </c>
       <c r="F105" s="6">
-        <v>288.9</v>
+        <v>588.4</v>
       </c>
       <c r="G105" s="6">
-        <v>19356.3</v>
-      </c>
-      <c r="H105" s="12">
-        <v>-5733.8</v>
-      </c>
-      <c r="I105" s="13">
-        <v>-0.2285</v>
+        <v>588.4</v>
+      </c>
+      <c r="H105" s="11">
+        <v>326.4</v>
+      </c>
+      <c r="I105" s="8">
+        <v>1.2458</v>
       </c>
       <c r="J105" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K105" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L105" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="106">
-      <c r="B106" s="10" t="s">
-        <v>173</v>
+      <c r="B106" s="3" t="s">
+        <v>175</v>
       </c>
       <c r="C106" s="5">
-        <v>24.0</v>
+        <v>50.0</v>
       </c>
       <c r="D106" s="6">
-        <v>829.45</v>
+        <v>238.76</v>
       </c>
       <c r="E106" s="6">
-        <v>19906.8</v>
+        <v>11938.1</v>
       </c>
       <c r="F106" s="6">
-        <v>805.0</v>
+        <v>244.45</v>
       </c>
       <c r="G106" s="6">
-        <v>19320.0</v>
-      </c>
-      <c r="H106" s="12">
-        <v>-586.8</v>
-      </c>
-      <c r="I106" s="13">
-        <v>-0.0295</v>
+        <v>12222.5</v>
+      </c>
+      <c r="H106" s="11">
+        <v>284.4</v>
+      </c>
+      <c r="I106" s="8">
+        <v>0.0238</v>
       </c>
       <c r="J106" s="9" t="s">
         <v>26</v>
@@ -4736,34 +4730,34 @@
     </row>
     <row r="107">
       <c r="B107" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C107" s="5">
-        <v>15.0</v>
+        <v>1.0</v>
       </c>
       <c r="D107" s="6">
-        <v>1320.0</v>
+        <v>119.7</v>
       </c>
       <c r="E107" s="6">
-        <v>19800.0</v>
+        <v>119.7</v>
       </c>
       <c r="F107" s="6">
-        <v>1278.45</v>
+        <v>330.19</v>
       </c>
       <c r="G107" s="6">
-        <v>19176.75</v>
-      </c>
-      <c r="H107" s="12">
-        <v>-623.25</v>
-      </c>
-      <c r="I107" s="13">
-        <v>-0.0315</v>
+        <v>330.19</v>
+      </c>
+      <c r="H107" s="11">
+        <v>210.49</v>
+      </c>
+      <c r="I107" s="8">
+        <v>1.7585</v>
       </c>
       <c r="J107" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K107" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L107" s="9" t="s">
         <v>17</v>
@@ -4771,69 +4765,69 @@
     </row>
     <row r="108">
       <c r="B108" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C108" s="5">
-        <v>21.0</v>
+        <v>1.0</v>
       </c>
       <c r="D108" s="6">
-        <v>1220.91</v>
+        <v>588.9</v>
       </c>
       <c r="E108" s="6">
-        <v>25639.1</v>
+        <v>588.9</v>
       </c>
       <c r="F108" s="6">
-        <v>910.15</v>
+        <v>762.95</v>
       </c>
       <c r="G108" s="6">
-        <v>19113.15</v>
-      </c>
-      <c r="H108" s="12">
-        <v>-6525.95</v>
-      </c>
-      <c r="I108" s="13">
-        <v>-0.2545</v>
+        <v>762.95</v>
+      </c>
+      <c r="H108" s="11">
+        <v>174.05</v>
+      </c>
+      <c r="I108" s="8">
+        <v>0.2956</v>
       </c>
       <c r="J108" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K108" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L108" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="109">
-      <c r="B109" s="10" t="s">
-        <v>176</v>
+      <c r="B109" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="C109" s="5">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="D109" s="6">
-        <v>3125.67</v>
+        <v>111.28</v>
       </c>
       <c r="E109" s="6">
-        <v>21879.7</v>
+        <v>111.28</v>
       </c>
       <c r="F109" s="6">
-        <v>2695.3</v>
+        <v>225.22</v>
       </c>
       <c r="G109" s="6">
-        <v>18867.1</v>
-      </c>
-      <c r="H109" s="12">
-        <v>-3012.6</v>
-      </c>
-      <c r="I109" s="13">
-        <v>-0.1377</v>
+        <v>225.22</v>
+      </c>
+      <c r="H109" s="11">
+        <v>113.94</v>
+      </c>
+      <c r="I109" s="8">
+        <v>1.0239</v>
       </c>
       <c r="J109" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K109" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L109" s="9" t="s">
         <v>17</v>
@@ -4841,1069 +4835,1338 @@
     </row>
     <row r="110">
       <c r="B110" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C110" s="5">
-        <v>20.0</v>
+        <v>1.0</v>
       </c>
       <c r="D110" s="6">
-        <v>988.13</v>
+        <v>142.65</v>
       </c>
       <c r="E110" s="6">
-        <v>19762.5</v>
+        <v>142.65</v>
       </c>
       <c r="F110" s="6">
-        <v>929.3</v>
+        <v>241.5</v>
       </c>
       <c r="G110" s="6">
-        <v>18586.0</v>
-      </c>
-      <c r="H110" s="12">
-        <v>-1176.5</v>
-      </c>
-      <c r="I110" s="13">
-        <v>-0.0595</v>
+        <v>241.5</v>
+      </c>
+      <c r="H110" s="11">
+        <v>98.85</v>
+      </c>
+      <c r="I110" s="8">
+        <v>0.693</v>
+      </c>
+      <c r="J110" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K110" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L110" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="111">
       <c r="B111" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C111" s="5">
-        <v>110.0</v>
+        <v>1.0</v>
       </c>
       <c r="D111" s="5">
-        <v>181.04</v>
+        <v>165.85</v>
       </c>
       <c r="E111" s="6">
-        <v>19914.4</v>
+        <v>165.85</v>
       </c>
       <c r="F111" s="6">
-        <v>167.95</v>
+        <v>252.6</v>
       </c>
       <c r="G111" s="6">
-        <v>18474.5</v>
-      </c>
-      <c r="H111" s="12">
-        <v>-1439.9</v>
-      </c>
-      <c r="I111" s="13">
-        <v>-0.0723</v>
+        <v>252.6</v>
+      </c>
+      <c r="H111" s="11">
+        <v>86.75</v>
+      </c>
+      <c r="I111" s="8">
+        <v>0.5231</v>
+      </c>
+      <c r="J111" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K111" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L111" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="112">
-      <c r="B112" s="10" t="s">
-        <v>179</v>
+      <c r="B112" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="C112" s="5">
-        <v>91.0</v>
+        <v>1.0</v>
       </c>
       <c r="D112" s="5">
-        <v>173.53</v>
+        <v>25.25</v>
       </c>
       <c r="E112" s="6">
-        <v>15791.45</v>
+        <v>25.25</v>
       </c>
       <c r="F112" s="6">
-        <v>201.07</v>
+        <v>109.0</v>
       </c>
       <c r="G112" s="6">
-        <v>18297.37</v>
+        <v>109.0</v>
       </c>
       <c r="H112" s="11">
-        <v>2505.92</v>
+        <v>83.75</v>
       </c>
       <c r="I112" s="8">
-        <v>0.1587</v>
+        <v>3.3168</v>
+      </c>
+      <c r="J112" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K112" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L112" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="113">
       <c r="B113" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C113" s="5">
-        <v>72.0</v>
+        <v>20.0</v>
       </c>
       <c r="D113" s="5">
-        <v>275.75</v>
+        <v>988.13</v>
       </c>
       <c r="E113" s="6">
-        <v>19853.65</v>
+        <v>19762.5</v>
       </c>
       <c r="F113" s="6">
-        <v>251.75</v>
+        <v>991.55</v>
       </c>
       <c r="G113" s="6">
-        <v>18126.0</v>
-      </c>
-      <c r="H113" s="12">
-        <v>-1727.65</v>
-      </c>
-      <c r="I113" s="13">
-        <v>-0.087</v>
+        <v>19831.0</v>
+      </c>
+      <c r="H113" s="11">
+        <v>68.5</v>
+      </c>
+      <c r="I113" s="8">
+        <v>0.0035</v>
+      </c>
+      <c r="J113" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K113" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L113" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="114">
-      <c r="B114" s="3" t="s">
-        <v>181</v>
+      <c r="B114" s="10" t="s">
+        <v>183</v>
       </c>
       <c r="C114" s="5">
-        <v>32.0</v>
+        <v>42.0</v>
       </c>
       <c r="D114" s="6">
-        <v>619.5</v>
+        <v>820.32</v>
       </c>
       <c r="E114" s="6">
-        <v>19824.0</v>
+        <v>34453.5</v>
       </c>
       <c r="F114" s="6">
-        <v>562.0</v>
+        <v>821.95</v>
       </c>
       <c r="G114" s="6">
-        <v>17984.0</v>
-      </c>
-      <c r="H114" s="12">
-        <v>-1840.0</v>
-      </c>
-      <c r="I114" s="13">
-        <v>-0.0928</v>
+        <v>34521.9</v>
+      </c>
+      <c r="H114" s="11">
+        <v>68.4</v>
+      </c>
+      <c r="I114" s="8">
+        <v>0.002</v>
+      </c>
+      <c r="J114" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K114" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L114" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="115">
       <c r="B115" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C115" s="5">
-        <v>221.0</v>
+        <v>1.0</v>
       </c>
       <c r="D115" s="5">
-        <v>126.22</v>
+        <v>51.86</v>
       </c>
       <c r="E115" s="6">
-        <v>27894.4</v>
+        <v>51.86</v>
       </c>
       <c r="F115" s="6">
-        <v>80.44</v>
+        <v>100.48</v>
       </c>
       <c r="G115" s="6">
-        <v>17777.24</v>
-      </c>
-      <c r="H115" s="12">
-        <v>-10117.16</v>
-      </c>
-      <c r="I115" s="13">
-        <v>-0.3627</v>
+        <v>100.48</v>
+      </c>
+      <c r="H115" s="11">
+        <v>48.62</v>
+      </c>
+      <c r="I115" s="8">
+        <v>0.9375</v>
+      </c>
+      <c r="J115" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K115" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L115" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="116">
       <c r="B116" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C116" s="5">
-        <v>23.0</v>
+        <v>1.0</v>
       </c>
       <c r="D116" s="6">
-        <v>1205.77</v>
+        <v>116.0</v>
       </c>
       <c r="E116" s="6">
-        <v>27732.8</v>
+        <v>116.0</v>
       </c>
       <c r="F116" s="6">
-        <v>769.35</v>
+        <v>99.15</v>
       </c>
       <c r="G116" s="6">
-        <v>17695.05</v>
-      </c>
-      <c r="H116" s="12">
-        <v>-10037.75</v>
-      </c>
-      <c r="I116" s="13">
-        <v>-0.3619</v>
+        <v>99.15</v>
+      </c>
+      <c r="H116" s="13">
+        <v>-16.85</v>
+      </c>
+      <c r="I116" s="14">
+        <v>-0.1453</v>
+      </c>
+      <c r="J116" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K116" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L116" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="117">
       <c r="B117" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C117" s="5">
-        <v>46.0</v>
-      </c>
-      <c r="D117" s="5">
-        <v>430.98</v>
+        <v>1.0</v>
+      </c>
+      <c r="D117" s="6">
+        <v>1935.3</v>
       </c>
       <c r="E117" s="6">
-        <v>19824.9</v>
+        <v>1935.3</v>
       </c>
       <c r="F117" s="6">
-        <v>380.0</v>
+        <v>1790.0</v>
       </c>
       <c r="G117" s="6">
-        <v>17480.0</v>
-      </c>
-      <c r="H117" s="12">
-        <v>-2344.9</v>
-      </c>
-      <c r="I117" s="13">
-        <v>-0.1183</v>
+        <v>1790.0</v>
+      </c>
+      <c r="H117" s="13">
+        <v>-145.3</v>
+      </c>
+      <c r="I117" s="14">
+        <v>-0.0751</v>
+      </c>
+      <c r="J117" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K117" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="L117" s="9" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="118">
       <c r="B118" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C118" s="5">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="D118" s="6">
-        <v>1963.23</v>
+        <v>162.33</v>
       </c>
       <c r="E118" s="6">
-        <v>19632.3</v>
+        <v>811.65</v>
       </c>
       <c r="F118" s="6">
-        <v>1721.8</v>
+        <v>126.6</v>
       </c>
       <c r="G118" s="6">
-        <v>17218.0</v>
-      </c>
-      <c r="H118" s="12">
-        <v>-2414.3</v>
-      </c>
-      <c r="I118" s="13">
-        <v>-0.123</v>
+        <v>633.0</v>
+      </c>
+      <c r="H118" s="13">
+        <v>-178.65</v>
+      </c>
+      <c r="I118" s="14">
+        <v>-0.2201</v>
+      </c>
+      <c r="J118" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K118" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L118" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="119">
       <c r="B119" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C119" s="5">
-        <v>72.0</v>
+        <v>3.0</v>
       </c>
       <c r="D119" s="5">
-        <v>278.55</v>
+        <v>394.42</v>
       </c>
       <c r="E119" s="6">
-        <v>20055.6</v>
+        <v>1183.25</v>
       </c>
       <c r="F119" s="6">
-        <v>211.35</v>
+        <v>304.65</v>
       </c>
       <c r="G119" s="6">
-        <v>15217.2</v>
-      </c>
-      <c r="H119" s="14">
-        <v>-4838.4</v>
-      </c>
-      <c r="I119" s="13">
-        <v>-0.2412</v>
+        <v>913.95</v>
+      </c>
+      <c r="H119" s="15">
+        <v>-269.3</v>
+      </c>
+      <c r="I119" s="14">
+        <v>-0.2276</v>
+      </c>
+      <c r="J119" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K119" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L119" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="120">
-      <c r="B120" s="10" t="s">
-        <v>187</v>
+      <c r="B120" s="3" t="s">
+        <v>189</v>
       </c>
       <c r="C120" s="5">
-        <v>50.0</v>
+        <v>32.0</v>
       </c>
       <c r="D120" s="6">
-        <v>292.7</v>
+        <v>619.5</v>
       </c>
       <c r="E120" s="6">
-        <v>14635.0</v>
+        <v>19824.0</v>
       </c>
       <c r="F120" s="6">
-        <v>294.5</v>
+        <v>603.9</v>
       </c>
       <c r="G120" s="6">
-        <v>14725.0</v>
+        <v>19324.8</v>
       </c>
       <c r="H120" s="15">
-        <v>90.0</v>
-      </c>
-      <c r="I120" s="8">
-        <v>0.0061</v>
+        <v>-499.2</v>
+      </c>
+      <c r="I120" s="14">
+        <v>-0.0252</v>
+      </c>
+      <c r="J120" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K120" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L120" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="121">
-      <c r="B121" s="3" t="s">
-        <v>188</v>
+      <c r="B121" s="10" t="s">
+        <v>190</v>
       </c>
       <c r="C121" s="5">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
       <c r="D121" s="6">
-        <v>6635.5</v>
+        <v>855.56</v>
       </c>
       <c r="E121" s="6">
-        <v>13271.0</v>
+        <v>11122.3</v>
       </c>
       <c r="F121" s="6">
-        <v>7283.5</v>
+        <v>801.0</v>
       </c>
       <c r="G121" s="6">
-        <v>14567.0</v>
-      </c>
-      <c r="H121" s="11">
-        <v>1296.0</v>
-      </c>
-      <c r="I121" s="8">
-        <v>0.0977</v>
+        <v>10413.0</v>
+      </c>
+      <c r="H121" s="13">
+        <v>-709.3</v>
+      </c>
+      <c r="I121" s="14">
+        <v>-0.0638</v>
+      </c>
+      <c r="J121" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K121" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L121" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="122">
       <c r="B122" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C122" s="5">
-        <v>10.0</v>
-      </c>
-      <c r="D122" s="5">
-        <v>975.8</v>
+        <v>1.0</v>
+      </c>
+      <c r="D122" s="6">
+        <v>1526.5</v>
       </c>
       <c r="E122" s="6">
-        <v>9758.0</v>
+        <v>1526.5</v>
       </c>
       <c r="F122" s="6">
-        <v>1433.0</v>
+        <v>761.55</v>
       </c>
       <c r="G122" s="6">
-        <v>14330.0</v>
-      </c>
-      <c r="H122" s="11">
-        <v>4572.0</v>
-      </c>
-      <c r="I122" s="8">
-        <v>0.4685</v>
+        <v>761.55</v>
+      </c>
+      <c r="H122" s="13">
+        <v>-764.95</v>
+      </c>
+      <c r="I122" s="14">
+        <v>-0.5011</v>
+      </c>
+      <c r="J122" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K122" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L122" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="123">
-      <c r="B123" s="10" t="s">
-        <v>190</v>
+      <c r="B123" s="3" t="s">
+        <v>192</v>
       </c>
       <c r="C123" s="5">
-        <v>9.0</v>
+        <v>72.0</v>
       </c>
       <c r="D123" s="6">
-        <v>1722.96</v>
+        <v>275.75</v>
       </c>
       <c r="E123" s="6">
-        <v>15506.6</v>
+        <v>19853.65</v>
       </c>
       <c r="F123" s="6">
-        <v>1562.6</v>
+        <v>265.1</v>
       </c>
       <c r="G123" s="6">
-        <v>14063.4</v>
-      </c>
-      <c r="H123" s="12">
-        <v>-1443.2</v>
-      </c>
-      <c r="I123" s="13">
-        <v>-0.0931</v>
+        <v>19087.2</v>
+      </c>
+      <c r="H123" s="13">
+        <v>-766.45</v>
+      </c>
+      <c r="I123" s="14">
+        <v>-0.0386</v>
+      </c>
+      <c r="J123" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K123" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L123" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="124">
       <c r="B124" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C124" s="5">
-        <v>3.0</v>
+        <v>148.0</v>
       </c>
       <c r="D124" s="6">
-        <v>5480.0</v>
+        <v>67.59</v>
       </c>
       <c r="E124" s="6">
-        <v>16440.0</v>
+        <v>10003.56</v>
       </c>
       <c r="F124" s="6">
-        <v>4353.5</v>
+        <v>62.23</v>
       </c>
       <c r="G124" s="6">
-        <v>13060.5</v>
-      </c>
-      <c r="H124" s="12">
-        <v>-3379.5</v>
-      </c>
-      <c r="I124" s="13">
-        <v>-0.2056</v>
+        <v>9210.04</v>
+      </c>
+      <c r="H124" s="13">
+        <v>-793.52</v>
+      </c>
+      <c r="I124" s="14">
+        <v>-0.0793</v>
+      </c>
+      <c r="J124" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K124" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L124" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="125">
       <c r="B125" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C125" s="5">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
       <c r="D125" s="6">
-        <v>1023.34</v>
+        <v>1722.96</v>
       </c>
       <c r="E125" s="6">
-        <v>15350.15</v>
+        <v>15506.6</v>
       </c>
       <c r="F125" s="6">
-        <v>816.8</v>
+        <v>1628.5</v>
       </c>
       <c r="G125" s="6">
-        <v>12252.0</v>
-      </c>
-      <c r="H125" s="12">
-        <v>-3098.15</v>
-      </c>
-      <c r="I125" s="13">
-        <v>-0.2018</v>
+        <v>14656.5</v>
+      </c>
+      <c r="H125" s="13">
+        <v>-850.1</v>
+      </c>
+      <c r="I125" s="14">
+        <v>-0.0548</v>
+      </c>
+      <c r="J125" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K125" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L125" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="126">
       <c r="B126" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C126" s="5">
-        <v>50.0</v>
+        <v>110.0</v>
       </c>
       <c r="D126" s="5">
-        <v>238.76</v>
+        <v>181.04</v>
       </c>
       <c r="E126" s="6">
-        <v>11938.1</v>
+        <v>19914.4</v>
       </c>
       <c r="F126" s="6">
-        <v>242.12</v>
+        <v>170.65</v>
       </c>
       <c r="G126" s="6">
-        <v>12106.0</v>
-      </c>
-      <c r="H126" s="11">
-        <v>167.9</v>
-      </c>
-      <c r="I126" s="8">
-        <v>0.0141</v>
+        <v>18771.5</v>
+      </c>
+      <c r="H126" s="13">
+        <v>-1142.9</v>
+      </c>
+      <c r="I126" s="14">
+        <v>-0.0574</v>
+      </c>
+      <c r="J126" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K126" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L126" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="127">
       <c r="B127" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C127" s="5">
-        <v>68.0</v>
+        <v>228.0</v>
       </c>
       <c r="D127" s="6">
-        <v>174.16</v>
+        <v>94.74</v>
       </c>
       <c r="E127" s="6">
-        <v>11842.88</v>
+        <v>21599.94</v>
       </c>
       <c r="F127" s="6">
-        <v>176.29</v>
+        <v>89.57</v>
       </c>
       <c r="G127" s="6">
-        <v>11987.72</v>
-      </c>
-      <c r="H127" s="11">
-        <v>144.84</v>
-      </c>
-      <c r="I127" s="8">
-        <v>0.0122</v>
+        <v>20421.96</v>
+      </c>
+      <c r="H127" s="13">
+        <v>-1177.98</v>
+      </c>
+      <c r="I127" s="14">
+        <v>-0.0545</v>
+      </c>
+      <c r="J127" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K127" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L127" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="128">
       <c r="B128" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C128" s="5">
-        <v>14.0</v>
-      </c>
-      <c r="D128" s="5">
-        <v>855.63</v>
+        <v>10.0</v>
+      </c>
+      <c r="D128" s="6">
+        <v>1963.23</v>
       </c>
       <c r="E128" s="6">
-        <v>11978.75</v>
+        <v>19632.3</v>
       </c>
       <c r="F128" s="6">
-        <v>819.25</v>
+        <v>1842.9</v>
       </c>
       <c r="G128" s="6">
-        <v>11469.5</v>
-      </c>
-      <c r="H128" s="12">
-        <v>-509.25</v>
-      </c>
-      <c r="I128" s="13">
-        <v>-0.0425</v>
+        <v>18429.0</v>
+      </c>
+      <c r="H128" s="13">
+        <v>-1203.3</v>
+      </c>
+      <c r="I128" s="14">
+        <v>-0.0613</v>
+      </c>
+      <c r="J128" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K128" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L128" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="129">
-      <c r="B129" s="10" t="s">
-        <v>196</v>
+      <c r="B129" s="3" t="s">
+        <v>198</v>
       </c>
       <c r="C129" s="5">
-        <v>95.0</v>
+        <v>249.0</v>
       </c>
       <c r="D129" s="6">
-        <v>158.81</v>
+        <v>134.11</v>
       </c>
       <c r="E129" s="6">
-        <v>15087.3</v>
+        <v>33392.27</v>
       </c>
       <c r="F129" s="6">
-        <v>112.2</v>
+        <v>128.28</v>
       </c>
       <c r="G129" s="6">
-        <v>10659.0</v>
-      </c>
-      <c r="H129" s="12">
-        <v>-4428.3</v>
-      </c>
-      <c r="I129" s="13">
-        <v>-0.2935</v>
+        <v>31941.72</v>
+      </c>
+      <c r="H129" s="13">
+        <v>-1450.55</v>
+      </c>
+      <c r="I129" s="14">
+        <v>-0.0434</v>
+      </c>
+      <c r="J129" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K129" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L129" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="130">
       <c r="B130" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C130" s="5">
-        <v>92.0</v>
+        <v>46.0</v>
       </c>
       <c r="D130" s="6">
-        <v>108.55</v>
+        <v>430.98</v>
       </c>
       <c r="E130" s="6">
-        <v>9986.6</v>
+        <v>19824.9</v>
       </c>
       <c r="F130" s="6">
-        <v>102.84</v>
+        <v>390.45</v>
       </c>
       <c r="G130" s="6">
-        <v>9461.28</v>
-      </c>
-      <c r="H130" s="12">
-        <v>-525.32</v>
-      </c>
-      <c r="I130" s="13">
-        <v>-0.0526</v>
+        <v>17960.7</v>
+      </c>
+      <c r="H130" s="13">
+        <v>-1864.2</v>
+      </c>
+      <c r="I130" s="14">
+        <v>-0.094</v>
+      </c>
+      <c r="J130" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K130" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L130" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="131">
       <c r="B131" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C131" s="5">
-        <v>50.0</v>
-      </c>
-      <c r="D131" s="5">
-        <v>198.2</v>
+        <v>7.0</v>
+      </c>
+      <c r="D131" s="6">
+        <v>3125.67</v>
       </c>
       <c r="E131" s="6">
-        <v>9910.0</v>
+        <v>21879.7</v>
       </c>
       <c r="F131" s="6">
-        <v>182.7</v>
+        <v>2806.6</v>
       </c>
       <c r="G131" s="6">
-        <v>9135.0</v>
-      </c>
-      <c r="H131" s="14">
-        <v>-775.0</v>
-      </c>
-      <c r="I131" s="13">
-        <v>-0.0782</v>
+        <v>19646.2</v>
+      </c>
+      <c r="H131" s="15">
+        <v>-2233.5</v>
+      </c>
+      <c r="I131" s="14">
+        <v>-0.1021</v>
+      </c>
+      <c r="J131" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K131" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L131" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="132">
       <c r="B132" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C132" s="5">
-        <v>20.0</v>
+        <v>3.0</v>
       </c>
       <c r="D132" s="6">
-        <v>369.45</v>
+        <v>5480.0</v>
       </c>
       <c r="E132" s="6">
-        <v>7389.0</v>
+        <v>16440.0</v>
       </c>
       <c r="F132" s="6">
-        <v>436.7</v>
+        <v>4610.0</v>
       </c>
       <c r="G132" s="6">
-        <v>8734.0</v>
-      </c>
-      <c r="H132" s="11">
-        <v>1345.0</v>
-      </c>
-      <c r="I132" s="8">
-        <v>0.182</v>
+        <v>13830.0</v>
+      </c>
+      <c r="H132" s="13">
+        <v>-2610.0</v>
+      </c>
+      <c r="I132" s="14">
+        <v>-0.1588</v>
+      </c>
+      <c r="J132" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K132" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L132" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="133">
       <c r="B133" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C133" s="5">
-        <v>148.0</v>
-      </c>
-      <c r="D133" s="5">
-        <v>67.59</v>
+        <v>15.0</v>
+      </c>
+      <c r="D133" s="6">
+        <v>1023.34</v>
       </c>
       <c r="E133" s="6">
-        <v>10003.56</v>
+        <v>15350.15</v>
       </c>
       <c r="F133" s="6">
-        <v>56.38</v>
+        <v>833.0</v>
       </c>
       <c r="G133" s="6">
-        <v>8344.24</v>
-      </c>
-      <c r="H133" s="12">
-        <v>-1659.32</v>
-      </c>
-      <c r="I133" s="13">
-        <v>-0.1659</v>
+        <v>12495.0</v>
+      </c>
+      <c r="H133" s="13">
+        <v>-2855.15</v>
+      </c>
+      <c r="I133" s="14">
+        <v>-0.186</v>
+      </c>
+      <c r="J133" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K133" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L133" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="134">
-      <c r="B134" s="10" t="s">
-        <v>201</v>
+      <c r="B134" s="3" t="s">
+        <v>203</v>
       </c>
       <c r="C134" s="5">
-        <v>3.0</v>
+        <v>72.0</v>
       </c>
       <c r="D134" s="6">
-        <v>1154.83</v>
+        <v>278.55</v>
       </c>
       <c r="E134" s="6">
-        <v>3464.5</v>
+        <v>20055.6</v>
       </c>
       <c r="F134" s="6">
-        <v>1940.0</v>
+        <v>228.86</v>
       </c>
       <c r="G134" s="6">
-        <v>5820.0</v>
+        <v>16477.92</v>
       </c>
       <c r="H134" s="15">
-        <v>2355.5</v>
-      </c>
-      <c r="I134" s="8">
-        <v>0.6799</v>
+        <v>-3577.68</v>
+      </c>
+      <c r="I134" s="14">
+        <v>-0.1784</v>
+      </c>
+      <c r="J134" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K134" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L134" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="135">
       <c r="B135" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C135" s="5">
-        <v>39.0</v>
+        <v>95.0</v>
       </c>
       <c r="D135" s="5">
-        <v>379.94</v>
+        <v>158.81</v>
       </c>
       <c r="E135" s="6">
-        <v>14817.69</v>
+        <v>15087.3</v>
       </c>
       <c r="F135" s="6">
-        <v>90.83</v>
+        <v>120.2</v>
       </c>
       <c r="G135" s="6">
-        <v>3542.37</v>
-      </c>
-      <c r="H135" s="12">
-        <v>-11275.32</v>
-      </c>
-      <c r="I135" s="13">
-        <v>-0.7609</v>
+        <v>11419.0</v>
+      </c>
+      <c r="H135" s="13">
+        <v>-3668.3</v>
+      </c>
+      <c r="I135" s="14">
+        <v>-0.2431</v>
+      </c>
+      <c r="J135" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K135" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L135" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="136">
       <c r="B136" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C136" s="5">
-        <v>11.0</v>
+        <v>67.0</v>
       </c>
       <c r="D136" s="5">
-        <v>80.54</v>
+        <v>374.48</v>
       </c>
       <c r="E136" s="6">
-        <v>885.9</v>
+        <v>25090.1</v>
       </c>
       <c r="F136" s="6">
-        <v>262.3</v>
+        <v>300.75</v>
       </c>
       <c r="G136" s="6">
-        <v>2885.3</v>
-      </c>
-      <c r="H136" s="11">
-        <v>1999.4</v>
-      </c>
-      <c r="I136" s="8">
-        <v>2.2569</v>
+        <v>20150.25</v>
+      </c>
+      <c r="H136" s="13">
+        <v>-4939.85</v>
+      </c>
+      <c r="I136" s="14">
+        <v>-0.1969</v>
+      </c>
+      <c r="J136" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K136" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L136" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="137">
       <c r="B137" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C137" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D137" s="5">
-        <v>415.9</v>
+        <v>21.0</v>
+      </c>
+      <c r="D137" s="6">
+        <v>1220.91</v>
       </c>
       <c r="E137" s="6">
-        <v>415.9</v>
+        <v>25639.1</v>
       </c>
       <c r="F137" s="6">
-        <v>1923.8</v>
+        <v>984.7</v>
       </c>
       <c r="G137" s="6">
-        <v>1923.8</v>
+        <v>20678.7</v>
       </c>
       <c r="H137" s="15">
-        <v>1507.9</v>
-      </c>
-      <c r="I137" s="8">
-        <v>3.6256</v>
+        <v>-4960.4</v>
+      </c>
+      <c r="I137" s="14">
+        <v>-0.1935</v>
+      </c>
+      <c r="J137" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K137" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L137" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="138">
-      <c r="B138" s="10" t="s">
-        <v>205</v>
+      <c r="B138" s="3" t="s">
+        <v>207</v>
       </c>
       <c r="C138" s="5">
-        <v>1.0</v>
+        <v>53.0</v>
       </c>
       <c r="D138" s="6">
-        <v>1935.3</v>
+        <v>729.68</v>
       </c>
       <c r="E138" s="6">
-        <v>1935.3</v>
+        <v>38672.9</v>
       </c>
       <c r="F138" s="6">
-        <v>1683.95</v>
+        <v>620.4</v>
       </c>
       <c r="G138" s="6">
-        <v>1683.95</v>
-      </c>
-      <c r="H138" s="14">
-        <v>-251.35</v>
-      </c>
-      <c r="I138" s="13">
-        <v>-0.1299</v>
+        <v>32881.2</v>
+      </c>
+      <c r="H138" s="15">
+        <v>-5791.7</v>
+      </c>
+      <c r="I138" s="14">
+        <v>-0.1498</v>
+      </c>
+      <c r="J138" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K138" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L138" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="139">
       <c r="B139" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C139" s="5">
-        <v>3.0</v>
+        <v>226.0</v>
       </c>
       <c r="D139" s="5">
-        <v>394.42</v>
+        <v>136.74</v>
       </c>
       <c r="E139" s="6">
-        <v>1183.25</v>
+        <v>30902.6</v>
       </c>
       <c r="F139" s="6">
-        <v>289.05</v>
+        <v>110.35</v>
       </c>
       <c r="G139" s="6">
-        <v>867.15</v>
-      </c>
-      <c r="H139" s="14">
-        <v>-316.1</v>
-      </c>
-      <c r="I139" s="13">
-        <v>-0.2671</v>
+        <v>24939.1</v>
+      </c>
+      <c r="H139" s="15">
+        <v>-5963.5</v>
+      </c>
+      <c r="I139" s="14">
+        <v>-0.193</v>
+      </c>
+      <c r="J139" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K139" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L139" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="140">
       <c r="B140" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C140" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D140" s="5">
-        <v>588.9</v>
+        <v>33.0</v>
+      </c>
+      <c r="D140" s="6">
+        <v>1071.83</v>
       </c>
       <c r="E140" s="6">
-        <v>588.9</v>
+        <v>35370.25</v>
       </c>
       <c r="F140" s="6">
-        <v>762.0</v>
+        <v>870.95</v>
       </c>
       <c r="G140" s="6">
-        <v>762.0</v>
+        <v>28741.35</v>
       </c>
       <c r="H140" s="15">
-        <v>173.1</v>
-      </c>
-      <c r="I140" s="8">
-        <v>0.2939</v>
+        <v>-6628.9</v>
+      </c>
+      <c r="I140" s="14">
+        <v>-0.1874</v>
+      </c>
+      <c r="J140" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K140" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L140" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="141">
       <c r="B141" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C141" s="5">
-        <v>1.0</v>
+        <v>221.0</v>
       </c>
       <c r="D141" s="6">
-        <v>1526.5</v>
+        <v>126.22</v>
       </c>
       <c r="E141" s="6">
-        <v>1526.5</v>
+        <v>27894.4</v>
       </c>
       <c r="F141" s="6">
-        <v>736.4</v>
+        <v>85.66</v>
       </c>
       <c r="G141" s="6">
-        <v>736.4</v>
-      </c>
-      <c r="H141" s="14">
-        <v>-790.1</v>
-      </c>
-      <c r="I141" s="13">
-        <v>-0.5176</v>
+        <v>18930.86</v>
+      </c>
+      <c r="H141" s="15">
+        <v>-8963.54</v>
+      </c>
+      <c r="I141" s="14">
+        <v>-0.3213</v>
+      </c>
+      <c r="J141" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K141" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L141" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="142">
       <c r="B142" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C142" s="5">
-        <v>1.0</v>
+        <v>59.0</v>
       </c>
       <c r="D142" s="5">
-        <v>262.0</v>
+        <v>576.82</v>
       </c>
       <c r="E142" s="6">
-        <v>262.0</v>
+        <v>34032.35</v>
       </c>
       <c r="F142" s="6">
-        <v>560.75</v>
+        <v>423.85</v>
       </c>
       <c r="G142" s="6">
-        <v>560.75</v>
+        <v>25007.15</v>
       </c>
       <c r="H142" s="15">
-        <v>298.75</v>
-      </c>
-      <c r="I142" s="8">
-        <v>1.1403</v>
+        <v>-9025.2</v>
+      </c>
+      <c r="I142" s="14">
+        <v>-0.2652</v>
+      </c>
+      <c r="J142" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K142" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L142" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="143">
       <c r="B143" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C143" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D143" s="5">
-        <v>53.6</v>
+        <v>23.0</v>
+      </c>
+      <c r="D143" s="6">
+        <v>1205.77</v>
       </c>
       <c r="E143" s="6">
-        <v>53.6</v>
+        <v>27732.8</v>
       </c>
       <c r="F143" s="6">
-        <v>480.1</v>
+        <v>796.0</v>
       </c>
       <c r="G143" s="6">
-        <v>480.1</v>
+        <v>18308.0</v>
       </c>
       <c r="H143" s="15">
-        <v>426.5</v>
-      </c>
-      <c r="I143" s="8">
-        <v>7.9571</v>
+        <v>-9424.8</v>
+      </c>
+      <c r="I143" s="14">
+        <v>-0.3398</v>
+      </c>
+      <c r="J143" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K143" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L143" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="144">
-      <c r="B144" s="10" t="s">
-        <v>211</v>
+      <c r="B144" s="3" t="s">
+        <v>213</v>
       </c>
       <c r="C144" s="5">
-        <v>1.0</v>
+        <v>69.0</v>
       </c>
       <c r="D144" s="5">
-        <v>119.7</v>
+        <v>463.0</v>
       </c>
       <c r="E144" s="6">
-        <v>119.7</v>
+        <v>31947.25</v>
       </c>
       <c r="F144" s="6">
-        <v>320.4</v>
+        <v>303.2</v>
       </c>
       <c r="G144" s="6">
-        <v>320.4</v>
+        <v>20920.8</v>
       </c>
       <c r="H144" s="15">
-        <v>200.7</v>
-      </c>
-      <c r="I144" s="8">
-        <v>1.6767</v>
+        <v>-11026.45</v>
+      </c>
+      <c r="I144" s="14">
+        <v>-0.3451</v>
+      </c>
+      <c r="J144" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K144" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="L144" s="9" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="145">
       <c r="B145" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C145" s="4">
-        <v>1.0</v>
+        <v>39.0</v>
       </c>
       <c r="D145" s="5">
-        <v>165.85</v>
+        <v>379.94</v>
       </c>
       <c r="E145" s="6">
-        <v>165.85</v>
+        <v>14817.69</v>
       </c>
       <c r="F145" s="6">
-        <v>249.2</v>
+        <v>90.86</v>
       </c>
       <c r="G145" s="6">
-        <v>249.2</v>
+        <v>3543.54</v>
       </c>
       <c r="H145" s="15">
-        <v>83.35</v>
-      </c>
-      <c r="I145" s="8">
-        <v>0.5026</v>
+        <v>-11274.15</v>
+      </c>
+      <c r="I145" s="14">
+        <v>-0.7609</v>
+      </c>
+      <c r="J145" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K145" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L145" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="146">
       <c r="B146" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C146" s="4">
-        <v>1.0</v>
+        <v>552.0</v>
       </c>
       <c r="D146" s="5">
-        <v>142.65</v>
+        <v>63.33</v>
       </c>
       <c r="E146" s="6">
-        <v>142.65</v>
+        <v>17796.09</v>
       </c>
       <c r="F146" s="6">
-        <v>231.04</v>
+        <v>34.0</v>
       </c>
       <c r="G146" s="6">
-        <v>231.04</v>
+        <v>18768.0</v>
       </c>
       <c r="H146" s="15">
-        <v>88.39</v>
-      </c>
-      <c r="I146" s="8">
-        <v>0.6196</v>
+        <v>-16188.61</v>
+      </c>
+      <c r="I146" s="14">
+        <v>-0.4631</v>
+      </c>
+      <c r="J146" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K146" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L146" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="147">
-      <c r="B147" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C147" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="D147" s="5">
-        <v>111.28</v>
-      </c>
-      <c r="E147" s="6">
-        <v>111.28</v>
-      </c>
-      <c r="F147" s="6">
-        <v>217.56</v>
-      </c>
-      <c r="G147" s="6">
-        <v>217.56</v>
-      </c>
-      <c r="H147" s="15">
-        <v>106.28</v>
-      </c>
-      <c r="I147" s="8">
-        <v>0.9551</v>
-      </c>
+      <c r="B147" s="3"/>
+      <c r="C147" s="4"/>
+      <c r="D147" s="5"/>
+      <c r="E147" s="6"/>
+      <c r="F147" s="6"/>
+      <c r="G147" s="6"/>
+      <c r="H147" s="12"/>
+      <c r="I147" s="8"/>
     </row>
     <row r="148">
-      <c r="B148" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C148" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="D148" s="5">
-        <v>25.25</v>
-      </c>
-      <c r="E148" s="6">
-        <v>25.25</v>
-      </c>
-      <c r="F148" s="6">
-        <v>103.32</v>
-      </c>
-      <c r="G148" s="6">
-        <v>103.32</v>
-      </c>
-      <c r="H148" s="15">
-        <v>78.07</v>
-      </c>
-      <c r="I148" s="8">
-        <v>3.0919</v>
-      </c>
+      <c r="B148" s="3"/>
+      <c r="C148" s="4"/>
+      <c r="D148" s="5"/>
+      <c r="E148" s="6"/>
+      <c r="F148" s="6"/>
+      <c r="G148" s="6"/>
+      <c r="H148" s="12"/>
+      <c r="I148" s="8"/>
     </row>
     <row r="149">
-      <c r="B149" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C149" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="D149" s="5">
-        <v>116.0</v>
-      </c>
-      <c r="E149" s="6">
-        <v>116.0</v>
-      </c>
-      <c r="F149" s="6">
-        <v>101.15</v>
-      </c>
-      <c r="G149" s="6">
-        <v>101.15</v>
-      </c>
-      <c r="H149" s="14">
-        <v>-14.85</v>
-      </c>
-      <c r="I149" s="13">
-        <v>-0.128</v>
-      </c>
+      <c r="B149" s="3"/>
+      <c r="C149" s="4"/>
+      <c r="D149" s="5"/>
+      <c r="E149" s="6"/>
+      <c r="F149" s="6"/>
+      <c r="G149" s="6"/>
+      <c r="H149" s="15"/>
+      <c r="I149" s="14"/>
     </row>
     <row r="150">
-      <c r="B150" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C150" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D150" s="5">
-        <v>51.86</v>
-      </c>
-      <c r="E150" s="6">
-        <v>51.86</v>
-      </c>
-      <c r="F150" s="6">
-        <v>95.25</v>
-      </c>
-      <c r="G150" s="6">
-        <v>95.25</v>
-      </c>
-      <c r="H150" s="15">
-        <v>43.39</v>
-      </c>
-      <c r="I150" s="8">
-        <v>0.8366</v>
-      </c>
+      <c r="B150" s="3"/>
+      <c r="C150" s="5"/>
+      <c r="D150" s="5"/>
+      <c r="E150" s="6"/>
+      <c r="F150" s="6"/>
+      <c r="G150" s="6"/>
+      <c r="H150" s="12"/>
+      <c r="I150" s="8"/>
     </row>
     <row r="151">
       <c r="E151" s="16"/>

--- a/data/portfolio.xlsx
+++ b/data/portfolio.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="225">
   <si>
     <t>Symbol</t>
   </si>
@@ -52,10 +52,10 @@
     <t>3,08,166.76</t>
   </si>
   <si>
-    <t>11,75,860.92</t>
-  </si>
-  <si>
-    <t>8,67,694.16</t>
+    <t>11,61,900.48</t>
+  </si>
+  <si>
+    <t>8,53,733.72</t>
   </si>
   <si>
     <t>N</t>
@@ -73,22 +73,22 @@
     <t>1,83,396.90</t>
   </si>
   <si>
-    <t>6,98,553.90</t>
-  </si>
-  <si>
-    <t>5,15,157.00</t>
+    <t>6,93,000.45</t>
+  </si>
+  <si>
+    <t>5,09,603.55</t>
   </si>
   <si>
     <t>AEROFLEX</t>
   </si>
   <si>
-    <t>1,79,710.57</t>
-  </si>
-  <si>
-    <t>4,50,576.00</t>
-  </si>
-  <si>
-    <t>2,70,865.43</t>
+    <t>1,89,534.37</t>
+  </si>
+  <si>
+    <t>4,77,697.95</t>
+  </si>
+  <si>
+    <t>2,88,163.58</t>
   </si>
   <si>
     <t>G</t>
@@ -106,10 +106,10 @@
     <t>1,24,501.80</t>
   </si>
   <si>
-    <t>3,74,775.20</t>
-  </si>
-  <si>
-    <t>2,50,273.40</t>
+    <t>3,81,191.00</t>
+  </si>
+  <si>
+    <t>2,56,689.20</t>
   </si>
   <si>
     <t>HCG</t>
@@ -118,547 +118,574 @@
     <t>1,91,353.60</t>
   </si>
   <si>
-    <t>3,88,389.75</t>
-  </si>
-  <si>
-    <t>1,97,036.15</t>
+    <t>3,80,625.00</t>
+  </si>
+  <si>
+    <t>1,89,271.40</t>
+  </si>
+  <si>
+    <t>PARKHOSPS</t>
+  </si>
+  <si>
+    <t>1,42,295.53</t>
+  </si>
+  <si>
+    <t>2,45,324.80</t>
+  </si>
+  <si>
+    <t>1,03,029.27</t>
+  </si>
+  <si>
+    <t>1. Oct'25 Must buy</t>
+  </si>
+  <si>
+    <t>SONACOMS</t>
+  </si>
+  <si>
+    <t>2,26,780.25</t>
+  </si>
+  <si>
+    <t>2,43,060.75</t>
+  </si>
+  <si>
+    <t>KAMDHENU</t>
+  </si>
+  <si>
+    <t>1,85,908.02</t>
+  </si>
+  <si>
+    <t>2,01,883.08</t>
+  </si>
+  <si>
+    <t>3.May'26 Must buy</t>
+  </si>
+  <si>
+    <t>3MINDIA</t>
+  </si>
+  <si>
+    <t>DEEDEV-T</t>
+  </si>
+  <si>
+    <t>1,84,607.25</t>
+  </si>
+  <si>
+    <t>1,17,833.30</t>
+  </si>
+  <si>
+    <t>SANSERA</t>
+  </si>
+  <si>
+    <t>1,65,480.00</t>
+  </si>
+  <si>
+    <t>INGERRAND</t>
+  </si>
+  <si>
+    <t>1,57,606.20</t>
+  </si>
+  <si>
+    <t>TRITURBINE</t>
+  </si>
+  <si>
+    <t>1,26,763.15</t>
+  </si>
+  <si>
+    <t>1,53,571.00</t>
+  </si>
+  <si>
+    <t>INOXINDIA</t>
+  </si>
+  <si>
+    <t>1,07,617.20</t>
+  </si>
+  <si>
+    <t>1,51,624.40</t>
+  </si>
+  <si>
+    <t>ELGIEQUIP</t>
+  </si>
+  <si>
+    <t>1,35,467.90</t>
+  </si>
+  <si>
+    <t>1,50,160.50</t>
+  </si>
+  <si>
+    <t>NEPHROPLUS</t>
+  </si>
+  <si>
+    <t>1,29,287.90</t>
+  </si>
+  <si>
+    <t>1,47,512.40</t>
+  </si>
+  <si>
+    <t>ASTRAMICRO</t>
+  </si>
+  <si>
+    <t>1,45,864.20</t>
+  </si>
+  <si>
+    <t>1,23,166.50</t>
+  </si>
+  <si>
+    <t>ASTERDM</t>
+  </si>
+  <si>
+    <t>1,44,304.65</t>
+  </si>
+  <si>
+    <t>THERMAX</t>
+  </si>
+  <si>
+    <t>1,32,916.50</t>
+  </si>
+  <si>
+    <t>1,42,665.00</t>
   </si>
   <si>
     <t>POWERINDIA</t>
   </si>
   <si>
-    <t>1,37,780.00</t>
-  </si>
-  <si>
-    <t>1,28,996.35</t>
-  </si>
-  <si>
-    <t>ASTRAMICRO</t>
-  </si>
-  <si>
-    <t>1,48,187.20</t>
-  </si>
-  <si>
-    <t>1,25,489.50</t>
-  </si>
-  <si>
-    <t>DEEDEV-T</t>
-  </si>
-  <si>
-    <t>1,75,822.50</t>
-  </si>
-  <si>
-    <t>1,09,048.55</t>
-  </si>
-  <si>
-    <t>PARKHOSPS</t>
-  </si>
-  <si>
-    <t>1,42,295.53</t>
-  </si>
-  <si>
-    <t>2,45,728.00</t>
-  </si>
-  <si>
-    <t>1,03,432.47</t>
-  </si>
-  <si>
-    <t>1. Oct'25 Must buy</t>
+    <t>1,39,020.00</t>
+  </si>
+  <si>
+    <t>1,30,236.35</t>
   </si>
   <si>
     <t>MTARTECH</t>
   </si>
   <si>
-    <t>1,27,368.00</t>
-  </si>
-  <si>
-    <t>ASTERDM</t>
-  </si>
-  <si>
-    <t>1,49,840.40</t>
+    <t>1,32,534.00</t>
+  </si>
+  <si>
+    <t>1,03,666.65</t>
+  </si>
+  <si>
+    <t>NLCINDIA</t>
+  </si>
+  <si>
+    <t>1,14,553.65</t>
+  </si>
+  <si>
+    <t>1,27,273.20</t>
+  </si>
+  <si>
+    <t>CYIENTDLM</t>
+  </si>
+  <si>
+    <t>1,14,647.15</t>
+  </si>
+  <si>
+    <t>1,18,208.45</t>
+  </si>
+  <si>
+    <t>SIEMENS</t>
+  </si>
+  <si>
+    <t>JNKINDIA</t>
+  </si>
+  <si>
+    <t>1,12,443.75</t>
+  </si>
+  <si>
+    <t>KENNAMET</t>
+  </si>
+  <si>
+    <t>1,09,360.80</t>
+  </si>
+  <si>
+    <t>SJVN</t>
+  </si>
+  <si>
+    <t>1,09,462.55</t>
+  </si>
+  <si>
+    <t>1,07,252.65</t>
+  </si>
+  <si>
+    <t>GALAPREC</t>
+  </si>
+  <si>
+    <t>1,03,241.95</t>
   </si>
   <si>
     <t>NEULANDLAB</t>
   </si>
   <si>
-    <t>1,02,294.00</t>
+    <t>1,02,211.80</t>
+  </si>
+  <si>
+    <t>MODISONLTD-T</t>
+  </si>
+  <si>
+    <t>TRIVENI</t>
   </si>
   <si>
     <t>AVANTEL</t>
   </si>
   <si>
-    <t>SANSERA</t>
-  </si>
-  <si>
-    <t>1,63,534.00</t>
+    <t>ISGEC</t>
+  </si>
+  <si>
+    <t>1,02,322.55</t>
+  </si>
+  <si>
+    <t>SOUTHWEST</t>
+  </si>
+  <si>
+    <t>SASKEN</t>
+  </si>
+  <si>
+    <t>MENONBE</t>
+  </si>
+  <si>
+    <t>NIFTYBEES</t>
   </si>
   <si>
     <t>HBLENGINE</t>
   </si>
   <si>
-    <t>JNKINDIA</t>
-  </si>
-  <si>
-    <t>1,13,006.25</t>
-  </si>
-  <si>
-    <t>INOXINDIA</t>
-  </si>
-  <si>
-    <t>1,07,617.20</t>
-  </si>
-  <si>
-    <t>1,51,192.80</t>
-  </si>
-  <si>
-    <t>MODISONLTD-T</t>
+    <t>HAPPYFORGE</t>
+  </si>
+  <si>
+    <t>PFC</t>
+  </si>
+  <si>
+    <t>GRINDWELL</t>
+  </si>
+  <si>
+    <t>ENRIN</t>
+  </si>
+  <si>
+    <t>SUZLON</t>
+  </si>
+  <si>
+    <t>ARE&amp;M</t>
+  </si>
+  <si>
+    <t>SKFINDUS</t>
+  </si>
+  <si>
+    <t>INDGN</t>
+  </si>
+  <si>
+    <t>SCODATUBES</t>
+  </si>
+  <si>
+    <t>UTI NIFTY 50 INDEX FUND - DIRECT PLAN</t>
+  </si>
+  <si>
+    <t>WELCORP</t>
   </si>
   <si>
     <t>RIR</t>
   </si>
   <si>
-    <t>UTI NIFTY 50 INDEX FUND - DIRECT PLAN</t>
-  </si>
-  <si>
-    <t>SOUTHWEST</t>
-  </si>
-  <si>
-    <t>TRITURBINE</t>
-  </si>
-  <si>
-    <t>1,26,763.15</t>
-  </si>
-  <si>
-    <t>1,53,559.50</t>
+    <t>HLEGLAS</t>
+  </si>
+  <si>
+    <t>SALZERELEC</t>
   </si>
   <si>
     <t>RUBICON</t>
   </si>
   <si>
-    <t>GALAPREC</t>
+    <t>GIPCL</t>
+  </si>
+  <si>
+    <t>WENDT</t>
+  </si>
+  <si>
+    <t>HEG</t>
+  </si>
+  <si>
+    <t>POWERICA</t>
+  </si>
+  <si>
+    <t>SCI</t>
+  </si>
+  <si>
+    <t>ASHIANA</t>
+  </si>
+  <si>
+    <t>RKSWAMY</t>
+  </si>
+  <si>
+    <t>BLUEJET</t>
+  </si>
+  <si>
+    <t>RATEGAIN</t>
+  </si>
+  <si>
+    <t>KPIGREEN</t>
+  </si>
+  <si>
+    <t>INDUSTOWER</t>
+  </si>
+  <si>
+    <t>TREL</t>
+  </si>
+  <si>
+    <t>LAXMIDENTL</t>
+  </si>
+  <si>
+    <t>EIMCOELECO</t>
+  </si>
+  <si>
+    <t>RAMCOSYS</t>
+  </si>
+  <si>
+    <t>CARBORUNIV</t>
   </si>
   <si>
     <t>SHREEJISPG</t>
   </si>
   <si>
-    <t>SASKEN</t>
-  </si>
-  <si>
-    <t>HAPPYFORGE</t>
-  </si>
-  <si>
-    <t>NEPHROPLUS</t>
-  </si>
-  <si>
-    <t>1,29,287.90</t>
-  </si>
-  <si>
-    <t>1,46,013.00</t>
-  </si>
-  <si>
-    <t>SONACOMS</t>
-  </si>
-  <si>
-    <t>2,26,780.25</t>
-  </si>
-  <si>
-    <t>2,42,736.75</t>
-  </si>
-  <si>
-    <t>WELCORP</t>
-  </si>
-  <si>
-    <t>NIFTYBEES</t>
+    <t>SGIL</t>
+  </si>
+  <si>
+    <t>STALLION</t>
+  </si>
+  <si>
+    <t>GMDCLTD</t>
+  </si>
+  <si>
+    <t>ENTERO</t>
   </si>
   <si>
     <t>NETWEB</t>
   </si>
   <si>
-    <t>NLCINDIA</t>
-  </si>
-  <si>
-    <t>ELGIEQUIP</t>
-  </si>
-  <si>
-    <t>1,35,467.90</t>
-  </si>
-  <si>
-    <t>1,48,408.75</t>
-  </si>
-  <si>
-    <t>KENNAMET</t>
-  </si>
-  <si>
-    <t>1,02,884.40</t>
-  </si>
-  <si>
-    <t>3.May'26 Must buy</t>
-  </si>
-  <si>
-    <t>KAMDHENU</t>
-  </si>
-  <si>
-    <t>RAMCOSYS</t>
-  </si>
-  <si>
-    <t>MENONBE</t>
-  </si>
-  <si>
-    <t>THERMAX</t>
-  </si>
-  <si>
-    <t>1,32,916.50</t>
-  </si>
-  <si>
-    <t>1,40,329.50</t>
-  </si>
-  <si>
-    <t>RATEGAIN</t>
-  </si>
-  <si>
-    <t>GMDCLTD</t>
-  </si>
-  <si>
-    <t>ENRIN</t>
-  </si>
-  <si>
-    <t>SKFINDUS</t>
-  </si>
-  <si>
-    <t>INDUSTOWER</t>
-  </si>
-  <si>
-    <t>LAXMIDENTL</t>
-  </si>
-  <si>
-    <t>TRIVENI</t>
-  </si>
-  <si>
-    <t>SCI</t>
-  </si>
-  <si>
-    <t>RKSWAMY</t>
-  </si>
-  <si>
-    <t>ASHIANA</t>
-  </si>
-  <si>
-    <t>ENTERO</t>
-  </si>
-  <si>
-    <t>HEG</t>
-  </si>
-  <si>
-    <t>CYIENTDLM</t>
-  </si>
-  <si>
-    <t>1,14,647.15</t>
-  </si>
-  <si>
-    <t>1,14,004.20</t>
-  </si>
-  <si>
-    <t>PFC</t>
-  </si>
-  <si>
-    <t>CARBORUNIV</t>
-  </si>
-  <si>
-    <t>TREL</t>
-  </si>
-  <si>
-    <t>SJVN</t>
-  </si>
-  <si>
-    <t>1,09,462.55</t>
-  </si>
-  <si>
-    <t>1,07,633.55</t>
-  </si>
-  <si>
-    <t>GIPCL</t>
-  </si>
-  <si>
-    <t>SIEMENS</t>
-  </si>
-  <si>
-    <t>1,18,257.30</t>
-  </si>
-  <si>
-    <t>1,15,345.60</t>
-  </si>
-  <si>
-    <t>BLUEJET</t>
-  </si>
-  <si>
-    <t>INGERRAND</t>
-  </si>
-  <si>
-    <t>1,55,891.70</t>
-  </si>
-  <si>
-    <t>1,51,675.20</t>
-  </si>
-  <si>
-    <t>INDGN</t>
-  </si>
-  <si>
-    <t>POWERICA</t>
-  </si>
-  <si>
-    <t>ARE&amp;M</t>
-  </si>
-  <si>
-    <t>SCODATUBES</t>
-  </si>
-  <si>
-    <t>NESCO</t>
-  </si>
-  <si>
-    <t>EIMCOELECO</t>
-  </si>
-  <si>
-    <t>3MINDIA</t>
-  </si>
-  <si>
-    <t>1,99,812.35</t>
-  </si>
-  <si>
-    <t>1,90,212.00</t>
-  </si>
-  <si>
-    <t>ISGEC</t>
-  </si>
-  <si>
-    <t>1,02,322.55</t>
-  </si>
-  <si>
-    <t>SALZERELEC</t>
-  </si>
-  <si>
     <t>RPTECH</t>
   </si>
   <si>
+    <t>TEJASNET</t>
+  </si>
+  <si>
+    <t>AVALON</t>
+  </si>
+  <si>
+    <t>RAYMOND</t>
+  </si>
+  <si>
+    <t>HONAUT</t>
+  </si>
+  <si>
     <t>UNIVCABLES</t>
   </si>
   <si>
+    <t>YATHARTH</t>
+  </si>
+  <si>
+    <t>SIGNPOST</t>
+  </si>
+  <si>
+    <t>BOROSCI</t>
+  </si>
+  <si>
+    <t>PROTEAN</t>
+  </si>
+  <si>
+    <t>GMRAIRPORT</t>
+  </si>
+  <si>
+    <t>URBANCO</t>
+  </si>
+  <si>
+    <t>FRACTAL</t>
+  </si>
+  <si>
+    <t>MAPMYINDIA</t>
+  </si>
+  <si>
+    <t>GRAPHITE</t>
+  </si>
+  <si>
+    <t>GESHIP</t>
+  </si>
+  <si>
+    <t>BIOCON</t>
+  </si>
+  <si>
+    <t>SHILPAMED</t>
+  </si>
+  <si>
+    <t>DLINKINDIA</t>
+  </si>
+  <si>
+    <t>SHANKARA-T</t>
+  </si>
+  <si>
+    <t>ANURAS</t>
+  </si>
+  <si>
+    <t>LANDMARK</t>
+  </si>
+  <si>
     <t>INCAP-X</t>
   </si>
   <si>
+    <t>KIRLPNU</t>
+  </si>
+  <si>
+    <t>PTC</t>
+  </si>
+  <si>
+    <t>DIFFNKG</t>
+  </si>
+  <si>
     <t>DATAPATTNS</t>
   </si>
   <si>
-    <t>SHILPAMED</t>
-  </si>
-  <si>
     <t>FREDUN-X</t>
   </si>
   <si>
-    <t>GESHIP</t>
-  </si>
-  <si>
-    <t>TEJASNET</t>
-  </si>
-  <si>
-    <t>AVALON</t>
+    <t>LATENTVIEW</t>
+  </si>
+  <si>
+    <t>GULFOILLUB</t>
+  </si>
+  <si>
+    <t>KSB</t>
+  </si>
+  <si>
+    <t>NIITLTD</t>
+  </si>
+  <si>
+    <t>CMSINFO</t>
+  </si>
+  <si>
+    <t>RAYMONDREL</t>
+  </si>
+  <si>
+    <t>PITTIENG</t>
+  </si>
+  <si>
+    <t>MOSCHIP</t>
+  </si>
+  <si>
+    <t>MMP</t>
+  </si>
+  <si>
+    <t>BBL</t>
+  </si>
+  <si>
+    <t>CLEANMAX</t>
+  </si>
+  <si>
+    <t>OMINFRAL</t>
+  </si>
+  <si>
+    <t>CESC</t>
+  </si>
+  <si>
+    <t>WHIRLPOOL</t>
+  </si>
+  <si>
+    <t>INTERARCH</t>
+  </si>
+  <si>
+    <t>RUSTOMJEE</t>
+  </si>
+  <si>
+    <t>CAPACITE</t>
+  </si>
+  <si>
+    <t>RAILTEL</t>
   </si>
   <si>
     <t>AFFLE</t>
   </si>
   <si>
-    <t>RAYMOND</t>
-  </si>
-  <si>
-    <t>PTC</t>
-  </si>
-  <si>
-    <t>MOSCHIP</t>
-  </si>
-  <si>
-    <t>BOROSCI</t>
-  </si>
-  <si>
-    <t>DIFFNKG</t>
-  </si>
-  <si>
-    <t>GRAPHITE</t>
-  </si>
-  <si>
-    <t>GMRAIRPORT</t>
-  </si>
-  <si>
-    <t>ANURAS</t>
+    <t>SKFINDIA</t>
+  </si>
+  <si>
+    <t>VSTTILLERS</t>
+  </si>
+  <si>
+    <t>GREAVESCOT</t>
+  </si>
+  <si>
+    <t>ASALCBR</t>
+  </si>
+  <si>
+    <t>QUESS</t>
+  </si>
+  <si>
+    <t>ARIS</t>
+  </si>
+  <si>
+    <t>ELDEHSG</t>
+  </si>
+  <si>
+    <t>JYOTICNC</t>
+  </si>
+  <si>
+    <t>IFGLEXPOR</t>
+  </si>
+  <si>
+    <t>TVSELECT</t>
+  </si>
+  <si>
+    <t>EMBDL</t>
+  </si>
+  <si>
+    <t>VASCONEQ-T</t>
   </si>
   <si>
     <t>TATACOMM</t>
   </si>
   <si>
+    <t>UNIECOM</t>
+  </si>
+  <si>
     <t>SUVEN</t>
   </si>
   <si>
-    <t>BIOCON</t>
-  </si>
-  <si>
-    <t>TVSELECT</t>
-  </si>
-  <si>
-    <t>KIRLPNU</t>
-  </si>
-  <si>
-    <t>GRINDWELL</t>
-  </si>
-  <si>
     <t>WOCKPHARMA</t>
   </si>
   <si>
-    <t>STALLION</t>
-  </si>
-  <si>
-    <t>RAILTEL</t>
-  </si>
-  <si>
-    <t>GREAVESCOT</t>
-  </si>
-  <si>
-    <t>FRACTAL</t>
-  </si>
-  <si>
-    <t>HONAUT</t>
-  </si>
-  <si>
-    <t>DLINKINDIA</t>
-  </si>
-  <si>
-    <t>SIGNPOST</t>
+    <t>TEGA</t>
+  </si>
+  <si>
+    <t>EIHOTEL</t>
+  </si>
+  <si>
+    <t>KPITTECH</t>
+  </si>
+  <si>
+    <t>LAKSELEC-X</t>
+  </si>
+  <si>
+    <t>ECOSMOBLTY-T</t>
+  </si>
+  <si>
+    <t>MSTCLTD</t>
   </si>
   <si>
     <t>USHAMART</t>
   </si>
   <si>
-    <t>MSTCLTD</t>
-  </si>
-  <si>
-    <t>QUESS</t>
-  </si>
-  <si>
     <t>MON100-E</t>
   </si>
   <si>
-    <t>LAKSELEC-X</t>
+    <t>VIYASH</t>
+  </si>
+  <si>
+    <t>REDINGTON</t>
   </si>
   <si>
     <t>BOROLTD</t>
   </si>
   <si>
-    <t>REDINGTON</t>
-  </si>
-  <si>
-    <t>VIYASH</t>
-  </si>
-  <si>
     <t>ORIENTHOT</t>
   </si>
   <si>
-    <t>PITTIENG</t>
-  </si>
-  <si>
-    <t>YATHARTH</t>
-  </si>
-  <si>
     <t>ABLBL</t>
   </si>
   <si>
     <t>GAUDIUMIVF-T</t>
-  </si>
-  <si>
-    <t>TEGA</t>
-  </si>
-  <si>
-    <t>ECOSMOBLTY-T</t>
-  </si>
-  <si>
-    <t>EIHOTEL</t>
-  </si>
-  <si>
-    <t>RAYMONDREL</t>
-  </si>
-  <si>
-    <t>ELDEHSG</t>
-  </si>
-  <si>
-    <t>KPITTECH</t>
-  </si>
-  <si>
-    <t>MMP</t>
-  </si>
-  <si>
-    <t>EMBDL</t>
-  </si>
-  <si>
-    <t>SKFINDIA</t>
-  </si>
-  <si>
-    <t>CESC</t>
-  </si>
-  <si>
-    <t>NIITLTD</t>
-  </si>
-  <si>
-    <t>INTERARCH</t>
-  </si>
-  <si>
-    <t>URBANCO</t>
-  </si>
-  <si>
-    <t>RUSTOMJEE</t>
-  </si>
-  <si>
-    <t>BBL</t>
-  </si>
-  <si>
-    <t>VSTTILLERS</t>
-  </si>
-  <si>
-    <t>ASALCBR</t>
-  </si>
-  <si>
-    <t>CAPACITE</t>
-  </si>
-  <si>
-    <t>ARIS</t>
-  </si>
-  <si>
-    <t>CMSINFO</t>
-  </si>
-  <si>
-    <t>GULFOILLUB</t>
-  </si>
-  <si>
-    <t>PROTEAN</t>
-  </si>
-  <si>
-    <t>SHANKARA-T</t>
-  </si>
-  <si>
-    <t>MAPMYINDIA</t>
-  </si>
-  <si>
-    <t>OMINFRAL</t>
-  </si>
-  <si>
-    <t>LANDMARK</t>
-  </si>
-  <si>
-    <t>WHIRLPOOL</t>
-  </si>
-  <si>
-    <t>LATENTVIEW</t>
-  </si>
-  <si>
-    <t>UNIECOM</t>
-  </si>
-  <si>
-    <t>VASCONEQ-T</t>
   </si>
 </sst>
 </file>
@@ -678,6 +705,11 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;Aptos Narrow&quot;"/>
+    </font>
+    <font>
       <sz val="7.0"/>
       <color rgb="FF444444"/>
       <name val="Arial"/>
@@ -686,11 +718,6 @@
       <sz val="7.0"/>
       <color rgb="FF10B983"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <name val="&quot;Aptos Narrow&quot;"/>
     </font>
     <font>
       <sz val="7.0"/>
@@ -743,7 +770,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="28">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -753,34 +780,31 @@
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="5" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -789,8 +813,38 @@
     <xf borderId="1" fillId="3" fontId="5" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="2" fontId="5" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="5" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
@@ -1067,7 +1121,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="5">
-        <v>192.04</v>
+        <v>189.76</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>13</v>
@@ -1076,7 +1130,7 @@
         <v>14</v>
       </c>
       <c r="I2" s="8">
-        <v>2.8157</v>
+        <v>2.7704</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>15</v>
@@ -1102,7 +1156,7 @@
         <v>19</v>
       </c>
       <c r="F3" s="6">
-        <v>1893.1</v>
+        <v>1878.05</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>20</v>
@@ -1111,7 +1165,7 @@
         <v>21</v>
       </c>
       <c r="I3" s="8">
-        <v>2.809</v>
+        <v>2.7787</v>
       </c>
       <c r="J3" s="9" t="s">
         <v>15</v>
@@ -1124,20 +1178,20 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="5">
-        <v>960.0</v>
+        <v>981.0</v>
       </c>
       <c r="D4" s="5">
-        <v>187.2</v>
+        <v>193.21</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>23</v>
       </c>
       <c r="F4" s="5">
-        <v>469.35</v>
+        <v>486.95</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>24</v>
@@ -1146,7 +1200,7 @@
         <v>25</v>
       </c>
       <c r="I4" s="8">
-        <v>1.5072</v>
+        <v>1.5204</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>26</v>
@@ -1159,7 +1213,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="10" t="s">
         <v>29</v>
       </c>
       <c r="C5" s="5">
@@ -1172,7 +1226,7 @@
         <v>30</v>
       </c>
       <c r="F5" s="6">
-        <v>1296.8</v>
+        <v>1319.0</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>31</v>
@@ -1181,7 +1235,7 @@
         <v>32</v>
       </c>
       <c r="I5" s="8">
-        <v>2.0102</v>
+        <v>2.0617</v>
       </c>
       <c r="J5" s="9" t="s">
         <v>15</v>
@@ -1194,7 +1248,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="10" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="5">
@@ -1207,7 +1261,7 @@
         <v>34</v>
       </c>
       <c r="F6" s="6">
-        <v>637.75</v>
+        <v>625.0</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>35</v>
@@ -1216,7 +1270,7 @@
         <v>36</v>
       </c>
       <c r="I6" s="8">
-        <v>1.0297</v>
+        <v>0.9891</v>
       </c>
       <c r="J6" s="9" t="s">
         <v>15</v>
@@ -1229,140 +1283,140 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="10" t="s">
         <v>37</v>
       </c>
       <c r="C7" s="5">
-        <v>4.0</v>
+        <v>896.0</v>
       </c>
       <c r="D7" s="6">
-        <v>2195.91</v>
-      </c>
-      <c r="E7" s="6">
-        <v>8783.65</v>
+        <v>158.81</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>38</v>
       </c>
       <c r="F7" s="6">
-        <v>34445.0</v>
+        <v>273.8</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I7" s="8">
-        <v>14.686</v>
+        <v>0.7241</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C8" s="5">
-        <v>101.0</v>
+        <v>405.0</v>
       </c>
       <c r="D8" s="5">
-        <v>224.73</v>
-      </c>
-      <c r="E8" s="6">
-        <v>22697.7</v>
+        <v>559.95</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F8" s="6">
-        <v>1467.2</v>
+        <v>600.15</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="H8" s="11">
+        <v>16280.5</v>
       </c>
       <c r="I8" s="8">
-        <v>5.5287</v>
+        <v>0.0718</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C9" s="5">
-        <v>255.0</v>
+        <v>6452.0</v>
       </c>
       <c r="D9" s="6">
-        <v>261.86</v>
-      </c>
-      <c r="E9" s="6">
-        <v>66773.95</v>
+        <v>28.81</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="F9" s="6">
-        <v>689.5</v>
+        <v>31.29</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="H9" s="11">
+        <v>15975.06</v>
       </c>
       <c r="I9" s="8">
-        <v>1.6331</v>
+        <v>0.0859</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="3" t="s">
-        <v>46</v>
+      <c r="B10" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="C10" s="5">
-        <v>896.0</v>
+        <v>6.0</v>
       </c>
       <c r="D10" s="6">
-        <v>158.81</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>47</v>
+        <v>33302.06</v>
+      </c>
+      <c r="E10" s="6">
+        <v>199812.35</v>
       </c>
       <c r="F10" s="6">
-        <v>274.25</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="I10" s="8">
-        <v>0.7269</v>
+        <v>31595.05</v>
+      </c>
+      <c r="G10" s="6">
+        <v>189570.3</v>
+      </c>
+      <c r="H10" s="12">
+        <v>-10242.05</v>
+      </c>
+      <c r="I10" s="13">
+        <v>-0.0513</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="L10" s="9" t="s">
         <v>28</v>
@@ -1370,168 +1424,168 @@
     </row>
     <row r="11">
       <c r="B11" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="5">
+        <v>255.0</v>
+      </c>
+      <c r="D11" s="6">
+        <v>261.86</v>
+      </c>
+      <c r="E11" s="6">
+        <v>66773.95</v>
+      </c>
+      <c r="F11" s="6">
+        <v>723.95</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="5">
-        <v>18.0</v>
-      </c>
-      <c r="D11" s="6">
-        <v>1603.74</v>
-      </c>
-      <c r="E11" s="6">
-        <v>28867.35</v>
-      </c>
-      <c r="F11" s="6">
-        <v>7076.0</v>
-      </c>
-      <c r="G11" s="5" t="s">
+      <c r="H11" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H11" s="11">
-        <v>98500.65</v>
-      </c>
       <c r="I11" s="8">
-        <v>3.4122</v>
+        <v>1.7647</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="L11" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="10" t="s">
         <v>53</v>
       </c>
       <c r="C12" s="5">
-        <v>183.0</v>
+        <v>56.0</v>
       </c>
       <c r="D12" s="6">
-        <v>283.78</v>
+        <v>1524.46</v>
       </c>
       <c r="E12" s="6">
-        <v>51931.5</v>
+        <v>85369.7</v>
       </c>
       <c r="F12" s="6">
-        <v>818.8</v>
+        <v>2955.0</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>54</v>
       </c>
       <c r="H12" s="11">
-        <v>97908.9</v>
+        <v>80110.3</v>
       </c>
       <c r="I12" s="8">
-        <v>1.8853</v>
+        <v>0.9384</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="10" t="s">
         <v>55</v>
       </c>
       <c r="C13" s="5">
-        <v>6.0</v>
+        <v>36.0</v>
       </c>
       <c r="D13" s="6">
-        <v>1031.85</v>
+        <v>4330.32</v>
       </c>
       <c r="E13" s="6">
-        <v>6191.1</v>
+        <v>155891.7</v>
       </c>
       <c r="F13" s="6">
-        <v>17049.0</v>
+        <v>4377.95</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>56</v>
       </c>
       <c r="H13" s="11">
-        <v>96102.9</v>
+        <v>1714.5</v>
       </c>
       <c r="I13" s="8">
-        <v>15.5228</v>
+        <v>0.011</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="10" t="s">
         <v>57</v>
       </c>
       <c r="C14" s="5">
-        <v>540.0</v>
+        <v>230.0</v>
       </c>
       <c r="D14" s="5">
-        <v>13.39</v>
-      </c>
-      <c r="E14" s="6">
-        <v>7229.6</v>
+        <v>551.14</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="F14" s="6">
-        <v>168.41</v>
-      </c>
-      <c r="G14" s="6">
-        <v>90941.4</v>
-      </c>
-      <c r="H14" s="11">
-        <v>83711.8</v>
-      </c>
-      <c r="I14" s="8">
-        <v>11.579</v>
+        <v>667.7</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="12">
+        <v>26807.85</v>
+      </c>
+      <c r="I14" s="13">
+        <v>0.2115</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="3" t="s">
-        <v>58</v>
+      <c r="B15" s="10" t="s">
+        <v>60</v>
       </c>
       <c r="C15" s="5">
-        <v>56.0</v>
+        <v>83.0</v>
       </c>
       <c r="D15" s="6">
-        <v>1524.46</v>
-      </c>
-      <c r="E15" s="6">
-        <v>85369.7</v>
+        <v>1296.59</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="F15" s="6">
-        <v>2920.25</v>
+        <v>1826.8</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H15" s="11">
-        <v>78164.3</v>
+        <v>44007.2</v>
       </c>
       <c r="I15" s="8">
-        <v>0.9156</v>
+        <v>0.4089</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>26</v>
@@ -1544,140 +1598,140 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="3" t="s">
-        <v>60</v>
+      <c r="B16" s="10" t="s">
+        <v>63</v>
       </c>
       <c r="C16" s="5">
-        <v>100.0</v>
+        <v>245.0</v>
       </c>
       <c r="D16" s="6">
-        <v>290.95</v>
-      </c>
-      <c r="E16" s="6">
-        <v>29095.0</v>
+        <v>552.93</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="F16" s="6">
-        <v>800.2</v>
-      </c>
-      <c r="G16" s="6">
-        <v>80020.0</v>
-      </c>
-      <c r="H16" s="11">
-        <v>50925.0</v>
-      </c>
-      <c r="I16" s="8">
-        <v>1.7503</v>
+        <v>612.9</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H16" s="12">
+        <v>14692.6</v>
+      </c>
+      <c r="I16" s="13">
+        <v>0.1085</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="s">
-        <v>61</v>
+      <c r="B17" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="C17" s="5">
-        <v>225.0</v>
+        <v>204.0</v>
       </c>
       <c r="D17" s="6">
-        <v>300.93</v>
-      </c>
-      <c r="E17" s="6">
-        <v>67709.81</v>
+        <v>633.76</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="F17" s="6">
-        <v>502.25</v>
+        <v>723.1</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H17" s="11">
-        <v>45296.44</v>
-      </c>
-      <c r="I17" s="8">
-        <v>0.669</v>
+        <v>68</v>
+      </c>
+      <c r="H17" s="12">
+        <v>18224.5</v>
+      </c>
+      <c r="I17" s="13">
+        <v>0.141</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="3" t="s">
-        <v>63</v>
+      <c r="B18" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="C18" s="5">
-        <v>83.0</v>
+        <v>101.0</v>
       </c>
       <c r="D18" s="4">
-        <v>1296.59</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>64</v>
+        <v>224.73</v>
+      </c>
+      <c r="E18" s="6">
+        <v>22697.7</v>
       </c>
       <c r="F18" s="6">
-        <v>1821.6</v>
+        <v>1444.2</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="H18" s="11">
-        <v>43575.6</v>
+        <v>70</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="I18" s="8">
-        <v>0.4049</v>
+        <v>5.4264</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="s">
-        <v>66</v>
+      <c r="B19" s="10" t="s">
+        <v>72</v>
       </c>
       <c r="C19" s="5">
-        <v>269.0</v>
+        <v>183.0</v>
       </c>
       <c r="D19" s="6">
-        <v>171.27</v>
+        <v>283.78</v>
       </c>
       <c r="E19" s="6">
-        <v>46072.27</v>
+        <v>51931.5</v>
       </c>
       <c r="F19" s="6">
-        <v>294.2</v>
-      </c>
-      <c r="G19" s="6">
-        <v>79139.8</v>
+        <v>788.55</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="H19" s="11">
-        <v>33067.53</v>
+        <v>92373.15</v>
       </c>
       <c r="I19" s="8">
-        <v>0.7177</v>
+        <v>1.7787</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L19" s="9" t="s">
         <v>17</v>
@@ -1685,133 +1739,133 @@
     </row>
     <row r="20">
       <c r="B20" s="3" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C20" s="5">
-        <v>401.0</v>
+        <v>30.0</v>
       </c>
       <c r="D20" s="6">
-        <v>91.09</v>
-      </c>
-      <c r="E20" s="6">
-        <v>36527.75</v>
+        <v>4430.55</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="F20" s="6">
-        <v>170.5</v>
-      </c>
-      <c r="G20" s="6">
-        <v>68370.5</v>
+        <v>4755.5</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="H20" s="11">
-        <v>31842.75</v>
+        <v>9748.5</v>
       </c>
       <c r="I20" s="8">
-        <v>0.8717</v>
+        <v>0.0733</v>
       </c>
       <c r="J20" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="D21" s="6">
+        <v>2195.91</v>
+      </c>
+      <c r="E21" s="6">
+        <v>8783.65</v>
+      </c>
+      <c r="F21" s="6">
+        <v>34755.0</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="I21" s="8">
+        <v>14.8271</v>
+      </c>
+      <c r="J21" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="K20" s="9" t="s">
+      <c r="K21" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="L20" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21" s="5">
-        <v>432.33</v>
-      </c>
-      <c r="D21" s="6">
-        <v>92.52</v>
-      </c>
-      <c r="E21" s="6">
-        <v>39998.01</v>
-      </c>
-      <c r="F21" s="6">
-        <v>165.52</v>
-      </c>
-      <c r="G21" s="6">
-        <v>71559.78</v>
-      </c>
-      <c r="H21" s="11">
-        <v>31561.77</v>
-      </c>
-      <c r="I21" s="8">
-        <v>0.7891</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>26</v>
-      </c>
       <c r="L21" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="3" t="s">
-        <v>69</v>
+      <c r="B22" s="10" t="s">
+        <v>80</v>
       </c>
       <c r="C22" s="5">
-        <v>350.0</v>
+        <v>18.0</v>
       </c>
       <c r="D22" s="6">
-        <v>165.99</v>
+        <v>1603.74</v>
       </c>
       <c r="E22" s="6">
-        <v>58095.38</v>
+        <v>28867.35</v>
       </c>
       <c r="F22" s="6">
-        <v>248.1</v>
-      </c>
-      <c r="G22" s="6">
-        <v>86835.0</v>
-      </c>
-      <c r="H22" s="12">
-        <v>28739.62</v>
+        <v>7363.0</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>82</v>
       </c>
       <c r="I22" s="8">
-        <v>0.4947</v>
+        <v>3.5911</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L22" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="3" t="s">
-        <v>70</v>
+      <c r="B23" s="10" t="s">
+        <v>83</v>
       </c>
       <c r="C23" s="4">
-        <v>230.0</v>
+        <v>402.0</v>
       </c>
       <c r="D23" s="6">
-        <v>551.14</v>
+        <v>284.96</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="F23" s="6">
-        <v>667.65</v>
+        <v>316.6</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H23" s="11">
-        <v>26796.35</v>
-      </c>
-      <c r="I23" s="8">
-        <v>0.2114</v>
+        <v>85</v>
+      </c>
+      <c r="H23" s="12">
+        <v>12719.55</v>
+      </c>
+      <c r="I23" s="13">
+        <v>0.111</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>26</v>
@@ -1824,29 +1878,29 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="3" t="s">
-        <v>73</v>
+      <c r="B24" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="C24" s="5">
-        <v>43.0</v>
+        <v>251.0</v>
       </c>
       <c r="D24" s="6">
-        <v>722.52</v>
-      </c>
-      <c r="E24" s="6">
-        <v>31068.3</v>
+        <v>456.76</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="F24" s="6">
-        <v>1277.4</v>
-      </c>
-      <c r="G24" s="6">
-        <v>54928.2</v>
+        <v>470.95</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="H24" s="11">
-        <v>23859.9</v>
+        <v>3561.3</v>
       </c>
       <c r="I24" s="8">
-        <v>0.768</v>
+        <v>0.0311</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>26</v>
@@ -1859,169 +1913,169 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="3" t="s">
-        <v>68</v>
+      <c r="B25" s="10" t="s">
+        <v>89</v>
       </c>
       <c r="C25" s="4">
-        <v>520.788</v>
+        <v>32.0</v>
       </c>
       <c r="D25" s="6">
-        <v>38.4</v>
+        <v>3695.54</v>
       </c>
       <c r="E25" s="6">
-        <v>19998.99</v>
+        <v>118257.3</v>
       </c>
       <c r="F25" s="6">
-        <v>83.39</v>
+        <v>3646.0</v>
       </c>
       <c r="G25" s="6">
-        <v>43429.5</v>
+        <v>116672.0</v>
       </c>
       <c r="H25" s="11">
-        <v>23430.51</v>
+        <v>-1585.3</v>
       </c>
       <c r="I25" s="8">
-        <v>1.1716</v>
+        <v>-0.0134</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="3" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="C26" s="5">
+        <v>225.0</v>
+      </c>
+      <c r="D26" s="6">
+        <v>300.93</v>
+      </c>
+      <c r="E26" s="6">
+        <v>67709.81</v>
+      </c>
+      <c r="F26" s="6">
+        <v>499.75</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H26" s="11">
+        <v>44733.94</v>
+      </c>
+      <c r="I26" s="8">
+        <v>0.6607</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" s="5">
+        <v>36.0</v>
+      </c>
+      <c r="D27" s="6">
+        <v>2574.11</v>
+      </c>
+      <c r="E27" s="6">
+        <v>92668.05</v>
+      </c>
+      <c r="F27" s="6">
+        <v>3037.8</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="H27" s="12">
+        <v>16692.75</v>
+      </c>
+      <c r="I27" s="13">
+        <v>0.1801</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="5">
+        <v>1465.0</v>
+      </c>
+      <c r="D28" s="6">
+        <v>74.72</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F28" s="6">
+        <v>73.21</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H28" s="11">
+        <v>-2209.9</v>
+      </c>
+      <c r="I28" s="8">
+        <v>-0.0202</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="5">
         <v>97.0</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D29" s="6">
         <v>768.77</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E29" s="6">
         <v>74571.2</v>
       </c>
-      <c r="F26" s="6">
-        <v>1004.5</v>
-      </c>
-      <c r="G26" s="6">
-        <v>97436.5</v>
-      </c>
-      <c r="H26" s="11">
-        <v>22865.3</v>
-      </c>
-      <c r="I26" s="8">
-        <v>0.3066</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K26" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" s="5">
-        <v>94.0</v>
-      </c>
-      <c r="D27" s="6">
-        <v>267.98</v>
-      </c>
-      <c r="E27" s="6">
-        <v>25190.12</v>
-      </c>
-      <c r="F27" s="6">
-        <v>488.15</v>
-      </c>
-      <c r="G27" s="6">
-        <v>45886.1</v>
-      </c>
-      <c r="H27" s="11">
-        <v>20695.98</v>
-      </c>
-      <c r="I27" s="8">
-        <v>0.8216</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" s="5">
-        <v>41.0</v>
-      </c>
-      <c r="D28" s="6">
-        <v>1676.93</v>
-      </c>
-      <c r="E28" s="6">
-        <v>68754.3</v>
-      </c>
-      <c r="F28" s="6">
-        <v>2167.4</v>
-      </c>
-      <c r="G28" s="6">
-        <v>88863.4</v>
-      </c>
-      <c r="H28" s="11">
-        <v>20109.1</v>
-      </c>
-      <c r="I28" s="8">
-        <v>0.2925</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L28" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" s="5">
-        <v>59.0</v>
-      </c>
-      <c r="D29" s="6">
-        <v>1056.13</v>
-      </c>
-      <c r="E29" s="6">
-        <v>62311.85</v>
-      </c>
       <c r="F29" s="6">
-        <v>1359.8</v>
-      </c>
-      <c r="G29" s="6">
-        <v>80228.2</v>
+        <v>1064.35</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>98</v>
       </c>
       <c r="H29" s="11">
-        <v>17916.35</v>
+        <v>28670.75</v>
       </c>
       <c r="I29" s="8">
-        <v>0.2875</v>
+        <v>0.3845</v>
       </c>
       <c r="J29" s="9" t="s">
         <v>26</v>
@@ -2035,133 +2089,133 @@
     </row>
     <row r="30">
       <c r="B30" s="10" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="C30" s="4">
-        <v>204.0</v>
+        <v>6.0</v>
       </c>
       <c r="D30" s="6">
-        <v>633.76</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>79</v>
+        <v>1031.85</v>
+      </c>
+      <c r="E30" s="6">
+        <v>6191.1</v>
       </c>
       <c r="F30" s="6">
-        <v>715.75</v>
+        <v>17035.3</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H30" s="11">
-        <v>16725.1</v>
+        <v>96020.7</v>
       </c>
       <c r="I30" s="8">
-        <v>0.1294</v>
+        <v>15.5095</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L30" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="3" t="s">
-        <v>81</v>
+      <c r="B31" s="10" t="s">
+        <v>101</v>
       </c>
       <c r="C31" s="5">
-        <v>405.0</v>
+        <v>334.0</v>
       </c>
       <c r="D31" s="6">
-        <v>559.95</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>82</v>
+        <v>197.26</v>
+      </c>
+      <c r="E31" s="6">
+        <v>65886.52</v>
       </c>
       <c r="F31" s="6">
-        <v>599.35</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="H31" s="12">
-        <v>15956.5</v>
+        <v>295.0</v>
+      </c>
+      <c r="G31" s="6">
+        <v>98530.0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>32643.48</v>
       </c>
       <c r="I31" s="8">
-        <v>0.0704</v>
+        <v>0.4955</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="3" t="s">
-        <v>84</v>
+      <c r="B32" s="10" t="s">
+        <v>102</v>
       </c>
       <c r="C32" s="5">
-        <v>51.0</v>
+        <v>246.0</v>
       </c>
       <c r="D32" s="6">
-        <v>1099.22</v>
+        <v>384.17</v>
       </c>
       <c r="E32" s="6">
-        <v>56060.4</v>
+        <v>94506.1</v>
       </c>
       <c r="F32" s="6">
-        <v>1409.6</v>
+        <v>397.9</v>
       </c>
       <c r="G32" s="6">
-        <v>71889.6</v>
+        <v>97883.4</v>
       </c>
       <c r="H32" s="11">
-        <v>15829.2</v>
+        <v>3377.3</v>
       </c>
       <c r="I32" s="8">
-        <v>0.2824</v>
+        <v>0.0357</v>
       </c>
       <c r="J32" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K32" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="10" t="s">
-        <v>85</v>
+      <c r="B33" s="3" t="s">
+        <v>103</v>
       </c>
       <c r="C33" s="5">
-        <v>300.0</v>
+        <v>540.0</v>
       </c>
       <c r="D33" s="6">
-        <v>220.39</v>
+        <v>13.39</v>
       </c>
       <c r="E33" s="6">
-        <v>66117.0</v>
+        <v>7229.6</v>
       </c>
       <c r="F33" s="6">
-        <v>271.21</v>
+        <v>168.08</v>
       </c>
       <c r="G33" s="6">
-        <v>81363.0</v>
+        <v>90763.2</v>
       </c>
       <c r="H33" s="11">
-        <v>15246.0</v>
+        <v>83533.6</v>
       </c>
       <c r="I33" s="8">
-        <v>0.2306</v>
+        <v>11.5544</v>
       </c>
       <c r="J33" s="9" t="s">
         <v>15</v>
@@ -2174,204 +2228,204 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="3" t="s">
-        <v>86</v>
+      <c r="B34" s="10" t="s">
+        <v>104</v>
       </c>
       <c r="C34" s="5">
-        <v>9.0</v>
+        <v>97.0</v>
       </c>
       <c r="D34" s="6">
-        <v>3066.43</v>
-      </c>
-      <c r="E34" s="6">
-        <v>27597.85</v>
+        <v>1054.87</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="F34" s="6">
-        <v>4643.8</v>
+        <v>919.2</v>
       </c>
       <c r="G34" s="6">
-        <v>41794.2</v>
-      </c>
-      <c r="H34" s="11">
-        <v>14196.35</v>
-      </c>
-      <c r="I34" s="8">
-        <v>0.5144</v>
+        <v>89162.4</v>
+      </c>
+      <c r="H34" s="12">
+        <v>-13160.15</v>
+      </c>
+      <c r="I34" s="13">
+        <v>-0.1286</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="L34" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="3" t="s">
-        <v>87</v>
+      <c r="B35" s="10" t="s">
+        <v>106</v>
       </c>
       <c r="C35" s="5">
-        <v>215.0</v>
+        <v>350.0</v>
       </c>
       <c r="D35" s="6">
-        <v>255.12</v>
+        <v>165.99</v>
       </c>
       <c r="E35" s="6">
-        <v>54850.65</v>
+        <v>58095.38</v>
       </c>
       <c r="F35" s="6">
-        <v>319.1</v>
+        <v>254.0</v>
       </c>
       <c r="G35" s="6">
-        <v>68606.5</v>
+        <v>88900.0</v>
       </c>
       <c r="H35" s="11">
-        <v>13755.85</v>
+        <v>30804.62</v>
       </c>
       <c r="I35" s="8">
-        <v>0.2508</v>
+        <v>0.5302</v>
       </c>
       <c r="J35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L35" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="3" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C36" s="5">
-        <v>245.0</v>
+        <v>41.0</v>
       </c>
       <c r="D36" s="6">
-        <v>552.93</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>89</v>
+        <v>1676.93</v>
+      </c>
+      <c r="E36" s="6">
+        <v>68754.3</v>
       </c>
       <c r="F36" s="6">
-        <v>605.75</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>90</v>
+        <v>2153.9</v>
+      </c>
+      <c r="G36" s="6">
+        <v>88309.9</v>
       </c>
       <c r="H36" s="11">
-        <v>12940.85</v>
+        <v>19555.6</v>
       </c>
       <c r="I36" s="8">
-        <v>0.0955</v>
+        <v>0.2844</v>
       </c>
       <c r="J36" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L36" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="3" t="s">
-        <v>91</v>
+      <c r="B37" s="10" t="s">
+        <v>108</v>
       </c>
       <c r="C37" s="5">
-        <v>36.0</v>
+        <v>522.0</v>
       </c>
       <c r="D37" s="6">
-        <v>2574.11</v>
+        <v>151.95</v>
       </c>
       <c r="E37" s="6">
-        <v>92668.05</v>
+        <v>79316.53</v>
       </c>
       <c r="F37" s="6">
-        <v>2857.9</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="H37" s="11">
-        <v>10216.35</v>
-      </c>
-      <c r="I37" s="8">
-        <v>0.1102</v>
+        <v>169.09</v>
+      </c>
+      <c r="G37" s="6">
+        <v>88264.98</v>
+      </c>
+      <c r="H37" s="12">
+        <v>8948.45</v>
+      </c>
+      <c r="I37" s="13">
+        <v>0.1128</v>
       </c>
       <c r="J37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K37" s="9" t="s">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="L37" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="3" t="s">
-        <v>94</v>
+      <c r="B38" s="10" t="s">
+        <v>109</v>
       </c>
       <c r="C38" s="4">
-        <v>3161.0</v>
+        <v>300.0</v>
       </c>
       <c r="D38" s="6">
-        <v>27.17</v>
+        <v>220.39</v>
       </c>
       <c r="E38" s="6">
-        <v>85878.13</v>
+        <v>66117.0</v>
       </c>
       <c r="F38" s="6">
-        <v>30.3</v>
+        <v>271.39</v>
       </c>
       <c r="G38" s="6">
-        <v>95778.3</v>
+        <v>81417.0</v>
       </c>
       <c r="H38" s="11">
-        <v>9900.17</v>
+        <v>15300.0</v>
       </c>
       <c r="I38" s="8">
-        <v>0.1153</v>
+        <v>0.2314</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="L38" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="3" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="C39" s="5">
-        <v>86.0</v>
+        <v>100.0</v>
       </c>
       <c r="D39" s="6">
-        <v>458.8</v>
+        <v>290.95</v>
       </c>
       <c r="E39" s="6">
-        <v>39456.85</v>
+        <v>29095.0</v>
       </c>
       <c r="F39" s="6">
-        <v>570.0</v>
+        <v>798.35</v>
       </c>
       <c r="G39" s="6">
-        <v>49020.0</v>
+        <v>79835.0</v>
       </c>
       <c r="H39" s="11">
-        <v>9563.15</v>
+        <v>50740.0</v>
       </c>
       <c r="I39" s="8">
-        <v>0.2424</v>
+        <v>1.7439</v>
       </c>
       <c r="J39" s="9" t="s">
         <v>26</v>
@@ -2384,64 +2438,64 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="3" t="s">
-        <v>96</v>
+      <c r="B40" s="10" t="s">
+        <v>111</v>
       </c>
       <c r="C40" s="5">
-        <v>464.0</v>
+        <v>59.0</v>
       </c>
       <c r="D40" s="6">
-        <v>149.72</v>
+        <v>1056.13</v>
       </c>
       <c r="E40" s="6">
-        <v>69468.13</v>
+        <v>62311.85</v>
       </c>
       <c r="F40" s="6">
-        <v>169.2</v>
+        <v>1351.4</v>
       </c>
       <c r="G40" s="6">
-        <v>78508.8</v>
+        <v>79732.6</v>
       </c>
       <c r="H40" s="11">
-        <v>9040.67</v>
+        <v>17420.75</v>
       </c>
       <c r="I40" s="8">
-        <v>0.1301</v>
+        <v>0.2796</v>
       </c>
       <c r="J40" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="L40" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="3" t="s">
-        <v>97</v>
+      <c r="B41" s="10" t="s">
+        <v>112</v>
       </c>
       <c r="C41" s="5">
-        <v>30.0</v>
+        <v>184.0</v>
       </c>
       <c r="D41" s="6">
-        <v>4430.55</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>98</v>
+        <v>431.44</v>
+      </c>
+      <c r="E41" s="6">
+        <v>79384.9</v>
       </c>
       <c r="F41" s="6">
-        <v>4677.65</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>99</v>
+        <v>428.6</v>
+      </c>
+      <c r="G41" s="6">
+        <v>78862.4</v>
       </c>
       <c r="H41" s="11">
-        <v>7413.0</v>
+        <v>-522.5</v>
       </c>
       <c r="I41" s="8">
-        <v>0.0558</v>
+        <v>-0.0066</v>
       </c>
       <c r="J41" s="9" t="s">
         <v>26</v>
@@ -2454,64 +2508,64 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="3" t="s">
-        <v>100</v>
+      <c r="B42" s="10" t="s">
+        <v>113</v>
       </c>
       <c r="C42" s="5">
-        <v>63.0</v>
+        <v>38.0</v>
       </c>
       <c r="D42" s="6">
-        <v>724.23</v>
+        <v>1934.05</v>
       </c>
       <c r="E42" s="6">
-        <v>45626.35</v>
+        <v>73494.0</v>
       </c>
       <c r="F42" s="6">
-        <v>835.75</v>
+        <v>2033.3</v>
       </c>
       <c r="G42" s="6">
-        <v>52652.25</v>
-      </c>
-      <c r="H42" s="12">
-        <v>7025.9</v>
+        <v>77265.4</v>
+      </c>
+      <c r="H42" s="14">
+        <v>3771.4</v>
       </c>
       <c r="I42" s="8">
-        <v>0.154</v>
+        <v>0.0513</v>
       </c>
       <c r="J42" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="L42" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="3" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C43" s="5">
-        <v>72.0</v>
+        <v>21.0</v>
       </c>
       <c r="D43" s="6">
-        <v>529.68</v>
+        <v>3292.31</v>
       </c>
       <c r="E43" s="6">
-        <v>38136.95</v>
+        <v>69138.6</v>
       </c>
       <c r="F43" s="6">
-        <v>619.0</v>
+        <v>3575.0</v>
       </c>
       <c r="G43" s="6">
-        <v>44568.0</v>
+        <v>75075.0</v>
       </c>
       <c r="H43" s="11">
-        <v>6431.05</v>
+        <v>5936.4</v>
       </c>
       <c r="I43" s="8">
-        <v>0.1686</v>
+        <v>0.0859</v>
       </c>
       <c r="J43" s="9" t="s">
         <v>26</v>
@@ -2524,29 +2578,29 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="3" t="s">
-        <v>102</v>
+      <c r="B44" s="10" t="s">
+        <v>115</v>
       </c>
       <c r="C44" s="5">
-        <v>21.0</v>
+        <v>1338.0</v>
       </c>
       <c r="D44" s="6">
-        <v>3292.31</v>
+        <v>56.0</v>
       </c>
       <c r="E44" s="6">
-        <v>69138.6</v>
+        <v>74929.54</v>
       </c>
       <c r="F44" s="6">
-        <v>3589.0</v>
+        <v>56.07</v>
       </c>
       <c r="G44" s="6">
-        <v>75369.0</v>
+        <v>75021.66</v>
       </c>
       <c r="H44" s="11">
-        <v>6230.4</v>
+        <v>92.12</v>
       </c>
       <c r="I44" s="8">
-        <v>0.0901</v>
+        <v>0.0012</v>
       </c>
       <c r="J44" s="9" t="s">
         <v>26</v>
@@ -2559,99 +2613,99 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="3" t="s">
-        <v>103</v>
+      <c r="B45" s="10" t="s">
+        <v>116</v>
       </c>
       <c r="C45" s="5">
-        <v>29.0</v>
+        <v>87.0</v>
       </c>
       <c r="D45" s="6">
-        <v>2346.85</v>
+        <v>903.4</v>
       </c>
       <c r="E45" s="6">
-        <v>68058.7</v>
+        <v>78595.7</v>
       </c>
       <c r="F45" s="6">
-        <v>2447.0</v>
+        <v>842.35</v>
       </c>
       <c r="G45" s="6">
-        <v>70963.0</v>
-      </c>
-      <c r="H45" s="11">
-        <v>2904.3</v>
-      </c>
-      <c r="I45" s="8">
-        <v>0.0427</v>
+        <v>73284.45</v>
+      </c>
+      <c r="H45" s="12">
+        <v>-5311.25</v>
+      </c>
+      <c r="I45" s="13">
+        <v>-0.0676</v>
       </c>
       <c r="J45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="10" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C46" s="5">
-        <v>120.0</v>
+        <v>29.0</v>
       </c>
       <c r="D46" s="6">
-        <v>401.67</v>
+        <v>2346.85</v>
       </c>
       <c r="E46" s="6">
-        <v>48200.4</v>
+        <v>68058.7</v>
       </c>
       <c r="F46" s="6">
-        <v>423.0</v>
+        <v>2500.0</v>
       </c>
       <c r="G46" s="6">
-        <v>50760.0</v>
+        <v>72500.0</v>
       </c>
       <c r="H46" s="11">
-        <v>2559.6</v>
+        <v>4441.3</v>
       </c>
       <c r="I46" s="8">
-        <v>0.0531</v>
+        <v>0.0653</v>
       </c>
       <c r="J46" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K46" s="9" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="L46" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="3" t="s">
-        <v>105</v>
+      <c r="B47" s="10" t="s">
+        <v>118</v>
       </c>
       <c r="C47" s="5">
-        <v>215.0</v>
+        <v>139.0</v>
       </c>
       <c r="D47" s="6">
-        <v>216.6</v>
+        <v>545.81</v>
       </c>
       <c r="E47" s="6">
-        <v>46569.23</v>
+        <v>75867.25</v>
       </c>
       <c r="F47" s="6">
-        <v>228.3</v>
+        <v>520.6</v>
       </c>
       <c r="G47" s="6">
-        <v>49084.5</v>
+        <v>72363.4</v>
       </c>
       <c r="H47" s="11">
-        <v>2515.27</v>
+        <v>-3503.85</v>
       </c>
       <c r="I47" s="8">
-        <v>0.054</v>
+        <v>-0.0462</v>
       </c>
       <c r="J47" s="9" t="s">
         <v>26</v>
@@ -2665,28 +2719,28 @@
     </row>
     <row r="48">
       <c r="B48" s="3" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C48" s="5">
-        <v>246.0</v>
+        <v>546.0</v>
       </c>
       <c r="D48" s="6">
-        <v>384.17</v>
+        <v>135.91</v>
       </c>
       <c r="E48" s="6">
-        <v>94506.1</v>
+        <v>74208.27</v>
       </c>
       <c r="F48" s="6">
-        <v>393.05</v>
+        <v>132.0</v>
       </c>
       <c r="G48" s="6">
-        <v>96690.3</v>
+        <v>72072.0</v>
       </c>
       <c r="H48" s="11">
-        <v>2184.2</v>
+        <v>-2136.27</v>
       </c>
       <c r="I48" s="8">
-        <v>0.0231</v>
+        <v>-0.0288</v>
       </c>
       <c r="J48" s="9" t="s">
         <v>26</v>
@@ -2699,204 +2753,204 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="3" t="s">
-        <v>107</v>
+      <c r="B49" s="10" t="s">
+        <v>120</v>
       </c>
       <c r="C49" s="5">
-        <v>172.0</v>
+        <v>432.33</v>
       </c>
       <c r="D49" s="6">
-        <v>302.02</v>
+        <v>92.52</v>
       </c>
       <c r="E49" s="6">
-        <v>51947.55</v>
+        <v>39998.01</v>
       </c>
       <c r="F49" s="6">
-        <v>312.45</v>
+        <v>165.52</v>
       </c>
       <c r="G49" s="6">
-        <v>53741.4</v>
+        <v>71559.78</v>
       </c>
       <c r="H49" s="11">
-        <v>1793.85</v>
+        <v>31561.77</v>
       </c>
       <c r="I49" s="8">
-        <v>0.0345</v>
+        <v>0.7891</v>
       </c>
       <c r="J49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L49" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C50" s="5">
+        <v>51.0</v>
+      </c>
+      <c r="D50" s="6">
+        <v>1099.22</v>
+      </c>
+      <c r="E50" s="6">
+        <v>56060.4</v>
+      </c>
+      <c r="F50" s="6">
+        <v>1396.5</v>
+      </c>
+      <c r="G50" s="6">
+        <v>71221.5</v>
+      </c>
+      <c r="H50" s="11">
+        <v>15161.1</v>
+      </c>
+      <c r="I50" s="8">
+        <v>0.2704</v>
+      </c>
+      <c r="J50" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K50" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="L49" s="9" t="s">
+      <c r="L50" s="9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C50" s="5">
-        <v>516.0</v>
-      </c>
-      <c r="D50" s="6">
-        <v>97.49</v>
-      </c>
-      <c r="E50" s="6">
-        <v>50306.12</v>
-      </c>
-      <c r="F50" s="6">
-        <v>100.81</v>
-      </c>
-      <c r="G50" s="6">
-        <v>52017.96</v>
-      </c>
-      <c r="H50" s="11">
-        <v>1711.84</v>
-      </c>
-      <c r="I50" s="8">
-        <v>0.034</v>
-      </c>
-      <c r="J50" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K50" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L50" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
     <row r="51">
-      <c r="B51" s="3" t="s">
-        <v>109</v>
+      <c r="B51" s="10" t="s">
+        <v>122</v>
       </c>
       <c r="C51" s="5">
-        <v>145.0</v>
+        <v>401.0</v>
       </c>
       <c r="D51" s="6">
-        <v>362.06</v>
+        <v>91.09</v>
       </c>
       <c r="E51" s="6">
-        <v>52499.2</v>
+        <v>36527.75</v>
       </c>
       <c r="F51" s="6">
-        <v>368.1</v>
+        <v>171.1</v>
       </c>
       <c r="G51" s="6">
-        <v>53374.5</v>
+        <v>68611.1</v>
       </c>
       <c r="H51" s="11">
-        <v>875.3</v>
+        <v>32083.35</v>
       </c>
       <c r="I51" s="8">
-        <v>0.0167</v>
+        <v>0.8783</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="L51" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="3" t="s">
-        <v>110</v>
+      <c r="B52" s="10" t="s">
+        <v>123</v>
       </c>
       <c r="C52" s="5">
-        <v>38.0</v>
+        <v>169.0</v>
       </c>
       <c r="D52" s="6">
-        <v>1111.19</v>
+        <v>353.03</v>
       </c>
       <c r="E52" s="6">
-        <v>42225.2</v>
+        <v>59661.5</v>
       </c>
       <c r="F52" s="6">
-        <v>1128.8</v>
+        <v>386.85</v>
       </c>
       <c r="G52" s="6">
-        <v>42894.4</v>
+        <v>65377.65</v>
       </c>
       <c r="H52" s="11">
-        <v>669.2</v>
+        <v>5716.15</v>
       </c>
       <c r="I52" s="8">
-        <v>0.0158</v>
+        <v>0.0958</v>
       </c>
       <c r="J52" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K52" s="9" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="L52" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="3" t="s">
-        <v>111</v>
+      <c r="B53" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="C53" s="5">
-        <v>102.0</v>
+        <v>94.0</v>
       </c>
       <c r="D53" s="6">
-        <v>540.91</v>
+        <v>846.21</v>
       </c>
       <c r="E53" s="6">
-        <v>55172.45</v>
+        <v>79544.0</v>
       </c>
       <c r="F53" s="6">
-        <v>535.0</v>
+        <v>639.9</v>
       </c>
       <c r="G53" s="6">
-        <v>54570.0</v>
-      </c>
-      <c r="H53" s="13">
-        <v>-602.45</v>
-      </c>
-      <c r="I53" s="14">
-        <v>-0.0109</v>
+        <v>60150.6</v>
+      </c>
+      <c r="H53" s="12">
+        <v>-19393.4</v>
+      </c>
+      <c r="I53" s="13">
+        <v>-0.2438</v>
       </c>
       <c r="J53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K53" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L53" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="3" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="C54" s="5">
-        <v>251.0</v>
+        <v>43.0</v>
       </c>
       <c r="D54" s="6">
-        <v>456.76</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>113</v>
+        <v>722.52</v>
+      </c>
+      <c r="E54" s="6">
+        <v>31068.3</v>
       </c>
       <c r="F54" s="6">
-        <v>454.2</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="H54" s="13">
-        <v>-642.95</v>
-      </c>
-      <c r="I54" s="14">
-        <v>-0.0056</v>
+        <v>1371.45</v>
+      </c>
+      <c r="G54" s="6">
+        <v>58972.35</v>
+      </c>
+      <c r="H54" s="11">
+        <v>27904.05</v>
+      </c>
+      <c r="I54" s="8">
+        <v>0.8982</v>
       </c>
       <c r="J54" s="9" t="s">
         <v>26</v>
@@ -2909,140 +2963,140 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="3" t="s">
-        <v>115</v>
+      <c r="B55" s="10" t="s">
+        <v>126</v>
       </c>
       <c r="C55" s="5">
-        <v>184.0</v>
+        <v>349.0</v>
       </c>
       <c r="D55" s="6">
-        <v>431.44</v>
+        <v>171.34</v>
       </c>
       <c r="E55" s="6">
-        <v>79384.9</v>
+        <v>59799.44</v>
       </c>
       <c r="F55" s="6">
-        <v>427.4</v>
+        <v>163.0</v>
       </c>
       <c r="G55" s="6">
-        <v>78641.6</v>
-      </c>
-      <c r="H55" s="13">
-        <v>-743.3</v>
-      </c>
-      <c r="I55" s="14">
-        <v>-0.0094</v>
+        <v>56887.0</v>
+      </c>
+      <c r="H55" s="11">
+        <v>-2912.44</v>
+      </c>
+      <c r="I55" s="8">
+        <v>-0.0487</v>
       </c>
       <c r="J55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K55" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L55" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="3" t="s">
-        <v>116</v>
+      <c r="B56" s="10" t="s">
+        <v>127</v>
       </c>
       <c r="C56" s="5">
-        <v>43.0</v>
+        <v>7.0</v>
       </c>
       <c r="D56" s="6">
-        <v>1097.89</v>
+        <v>7710.0</v>
       </c>
       <c r="E56" s="6">
-        <v>47209.5</v>
+        <v>53970.0</v>
       </c>
       <c r="F56" s="6">
-        <v>1076.5</v>
+        <v>8000.0</v>
       </c>
       <c r="G56" s="6">
-        <v>46289.5</v>
-      </c>
-      <c r="H56" s="13">
-        <v>-920.0</v>
-      </c>
-      <c r="I56" s="14">
-        <v>-0.0195</v>
+        <v>56000.0</v>
+      </c>
+      <c r="H56" s="11">
+        <v>2030.0</v>
+      </c>
+      <c r="I56" s="8">
+        <v>0.0376</v>
       </c>
       <c r="J56" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K56" s="9" t="s">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="L56" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="3" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="C57" s="4">
-        <v>1891.0</v>
+        <v>102.0</v>
       </c>
       <c r="D57" s="4">
-        <v>26.43</v>
+        <v>540.91</v>
       </c>
       <c r="E57" s="6">
-        <v>49985.02</v>
+        <v>55172.45</v>
       </c>
       <c r="F57" s="6">
-        <v>25.76</v>
+        <v>545.2</v>
       </c>
       <c r="G57" s="6">
-        <v>48712.16</v>
-      </c>
-      <c r="H57" s="13">
-        <v>-1272.86</v>
-      </c>
-      <c r="I57" s="14">
-        <v>-0.0255</v>
+        <v>55610.4</v>
+      </c>
+      <c r="H57" s="11">
+        <v>437.95</v>
+      </c>
+      <c r="I57" s="8">
+        <v>0.0079</v>
       </c>
       <c r="J57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K57" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L57" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="3" t="s">
-        <v>118</v>
+      <c r="B58" s="10" t="s">
+        <v>129</v>
       </c>
       <c r="C58" s="4">
-        <v>1465.0</v>
+        <v>115.0</v>
       </c>
       <c r="D58" s="6">
-        <v>74.72</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>119</v>
+        <v>511.33</v>
+      </c>
+      <c r="E58" s="6">
+        <v>58802.9</v>
       </c>
       <c r="F58" s="6">
-        <v>73.47</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="H58" s="13">
-        <v>-1829.0</v>
-      </c>
-      <c r="I58" s="14">
-        <v>-0.0167</v>
+        <v>479.85</v>
+      </c>
+      <c r="G58" s="6">
+        <v>55182.75</v>
+      </c>
+      <c r="H58" s="12">
+        <v>-3620.15</v>
+      </c>
+      <c r="I58" s="13">
+        <v>-0.0616</v>
       </c>
       <c r="J58" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K58" s="9" t="s">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="L58" s="9" t="s">
         <v>28</v>
@@ -3050,98 +3104,98 @@
     </row>
     <row r="59">
       <c r="B59" s="3" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C59" s="5">
-        <v>349.0</v>
+        <v>172.0</v>
       </c>
       <c r="D59" s="6">
-        <v>171.34</v>
+        <v>302.02</v>
       </c>
       <c r="E59" s="6">
-        <v>59799.44</v>
+        <v>51947.55</v>
       </c>
       <c r="F59" s="6">
-        <v>164.0</v>
+        <v>313.85</v>
       </c>
       <c r="G59" s="6">
-        <v>57236.0</v>
-      </c>
-      <c r="H59" s="13">
-        <v>-2563.44</v>
-      </c>
-      <c r="I59" s="14">
-        <v>-0.0429</v>
+        <v>53982.2</v>
+      </c>
+      <c r="H59" s="11">
+        <v>2034.65</v>
+      </c>
+      <c r="I59" s="8">
+        <v>0.0392</v>
       </c>
       <c r="J59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K59" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L59" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="3" t="s">
-        <v>122</v>
+      <c r="B60" s="10" t="s">
+        <v>131</v>
       </c>
       <c r="C60" s="5">
-        <v>32.0</v>
+        <v>145.0</v>
       </c>
       <c r="D60" s="6">
-        <v>3695.54</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>123</v>
+        <v>362.06</v>
+      </c>
+      <c r="E60" s="6">
+        <v>52499.2</v>
       </c>
       <c r="F60" s="6">
-        <v>3604.55</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="H60" s="13">
-        <v>-2911.7</v>
-      </c>
-      <c r="I60" s="14">
-        <v>-0.0246</v>
+        <v>370.1</v>
+      </c>
+      <c r="G60" s="6">
+        <v>53664.5</v>
+      </c>
+      <c r="H60" s="11">
+        <v>1165.3</v>
+      </c>
+      <c r="I60" s="8">
+        <v>0.0222</v>
       </c>
       <c r="J60" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K60" s="9" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="L60" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="3" t="s">
-        <v>125</v>
+      <c r="B61" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="C61" s="5">
-        <v>102.0</v>
+        <v>516.0</v>
       </c>
       <c r="D61" s="5">
-        <v>550.05</v>
+        <v>97.49</v>
       </c>
       <c r="E61" s="6">
-        <v>56105.6</v>
+        <v>50306.12</v>
       </c>
       <c r="F61" s="6">
-        <v>509.15</v>
+        <v>101.35</v>
       </c>
       <c r="G61" s="6">
-        <v>51933.3</v>
-      </c>
-      <c r="H61" s="13">
-        <v>-4172.3</v>
-      </c>
-      <c r="I61" s="14">
-        <v>-0.0744</v>
+        <v>52296.6</v>
+      </c>
+      <c r="H61" s="11">
+        <v>1990.48</v>
+      </c>
+      <c r="I61" s="8">
+        <v>0.0396</v>
       </c>
       <c r="J61" s="9" t="s">
         <v>26</v>
@@ -3155,63 +3209,63 @@
     </row>
     <row r="62">
       <c r="B62" s="3" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C62" s="4">
-        <v>36.0</v>
+        <v>102.0</v>
       </c>
       <c r="D62" s="6">
-        <v>4330.32</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>127</v>
+        <v>550.05</v>
+      </c>
+      <c r="E62" s="6">
+        <v>56105.6</v>
       </c>
       <c r="F62" s="6">
-        <v>4213.2</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="H62" s="13">
-        <v>-4216.5</v>
-      </c>
-      <c r="I62" s="14">
-        <v>-0.027</v>
+        <v>507.7</v>
+      </c>
+      <c r="G62" s="6">
+        <v>51785.4</v>
+      </c>
+      <c r="H62" s="12">
+        <v>-4320.2</v>
+      </c>
+      <c r="I62" s="13">
+        <v>-0.077</v>
       </c>
       <c r="J62" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K62" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L62" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="3" t="s">
-        <v>129</v>
+      <c r="B63" s="10" t="s">
+        <v>134</v>
       </c>
       <c r="C63" s="4">
-        <v>139.0</v>
+        <v>63.0</v>
       </c>
       <c r="D63" s="5">
-        <v>545.81</v>
+        <v>724.23</v>
       </c>
       <c r="E63" s="6">
-        <v>75867.25</v>
+        <v>45626.35</v>
       </c>
       <c r="F63" s="6">
-        <v>513.4</v>
+        <v>821.7</v>
       </c>
       <c r="G63" s="6">
-        <v>71362.6</v>
-      </c>
-      <c r="H63" s="13">
-        <v>-4504.65</v>
-      </c>
-      <c r="I63" s="14">
-        <v>-0.0594</v>
+        <v>51767.1</v>
+      </c>
+      <c r="H63" s="12">
+        <v>6140.75</v>
+      </c>
+      <c r="I63" s="13">
+        <v>0.1346</v>
       </c>
       <c r="J63" s="9" t="s">
         <v>26</v>
@@ -3224,64 +3278,64 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="3" t="s">
-        <v>130</v>
+      <c r="B64" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="C64" s="5">
-        <v>115.0</v>
+        <v>122.0</v>
       </c>
       <c r="D64" s="5">
-        <v>511.33</v>
+        <v>409.24</v>
       </c>
       <c r="E64" s="6">
-        <v>58802.9</v>
+        <v>49926.75</v>
       </c>
       <c r="F64" s="6">
-        <v>472.1</v>
+        <v>408.1</v>
       </c>
       <c r="G64" s="6">
-        <v>54291.5</v>
-      </c>
-      <c r="H64" s="15">
-        <v>-4511.4</v>
-      </c>
-      <c r="I64" s="14">
-        <v>-0.0767</v>
+        <v>49788.2</v>
+      </c>
+      <c r="H64" s="14">
+        <v>-138.55</v>
+      </c>
+      <c r="I64" s="8">
+        <v>-0.0028</v>
       </c>
       <c r="J64" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K64" s="9" t="s">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="L64" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C65" s="5">
-        <v>87.0</v>
+        <v>120.0</v>
       </c>
       <c r="D65" s="6">
-        <v>903.4</v>
+        <v>401.67</v>
       </c>
       <c r="E65" s="6">
-        <v>78595.7</v>
+        <v>48200.4</v>
       </c>
       <c r="F65" s="6">
-        <v>845.35</v>
+        <v>412.95</v>
       </c>
       <c r="G65" s="6">
-        <v>73545.45</v>
-      </c>
-      <c r="H65" s="13">
-        <v>-5050.25</v>
-      </c>
-      <c r="I65" s="14">
-        <v>-0.0643</v>
+        <v>49554.0</v>
+      </c>
+      <c r="H65" s="11">
+        <v>1353.6</v>
+      </c>
+      <c r="I65" s="8">
+        <v>0.0281</v>
       </c>
       <c r="J65" s="9" t="s">
         <v>26</v>
@@ -3294,29 +3348,29 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="3" t="s">
-        <v>132</v>
+      <c r="B66" s="10" t="s">
+        <v>137</v>
       </c>
       <c r="C66" s="5">
-        <v>546.0</v>
+        <v>1891.0</v>
       </c>
       <c r="D66" s="6">
-        <v>135.91</v>
+        <v>26.43</v>
       </c>
       <c r="E66" s="6">
-        <v>74208.27</v>
+        <v>49985.02</v>
       </c>
       <c r="F66" s="6">
-        <v>126.1</v>
+        <v>25.72</v>
       </c>
       <c r="G66" s="6">
-        <v>68850.6</v>
-      </c>
-      <c r="H66" s="13">
-        <v>-5357.67</v>
-      </c>
-      <c r="I66" s="14">
-        <v>-0.0722</v>
+        <v>48636.52</v>
+      </c>
+      <c r="H66" s="11">
+        <v>-1348.5</v>
+      </c>
+      <c r="I66" s="8">
+        <v>-0.027</v>
       </c>
       <c r="J66" s="9" t="s">
         <v>26</v>
@@ -3329,43 +3383,43 @@
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="3" t="s">
-        <v>133</v>
+      <c r="B67" s="10" t="s">
+        <v>138</v>
       </c>
       <c r="C67" s="5">
-        <v>56.0</v>
+        <v>215.0</v>
       </c>
       <c r="D67" s="6">
-        <v>1229.79</v>
+        <v>216.6</v>
       </c>
       <c r="E67" s="6">
-        <v>68868.1</v>
+        <v>46569.23</v>
       </c>
       <c r="F67" s="6">
-        <v>1107.0</v>
+        <v>225.97</v>
       </c>
       <c r="G67" s="6">
-        <v>61992.0</v>
-      </c>
-      <c r="H67" s="13">
-        <v>-6876.1</v>
-      </c>
-      <c r="I67" s="14">
-        <v>-0.0998</v>
+        <v>48583.55</v>
+      </c>
+      <c r="H67" s="11">
+        <v>2014.32</v>
+      </c>
+      <c r="I67" s="8">
+        <v>0.0433</v>
       </c>
       <c r="J67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K67" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L67" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="3" t="s">
-        <v>134</v>
+      <c r="B68" s="10" t="s">
+        <v>139</v>
       </c>
       <c r="C68" s="5">
         <v>30.0</v>
@@ -3377,16 +3431,16 @@
         <v>54699.2</v>
       </c>
       <c r="F68" s="6">
-        <v>1574.0</v>
+        <v>1618.3</v>
       </c>
       <c r="G68" s="6">
-        <v>47220.0</v>
-      </c>
-      <c r="H68" s="13">
-        <v>-7479.2</v>
-      </c>
-      <c r="I68" s="14">
-        <v>-0.1367</v>
+        <v>48549.0</v>
+      </c>
+      <c r="H68" s="12">
+        <v>-6150.2</v>
+      </c>
+      <c r="I68" s="13">
+        <v>-0.1124</v>
       </c>
       <c r="J68" s="9" t="s">
         <v>26</v>
@@ -3399,70 +3453,70 @@
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="3" t="s">
-        <v>135</v>
+      <c r="B69" s="10" t="s">
+        <v>140</v>
       </c>
       <c r="C69" s="5">
-        <v>6.0</v>
+        <v>86.0</v>
       </c>
       <c r="D69" s="6">
-        <v>33302.06</v>
-      </c>
-      <c r="E69" s="6" t="s">
-        <v>136</v>
+        <v>458.8</v>
+      </c>
+      <c r="E69" s="6">
+        <v>39456.85</v>
       </c>
       <c r="F69" s="6">
-        <v>31702.0</v>
-      </c>
-      <c r="G69" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="H69" s="13">
-        <v>-9600.35</v>
-      </c>
-      <c r="I69" s="14">
-        <v>-0.048</v>
+        <v>550.55</v>
+      </c>
+      <c r="G69" s="6">
+        <v>47347.3</v>
+      </c>
+      <c r="H69" s="12">
+        <v>7890.45</v>
+      </c>
+      <c r="I69" s="13">
+        <v>0.2</v>
       </c>
       <c r="J69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K69" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L69" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C70" s="5">
-        <v>97.0</v>
+        <v>43.0</v>
       </c>
       <c r="D70" s="6">
-        <v>1054.87</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>139</v>
+        <v>1097.89</v>
+      </c>
+      <c r="E70" s="6">
+        <v>47209.5</v>
       </c>
       <c r="F70" s="6">
-        <v>923.6</v>
+        <v>1062.75</v>
       </c>
       <c r="G70" s="6">
-        <v>89589.2</v>
-      </c>
-      <c r="H70" s="13">
-        <v>-12733.35</v>
-      </c>
-      <c r="I70" s="14">
-        <v>-0.1244</v>
+        <v>45698.25</v>
+      </c>
+      <c r="H70" s="11">
+        <v>-1511.25</v>
+      </c>
+      <c r="I70" s="8">
+        <v>-0.032</v>
       </c>
       <c r="J70" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K70" s="9" t="s">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="L70" s="9" t="s">
         <v>28</v>
@@ -3470,28 +3524,28 @@
     </row>
     <row r="71">
       <c r="B71" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C71" s="5">
         <v>94.0</v>
       </c>
       <c r="D71" s="6">
-        <v>846.21</v>
+        <v>267.98</v>
       </c>
       <c r="E71" s="6">
-        <v>79544.0</v>
+        <v>25190.12</v>
       </c>
       <c r="F71" s="6">
-        <v>646.45</v>
+        <v>477.45</v>
       </c>
       <c r="G71" s="6">
-        <v>60766.3</v>
-      </c>
-      <c r="H71" s="13">
-        <v>-18777.7</v>
-      </c>
-      <c r="I71" s="14">
-        <v>-0.2361</v>
+        <v>44880.3</v>
+      </c>
+      <c r="H71" s="11">
+        <v>19690.18</v>
+      </c>
+      <c r="I71" s="8">
+        <v>0.7817</v>
       </c>
       <c r="J71" s="9" t="s">
         <v>26</v>
@@ -3505,28 +3559,28 @@
     </row>
     <row r="72">
       <c r="B72" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C72" s="5">
-        <v>70.0</v>
+        <v>78.0</v>
       </c>
       <c r="D72" s="5">
-        <v>331.82</v>
+        <v>549.37</v>
       </c>
       <c r="E72" s="6">
-        <v>23227.6</v>
+        <v>42850.65</v>
       </c>
       <c r="F72" s="6">
-        <v>562.25</v>
+        <v>564.8</v>
       </c>
       <c r="G72" s="6">
-        <v>39357.5</v>
+        <v>44054.4</v>
       </c>
       <c r="H72" s="11">
-        <v>16129.9</v>
+        <v>1203.75</v>
       </c>
       <c r="I72" s="8">
-        <v>0.6944</v>
+        <v>0.0281</v>
       </c>
       <c r="J72" s="9" t="s">
         <v>26</v>
@@ -3535,33 +3589,33 @@
         <v>26</v>
       </c>
       <c r="L72" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C73" s="5">
-        <v>28.0</v>
+        <v>218.0</v>
       </c>
       <c r="D73" s="5">
-        <v>702.63</v>
+        <v>182.99</v>
       </c>
       <c r="E73" s="6">
-        <v>19673.6</v>
+        <v>39890.84</v>
       </c>
       <c r="F73" s="6">
-        <v>1159.5</v>
+        <v>201.47</v>
       </c>
       <c r="G73" s="6">
-        <v>32466.0</v>
+        <v>43920.46</v>
       </c>
       <c r="H73" s="11">
-        <v>12792.4</v>
+        <v>4029.62</v>
       </c>
       <c r="I73" s="8">
-        <v>0.6502</v>
+        <v>0.101</v>
       </c>
       <c r="J73" s="9" t="s">
         <v>26</v>
@@ -3574,29 +3628,29 @@
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="3" t="s">
-        <v>143</v>
+      <c r="B74" s="10" t="s">
+        <v>145</v>
       </c>
       <c r="C74" s="5">
-        <v>298.0</v>
+        <v>72.0</v>
       </c>
       <c r="D74" s="6">
-        <v>41.79</v>
+        <v>529.68</v>
       </c>
       <c r="E74" s="6">
-        <v>12454.04</v>
+        <v>38136.95</v>
       </c>
       <c r="F74" s="6">
-        <v>79.38</v>
+        <v>606.15</v>
       </c>
       <c r="G74" s="6">
-        <v>23655.24</v>
-      </c>
-      <c r="H74" s="11">
-        <v>11201.2</v>
-      </c>
-      <c r="I74" s="8">
-        <v>0.8994</v>
+        <v>43642.8</v>
+      </c>
+      <c r="H74" s="12">
+        <v>5505.85</v>
+      </c>
+      <c r="I74" s="13">
+        <v>0.1444</v>
       </c>
       <c r="J74" s="9" t="s">
         <v>26</v>
@@ -3610,147 +3664,147 @@
     </row>
     <row r="75">
       <c r="B75" s="3" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="C75" s="5">
-        <v>5.0</v>
+        <v>520.79</v>
       </c>
       <c r="D75" s="6">
-        <v>2134.6</v>
+        <v>38.4</v>
       </c>
       <c r="E75" s="6">
-        <v>10673.0</v>
+        <v>19998.99</v>
       </c>
       <c r="F75" s="6">
-        <v>4356.2</v>
+        <v>83.39</v>
       </c>
       <c r="G75" s="6">
-        <v>21781.0</v>
+        <v>43429.5</v>
       </c>
       <c r="H75" s="11">
-        <v>11108.0</v>
+        <v>23430.51</v>
       </c>
       <c r="I75" s="8">
-        <v>1.0408</v>
+        <v>1.1716</v>
       </c>
       <c r="J75" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K75" s="9" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="L75" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="3" t="s">
-        <v>145</v>
+      <c r="B76" s="10" t="s">
+        <v>146</v>
       </c>
       <c r="C76" s="5">
-        <v>49.0</v>
+        <v>38.0</v>
       </c>
       <c r="D76" s="6">
-        <v>333.15</v>
+        <v>1111.19</v>
       </c>
       <c r="E76" s="6">
-        <v>16324.5</v>
+        <v>42225.2</v>
       </c>
       <c r="F76" s="6">
-        <v>541.0</v>
+        <v>1123.8</v>
       </c>
       <c r="G76" s="6">
-        <v>26509.0</v>
+        <v>42704.4</v>
       </c>
       <c r="H76" s="11">
-        <v>10184.5</v>
+        <v>479.2</v>
       </c>
       <c r="I76" s="8">
-        <v>0.6239</v>
+        <v>0.0113</v>
       </c>
       <c r="J76" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K76" s="9" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="L76" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C77" s="5">
         <v>9.0</v>
       </c>
       <c r="D77" s="4">
-        <v>1395.0</v>
+        <v>3066.43</v>
       </c>
       <c r="E77" s="6">
-        <v>12555.0</v>
+        <v>27597.85</v>
       </c>
       <c r="F77" s="6">
-        <v>2353.0</v>
+        <v>4658.4</v>
       </c>
       <c r="G77" s="6">
-        <v>21177.0</v>
+        <v>41925.6</v>
       </c>
       <c r="H77" s="11">
-        <v>8622.0</v>
+        <v>14327.75</v>
       </c>
       <c r="I77" s="8">
-        <v>0.6867</v>
+        <v>0.5192</v>
       </c>
       <c r="J77" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K77" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L77" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="3" t="s">
-        <v>147</v>
+      <c r="B78" s="10" t="s">
+        <v>148</v>
       </c>
       <c r="C78" s="5">
-        <v>20.0</v>
+        <v>70.0</v>
       </c>
       <c r="D78" s="6">
-        <v>1040.96</v>
+        <v>331.82</v>
       </c>
       <c r="E78" s="6">
-        <v>20819.2</v>
+        <v>23227.6</v>
       </c>
       <c r="F78" s="6">
-        <v>1449.0</v>
+        <v>587.0</v>
       </c>
       <c r="G78" s="6">
-        <v>28980.0</v>
+        <v>41090.0</v>
       </c>
       <c r="H78" s="11">
-        <v>8160.8</v>
+        <v>17862.4</v>
       </c>
       <c r="I78" s="8">
-        <v>0.392</v>
+        <v>0.769</v>
       </c>
       <c r="J78" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K78" s="9" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="L78" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="3" t="s">
-        <v>148</v>
+      <c r="B79" s="10" t="s">
+        <v>149</v>
       </c>
       <c r="C79" s="5">
         <v>67.0</v>
@@ -3762,16 +3816,16 @@
         <v>34555.15</v>
       </c>
       <c r="F79" s="6">
-        <v>596.35</v>
+        <v>584.95</v>
       </c>
       <c r="G79" s="6">
-        <v>39955.45</v>
-      </c>
-      <c r="H79" s="11">
-        <v>5400.3</v>
-      </c>
-      <c r="I79" s="8">
-        <v>0.1563</v>
+        <v>39191.65</v>
+      </c>
+      <c r="H79" s="12">
+        <v>4636.5</v>
+      </c>
+      <c r="I79" s="13">
+        <v>0.1342</v>
       </c>
       <c r="J79" s="9" t="s">
         <v>26</v>
@@ -3785,7 +3839,7 @@
     </row>
     <row r="80">
       <c r="B80" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C80" s="5">
         <v>21.0</v>
@@ -3797,16 +3851,16 @@
         <v>31326.8</v>
       </c>
       <c r="F80" s="6">
-        <v>1740.0</v>
+        <v>1741.9</v>
       </c>
       <c r="G80" s="6">
-        <v>36540.0</v>
-      </c>
-      <c r="H80" s="11">
-        <v>5213.2</v>
-      </c>
-      <c r="I80" s="8">
-        <v>0.1664</v>
+        <v>36579.9</v>
+      </c>
+      <c r="H80" s="12">
+        <v>5253.1</v>
+      </c>
+      <c r="I80" s="13">
+        <v>0.1677</v>
       </c>
       <c r="J80" s="9" t="s">
         <v>26</v>
@@ -3819,99 +3873,99 @@
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="3" t="s">
-        <v>150</v>
+      <c r="B81" s="10" t="s">
+        <v>151</v>
       </c>
       <c r="C81" s="5">
-        <v>10.0</v>
+        <v>60.0</v>
       </c>
       <c r="D81" s="5">
-        <v>975.8</v>
+        <v>527.58</v>
       </c>
       <c r="E81" s="6">
-        <v>9758.0</v>
+        <v>31655.0</v>
       </c>
       <c r="F81" s="6">
-        <v>1463.2</v>
+        <v>601.0</v>
       </c>
       <c r="G81" s="6">
-        <v>14632.0</v>
-      </c>
-      <c r="H81" s="11">
-        <v>4874.0</v>
-      </c>
-      <c r="I81" s="8">
-        <v>0.4995</v>
+        <v>36060.0</v>
+      </c>
+      <c r="H81" s="12">
+        <v>4405.0</v>
+      </c>
+      <c r="I81" s="13">
+        <v>0.1392</v>
       </c>
       <c r="J81" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K81" s="9" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="L81" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="3" t="s">
-        <v>151</v>
+      <c r="B82" s="10" t="s">
+        <v>152</v>
       </c>
       <c r="C82" s="5">
-        <v>60.0</v>
+        <v>1.0</v>
       </c>
       <c r="D82" s="6">
-        <v>527.58</v>
+        <v>35975.0</v>
       </c>
       <c r="E82" s="6">
-        <v>31655.0</v>
+        <v>35975.0</v>
       </c>
       <c r="F82" s="6">
-        <v>601.05</v>
+        <v>35890.0</v>
       </c>
       <c r="G82" s="6">
-        <v>36063.0</v>
+        <v>35890.0</v>
       </c>
       <c r="H82" s="11">
-        <v>4408.0</v>
+        <v>-85.0</v>
       </c>
       <c r="I82" s="8">
-        <v>0.1393</v>
+        <v>-0.0024</v>
       </c>
       <c r="J82" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K82" s="9" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="L82" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C83" s="5">
-        <v>124.0</v>
+        <v>28.0</v>
       </c>
       <c r="D83" s="5">
-        <v>160.5</v>
+        <v>702.63</v>
       </c>
       <c r="E83" s="6">
-        <v>19902.66</v>
+        <v>19673.6</v>
       </c>
       <c r="F83" s="6">
-        <v>192.95</v>
+        <v>1250.9</v>
       </c>
       <c r="G83" s="6">
-        <v>23925.8</v>
+        <v>35025.2</v>
       </c>
       <c r="H83" s="11">
-        <v>4023.14</v>
+        <v>15351.6</v>
       </c>
       <c r="I83" s="8">
-        <v>0.2021</v>
+        <v>0.7803</v>
       </c>
       <c r="J83" s="9" t="s">
         <v>26</v>
@@ -3925,98 +3979,98 @@
     </row>
     <row r="84">
       <c r="B84" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C84" s="5">
-        <v>91.0</v>
+        <v>42.0</v>
       </c>
       <c r="D84" s="6">
-        <v>173.53</v>
+        <v>820.32</v>
       </c>
       <c r="E84" s="6">
-        <v>15791.45</v>
+        <v>34453.5</v>
       </c>
       <c r="F84" s="6">
-        <v>214.78</v>
+        <v>832.0</v>
       </c>
       <c r="G84" s="6">
-        <v>19544.98</v>
+        <v>34944.0</v>
       </c>
       <c r="H84" s="11">
-        <v>3753.53</v>
+        <v>490.5</v>
       </c>
       <c r="I84" s="8">
-        <v>0.2377</v>
+        <v>0.0142</v>
       </c>
       <c r="J84" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K84" s="9" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="L84" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="3" t="s">
-        <v>154</v>
+      <c r="B85" s="10" t="s">
+        <v>155</v>
       </c>
       <c r="C85" s="5">
+        <v>132.0</v>
+      </c>
+      <c r="D85" s="5">
+        <v>264.23</v>
+      </c>
+      <c r="E85" s="6">
+        <v>34878.4</v>
+      </c>
+      <c r="F85" s="6">
+        <v>261.0</v>
+      </c>
+      <c r="G85" s="6">
+        <v>34452.0</v>
+      </c>
+      <c r="H85" s="11">
+        <v>-426.4</v>
+      </c>
+      <c r="I85" s="8">
+        <v>-0.0122</v>
+      </c>
+      <c r="J85" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K85" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L85" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C86" s="5">
         <v>222.0</v>
       </c>
-      <c r="D85" s="5">
+      <c r="D86" s="5">
         <v>137.08</v>
       </c>
-      <c r="E85" s="6">
+      <c r="E86" s="6">
         <v>30430.92</v>
       </c>
-      <c r="F85" s="6">
-        <v>153.3</v>
-      </c>
-      <c r="G85" s="6">
-        <v>34032.6</v>
-      </c>
-      <c r="H85" s="11">
-        <v>3601.68</v>
-      </c>
-      <c r="I85" s="8">
-        <v>0.1184</v>
-      </c>
-      <c r="J85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L85" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C86" s="5">
-        <v>63.0</v>
-      </c>
-      <c r="D86" s="5">
-        <v>311.35</v>
-      </c>
-      <c r="E86" s="6">
-        <v>19614.9</v>
-      </c>
       <c r="F86" s="6">
-        <v>367.0</v>
+        <v>153.78</v>
       </c>
       <c r="G86" s="6">
-        <v>23121.0</v>
-      </c>
-      <c r="H86" s="11">
-        <v>3506.1</v>
-      </c>
-      <c r="I86" s="8">
-        <v>0.1787</v>
+        <v>34139.16</v>
+      </c>
+      <c r="H86" s="12">
+        <v>3708.24</v>
+      </c>
+      <c r="I86" s="13">
+        <v>0.1219</v>
       </c>
       <c r="J86" s="9" t="s">
         <v>26</v>
@@ -4029,29 +4083,29 @@
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="3" t="s">
-        <v>156</v>
+      <c r="B87" s="10" t="s">
+        <v>157</v>
       </c>
       <c r="C87" s="5">
-        <v>43.0</v>
+        <v>53.0</v>
       </c>
       <c r="D87" s="6">
-        <v>579.24</v>
+        <v>729.68</v>
       </c>
       <c r="E87" s="6">
-        <v>24907.3</v>
+        <v>38672.9</v>
       </c>
       <c r="F87" s="6">
-        <v>652.35</v>
+        <v>631.75</v>
       </c>
       <c r="G87" s="6">
-        <v>28051.05</v>
-      </c>
-      <c r="H87" s="11">
-        <v>3143.75</v>
-      </c>
-      <c r="I87" s="8">
-        <v>0.1262</v>
+        <v>33482.75</v>
+      </c>
+      <c r="H87" s="12">
+        <v>-5190.15</v>
+      </c>
+      <c r="I87" s="13">
+        <v>-0.1342</v>
       </c>
       <c r="J87" s="9" t="s">
         <v>26</v>
@@ -4064,8 +4118,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="3" t="s">
-        <v>157</v>
+      <c r="B88" s="10" t="s">
+        <v>158</v>
       </c>
       <c r="C88" s="5">
         <v>307.0</v>
@@ -4077,16 +4131,16 @@
         <v>29837.24</v>
       </c>
       <c r="F88" s="6">
-        <v>106.35</v>
+        <v>108.53</v>
       </c>
       <c r="G88" s="6">
-        <v>32649.45</v>
-      </c>
-      <c r="H88" s="11">
-        <v>2812.21</v>
-      </c>
-      <c r="I88" s="8">
-        <v>0.0943</v>
+        <v>33318.71</v>
+      </c>
+      <c r="H88" s="12">
+        <v>3481.47</v>
+      </c>
+      <c r="I88" s="13">
+        <v>0.1167</v>
       </c>
       <c r="J88" s="9" t="s">
         <v>26</v>
@@ -4099,29 +4153,29 @@
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="10" t="s">
-        <v>158</v>
+      <c r="B89" s="3" t="s">
+        <v>159</v>
       </c>
       <c r="C89" s="5">
-        <v>20.0</v>
+        <v>249.0</v>
       </c>
       <c r="D89" s="6">
-        <v>1099.4</v>
+        <v>134.11</v>
       </c>
       <c r="E89" s="6">
-        <v>21988.0</v>
+        <v>33392.27</v>
       </c>
       <c r="F89" s="6">
-        <v>1227.6</v>
+        <v>129.53</v>
       </c>
       <c r="G89" s="6">
-        <v>24552.0</v>
+        <v>32252.97</v>
       </c>
       <c r="H89" s="11">
-        <v>2564.0</v>
+        <v>-1139.3</v>
       </c>
       <c r="I89" s="8">
-        <v>0.1166</v>
+        <v>-0.0341</v>
       </c>
       <c r="J89" s="9" t="s">
         <v>26</v>
@@ -4134,29 +4188,29 @@
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="3" t="s">
-        <v>159</v>
+      <c r="B90" s="10" t="s">
+        <v>160</v>
       </c>
       <c r="C90" s="5">
-        <v>3.0</v>
+        <v>32.0</v>
       </c>
       <c r="D90" s="6">
-        <v>1154.83</v>
+        <v>934.45</v>
       </c>
       <c r="E90" s="6">
-        <v>3464.5</v>
+        <v>29902.4</v>
       </c>
       <c r="F90" s="6">
-        <v>1952.9</v>
+        <v>975.3</v>
       </c>
       <c r="G90" s="6">
-        <v>5858.7</v>
+        <v>31209.6</v>
       </c>
       <c r="H90" s="11">
-        <v>2394.2</v>
+        <v>1307.2</v>
       </c>
       <c r="I90" s="8">
-        <v>0.6911</v>
+        <v>0.0437</v>
       </c>
       <c r="J90" s="9" t="s">
         <v>26</v>
@@ -4169,64 +4223,64 @@
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="3" t="s">
-        <v>160</v>
+      <c r="B91" s="10" t="s">
+        <v>161</v>
       </c>
       <c r="C91" s="5">
-        <v>11.0</v>
+        <v>33.0</v>
       </c>
       <c r="D91" s="5">
-        <v>80.54</v>
+        <v>1071.83</v>
       </c>
       <c r="E91" s="6">
-        <v>885.9</v>
+        <v>35370.25</v>
       </c>
       <c r="F91" s="6">
-        <v>270.35</v>
+        <v>867.55</v>
       </c>
       <c r="G91" s="6">
-        <v>2973.85</v>
-      </c>
-      <c r="H91" s="11">
-        <v>2087.95</v>
-      </c>
-      <c r="I91" s="8">
-        <v>2.3569</v>
+        <v>28629.15</v>
+      </c>
+      <c r="H91" s="12">
+        <v>-6741.1</v>
+      </c>
+      <c r="I91" s="13">
+        <v>-0.1906</v>
       </c>
       <c r="J91" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K91" s="9" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="L91" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="3" t="s">
-        <v>161</v>
+      <c r="B92" s="10" t="s">
+        <v>162</v>
       </c>
       <c r="C92" s="5">
-        <v>66.0</v>
+        <v>43.0</v>
       </c>
       <c r="D92" s="6">
-        <v>387.23</v>
+        <v>579.24</v>
       </c>
       <c r="E92" s="6">
-        <v>25557.45</v>
+        <v>24907.3</v>
       </c>
       <c r="F92" s="6">
-        <v>417.95</v>
+        <v>661.0</v>
       </c>
       <c r="G92" s="6">
-        <v>27584.7</v>
-      </c>
-      <c r="H92" s="11">
-        <v>2027.25</v>
-      </c>
-      <c r="I92" s="8">
-        <v>0.0793</v>
+        <v>28423.0</v>
+      </c>
+      <c r="H92" s="12">
+        <v>3515.7</v>
+      </c>
+      <c r="I92" s="13">
+        <v>0.1412</v>
       </c>
       <c r="J92" s="9" t="s">
         <v>26</v>
@@ -4239,64 +4293,64 @@
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="3" t="s">
-        <v>162</v>
+      <c r="B93" s="10" t="s">
+        <v>163</v>
       </c>
       <c r="C93" s="5">
         <v>20.0</v>
       </c>
       <c r="D93" s="6">
-        <v>369.45</v>
+        <v>1040.96</v>
       </c>
       <c r="E93" s="6">
-        <v>7389.0</v>
+        <v>20819.2</v>
       </c>
       <c r="F93" s="6">
-        <v>465.0</v>
+        <v>1403.4</v>
       </c>
       <c r="G93" s="6">
-        <v>9300.0</v>
+        <v>28068.0</v>
       </c>
       <c r="H93" s="11">
-        <v>1911.0</v>
+        <v>7248.8</v>
       </c>
       <c r="I93" s="8">
-        <v>0.2586</v>
+        <v>0.3482</v>
       </c>
       <c r="J93" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K93" s="9" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="L93" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="3" t="s">
-        <v>163</v>
+      <c r="B94" s="10" t="s">
+        <v>164</v>
       </c>
       <c r="C94" s="5">
-        <v>15.0</v>
+        <v>66.0</v>
       </c>
       <c r="D94" s="6">
-        <v>1526.68</v>
+        <v>387.23</v>
       </c>
       <c r="E94" s="6">
-        <v>22900.2</v>
+        <v>25557.45</v>
       </c>
       <c r="F94" s="6">
-        <v>1628.2</v>
+        <v>418.0</v>
       </c>
       <c r="G94" s="6">
-        <v>24423.0</v>
+        <v>27588.0</v>
       </c>
       <c r="H94" s="11">
-        <v>1522.8</v>
+        <v>2030.55</v>
       </c>
       <c r="I94" s="8">
-        <v>0.0665</v>
+        <v>0.0795</v>
       </c>
       <c r="J94" s="9" t="s">
         <v>26</v>
@@ -4310,98 +4364,98 @@
     </row>
     <row r="95">
       <c r="B95" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C95" s="5">
-        <v>19.0</v>
+        <v>49.0</v>
       </c>
       <c r="D95" s="6">
-        <v>1886.49</v>
+        <v>333.15</v>
       </c>
       <c r="E95" s="6">
-        <v>35843.4</v>
+        <v>16324.5</v>
       </c>
       <c r="F95" s="6">
-        <v>1965.6</v>
+        <v>537.65</v>
       </c>
       <c r="G95" s="6">
-        <v>37346.4</v>
+        <v>26344.85</v>
       </c>
       <c r="H95" s="11">
-        <v>1503.0</v>
+        <v>10020.35</v>
       </c>
       <c r="I95" s="8">
-        <v>0.0419</v>
+        <v>0.6138</v>
       </c>
       <c r="J95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K95" s="9" t="s">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="L95" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="3" t="s">
-        <v>165</v>
+      <c r="B96" s="10" t="s">
+        <v>166</v>
       </c>
       <c r="C96" s="5">
-        <v>1.0</v>
+        <v>51.0</v>
       </c>
       <c r="D96" s="6">
-        <v>415.9</v>
+        <v>494.56</v>
       </c>
       <c r="E96" s="6">
-        <v>415.9</v>
+        <v>25222.6</v>
       </c>
       <c r="F96" s="6">
-        <v>1898.05</v>
+        <v>511.0</v>
       </c>
       <c r="G96" s="6">
-        <v>1898.05</v>
+        <v>26061.0</v>
       </c>
       <c r="H96" s="11">
-        <v>1482.15</v>
+        <v>838.4</v>
       </c>
       <c r="I96" s="8">
-        <v>3.5637</v>
+        <v>0.0332</v>
       </c>
       <c r="J96" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K96" s="9" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="L96" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="3" t="s">
-        <v>166</v>
+      <c r="B97" s="10" t="s">
+        <v>167</v>
       </c>
       <c r="C97" s="5">
-        <v>218.0</v>
+        <v>226.0</v>
       </c>
       <c r="D97" s="5">
-        <v>182.99</v>
+        <v>136.74</v>
       </c>
       <c r="E97" s="6">
-        <v>39890.84</v>
+        <v>30902.6</v>
       </c>
       <c r="F97" s="6">
-        <v>188.76</v>
+        <v>112.55</v>
       </c>
       <c r="G97" s="6">
-        <v>41149.68</v>
-      </c>
-      <c r="H97" s="11">
-        <v>1258.84</v>
-      </c>
-      <c r="I97" s="8">
-        <v>0.0316</v>
+        <v>25436.3</v>
+      </c>
+      <c r="H97" s="12">
+        <v>-5466.3</v>
+      </c>
+      <c r="I97" s="13">
+        <v>-0.1769</v>
       </c>
       <c r="J97" s="9" t="s">
         <v>26</v>
@@ -4414,29 +4468,29 @@
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="3" t="s">
-        <v>167</v>
+      <c r="B98" s="10" t="s">
+        <v>168</v>
       </c>
       <c r="C98" s="5">
-        <v>50.0</v>
+        <v>20.0</v>
       </c>
       <c r="D98" s="5">
-        <v>292.7</v>
+        <v>1099.4</v>
       </c>
       <c r="E98" s="6">
-        <v>14635.0</v>
+        <v>21988.0</v>
       </c>
       <c r="F98" s="6">
-        <v>316.55</v>
+        <v>1262.35</v>
       </c>
       <c r="G98" s="6">
-        <v>15827.5</v>
-      </c>
-      <c r="H98" s="11">
-        <v>1192.5</v>
-      </c>
-      <c r="I98" s="8">
-        <v>0.0815</v>
+        <v>25247.0</v>
+      </c>
+      <c r="H98" s="12">
+        <v>3259.0</v>
+      </c>
+      <c r="I98" s="13">
+        <v>0.1482</v>
       </c>
       <c r="J98" s="9" t="s">
         <v>26</v>
@@ -4449,29 +4503,29 @@
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="3" t="s">
-        <v>168</v>
+      <c r="B99" s="10" t="s">
+        <v>169</v>
       </c>
       <c r="C99" s="5">
-        <v>68.0</v>
+        <v>59.0</v>
       </c>
       <c r="D99" s="6">
-        <v>174.16</v>
+        <v>576.82</v>
       </c>
       <c r="E99" s="6">
-        <v>11842.88</v>
+        <v>34032.35</v>
       </c>
       <c r="F99" s="6">
-        <v>189.54</v>
+        <v>426.35</v>
       </c>
       <c r="G99" s="6">
-        <v>12888.72</v>
-      </c>
-      <c r="H99" s="12">
-        <v>1045.84</v>
-      </c>
-      <c r="I99" s="8">
-        <v>0.0883</v>
+        <v>25154.65</v>
+      </c>
+      <c r="H99" s="15">
+        <v>-8877.7</v>
+      </c>
+      <c r="I99" s="13">
+        <v>-0.2609</v>
       </c>
       <c r="J99" s="9" t="s">
         <v>26</v>
@@ -4485,28 +4539,28 @@
     </row>
     <row r="100">
       <c r="B100" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C100" s="5">
-        <v>32.0</v>
+        <v>298.0</v>
       </c>
       <c r="D100" s="6">
-        <v>934.45</v>
+        <v>41.79</v>
       </c>
       <c r="E100" s="6">
-        <v>29902.4</v>
+        <v>12454.04</v>
       </c>
       <c r="F100" s="6">
-        <v>956.0</v>
+        <v>82.65</v>
       </c>
       <c r="G100" s="6">
-        <v>30592.0</v>
+        <v>24629.7</v>
       </c>
       <c r="H100" s="11">
-        <v>689.6</v>
+        <v>12175.66</v>
       </c>
       <c r="I100" s="8">
-        <v>0.0231</v>
+        <v>0.9776</v>
       </c>
       <c r="J100" s="9" t="s">
         <v>26</v>
@@ -4520,63 +4574,63 @@
     </row>
     <row r="101">
       <c r="B101" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C101" s="5">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="D101" s="6">
-        <v>35975.0</v>
+        <v>1526.68</v>
       </c>
       <c r="E101" s="6">
-        <v>35975.0</v>
+        <v>22900.2</v>
       </c>
       <c r="F101" s="6">
-        <v>36660.0</v>
+        <v>1638.7</v>
       </c>
       <c r="G101" s="6">
-        <v>36660.0</v>
-      </c>
-      <c r="H101" s="12">
-        <v>685.0</v>
+        <v>24580.5</v>
+      </c>
+      <c r="H101" s="14">
+        <v>1680.3</v>
       </c>
       <c r="I101" s="8">
-        <v>0.019</v>
+        <v>0.0734</v>
       </c>
       <c r="J101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K101" s="9" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="L101" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="3" t="s">
-        <v>171</v>
+      <c r="B102" s="10" t="s">
+        <v>172</v>
       </c>
       <c r="C102" s="5">
-        <v>51.0</v>
+        <v>124.0</v>
       </c>
       <c r="D102" s="6">
-        <v>494.56</v>
+        <v>160.5</v>
       </c>
       <c r="E102" s="6">
-        <v>25222.6</v>
+        <v>19902.66</v>
       </c>
       <c r="F102" s="6">
-        <v>506.9</v>
+        <v>190.75</v>
       </c>
       <c r="G102" s="6">
-        <v>25851.9</v>
-      </c>
-      <c r="H102" s="11">
-        <v>629.3</v>
-      </c>
-      <c r="I102" s="8">
-        <v>0.0249</v>
+        <v>23653.0</v>
+      </c>
+      <c r="H102" s="12">
+        <v>3750.34</v>
+      </c>
+      <c r="I102" s="13">
+        <v>0.1884</v>
       </c>
       <c r="J102" s="9" t="s">
         <v>26</v>
@@ -4589,29 +4643,29 @@
       </c>
     </row>
     <row r="103">
-      <c r="B103" s="3" t="s">
-        <v>172</v>
+      <c r="B103" s="10" t="s">
+        <v>173</v>
       </c>
       <c r="C103" s="5">
-        <v>132.0</v>
+        <v>63.0</v>
       </c>
       <c r="D103" s="6">
-        <v>264.23</v>
+        <v>311.35</v>
       </c>
       <c r="E103" s="6">
-        <v>34878.4</v>
+        <v>19614.9</v>
       </c>
       <c r="F103" s="6">
-        <v>267.75</v>
+        <v>367.85</v>
       </c>
       <c r="G103" s="6">
-        <v>35343.0</v>
-      </c>
-      <c r="H103" s="11">
-        <v>464.6</v>
-      </c>
-      <c r="I103" s="8">
-        <v>0.0133</v>
+        <v>23174.55</v>
+      </c>
+      <c r="H103" s="12">
+        <v>3559.65</v>
+      </c>
+      <c r="I103" s="13">
+        <v>0.1815</v>
       </c>
       <c r="J103" s="9" t="s">
         <v>26</v>
@@ -4624,29 +4678,29 @@
       </c>
     </row>
     <row r="104">
-      <c r="B104" s="3" t="s">
-        <v>173</v>
+      <c r="B104" s="10" t="s">
+        <v>174</v>
       </c>
       <c r="C104" s="5">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="D104" s="6">
-        <v>53.6</v>
+        <v>2134.6</v>
       </c>
       <c r="E104" s="6">
-        <v>53.6</v>
+        <v>10673.0</v>
       </c>
       <c r="F104" s="6">
-        <v>496.8</v>
+        <v>4439.0</v>
       </c>
       <c r="G104" s="6">
-        <v>496.8</v>
+        <v>22195.0</v>
       </c>
       <c r="H104" s="11">
-        <v>443.2</v>
+        <v>11522.0</v>
       </c>
       <c r="I104" s="8">
-        <v>8.2687</v>
+        <v>1.0795</v>
       </c>
       <c r="J104" s="9" t="s">
         <v>15</v>
@@ -4659,344 +4713,344 @@
       </c>
     </row>
     <row r="105">
-      <c r="B105" s="3" t="s">
-        <v>174</v>
+      <c r="B105" s="10" t="s">
+        <v>175</v>
       </c>
       <c r="C105" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D105" s="5">
-        <v>262.0</v>
+        <v>9.0</v>
+      </c>
+      <c r="D105" s="6">
+        <v>1395.0</v>
       </c>
       <c r="E105" s="6">
-        <v>262.0</v>
+        <v>12555.0</v>
       </c>
       <c r="F105" s="6">
-        <v>588.4</v>
+        <v>2339.0</v>
       </c>
       <c r="G105" s="6">
-        <v>588.4</v>
+        <v>21051.0</v>
       </c>
       <c r="H105" s="11">
-        <v>326.4</v>
+        <v>8496.0</v>
       </c>
       <c r="I105" s="8">
-        <v>1.2458</v>
+        <v>0.6767</v>
       </c>
       <c r="J105" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K105" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L105" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="C106" s="5">
+        <v>69.0</v>
+      </c>
+      <c r="D106" s="6">
+        <v>463.0</v>
+      </c>
+      <c r="E106" s="6">
+        <v>31947.25</v>
+      </c>
+      <c r="F106" s="6">
+        <v>303.8</v>
+      </c>
+      <c r="G106" s="6">
+        <v>20962.2</v>
+      </c>
+      <c r="H106" s="12">
+        <v>-10985.05</v>
+      </c>
+      <c r="I106" s="13">
+        <v>-0.3438</v>
+      </c>
+      <c r="J106" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K106" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L106" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="C107" s="5">
+        <v>21.0</v>
+      </c>
+      <c r="D107" s="6">
+        <v>1220.91</v>
+      </c>
+      <c r="E107" s="6">
+        <v>25639.1</v>
+      </c>
+      <c r="F107" s="6">
+        <v>985.15</v>
+      </c>
+      <c r="G107" s="6">
+        <v>20688.15</v>
+      </c>
+      <c r="H107" s="12">
+        <v>-4950.95</v>
+      </c>
+      <c r="I107" s="13">
+        <v>-0.1931</v>
+      </c>
+      <c r="J107" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K107" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L107" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C108" s="5">
+        <v>24.0</v>
+      </c>
+      <c r="D108" s="6">
+        <v>829.45</v>
+      </c>
+      <c r="E108" s="6">
+        <v>19906.8</v>
+      </c>
+      <c r="F108" s="6">
+        <v>857.15</v>
+      </c>
+      <c r="G108" s="6">
+        <v>20571.6</v>
+      </c>
+      <c r="H108" s="11">
+        <v>664.8</v>
+      </c>
+      <c r="I108" s="8">
+        <v>0.0334</v>
+      </c>
+      <c r="J108" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K108" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L108" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="C109" s="5">
+        <v>228.0</v>
+      </c>
+      <c r="D109" s="6">
+        <v>94.74</v>
+      </c>
+      <c r="E109" s="6">
+        <v>21599.94</v>
+      </c>
+      <c r="F109" s="6">
+        <v>89.41</v>
+      </c>
+      <c r="G109" s="6">
+        <v>20385.48</v>
+      </c>
+      <c r="H109" s="12">
+        <v>-1214.46</v>
+      </c>
+      <c r="I109" s="13">
+        <v>-0.0562</v>
+      </c>
+      <c r="J109" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K109" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L109" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C110" s="5">
+        <v>67.0</v>
+      </c>
+      <c r="D110" s="6">
+        <v>374.48</v>
+      </c>
+      <c r="E110" s="6">
+        <v>25090.1</v>
+      </c>
+      <c r="F110" s="6">
+        <v>300.6</v>
+      </c>
+      <c r="G110" s="6">
+        <v>20140.2</v>
+      </c>
+      <c r="H110" s="12">
+        <v>-4949.9</v>
+      </c>
+      <c r="I110" s="13">
+        <v>-0.1973</v>
+      </c>
+      <c r="J110" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K110" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L110" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C111" s="5">
+        <v>32.0</v>
+      </c>
+      <c r="D111" s="5">
+        <v>619.5</v>
+      </c>
+      <c r="E111" s="6">
+        <v>19824.0</v>
+      </c>
+      <c r="F111" s="6">
+        <v>620.15</v>
+      </c>
+      <c r="G111" s="6">
+        <v>19844.8</v>
+      </c>
+      <c r="H111" s="11">
+        <v>20.8</v>
+      </c>
+      <c r="I111" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="J111" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K111" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L111" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C112" s="5">
+        <v>20.0</v>
+      </c>
+      <c r="D112" s="5">
+        <v>988.13</v>
+      </c>
+      <c r="E112" s="6">
+        <v>19762.5</v>
+      </c>
+      <c r="F112" s="6">
+        <v>989.6</v>
+      </c>
+      <c r="G112" s="6">
+        <v>19792.0</v>
+      </c>
+      <c r="H112" s="11">
+        <v>29.5</v>
+      </c>
+      <c r="I112" s="8">
+        <v>0.0015</v>
+      </c>
+      <c r="J112" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K112" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L112" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="C113" s="5">
+        <v>91.0</v>
+      </c>
+      <c r="D113" s="5">
+        <v>173.53</v>
+      </c>
+      <c r="E113" s="6">
+        <v>15791.45</v>
+      </c>
+      <c r="F113" s="6">
+        <v>217.2</v>
+      </c>
+      <c r="G113" s="6">
+        <v>19765.2</v>
+      </c>
+      <c r="H113" s="11">
+        <v>3973.75</v>
+      </c>
+      <c r="I113" s="8">
+        <v>0.2516</v>
+      </c>
+      <c r="J113" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="K105" s="9" t="s">
+      <c r="K113" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="L105" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="B106" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C106" s="5">
-        <v>50.0</v>
-      </c>
-      <c r="D106" s="6">
-        <v>238.76</v>
-      </c>
-      <c r="E106" s="6">
-        <v>11938.1</v>
-      </c>
-      <c r="F106" s="6">
-        <v>244.45</v>
-      </c>
-      <c r="G106" s="6">
-        <v>12222.5</v>
-      </c>
-      <c r="H106" s="11">
-        <v>284.4</v>
-      </c>
-      <c r="I106" s="8">
-        <v>0.0238</v>
-      </c>
-      <c r="J106" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K106" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L106" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="B107" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C107" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D107" s="6">
-        <v>119.7</v>
-      </c>
-      <c r="E107" s="6">
-        <v>119.7</v>
-      </c>
-      <c r="F107" s="6">
-        <v>330.19</v>
-      </c>
-      <c r="G107" s="6">
-        <v>330.19</v>
-      </c>
-      <c r="H107" s="11">
-        <v>210.49</v>
-      </c>
-      <c r="I107" s="8">
-        <v>1.7585</v>
-      </c>
-      <c r="J107" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K107" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="L107" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="B108" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C108" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D108" s="6">
-        <v>588.9</v>
-      </c>
-      <c r="E108" s="6">
-        <v>588.9</v>
-      </c>
-      <c r="F108" s="6">
-        <v>762.95</v>
-      </c>
-      <c r="G108" s="6">
-        <v>762.95</v>
-      </c>
-      <c r="H108" s="11">
-        <v>174.05</v>
-      </c>
-      <c r="I108" s="8">
-        <v>0.2956</v>
-      </c>
-      <c r="J108" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K108" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="L108" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="B109" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C109" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D109" s="6">
-        <v>111.28</v>
-      </c>
-      <c r="E109" s="6">
-        <v>111.28</v>
-      </c>
-      <c r="F109" s="6">
-        <v>225.22</v>
-      </c>
-      <c r="G109" s="6">
-        <v>225.22</v>
-      </c>
-      <c r="H109" s="11">
-        <v>113.94</v>
-      </c>
-      <c r="I109" s="8">
-        <v>1.0239</v>
-      </c>
-      <c r="J109" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K109" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="L109" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="B110" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C110" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D110" s="6">
-        <v>142.65</v>
-      </c>
-      <c r="E110" s="6">
-        <v>142.65</v>
-      </c>
-      <c r="F110" s="6">
-        <v>241.5</v>
-      </c>
-      <c r="G110" s="6">
-        <v>241.5</v>
-      </c>
-      <c r="H110" s="11">
-        <v>98.85</v>
-      </c>
-      <c r="I110" s="8">
-        <v>0.693</v>
-      </c>
-      <c r="J110" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K110" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="L110" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="B111" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C111" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D111" s="5">
-        <v>165.85</v>
-      </c>
-      <c r="E111" s="6">
-        <v>165.85</v>
-      </c>
-      <c r="F111" s="6">
-        <v>252.6</v>
-      </c>
-      <c r="G111" s="6">
-        <v>252.6</v>
-      </c>
-      <c r="H111" s="11">
-        <v>86.75</v>
-      </c>
-      <c r="I111" s="8">
-        <v>0.5231</v>
-      </c>
-      <c r="J111" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K111" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="L111" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="B112" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C112" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D112" s="5">
-        <v>25.25</v>
-      </c>
-      <c r="E112" s="6">
-        <v>25.25</v>
-      </c>
-      <c r="F112" s="6">
-        <v>109.0</v>
-      </c>
-      <c r="G112" s="6">
-        <v>109.0</v>
-      </c>
-      <c r="H112" s="11">
-        <v>83.75</v>
-      </c>
-      <c r="I112" s="8">
-        <v>3.3168</v>
-      </c>
-      <c r="J112" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K112" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="L112" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="B113" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C113" s="5">
-        <v>20.0</v>
-      </c>
-      <c r="D113" s="5">
-        <v>988.13</v>
-      </c>
-      <c r="E113" s="6">
-        <v>19762.5</v>
-      </c>
-      <c r="F113" s="6">
-        <v>991.55</v>
-      </c>
-      <c r="G113" s="6">
-        <v>19831.0</v>
-      </c>
-      <c r="H113" s="11">
-        <v>68.5</v>
-      </c>
-      <c r="I113" s="8">
-        <v>0.0035</v>
-      </c>
-      <c r="J113" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K113" s="9" t="s">
-        <v>26</v>
-      </c>
       <c r="L113" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="114">
-      <c r="B114" s="10" t="s">
-        <v>183</v>
+      <c r="B114" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="C114" s="5">
-        <v>42.0</v>
+        <v>72.0</v>
       </c>
       <c r="D114" s="6">
-        <v>820.32</v>
+        <v>275.75</v>
       </c>
       <c r="E114" s="6">
-        <v>34453.5</v>
+        <v>19853.65</v>
       </c>
       <c r="F114" s="6">
-        <v>821.95</v>
+        <v>273.9</v>
       </c>
       <c r="G114" s="6">
-        <v>34521.9</v>
+        <v>19720.8</v>
       </c>
       <c r="H114" s="11">
-        <v>68.4</v>
+        <v>-132.85</v>
       </c>
       <c r="I114" s="8">
-        <v>0.002</v>
+        <v>-0.0067</v>
       </c>
       <c r="J114" s="9" t="s">
         <v>26</v>
@@ -5009,134 +5063,134 @@
       </c>
     </row>
     <row r="115">
-      <c r="B115" s="3" t="s">
-        <v>184</v>
+      <c r="B115" s="10" t="s">
+        <v>185</v>
       </c>
       <c r="C115" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D115" s="5">
-        <v>51.86</v>
+        <v>7.0</v>
+      </c>
+      <c r="D115" s="6">
+        <v>3125.67</v>
       </c>
       <c r="E115" s="6">
-        <v>51.86</v>
+        <v>21879.7</v>
       </c>
       <c r="F115" s="6">
-        <v>100.48</v>
+        <v>2796.7</v>
       </c>
       <c r="G115" s="6">
-        <v>100.48</v>
-      </c>
-      <c r="H115" s="11">
-        <v>48.62</v>
-      </c>
-      <c r="I115" s="8">
-        <v>0.9375</v>
+        <v>19576.9</v>
+      </c>
+      <c r="H115" s="12">
+        <v>-2302.8</v>
+      </c>
+      <c r="I115" s="13">
+        <v>-0.1052</v>
       </c>
       <c r="J115" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K115" s="9" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="L115" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="116">
-      <c r="B116" s="3" t="s">
-        <v>185</v>
+      <c r="B116" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="C116" s="5">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="D116" s="6">
-        <v>116.0</v>
+        <v>1320.0</v>
       </c>
       <c r="E116" s="6">
-        <v>116.0</v>
+        <v>19800.0</v>
       </c>
       <c r="F116" s="6">
-        <v>99.15</v>
+        <v>1285.95</v>
       </c>
       <c r="G116" s="6">
-        <v>99.15</v>
-      </c>
-      <c r="H116" s="13">
-        <v>-16.85</v>
-      </c>
-      <c r="I116" s="14">
-        <v>-0.1453</v>
+        <v>19289.25</v>
+      </c>
+      <c r="H116" s="11">
+        <v>-510.75</v>
+      </c>
+      <c r="I116" s="8">
+        <v>-0.0258</v>
       </c>
       <c r="J116" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K116" s="9" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="L116" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="117">
-      <c r="B117" s="3" t="s">
-        <v>186</v>
+      <c r="B117" s="10" t="s">
+        <v>187</v>
       </c>
       <c r="C117" s="5">
-        <v>1.0</v>
+        <v>221.0</v>
       </c>
       <c r="D117" s="6">
-        <v>1935.3</v>
+        <v>126.22</v>
       </c>
       <c r="E117" s="6">
-        <v>1935.3</v>
+        <v>27894.4</v>
       </c>
       <c r="F117" s="6">
-        <v>1790.0</v>
+        <v>85.3</v>
       </c>
       <c r="G117" s="6">
-        <v>1790.0</v>
-      </c>
-      <c r="H117" s="13">
-        <v>-145.3</v>
-      </c>
-      <c r="I117" s="14">
-        <v>-0.0751</v>
+        <v>18851.3</v>
+      </c>
+      <c r="H117" s="12">
+        <v>-9043.1</v>
+      </c>
+      <c r="I117" s="13">
+        <v>-0.3242</v>
       </c>
       <c r="J117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K117" s="9" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="L117" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="118">
-      <c r="B118" s="3" t="s">
-        <v>187</v>
+      <c r="B118" s="10" t="s">
+        <v>188</v>
       </c>
       <c r="C118" s="5">
-        <v>5.0</v>
+        <v>110.0</v>
       </c>
       <c r="D118" s="6">
-        <v>162.33</v>
+        <v>181.04</v>
       </c>
       <c r="E118" s="6">
-        <v>811.65</v>
+        <v>19914.4</v>
       </c>
       <c r="F118" s="6">
-        <v>126.6</v>
+        <v>169.8</v>
       </c>
       <c r="G118" s="6">
-        <v>633.0</v>
-      </c>
-      <c r="H118" s="13">
-        <v>-178.65</v>
-      </c>
-      <c r="I118" s="14">
-        <v>-0.2201</v>
+        <v>18678.0</v>
+      </c>
+      <c r="H118" s="12">
+        <v>-1236.4</v>
+      </c>
+      <c r="I118" s="13">
+        <v>-0.0621</v>
       </c>
       <c r="J118" s="9" t="s">
         <v>26</v>
@@ -5149,64 +5203,64 @@
       </c>
     </row>
     <row r="119">
-      <c r="B119" s="3" t="s">
-        <v>188</v>
+      <c r="B119" s="10" t="s">
+        <v>189</v>
       </c>
       <c r="C119" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="D119" s="5">
-        <v>394.42</v>
+        <v>23.0</v>
+      </c>
+      <c r="D119" s="6">
+        <v>1205.77</v>
       </c>
       <c r="E119" s="6">
-        <v>1183.25</v>
+        <v>27732.8</v>
       </c>
       <c r="F119" s="6">
-        <v>304.65</v>
+        <v>804.2</v>
       </c>
       <c r="G119" s="6">
-        <v>913.95</v>
+        <v>18496.6</v>
       </c>
       <c r="H119" s="15">
-        <v>-269.3</v>
-      </c>
-      <c r="I119" s="14">
-        <v>-0.2276</v>
+        <v>-9236.2</v>
+      </c>
+      <c r="I119" s="13">
+        <v>-0.333</v>
       </c>
       <c r="J119" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K119" s="9" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="L119" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="120">
-      <c r="B120" s="3" t="s">
-        <v>189</v>
+      <c r="B120" s="10" t="s">
+        <v>190</v>
       </c>
       <c r="C120" s="5">
-        <v>32.0</v>
+        <v>10.0</v>
       </c>
       <c r="D120" s="6">
-        <v>619.5</v>
+        <v>1963.23</v>
       </c>
       <c r="E120" s="6">
-        <v>19824.0</v>
+        <v>19632.3</v>
       </c>
       <c r="F120" s="6">
-        <v>603.9</v>
+        <v>1846.1</v>
       </c>
       <c r="G120" s="6">
-        <v>19324.8</v>
+        <v>18461.0</v>
       </c>
       <c r="H120" s="15">
-        <v>-499.2</v>
-      </c>
-      <c r="I120" s="14">
-        <v>-0.0252</v>
+        <v>-1171.3</v>
+      </c>
+      <c r="I120" s="13">
+        <v>-0.0597</v>
       </c>
       <c r="J120" s="9" t="s">
         <v>26</v>
@@ -5220,28 +5274,28 @@
     </row>
     <row r="121">
       <c r="B121" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C121" s="5">
-        <v>13.0</v>
+        <v>46.0</v>
       </c>
       <c r="D121" s="6">
-        <v>855.56</v>
+        <v>430.98</v>
       </c>
       <c r="E121" s="6">
-        <v>11122.3</v>
+        <v>19824.9</v>
       </c>
       <c r="F121" s="6">
-        <v>801.0</v>
+        <v>400.0</v>
       </c>
       <c r="G121" s="6">
-        <v>10413.0</v>
-      </c>
-      <c r="H121" s="13">
-        <v>-709.3</v>
-      </c>
-      <c r="I121" s="14">
-        <v>-0.0638</v>
+        <v>18400.0</v>
+      </c>
+      <c r="H121" s="12">
+        <v>-1424.9</v>
+      </c>
+      <c r="I121" s="13">
+        <v>-0.0719</v>
       </c>
       <c r="J121" s="9" t="s">
         <v>26</v>
@@ -5254,105 +5308,105 @@
       </c>
     </row>
     <row r="122">
-      <c r="B122" s="3" t="s">
-        <v>191</v>
+      <c r="B122" s="10" t="s">
+        <v>192</v>
       </c>
       <c r="C122" s="5">
-        <v>1.0</v>
+        <v>72.0</v>
       </c>
       <c r="D122" s="6">
-        <v>1526.5</v>
+        <v>278.55</v>
       </c>
       <c r="E122" s="6">
-        <v>1526.5</v>
+        <v>20055.6</v>
       </c>
       <c r="F122" s="6">
-        <v>761.55</v>
+        <v>225.95</v>
       </c>
       <c r="G122" s="6">
-        <v>761.55</v>
-      </c>
-      <c r="H122" s="13">
-        <v>-764.95</v>
-      </c>
-      <c r="I122" s="14">
-        <v>-0.5011</v>
+        <v>16268.4</v>
+      </c>
+      <c r="H122" s="12">
+        <v>-3787.2</v>
+      </c>
+      <c r="I122" s="13">
+        <v>-0.1888</v>
       </c>
       <c r="J122" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K122" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L122" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C123" s="5">
+        <v>50.0</v>
+      </c>
+      <c r="D123" s="6">
+        <v>292.7</v>
+      </c>
+      <c r="E123" s="6">
+        <v>14635.0</v>
+      </c>
+      <c r="F123" s="6">
+        <v>320.05</v>
+      </c>
+      <c r="G123" s="6">
+        <v>16002.5</v>
+      </c>
+      <c r="H123" s="11">
+        <v>1367.5</v>
+      </c>
+      <c r="I123" s="8">
+        <v>0.0934</v>
+      </c>
+      <c r="J123" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K123" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L123" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C124" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="D124" s="6">
+        <v>975.8</v>
+      </c>
+      <c r="E124" s="6">
+        <v>9758.0</v>
+      </c>
+      <c r="F124" s="6">
+        <v>1516.95</v>
+      </c>
+      <c r="G124" s="6">
+        <v>15169.5</v>
+      </c>
+      <c r="H124" s="11">
+        <v>5411.5</v>
+      </c>
+      <c r="I124" s="8">
+        <v>0.5546</v>
+      </c>
+      <c r="J124" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="K122" s="9" t="s">
+      <c r="K124" s="9" t="s">
         <v>16</v>
-      </c>
-      <c r="L122" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="B123" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C123" s="5">
-        <v>72.0</v>
-      </c>
-      <c r="D123" s="6">
-        <v>275.75</v>
-      </c>
-      <c r="E123" s="6">
-        <v>19853.65</v>
-      </c>
-      <c r="F123" s="6">
-        <v>265.1</v>
-      </c>
-      <c r="G123" s="6">
-        <v>19087.2</v>
-      </c>
-      <c r="H123" s="13">
-        <v>-766.45</v>
-      </c>
-      <c r="I123" s="14">
-        <v>-0.0386</v>
-      </c>
-      <c r="J123" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K123" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L123" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="B124" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C124" s="5">
-        <v>148.0</v>
-      </c>
-      <c r="D124" s="6">
-        <v>67.59</v>
-      </c>
-      <c r="E124" s="6">
-        <v>10003.56</v>
-      </c>
-      <c r="F124" s="6">
-        <v>62.23</v>
-      </c>
-      <c r="G124" s="6">
-        <v>9210.04</v>
-      </c>
-      <c r="H124" s="13">
-        <v>-793.52</v>
-      </c>
-      <c r="I124" s="14">
-        <v>-0.0793</v>
-      </c>
-      <c r="J124" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K124" s="9" t="s">
-        <v>26</v>
       </c>
       <c r="L124" s="9" t="s">
         <v>17</v>
@@ -5360,7 +5414,7 @@
     </row>
     <row r="125">
       <c r="B125" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C125" s="5">
         <v>9.0</v>
@@ -5372,16 +5426,16 @@
         <v>15506.6</v>
       </c>
       <c r="F125" s="6">
-        <v>1628.5</v>
+        <v>1667.2</v>
       </c>
       <c r="G125" s="6">
-        <v>14656.5</v>
-      </c>
-      <c r="H125" s="13">
-        <v>-850.1</v>
-      </c>
-      <c r="I125" s="14">
-        <v>-0.0548</v>
+        <v>15004.8</v>
+      </c>
+      <c r="H125" s="11">
+        <v>-501.8</v>
+      </c>
+      <c r="I125" s="8">
+        <v>-0.0324</v>
       </c>
       <c r="J125" s="9" t="s">
         <v>15</v>
@@ -5394,29 +5448,29 @@
       </c>
     </row>
     <row r="126">
-      <c r="B126" s="3" t="s">
-        <v>195</v>
+      <c r="B126" s="10" t="s">
+        <v>196</v>
       </c>
       <c r="C126" s="5">
-        <v>110.0</v>
+        <v>3.0</v>
       </c>
       <c r="D126" s="5">
-        <v>181.04</v>
+        <v>5480.0</v>
       </c>
       <c r="E126" s="6">
-        <v>19914.4</v>
+        <v>16440.0</v>
       </c>
       <c r="F126" s="6">
-        <v>170.65</v>
+        <v>4662.3</v>
       </c>
       <c r="G126" s="6">
-        <v>18771.5</v>
-      </c>
-      <c r="H126" s="13">
-        <v>-1142.9</v>
-      </c>
-      <c r="I126" s="14">
-        <v>-0.0574</v>
+        <v>13986.9</v>
+      </c>
+      <c r="H126" s="12">
+        <v>-2453.1</v>
+      </c>
+      <c r="I126" s="13">
+        <v>-0.1492</v>
       </c>
       <c r="J126" s="9" t="s">
         <v>26</v>
@@ -5429,29 +5483,29 @@
       </c>
     </row>
     <row r="127">
-      <c r="B127" s="3" t="s">
-        <v>196</v>
+      <c r="B127" s="10" t="s">
+        <v>197</v>
       </c>
       <c r="C127" s="5">
-        <v>228.0</v>
+        <v>68.0</v>
       </c>
       <c r="D127" s="6">
-        <v>94.74</v>
+        <v>174.16</v>
       </c>
       <c r="E127" s="6">
-        <v>21599.94</v>
+        <v>11842.88</v>
       </c>
       <c r="F127" s="6">
-        <v>89.57</v>
+        <v>192.0</v>
       </c>
       <c r="G127" s="6">
-        <v>20421.96</v>
-      </c>
-      <c r="H127" s="13">
-        <v>-1177.98</v>
-      </c>
-      <c r="I127" s="14">
-        <v>-0.0545</v>
+        <v>13056.0</v>
+      </c>
+      <c r="H127" s="12">
+        <v>1213.12</v>
+      </c>
+      <c r="I127" s="13">
+        <v>0.1024</v>
       </c>
       <c r="J127" s="9" t="s">
         <v>26</v>
@@ -5464,29 +5518,29 @@
       </c>
     </row>
     <row r="128">
-      <c r="B128" s="3" t="s">
-        <v>197</v>
+      <c r="B128" s="10" t="s">
+        <v>198</v>
       </c>
       <c r="C128" s="5">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="D128" s="6">
-        <v>1963.23</v>
+        <v>1023.34</v>
       </c>
       <c r="E128" s="6">
-        <v>19632.3</v>
+        <v>15350.15</v>
       </c>
       <c r="F128" s="6">
-        <v>1842.9</v>
+        <v>829.05</v>
       </c>
       <c r="G128" s="6">
-        <v>18429.0</v>
-      </c>
-      <c r="H128" s="13">
-        <v>-1203.3</v>
-      </c>
-      <c r="I128" s="14">
-        <v>-0.0613</v>
+        <v>12435.75</v>
+      </c>
+      <c r="H128" s="12">
+        <v>-2914.4</v>
+      </c>
+      <c r="I128" s="13">
+        <v>-0.1899</v>
       </c>
       <c r="J128" s="9" t="s">
         <v>26</v>
@@ -5500,28 +5554,28 @@
     </row>
     <row r="129">
       <c r="B129" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C129" s="5">
-        <v>249.0</v>
+        <v>50.0</v>
       </c>
       <c r="D129" s="6">
-        <v>134.11</v>
+        <v>238.76</v>
       </c>
       <c r="E129" s="6">
-        <v>33392.27</v>
+        <v>11938.1</v>
       </c>
       <c r="F129" s="6">
-        <v>128.28</v>
+        <v>245.3</v>
       </c>
       <c r="G129" s="6">
-        <v>31941.72</v>
-      </c>
-      <c r="H129" s="13">
-        <v>-1450.55</v>
-      </c>
-      <c r="I129" s="14">
-        <v>-0.0434</v>
+        <v>12265.0</v>
+      </c>
+      <c r="H129" s="11">
+        <v>326.9</v>
+      </c>
+      <c r="I129" s="8">
+        <v>0.0274</v>
       </c>
       <c r="J129" s="9" t="s">
         <v>26</v>
@@ -5534,29 +5588,29 @@
       </c>
     </row>
     <row r="130">
-      <c r="B130" s="3" t="s">
-        <v>199</v>
+      <c r="B130" s="10" t="s">
+        <v>200</v>
       </c>
       <c r="C130" s="5">
-        <v>46.0</v>
+        <v>95.0</v>
       </c>
       <c r="D130" s="6">
-        <v>430.98</v>
+        <v>158.81</v>
       </c>
       <c r="E130" s="6">
-        <v>19824.9</v>
+        <v>15087.3</v>
       </c>
       <c r="F130" s="6">
-        <v>390.45</v>
+        <v>124.95</v>
       </c>
       <c r="G130" s="6">
-        <v>17960.7</v>
-      </c>
-      <c r="H130" s="13">
-        <v>-1864.2</v>
-      </c>
-      <c r="I130" s="14">
-        <v>-0.094</v>
+        <v>11870.25</v>
+      </c>
+      <c r="H130" s="12">
+        <v>-3217.05</v>
+      </c>
+      <c r="I130" s="13">
+        <v>-0.2132</v>
       </c>
       <c r="J130" s="9" t="s">
         <v>26</v>
@@ -5569,29 +5623,29 @@
       </c>
     </row>
     <row r="131">
-      <c r="B131" s="3" t="s">
-        <v>200</v>
+      <c r="B131" s="10" t="s">
+        <v>201</v>
       </c>
       <c r="C131" s="5">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="D131" s="6">
-        <v>3125.67</v>
+        <v>855.56</v>
       </c>
       <c r="E131" s="6">
-        <v>21879.7</v>
+        <v>11122.3</v>
       </c>
       <c r="F131" s="6">
-        <v>2806.6</v>
+        <v>795.35</v>
       </c>
       <c r="G131" s="6">
-        <v>19646.2</v>
+        <v>10339.55</v>
       </c>
       <c r="H131" s="15">
-        <v>-2233.5</v>
-      </c>
-      <c r="I131" s="14">
-        <v>-0.1021</v>
+        <v>-782.75</v>
+      </c>
+      <c r="I131" s="13">
+        <v>-0.0704</v>
       </c>
       <c r="J131" s="9" t="s">
         <v>26</v>
@@ -5605,28 +5659,28 @@
     </row>
     <row r="132">
       <c r="B132" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C132" s="5">
-        <v>3.0</v>
+        <v>14.0</v>
       </c>
       <c r="D132" s="6">
-        <v>5480.0</v>
+        <v>713.6</v>
       </c>
       <c r="E132" s="6">
-        <v>16440.0</v>
+        <v>9990.4</v>
       </c>
       <c r="F132" s="6">
-        <v>4610.0</v>
+        <v>692.05</v>
       </c>
       <c r="G132" s="6">
-        <v>13830.0</v>
-      </c>
-      <c r="H132" s="13">
-        <v>-2610.0</v>
-      </c>
-      <c r="I132" s="14">
-        <v>-0.1588</v>
+        <v>9688.7</v>
+      </c>
+      <c r="H132" s="11">
+        <v>-301.7</v>
+      </c>
+      <c r="I132" s="8">
+        <v>-0.0302</v>
       </c>
       <c r="J132" s="9" t="s">
         <v>26</v>
@@ -5639,29 +5693,29 @@
       </c>
     </row>
     <row r="133">
-      <c r="B133" s="3" t="s">
-        <v>202</v>
+      <c r="B133" s="10" t="s">
+        <v>203</v>
       </c>
       <c r="C133" s="5">
-        <v>15.0</v>
+        <v>50.0</v>
       </c>
       <c r="D133" s="6">
-        <v>1023.34</v>
+        <v>198.2</v>
       </c>
       <c r="E133" s="6">
-        <v>15350.15</v>
+        <v>9910.0</v>
       </c>
       <c r="F133" s="6">
-        <v>833.0</v>
+        <v>192.5</v>
       </c>
       <c r="G133" s="6">
-        <v>12495.0</v>
-      </c>
-      <c r="H133" s="13">
-        <v>-2855.15</v>
-      </c>
-      <c r="I133" s="14">
-        <v>-0.186</v>
+        <v>9625.0</v>
+      </c>
+      <c r="H133" s="11">
+        <v>-285.0</v>
+      </c>
+      <c r="I133" s="8">
+        <v>-0.0288</v>
       </c>
       <c r="J133" s="9" t="s">
         <v>26</v>
@@ -5674,64 +5728,64 @@
       </c>
     </row>
     <row r="134">
-      <c r="B134" s="3" t="s">
-        <v>203</v>
+      <c r="B134" s="10" t="s">
+        <v>204</v>
       </c>
       <c r="C134" s="5">
-        <v>72.0</v>
+        <v>20.0</v>
       </c>
       <c r="D134" s="6">
-        <v>278.55</v>
+        <v>369.45</v>
       </c>
       <c r="E134" s="6">
-        <v>20055.6</v>
+        <v>7389.0</v>
       </c>
       <c r="F134" s="6">
-        <v>228.86</v>
+        <v>457.2</v>
       </c>
       <c r="G134" s="6">
-        <v>16477.92</v>
-      </c>
-      <c r="H134" s="15">
-        <v>-3577.68</v>
-      </c>
-      <c r="I134" s="14">
-        <v>-0.1784</v>
+        <v>9144.0</v>
+      </c>
+      <c r="H134" s="14">
+        <v>1755.0</v>
+      </c>
+      <c r="I134" s="8">
+        <v>0.2375</v>
       </c>
       <c r="J134" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K134" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L134" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="135">
-      <c r="B135" s="3" t="s">
-        <v>204</v>
+      <c r="B135" s="10" t="s">
+        <v>205</v>
       </c>
       <c r="C135" s="5">
-        <v>95.0</v>
+        <v>148.0</v>
       </c>
       <c r="D135" s="5">
-        <v>158.81</v>
+        <v>67.59</v>
       </c>
       <c r="E135" s="6">
-        <v>15087.3</v>
+        <v>10003.56</v>
       </c>
       <c r="F135" s="6">
-        <v>120.2</v>
+        <v>61.72</v>
       </c>
       <c r="G135" s="6">
-        <v>11419.0</v>
-      </c>
-      <c r="H135" s="13">
-        <v>-3668.3</v>
-      </c>
-      <c r="I135" s="14">
-        <v>-0.2431</v>
+        <v>9134.56</v>
+      </c>
+      <c r="H135" s="12">
+        <v>-869.0</v>
+      </c>
+      <c r="I135" s="13">
+        <v>-0.0869</v>
       </c>
       <c r="J135" s="9" t="s">
         <v>26</v>
@@ -5745,28 +5799,28 @@
     </row>
     <row r="136">
       <c r="B136" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C136" s="5">
-        <v>67.0</v>
+        <v>252.0</v>
       </c>
       <c r="D136" s="5">
-        <v>374.48</v>
+        <v>63.35</v>
       </c>
       <c r="E136" s="6">
-        <v>25090.1</v>
+        <v>15965.18</v>
       </c>
       <c r="F136" s="6">
-        <v>300.75</v>
+        <v>34.67</v>
       </c>
       <c r="G136" s="6">
-        <v>20150.25</v>
-      </c>
-      <c r="H136" s="13">
-        <v>-4939.85</v>
-      </c>
-      <c r="I136" s="14">
-        <v>-0.1969</v>
+        <v>8736.84</v>
+      </c>
+      <c r="H136" s="12">
+        <v>-7228.34</v>
+      </c>
+      <c r="I136" s="13">
+        <v>-0.4528</v>
       </c>
       <c r="J136" s="9" t="s">
         <v>26</v>
@@ -5779,29 +5833,29 @@
       </c>
     </row>
     <row r="137">
-      <c r="B137" s="3" t="s">
-        <v>206</v>
+      <c r="B137" s="10" t="s">
+        <v>207</v>
       </c>
       <c r="C137" s="5">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
       <c r="D137" s="6">
-        <v>1220.91</v>
+        <v>1154.83</v>
       </c>
       <c r="E137" s="6">
-        <v>25639.1</v>
+        <v>3464.5</v>
       </c>
       <c r="F137" s="6">
-        <v>984.7</v>
+        <v>1942.35</v>
       </c>
       <c r="G137" s="6">
-        <v>20678.7</v>
-      </c>
-      <c r="H137" s="15">
-        <v>-4960.4</v>
-      </c>
-      <c r="I137" s="14">
-        <v>-0.1935</v>
+        <v>5827.05</v>
+      </c>
+      <c r="H137" s="14">
+        <v>2362.55</v>
+      </c>
+      <c r="I137" s="8">
+        <v>0.6819</v>
       </c>
       <c r="J137" s="9" t="s">
         <v>26</v>
@@ -5815,28 +5869,28 @@
     </row>
     <row r="138">
       <c r="B138" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C138" s="5">
-        <v>53.0</v>
-      </c>
-      <c r="D138" s="6">
-        <v>729.68</v>
-      </c>
-      <c r="E138" s="6">
-        <v>38672.9</v>
-      </c>
-      <c r="F138" s="6">
-        <v>620.4</v>
-      </c>
-      <c r="G138" s="6">
-        <v>32881.2</v>
-      </c>
-      <c r="H138" s="15">
-        <v>-5791.7</v>
-      </c>
-      <c r="I138" s="14">
-        <v>-0.1498</v>
+        <v>208</v>
+      </c>
+      <c r="C138" s="16">
+        <v>39.0</v>
+      </c>
+      <c r="D138" s="17">
+        <v>379.94</v>
+      </c>
+      <c r="E138" s="17">
+        <v>14817.69</v>
+      </c>
+      <c r="F138" s="17">
+        <v>91.59</v>
+      </c>
+      <c r="G138" s="17">
+        <v>3572.01</v>
+      </c>
+      <c r="H138" s="18">
+        <v>-11245.7</v>
+      </c>
+      <c r="I138" s="16">
+        <v>-0.7589</v>
       </c>
       <c r="J138" s="9" t="s">
         <v>26</v>
@@ -5849,239 +5903,239 @@
       </c>
     </row>
     <row r="139">
-      <c r="B139" s="3" t="s">
-        <v>208</v>
+      <c r="B139" s="10" t="s">
+        <v>209</v>
       </c>
       <c r="C139" s="5">
-        <v>226.0</v>
+        <v>11.0</v>
       </c>
       <c r="D139" s="5">
-        <v>136.74</v>
+        <v>80.54</v>
       </c>
       <c r="E139" s="6">
-        <v>30902.6</v>
+        <v>885.9</v>
       </c>
       <c r="F139" s="6">
-        <v>110.35</v>
+        <v>265.85</v>
       </c>
       <c r="G139" s="6">
-        <v>24939.1</v>
-      </c>
-      <c r="H139" s="15">
-        <v>-5963.5</v>
-      </c>
-      <c r="I139" s="14">
-        <v>-0.193</v>
+        <v>2924.35</v>
+      </c>
+      <c r="H139" s="14">
+        <v>2038.45</v>
+      </c>
+      <c r="I139" s="8">
+        <v>2.301</v>
       </c>
       <c r="J139" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K139" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L139" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="140">
-      <c r="B140" s="3" t="s">
-        <v>209</v>
+      <c r="B140" s="10" t="s">
+        <v>210</v>
       </c>
       <c r="C140" s="5">
-        <v>33.0</v>
+        <v>1.0</v>
       </c>
       <c r="D140" s="6">
-        <v>1071.83</v>
+        <v>415.9</v>
       </c>
       <c r="E140" s="6">
-        <v>35370.25</v>
+        <v>415.9</v>
       </c>
       <c r="F140" s="6">
-        <v>870.95</v>
+        <v>1918.55</v>
       </c>
       <c r="G140" s="6">
-        <v>28741.35</v>
-      </c>
-      <c r="H140" s="15">
-        <v>-6628.9</v>
-      </c>
-      <c r="I140" s="14">
-        <v>-0.1874</v>
+        <v>1918.55</v>
+      </c>
+      <c r="H140" s="14">
+        <v>1502.65</v>
+      </c>
+      <c r="I140" s="8">
+        <v>3.613</v>
       </c>
       <c r="J140" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K140" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L140" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="141">
-      <c r="B141" s="3" t="s">
-        <v>210</v>
+      <c r="B141" s="10" t="s">
+        <v>211</v>
       </c>
       <c r="C141" s="5">
-        <v>221.0</v>
+        <v>1.0</v>
       </c>
       <c r="D141" s="6">
-        <v>126.22</v>
+        <v>1935.3</v>
       </c>
       <c r="E141" s="6">
-        <v>27894.4</v>
+        <v>1935.3</v>
       </c>
       <c r="F141" s="6">
-        <v>85.66</v>
+        <v>1790.3</v>
       </c>
       <c r="G141" s="6">
-        <v>18930.86</v>
+        <v>1790.3</v>
       </c>
       <c r="H141" s="15">
-        <v>-8963.54</v>
-      </c>
-      <c r="I141" s="14">
-        <v>-0.3213</v>
+        <v>-145.0</v>
+      </c>
+      <c r="I141" s="13">
+        <v>-0.0749</v>
       </c>
       <c r="J141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K141" s="9" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="L141" s="9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="142">
       <c r="B142" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C142" s="5">
-        <v>59.0</v>
+        <v>3.0</v>
       </c>
       <c r="D142" s="5">
-        <v>576.82</v>
+        <v>394.42</v>
       </c>
       <c r="E142" s="6">
-        <v>34032.35</v>
+        <v>1183.25</v>
       </c>
       <c r="F142" s="6">
-        <v>423.85</v>
+        <v>312.55</v>
       </c>
       <c r="G142" s="6">
-        <v>25007.15</v>
+        <v>937.65</v>
       </c>
       <c r="H142" s="15">
-        <v>-9025.2</v>
-      </c>
-      <c r="I142" s="14">
-        <v>-0.2652</v>
+        <v>-245.6</v>
+      </c>
+      <c r="I142" s="13">
+        <v>-0.2076</v>
       </c>
       <c r="J142" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K142" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L142" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="143">
-      <c r="B143" s="3" t="s">
-        <v>212</v>
+      <c r="B143" s="10" t="s">
+        <v>213</v>
       </c>
       <c r="C143" s="5">
-        <v>23.0</v>
+        <v>1.0</v>
       </c>
       <c r="D143" s="6">
-        <v>1205.77</v>
+        <v>1526.5</v>
       </c>
       <c r="E143" s="6">
-        <v>27732.8</v>
+        <v>1526.5</v>
       </c>
       <c r="F143" s="6">
-        <v>796.0</v>
+        <v>760.45</v>
       </c>
       <c r="G143" s="6">
-        <v>18308.0</v>
+        <v>760.45</v>
       </c>
       <c r="H143" s="15">
-        <v>-9424.8</v>
-      </c>
-      <c r="I143" s="14">
-        <v>-0.3398</v>
+        <v>-766.05</v>
+      </c>
+      <c r="I143" s="13">
+        <v>-0.5018</v>
       </c>
       <c r="J143" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K143" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L143" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="144">
-      <c r="B144" s="3" t="s">
-        <v>213</v>
+      <c r="B144" s="10" t="s">
+        <v>214</v>
       </c>
       <c r="C144" s="5">
-        <v>69.0</v>
+        <v>1.0</v>
       </c>
       <c r="D144" s="5">
-        <v>463.0</v>
+        <v>588.9</v>
       </c>
       <c r="E144" s="6">
-        <v>31947.25</v>
+        <v>588.9</v>
       </c>
       <c r="F144" s="6">
-        <v>303.2</v>
+        <v>750.3</v>
       </c>
       <c r="G144" s="6">
-        <v>20920.8</v>
-      </c>
-      <c r="H144" s="15">
-        <v>-11026.45</v>
-      </c>
-      <c r="I144" s="14">
-        <v>-0.3451</v>
+        <v>750.3</v>
+      </c>
+      <c r="H144" s="14">
+        <v>161.4</v>
+      </c>
+      <c r="I144" s="8">
+        <v>0.2741</v>
       </c>
       <c r="J144" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K144" s="9" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="L144" s="9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="145">
-      <c r="B145" s="3" t="s">
-        <v>214</v>
+      <c r="B145" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="C145" s="4">
-        <v>39.0</v>
+        <v>5.0</v>
       </c>
       <c r="D145" s="5">
-        <v>379.94</v>
+        <v>162.33</v>
       </c>
       <c r="E145" s="6">
-        <v>14817.69</v>
+        <v>811.65</v>
       </c>
       <c r="F145" s="6">
-        <v>90.86</v>
+        <v>131.0</v>
       </c>
       <c r="G145" s="6">
-        <v>3543.54</v>
+        <v>655.0</v>
       </c>
       <c r="H145" s="15">
-        <v>-11274.15</v>
-      </c>
-      <c r="I145" s="14">
-        <v>-0.7609</v>
+        <v>-156.65</v>
+      </c>
+      <c r="I145" s="13">
+        <v>-0.193</v>
       </c>
       <c r="J145" s="9" t="s">
         <v>26</v>
@@ -6094,114 +6148,326 @@
       </c>
     </row>
     <row r="146">
-      <c r="B146" s="3" t="s">
-        <v>215</v>
+      <c r="B146" s="10" t="s">
+        <v>216</v>
       </c>
       <c r="C146" s="4">
-        <v>552.0</v>
+        <v>1.0</v>
       </c>
       <c r="D146" s="5">
-        <v>63.33</v>
+        <v>262.0</v>
       </c>
       <c r="E146" s="6">
-        <v>17796.09</v>
+        <v>262.0</v>
       </c>
       <c r="F146" s="6">
-        <v>34.0</v>
+        <v>640.9</v>
       </c>
       <c r="G146" s="6">
-        <v>18768.0</v>
-      </c>
-      <c r="H146" s="15">
-        <v>-16188.61</v>
-      </c>
-      <c r="I146" s="14">
-        <v>-0.4631</v>
+        <v>640.9</v>
+      </c>
+      <c r="H146" s="14">
+        <v>378.9</v>
+      </c>
+      <c r="I146" s="8">
+        <v>1.4462</v>
       </c>
       <c r="J146" s="9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K146" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L146" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="147">
-      <c r="B147" s="3"/>
-      <c r="C147" s="4"/>
-      <c r="D147" s="5"/>
-      <c r="E147" s="6"/>
-      <c r="F147" s="6"/>
-      <c r="G147" s="6"/>
-      <c r="H147" s="12"/>
-      <c r="I147" s="8"/>
+      <c r="B147" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C147" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D147" s="5">
+        <v>53.6</v>
+      </c>
+      <c r="E147" s="6">
+        <v>53.6</v>
+      </c>
+      <c r="F147" s="6">
+        <v>497.5</v>
+      </c>
+      <c r="G147" s="6">
+        <v>497.5</v>
+      </c>
+      <c r="H147" s="14">
+        <v>443.9</v>
+      </c>
+      <c r="I147" s="8">
+        <v>8.2817</v>
+      </c>
+      <c r="J147" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K147" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L147" s="9" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="148">
-      <c r="B148" s="3"/>
-      <c r="C148" s="4"/>
-      <c r="D148" s="5"/>
-      <c r="E148" s="6"/>
-      <c r="F148" s="6"/>
-      <c r="G148" s="6"/>
-      <c r="H148" s="12"/>
-      <c r="I148" s="8"/>
+      <c r="B148" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="C148" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D148" s="5">
+        <v>119.7</v>
+      </c>
+      <c r="E148" s="6">
+        <v>119.7</v>
+      </c>
+      <c r="F148" s="6">
+        <v>330.07</v>
+      </c>
+      <c r="G148" s="6">
+        <v>330.07</v>
+      </c>
+      <c r="H148" s="14">
+        <v>210.37</v>
+      </c>
+      <c r="I148" s="8">
+        <v>1.7575</v>
+      </c>
+      <c r="J148" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K148" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L148" s="9" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="149">
-      <c r="B149" s="3"/>
-      <c r="C149" s="4"/>
-      <c r="D149" s="5"/>
-      <c r="E149" s="6"/>
-      <c r="F149" s="6"/>
-      <c r="G149" s="6"/>
-      <c r="H149" s="15"/>
-      <c r="I149" s="14"/>
+      <c r="B149" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="C149" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D149" s="5">
+        <v>165.85</v>
+      </c>
+      <c r="E149" s="6">
+        <v>165.85</v>
+      </c>
+      <c r="F149" s="6">
+        <v>251.0</v>
+      </c>
+      <c r="G149" s="6">
+        <v>251.0</v>
+      </c>
+      <c r="H149" s="14">
+        <v>85.15</v>
+      </c>
+      <c r="I149" s="8">
+        <v>0.5134</v>
+      </c>
+      <c r="J149" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K149" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L149" s="9" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="150">
-      <c r="B150" s="3"/>
-      <c r="C150" s="5"/>
-      <c r="D150" s="5"/>
-      <c r="E150" s="6"/>
-      <c r="F150" s="6"/>
-      <c r="G150" s="6"/>
-      <c r="H150" s="12"/>
-      <c r="I150" s="8"/>
+      <c r="B150" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="C150" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D150" s="5">
+        <v>142.65</v>
+      </c>
+      <c r="E150" s="6">
+        <v>142.65</v>
+      </c>
+      <c r="F150" s="6">
+        <v>244.81</v>
+      </c>
+      <c r="G150" s="6">
+        <v>244.81</v>
+      </c>
+      <c r="H150" s="14">
+        <v>102.16</v>
+      </c>
+      <c r="I150" s="8">
+        <v>0.7162</v>
+      </c>
+      <c r="J150" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K150" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L150" s="9" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="151">
-      <c r="E151" s="16"/>
-      <c r="F151" s="16"/>
-      <c r="G151" s="16"/>
-      <c r="H151" s="17"/>
-      <c r="I151" s="18"/>
+      <c r="B151" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="C151" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D151" s="5">
+        <v>111.28</v>
+      </c>
+      <c r="E151" s="6">
+        <v>111.28</v>
+      </c>
+      <c r="F151" s="6">
+        <v>226.6</v>
+      </c>
+      <c r="G151" s="6">
+        <v>226.6</v>
+      </c>
+      <c r="H151" s="14">
+        <v>115.32</v>
+      </c>
+      <c r="I151" s="8">
+        <v>1.0363</v>
+      </c>
+      <c r="J151" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K151" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L151" s="9" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="152">
-      <c r="E152" s="16"/>
-      <c r="F152" s="16"/>
-      <c r="G152" s="16"/>
-      <c r="H152" s="17"/>
-      <c r="I152" s="18"/>
+      <c r="B152" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C152" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D152" s="5">
+        <v>25.25</v>
+      </c>
+      <c r="E152" s="6">
+        <v>25.25</v>
+      </c>
+      <c r="F152" s="6">
+        <v>118.07</v>
+      </c>
+      <c r="G152" s="6">
+        <v>118.07</v>
+      </c>
+      <c r="H152" s="14">
+        <v>92.82</v>
+      </c>
+      <c r="I152" s="8">
+        <v>3.676</v>
+      </c>
+      <c r="J152" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K152" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L152" s="9" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="153">
-      <c r="E153" s="16"/>
-      <c r="F153" s="16"/>
-      <c r="G153" s="16"/>
-      <c r="H153" s="17"/>
-      <c r="I153" s="18"/>
+      <c r="B153" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="C153" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D153" s="5">
+        <v>51.86</v>
+      </c>
+      <c r="E153" s="6">
+        <v>51.86</v>
+      </c>
+      <c r="F153" s="6">
+        <v>101.4</v>
+      </c>
+      <c r="G153" s="6">
+        <v>101.4</v>
+      </c>
+      <c r="H153" s="14">
+        <v>49.54</v>
+      </c>
+      <c r="I153" s="8">
+        <v>0.9552</v>
+      </c>
+      <c r="J153" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K153" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L153" s="9" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="154">
-      <c r="E154" s="16"/>
-      <c r="F154" s="16"/>
-      <c r="G154" s="16"/>
-      <c r="H154" s="17"/>
-      <c r="I154" s="18"/>
+      <c r="B154" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="C154" s="20">
+        <v>1.0</v>
+      </c>
+      <c r="D154" s="20">
+        <v>116.0</v>
+      </c>
+      <c r="E154" s="21">
+        <v>116.0</v>
+      </c>
+      <c r="F154" s="21">
+        <v>101.1</v>
+      </c>
+      <c r="G154" s="21">
+        <v>101.1</v>
+      </c>
+      <c r="H154" s="22">
+        <v>-14.9</v>
+      </c>
+      <c r="I154" s="23">
+        <v>-0.1284</v>
+      </c>
+      <c r="J154" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="K154" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="L154" s="24" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="155">
-      <c r="E155" s="16"/>
-      <c r="F155" s="16"/>
-      <c r="G155" s="16"/>
-      <c r="H155" s="17"/>
-      <c r="I155" s="18"/>
+      <c r="E155" s="25"/>
+      <c r="F155" s="25"/>
+      <c r="G155" s="25"/>
+      <c r="H155" s="26"/>
+      <c r="I155" s="27"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/data/portfolio.xlsx
+++ b/data/portfolio.xlsx
@@ -4,6 +4,7 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Portfolio" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="MB" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="229">
   <si>
     <t>Symbol</t>
   </si>
@@ -800,7 +801,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -885,6 +886,12 @@
     <xf borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -894,6 +901,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -6527,4 +6538,313 @@
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="B18" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="B19" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="B22" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="B24" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="B25" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="B26" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/portfolio.xlsx
+++ b/data/portfolio.xlsx
@@ -1190,16 +1190,16 @@
         <v>51.86</v>
       </c>
       <c r="F2" s="7">
-        <v>96.59</v>
+        <v>96.9</v>
       </c>
       <c r="G2" s="7">
-        <v>96.59</v>
+        <v>96.9</v>
       </c>
       <c r="H2" s="7">
-        <v>44.73</v>
+        <v>45.04</v>
       </c>
       <c r="I2" s="8">
-        <v>0.8624</v>
+        <v>0.8684</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>15</v>
@@ -1442,16 +1442,16 @@
         <v>110.1</v>
       </c>
       <c r="F8" s="11">
-        <v>526.5</v>
+        <v>527.0</v>
       </c>
       <c r="G8" s="11">
-        <v>526.5</v>
+        <v>527.0</v>
       </c>
       <c r="H8" s="11">
-        <v>416.4</v>
+        <v>416.9</v>
       </c>
       <c r="I8" s="12">
-        <v>3.782</v>
+        <v>3.7866</v>
       </c>
       <c r="J8" s="13" t="s">
         <v>26</v>
@@ -1484,16 +1484,16 @@
         <v>29095.0</v>
       </c>
       <c r="F9" s="11">
-        <v>807.5</v>
+        <v>807.65</v>
       </c>
       <c r="G9" s="11">
-        <v>80750.0</v>
+        <v>80765.0</v>
       </c>
       <c r="H9" s="11">
-        <v>51655.0</v>
+        <v>51670.0</v>
       </c>
       <c r="I9" s="12">
-        <v>1.7754</v>
+        <v>1.7759</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>26</v>
@@ -1526,16 +1526,16 @@
         <v>59793.8</v>
       </c>
       <c r="F10" s="11">
-        <v>654.3</v>
+        <v>652.6</v>
       </c>
       <c r="G10" s="7">
-        <v>136094.4</v>
+        <v>135740.8</v>
       </c>
       <c r="H10" s="11">
-        <v>76300.6</v>
+        <v>75947.0</v>
       </c>
       <c r="I10" s="12">
-        <v>1.2761</v>
+        <v>1.2701</v>
       </c>
       <c r="J10" s="13" t="s">
         <v>15</v>
@@ -1568,16 +1568,16 @@
         <v>3887.0</v>
       </c>
       <c r="F11" s="11">
-        <v>104.0</v>
+        <v>103.9</v>
       </c>
       <c r="G11" s="11">
-        <v>16640.0</v>
+        <v>16624.0</v>
       </c>
       <c r="H11" s="11">
-        <v>12753.0</v>
+        <v>12737.0</v>
       </c>
       <c r="I11" s="14">
-        <v>3.2809</v>
+        <v>3.2768</v>
       </c>
       <c r="J11" s="15" t="s">
         <v>15</v>
@@ -1610,16 +1610,16 @@
         <v>222.45</v>
       </c>
       <c r="F12" s="11">
-        <v>385.8</v>
+        <v>386.55</v>
       </c>
       <c r="G12" s="7">
-        <v>385.8</v>
+        <v>386.55</v>
       </c>
       <c r="H12" s="11">
-        <v>163.35</v>
+        <v>164.1</v>
       </c>
       <c r="I12" s="12">
-        <v>0.7343</v>
+        <v>0.7377</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>26</v>
@@ -1652,16 +1652,16 @@
         <v>588.9</v>
       </c>
       <c r="F13" s="11">
-        <v>787.45</v>
+        <v>784.1</v>
       </c>
       <c r="G13" s="7">
-        <v>787.45</v>
+        <v>784.1</v>
       </c>
       <c r="H13" s="11">
-        <v>198.55</v>
+        <v>195.2</v>
       </c>
       <c r="I13" s="14">
-        <v>0.3372</v>
+        <v>0.3315</v>
       </c>
       <c r="J13" s="15" t="s">
         <v>15</v>
@@ -1862,16 +1862,16 @@
         <v>102284.55</v>
       </c>
       <c r="F18" s="11">
-        <v>1999.1</v>
+        <v>2000.5</v>
       </c>
       <c r="G18" s="11">
-        <v>403818.2</v>
+        <v>404101.0</v>
       </c>
       <c r="H18" s="11">
-        <v>301533.65</v>
+        <v>301816.45</v>
       </c>
       <c r="I18" s="14">
-        <v>2.948</v>
+        <v>2.9508</v>
       </c>
       <c r="J18" s="15" t="s">
         <v>15</v>
@@ -1904,16 +1904,16 @@
         <v>25.25</v>
       </c>
       <c r="F19" s="11">
-        <v>138.15</v>
+        <v>138.27</v>
       </c>
       <c r="G19" s="7">
-        <v>138.15</v>
+        <v>138.27</v>
       </c>
       <c r="H19" s="11">
-        <v>112.9</v>
+        <v>113.02</v>
       </c>
       <c r="I19" s="14">
-        <v>4.4713</v>
+        <v>4.476</v>
       </c>
       <c r="J19" s="16" t="s">
         <v>15</v>
@@ -2072,16 +2072,16 @@
         <v>189012.0</v>
       </c>
       <c r="F23" s="11">
-        <v>14500.0</v>
+        <v>14524.4</v>
       </c>
       <c r="G23" s="7">
-        <v>449500.0</v>
+        <v>450256.4</v>
       </c>
       <c r="H23" s="11">
-        <v>260488.0</v>
+        <v>261244.4</v>
       </c>
       <c r="I23" s="12">
-        <v>1.3782</v>
+        <v>1.3822</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>15</v>
@@ -2114,16 +2114,16 @@
         <v>11538.0</v>
       </c>
       <c r="F24" s="11">
-        <v>1394.9</v>
+        <v>1391.5</v>
       </c>
       <c r="G24" s="7">
-        <v>55796.0</v>
+        <v>55660.0</v>
       </c>
       <c r="H24" s="11">
-        <v>44258.0</v>
+        <v>44122.0</v>
       </c>
       <c r="I24" s="12">
-        <v>3.8358</v>
+        <v>3.8241</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>15</v>
@@ -2156,16 +2156,16 @@
         <v>3464.5</v>
       </c>
       <c r="F25" s="7">
-        <v>1892.0</v>
+        <v>1892.45</v>
       </c>
       <c r="G25" s="7">
-        <v>5676.0</v>
+        <v>5677.35</v>
       </c>
       <c r="H25" s="7">
-        <v>2211.5</v>
+        <v>2212.85</v>
       </c>
       <c r="I25" s="17">
-        <v>0.6383</v>
+        <v>0.6387</v>
       </c>
       <c r="J25" s="16" t="s">
         <v>15</v>
@@ -2198,16 +2198,16 @@
         <v>53.6</v>
       </c>
       <c r="F26" s="7">
-        <v>514.3</v>
+        <v>514.55</v>
       </c>
       <c r="G26" s="7">
-        <v>514.3</v>
+        <v>514.55</v>
       </c>
       <c r="H26" s="7">
-        <v>460.7</v>
+        <v>460.95</v>
       </c>
       <c r="I26" s="17">
-        <v>8.5951</v>
+        <v>8.5998</v>
       </c>
       <c r="J26" s="16" t="s">
         <v>15</v>
@@ -2240,16 +2240,16 @@
         <v>415.9</v>
       </c>
       <c r="F27" s="11">
-        <v>1915.5</v>
+        <v>1915.7</v>
       </c>
       <c r="G27" s="11">
-        <v>1915.5</v>
+        <v>1915.7</v>
       </c>
       <c r="H27" s="11">
-        <v>1499.6</v>
+        <v>1499.8</v>
       </c>
       <c r="I27" s="14">
-        <v>3.6057</v>
+        <v>3.6062</v>
       </c>
       <c r="J27" s="16" t="s">
         <v>15</v>
@@ -2576,16 +2576,16 @@
         <v>24773.85</v>
       </c>
       <c r="F35" s="11">
-        <v>424.3</v>
+        <v>424.65</v>
       </c>
       <c r="G35" s="11">
-        <v>27155.2</v>
+        <v>27177.6</v>
       </c>
       <c r="H35" s="11">
-        <v>2381.35</v>
+        <v>2403.75</v>
       </c>
       <c r="I35" s="12">
-        <v>0.0961</v>
+        <v>0.097</v>
       </c>
       <c r="J35" s="9" t="s">
         <v>26</v>
@@ -2702,16 +2702,16 @@
         <v>19998.4</v>
       </c>
       <c r="F38" s="11">
-        <v>1148.0</v>
+        <v>1145.55</v>
       </c>
       <c r="G38" s="7">
-        <v>18368.0</v>
+        <v>18328.8</v>
       </c>
       <c r="H38" s="11">
-        <v>-1630.4</v>
+        <v>-1669.6</v>
       </c>
       <c r="I38" s="14">
-        <v>-0.0815</v>
+        <v>-0.0835</v>
       </c>
       <c r="J38" s="15" t="s">
         <v>26</v>
@@ -2744,16 +2744,16 @@
         <v>19800.0</v>
       </c>
       <c r="F39" s="11">
-        <v>1262.2</v>
+        <v>1262.55</v>
       </c>
       <c r="G39" s="7">
-        <v>18933.0</v>
+        <v>18938.25</v>
       </c>
       <c r="H39" s="11">
-        <v>-867.0</v>
+        <v>-861.75</v>
       </c>
       <c r="I39" s="12">
-        <v>-0.0438</v>
+        <v>-0.0435</v>
       </c>
       <c r="J39" s="9" t="s">
         <v>26</v>
@@ -2996,16 +2996,16 @@
         <v>394.05</v>
       </c>
       <c r="F45" s="11">
-        <v>334.7</v>
+        <v>334.4</v>
       </c>
       <c r="G45" s="11">
-        <v>334.7</v>
+        <v>334.4</v>
       </c>
       <c r="H45" s="11">
-        <v>-59.35</v>
+        <v>-59.65</v>
       </c>
       <c r="I45" s="12">
-        <v>-0.1506</v>
+        <v>-0.1514</v>
       </c>
       <c r="J45" s="9" t="s">
         <v>15</v>
@@ -3080,16 +3080,16 @@
         <v>11729.0</v>
       </c>
       <c r="F47" s="11">
-        <v>591.95</v>
+        <v>592.2</v>
       </c>
       <c r="G47" s="11">
-        <v>11839.0</v>
+        <v>11844.0</v>
       </c>
       <c r="H47" s="11">
-        <v>110.0</v>
+        <v>115.0</v>
       </c>
       <c r="I47" s="12">
-        <v>0.0094</v>
+        <v>0.0098</v>
       </c>
       <c r="J47" s="9" t="s">
         <v>26</v>
@@ -3122,16 +3122,16 @@
         <v>75624.0</v>
       </c>
       <c r="F48" s="11">
-        <v>3419.25</v>
+        <v>3420.3</v>
       </c>
       <c r="G48" s="7">
-        <v>68385.0</v>
+        <v>68406.0</v>
       </c>
       <c r="H48" s="11">
-        <v>-7239.0</v>
+        <v>-7218.0</v>
       </c>
       <c r="I48" s="12">
-        <v>-0.0957</v>
+        <v>-0.0954</v>
       </c>
       <c r="J48" s="13" t="s">
         <v>26</v>
@@ -3206,16 +3206,16 @@
         <v>12555.0</v>
       </c>
       <c r="F50" s="11">
-        <v>2574.0</v>
+        <v>2537.0</v>
       </c>
       <c r="G50" s="7">
-        <v>23166.0</v>
+        <v>22833.0</v>
       </c>
       <c r="H50" s="11">
-        <v>10611.0</v>
+        <v>10278.0</v>
       </c>
       <c r="I50" s="14">
-        <v>0.8452</v>
+        <v>0.8186</v>
       </c>
       <c r="J50" s="15" t="s">
         <v>26</v>
@@ -3374,16 +3374,16 @@
         <v>13793.3</v>
       </c>
       <c r="F54" s="7">
-        <v>620.5</v>
+        <v>620.75</v>
       </c>
       <c r="G54" s="7">
-        <v>14271.5</v>
+        <v>14277.25</v>
       </c>
       <c r="H54" s="7">
-        <v>478.2</v>
+        <v>483.95</v>
       </c>
       <c r="I54" s="8">
-        <v>0.0347</v>
+        <v>0.0351</v>
       </c>
       <c r="J54" s="9" t="s">
         <v>26</v>
@@ -3458,16 +3458,16 @@
         <v>45490.4</v>
       </c>
       <c r="F56" s="11">
-        <v>2083.1</v>
+        <v>2087.8</v>
       </c>
       <c r="G56" s="11">
-        <v>45828.2</v>
+        <v>45931.6</v>
       </c>
       <c r="H56" s="11">
-        <v>337.8</v>
+        <v>441.2</v>
       </c>
       <c r="I56" s="12">
-        <v>0.0074</v>
+        <v>0.0097</v>
       </c>
       <c r="J56" s="9" t="s">
         <v>26</v>
@@ -3668,16 +3668,16 @@
         <v>11919.9</v>
       </c>
       <c r="F61" s="11">
-        <v>4475.0</v>
+        <v>4453.8</v>
       </c>
       <c r="G61" s="7">
-        <v>13425.0</v>
+        <v>13361.4</v>
       </c>
       <c r="H61" s="11">
-        <v>1505.1</v>
+        <v>1441.5</v>
       </c>
       <c r="I61" s="8">
-        <v>0.1263</v>
+        <v>0.1209</v>
       </c>
       <c r="J61" s="9" t="s">
         <v>26</v>
@@ -3710,16 +3710,16 @@
         <v>72170.8</v>
       </c>
       <c r="F62" s="11">
-        <v>1872.05</v>
+        <v>1872.7</v>
       </c>
       <c r="G62" s="7">
-        <v>99218.65</v>
+        <v>99253.1</v>
       </c>
       <c r="H62" s="11">
-        <v>27047.85</v>
+        <v>27082.3</v>
       </c>
       <c r="I62" s="14">
-        <v>0.3748</v>
+        <v>0.3753</v>
       </c>
       <c r="J62" s="15" t="s">
         <v>26</v>
@@ -3794,16 +3794,16 @@
         <v>29686.25</v>
       </c>
       <c r="F64" s="11">
-        <v>796.0</v>
+        <v>800.8</v>
       </c>
       <c r="G64" s="11">
-        <v>35820.0</v>
+        <v>36036.0</v>
       </c>
       <c r="H64" s="11">
-        <v>6133.75</v>
+        <v>6349.75</v>
       </c>
       <c r="I64" s="12">
-        <v>0.2066</v>
+        <v>0.2139</v>
       </c>
       <c r="J64" s="9" t="s">
         <v>26</v>
@@ -4046,16 +4046,16 @@
         <v>10095.6</v>
       </c>
       <c r="F70" s="11">
-        <v>942.8</v>
+        <v>947.05</v>
       </c>
       <c r="G70" s="7">
-        <v>5656.8</v>
+        <v>5682.3</v>
       </c>
       <c r="H70" s="11">
-        <v>-4438.8</v>
+        <v>-4413.3</v>
       </c>
       <c r="I70" s="12">
-        <v>-0.4397</v>
+        <v>-0.4372</v>
       </c>
       <c r="J70" s="9" t="s">
         <v>26</v>
@@ -4172,16 +4172,16 @@
         <v>29813.65</v>
       </c>
       <c r="F73" s="11">
-        <v>673.0</v>
+        <v>675.9</v>
       </c>
       <c r="G73" s="7">
-        <v>26920.0</v>
+        <v>27036.0</v>
       </c>
       <c r="H73" s="11">
-        <v>-2893.65</v>
+        <v>-2777.65</v>
       </c>
       <c r="I73" s="12">
-        <v>-0.0971</v>
+        <v>-0.0932</v>
       </c>
       <c r="J73" s="9" t="s">
         <v>26</v>
@@ -4298,16 +4298,16 @@
         <v>39831.43</v>
       </c>
       <c r="F76" s="7">
-        <v>287.8</v>
+        <v>288.6</v>
       </c>
       <c r="G76" s="7">
-        <v>76842.6</v>
+        <v>77056.2</v>
       </c>
       <c r="H76" s="7">
-        <v>37011.17</v>
+        <v>37224.77</v>
       </c>
       <c r="I76" s="8">
-        <v>0.9292</v>
+        <v>0.9346</v>
       </c>
       <c r="J76" s="13" t="s">
         <v>26</v>
@@ -4676,16 +4676,16 @@
         <v>21722.1</v>
       </c>
       <c r="F85" s="11">
-        <v>1362.2</v>
+        <v>1362.85</v>
       </c>
       <c r="G85" s="7">
-        <v>42228.2</v>
+        <v>42248.35</v>
       </c>
       <c r="H85" s="11">
-        <v>20506.1</v>
+        <v>20526.25</v>
       </c>
       <c r="I85" s="12">
-        <v>0.944</v>
+        <v>0.9449</v>
       </c>
       <c r="J85" s="9" t="s">
         <v>26</v>
@@ -4844,16 +4844,16 @@
         <v>10241.0</v>
       </c>
       <c r="F89" s="11">
-        <v>151.0</v>
+        <v>151.32</v>
       </c>
       <c r="G89" s="7">
-        <v>9060.0</v>
+        <v>9079.2</v>
       </c>
       <c r="H89" s="11">
-        <v>-1181.0</v>
+        <v>-1161.8</v>
       </c>
       <c r="I89" s="17">
-        <v>-0.1153</v>
+        <v>-0.1134</v>
       </c>
       <c r="J89" s="15" t="s">
         <v>26</v>
@@ -5096,16 +5096,16 @@
         <v>68420.95</v>
       </c>
       <c r="F95" s="11">
-        <v>667.5</v>
+        <v>667.55</v>
       </c>
       <c r="G95" s="7">
-        <v>89445.0</v>
+        <v>89451.7</v>
       </c>
       <c r="H95" s="11">
-        <v>21024.05</v>
+        <v>21030.75</v>
       </c>
       <c r="I95" s="12">
-        <v>0.3073</v>
+        <v>0.3074</v>
       </c>
       <c r="J95" s="9" t="s">
         <v>26</v>
@@ -5222,16 +5222,16 @@
         <v>38589.0</v>
       </c>
       <c r="F98" s="11">
-        <v>4733.85</v>
+        <v>4736.5</v>
       </c>
       <c r="G98" s="7">
-        <v>37870.8</v>
+        <v>37892.0</v>
       </c>
       <c r="H98" s="11">
-        <v>-718.2</v>
+        <v>-697.0</v>
       </c>
       <c r="I98" s="14">
-        <v>-0.0186</v>
+        <v>-0.0181</v>
       </c>
       <c r="J98" s="15" t="s">
         <v>26</v>
@@ -5390,16 +5390,16 @@
         <v>9927.45</v>
       </c>
       <c r="F102" s="11">
-        <v>133.45</v>
+        <v>133.82</v>
       </c>
       <c r="G102" s="7">
-        <v>8674.25</v>
+        <v>8698.3</v>
       </c>
       <c r="H102" s="11">
-        <v>-1253.2</v>
+        <v>-1229.15</v>
       </c>
       <c r="I102" s="12">
-        <v>-0.1262</v>
+        <v>-0.1238</v>
       </c>
       <c r="J102" s="9" t="s">
         <v>26</v>
@@ -5642,16 +5642,16 @@
         <v>7303.1</v>
       </c>
       <c r="F108" s="11">
-        <v>1148.0</v>
+        <v>1145.55</v>
       </c>
       <c r="G108" s="11">
-        <v>8036.0</v>
+        <v>8018.85</v>
       </c>
       <c r="H108" s="11">
-        <v>732.9</v>
+        <v>715.75</v>
       </c>
       <c r="I108" s="12">
-        <v>0.1004</v>
+        <v>0.098</v>
       </c>
       <c r="J108" s="9" t="s">
         <v>26</v>
@@ -5684,16 +5684,16 @@
         <v>12681.65</v>
       </c>
       <c r="F109" s="11">
-        <v>591.95</v>
+        <v>592.2</v>
       </c>
       <c r="G109" s="11">
-        <v>13022.9</v>
+        <v>13028.4</v>
       </c>
       <c r="H109" s="11">
-        <v>341.25</v>
+        <v>346.75</v>
       </c>
       <c r="I109" s="12">
-        <v>0.0269</v>
+        <v>0.0273</v>
       </c>
       <c r="J109" s="9" t="s">
         <v>26</v>
@@ -5726,16 +5726,16 @@
         <v>11775.0</v>
       </c>
       <c r="F110" s="11">
-        <v>3419.25</v>
+        <v>3420.3</v>
       </c>
       <c r="G110" s="7">
-        <v>10257.75</v>
+        <v>10260.9</v>
       </c>
       <c r="H110" s="11">
-        <v>-1517.25</v>
+        <v>-1514.1</v>
       </c>
       <c r="I110" s="12">
-        <v>-0.1289</v>
+        <v>-0.1286</v>
       </c>
       <c r="J110" s="9" t="s">
         <v>26</v>
@@ -5768,16 +5768,16 @@
         <v>9925.04</v>
       </c>
       <c r="F111" s="11">
-        <v>113.4</v>
+        <v>113.45</v>
       </c>
       <c r="G111" s="7">
-        <v>10999.8</v>
+        <v>11004.65</v>
       </c>
       <c r="H111" s="11">
-        <v>1074.76</v>
+        <v>1079.61</v>
       </c>
       <c r="I111" s="12">
-        <v>0.1083</v>
+        <v>0.1088</v>
       </c>
       <c r="J111" s="9" t="s">
         <v>26</v>
@@ -5810,16 +5810,16 @@
         <v>9529.0</v>
       </c>
       <c r="F112" s="11">
-        <v>2083.1</v>
+        <v>2087.8</v>
       </c>
       <c r="G112" s="11">
-        <v>10415.5</v>
+        <v>10439.0</v>
       </c>
       <c r="H112" s="11">
-        <v>886.5</v>
+        <v>910.0</v>
       </c>
       <c r="I112" s="12">
-        <v>0.093</v>
+        <v>0.0955</v>
       </c>
       <c r="J112" s="9" t="s">
         <v>26</v>
@@ -5852,16 +5852,16 @@
         <v>13424.7</v>
       </c>
       <c r="F113" s="11">
-        <v>4475.0</v>
+        <v>4453.8</v>
       </c>
       <c r="G113" s="11">
-        <v>13425.0</v>
+        <v>13361.4</v>
       </c>
       <c r="H113" s="11">
-        <v>0.3</v>
+        <v>-63.3</v>
       </c>
       <c r="I113" s="12">
-        <v>0.0</v>
+        <v>-0.0047</v>
       </c>
       <c r="J113" s="13" t="s">
         <v>26</v>
@@ -5936,16 +5936,16 @@
         <v>10492.0</v>
       </c>
       <c r="F115" s="11">
-        <v>550.0</v>
+        <v>548.45</v>
       </c>
       <c r="G115" s="11">
-        <v>10450.0</v>
+        <v>10420.55</v>
       </c>
       <c r="H115" s="11">
-        <v>-42.0</v>
+        <v>-71.45</v>
       </c>
       <c r="I115" s="12">
-        <v>-0.004</v>
+        <v>-0.0068</v>
       </c>
       <c r="J115" s="9" t="s">
         <v>26</v>
@@ -5978,16 +5978,16 @@
         <v>14454.3</v>
       </c>
       <c r="F116" s="11">
-        <v>4733.85</v>
+        <v>4736.5</v>
       </c>
       <c r="G116" s="11">
-        <v>14201.55</v>
+        <v>14209.5</v>
       </c>
       <c r="H116" s="11">
-        <v>-252.75</v>
+        <v>-244.8</v>
       </c>
       <c r="I116" s="12">
-        <v>-0.0175</v>
+        <v>-0.0169</v>
       </c>
       <c r="J116" s="9" t="s">
         <v>26</v>
@@ -6020,16 +6020,16 @@
         <v>9850.1</v>
       </c>
       <c r="F117" s="11">
-        <v>463.4</v>
+        <v>464.05</v>
       </c>
       <c r="G117" s="11">
-        <v>12048.4</v>
+        <v>12065.3</v>
       </c>
       <c r="H117" s="11">
-        <v>2198.3</v>
+        <v>2215.2</v>
       </c>
       <c r="I117" s="12">
-        <v>0.2232</v>
+        <v>0.2249</v>
       </c>
       <c r="J117" s="9" t="s">
         <v>26</v>
@@ -6230,16 +6230,16 @@
         <v>1053.5</v>
       </c>
       <c r="F122" s="11">
-        <v>1849.8</v>
+        <v>1850.0</v>
       </c>
       <c r="G122" s="7">
-        <v>1849.8</v>
+        <v>1850.0</v>
       </c>
       <c r="H122" s="11">
-        <v>796.3</v>
+        <v>796.5</v>
       </c>
       <c r="I122" s="17">
-        <v>0.7559</v>
+        <v>0.7561</v>
       </c>
       <c r="J122" s="16" t="s">
         <v>15</v>
@@ -6398,16 +6398,16 @@
         <v>45461.6</v>
       </c>
       <c r="F126" s="11">
-        <v>654.3</v>
+        <v>652.6</v>
       </c>
       <c r="G126" s="7">
-        <v>157686.3</v>
+        <v>157276.6</v>
       </c>
       <c r="H126" s="11">
-        <v>112224.7</v>
+        <v>111815.0</v>
       </c>
       <c r="I126" s="14">
-        <v>2.4686</v>
+        <v>2.4595</v>
       </c>
       <c r="J126" s="15" t="s">
         <v>15</v>
@@ -6566,16 +6566,16 @@
         <v>1789.9</v>
       </c>
       <c r="F130" s="11">
-        <v>942.8</v>
+        <v>947.05</v>
       </c>
       <c r="G130" s="7">
-        <v>942.8</v>
+        <v>947.05</v>
       </c>
       <c r="H130" s="11">
-        <v>-847.1</v>
+        <v>-842.85</v>
       </c>
       <c r="I130" s="12">
-        <v>-0.4733</v>
+        <v>-0.4709</v>
       </c>
       <c r="J130" s="9" t="s">
         <v>26</v>
@@ -6608,16 +6608,16 @@
         <v>262.0</v>
       </c>
       <c r="F131" s="11">
-        <v>726.85</v>
+        <v>727.3</v>
       </c>
       <c r="G131" s="7">
-        <v>726.85</v>
+        <v>727.3</v>
       </c>
       <c r="H131" s="11">
-        <v>464.85</v>
+        <v>465.3</v>
       </c>
       <c r="I131" s="12">
-        <v>1.7742</v>
+        <v>1.776</v>
       </c>
       <c r="J131" s="9" t="s">
         <v>15</v>
@@ -6734,16 +6734,16 @@
         <v>79433.35</v>
       </c>
       <c r="F134" s="11">
-        <v>1999.1</v>
+        <v>2000.5</v>
       </c>
       <c r="G134" s="7">
-        <v>331850.6</v>
+        <v>332083.0</v>
       </c>
       <c r="H134" s="11">
-        <v>252417.25</v>
+        <v>252649.65</v>
       </c>
       <c r="I134" s="12">
-        <v>3.1777</v>
+        <v>3.1806</v>
       </c>
       <c r="J134" s="9" t="s">
         <v>15</v>
@@ -6944,16 +6944,16 @@
         <v>27243.0</v>
       </c>
       <c r="F139" s="11">
-        <v>14500.0</v>
+        <v>14500.25</v>
       </c>
       <c r="G139" s="7">
-        <v>43500.0</v>
+        <v>43500.75</v>
       </c>
       <c r="H139" s="11">
-        <v>16257.0</v>
+        <v>16257.75</v>
       </c>
       <c r="I139" s="8">
-        <v>0.5967</v>
+        <v>0.5968</v>
       </c>
       <c r="J139" s="9" t="s">
         <v>15</v>
@@ -7112,16 +7112,16 @@
         <v>885.9</v>
       </c>
       <c r="F143" s="11">
-        <v>314.5</v>
+        <v>314.9</v>
       </c>
       <c r="G143" s="7">
-        <v>3459.5</v>
+        <v>3463.9</v>
       </c>
       <c r="H143" s="11">
-        <v>2573.6</v>
+        <v>2578.0</v>
       </c>
       <c r="I143" s="14">
-        <v>2.9051</v>
+        <v>2.91</v>
       </c>
       <c r="J143" s="16" t="s">
         <v>15</v>
@@ -7154,16 +7154,16 @@
         <v>30662.25</v>
       </c>
       <c r="F144" s="11">
-        <v>1394.9</v>
+        <v>1391.5</v>
       </c>
       <c r="G144" s="11">
-        <v>111592.0</v>
+        <v>111320.0</v>
       </c>
       <c r="H144" s="11">
-        <v>80929.75</v>
+        <v>80657.75</v>
       </c>
       <c r="I144" s="12">
-        <v>2.6394</v>
+        <v>2.6305</v>
       </c>
       <c r="J144" s="9" t="s">
         <v>15</v>
@@ -7448,16 +7448,16 @@
         <v>24660.0</v>
       </c>
       <c r="F151" s="11">
-        <v>1262.2</v>
+        <v>1262.55</v>
       </c>
       <c r="G151" s="7">
-        <v>22719.6</v>
+        <v>22725.9</v>
       </c>
       <c r="H151" s="11">
-        <v>-1940.4</v>
+        <v>-1934.1</v>
       </c>
       <c r="I151" s="14">
-        <v>-0.0787</v>
+        <v>-0.0784</v>
       </c>
       <c r="J151" s="16" t="s">
         <v>26</v>
@@ -7742,16 +7742,16 @@
         <v>58774.2</v>
       </c>
       <c r="F158" s="20">
-        <v>591.95</v>
+        <v>592.2</v>
       </c>
       <c r="G158" s="21">
-        <v>62746.7</v>
+        <v>62773.2</v>
       </c>
       <c r="H158" s="20">
-        <v>3972.5</v>
+        <v>3999.0</v>
       </c>
       <c r="I158" s="12">
-        <v>0.0676</v>
+        <v>0.068</v>
       </c>
       <c r="J158" s="22" t="s">
         <v>26</v>
@@ -7825,16 +7825,16 @@
         <v>57363.6</v>
       </c>
       <c r="F160" s="7">
-        <v>3419.25</v>
+        <v>3420.3</v>
       </c>
       <c r="G160" s="7">
-        <v>61546.5</v>
+        <v>61565.4</v>
       </c>
       <c r="H160" s="25">
-        <v>4182.9</v>
+        <v>4201.8</v>
       </c>
       <c r="I160" s="26">
-        <v>0.0729</v>
+        <v>0.0732</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>26</v>
@@ -8071,16 +8071,16 @@
         <v>11114.0</v>
       </c>
       <c r="F166" s="7">
-        <v>620.5</v>
+        <v>620.75</v>
       </c>
       <c r="G166" s="7">
-        <v>12410.0</v>
+        <v>12415.0</v>
       </c>
       <c r="H166" s="25">
-        <v>1296.0</v>
+        <v>1301.0</v>
       </c>
       <c r="I166" s="26">
-        <v>0.1166</v>
+        <v>0.1171</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>26</v>
@@ -8153,16 +8153,16 @@
         <v>17812.6</v>
       </c>
       <c r="F168" s="7">
-        <v>2083.1</v>
+        <v>2087.8</v>
       </c>
       <c r="G168" s="7">
-        <v>18747.9</v>
+        <v>18790.2</v>
       </c>
       <c r="H168" s="25">
-        <v>935.3</v>
+        <v>977.6</v>
       </c>
       <c r="I168" s="26">
-        <v>0.0525</v>
+        <v>0.0549</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>26</v>
@@ -8235,16 +8235,16 @@
         <v>86098.2</v>
       </c>
       <c r="F170" s="7">
-        <v>654.3</v>
+        <v>652.6</v>
       </c>
       <c r="G170" s="7">
-        <v>104688.0</v>
+        <v>104416.0</v>
       </c>
       <c r="H170" s="25">
-        <v>18589.8</v>
+        <v>18317.8</v>
       </c>
       <c r="I170" s="26">
-        <v>0.2159</v>
+        <v>0.2128</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>15</v>
@@ -8399,16 +8399,16 @@
         <v>8567.04</v>
       </c>
       <c r="F174" s="28">
-        <v>104.0</v>
+        <v>103.9</v>
       </c>
       <c r="G174" s="28">
-        <v>14352.0</v>
+        <v>14338.2</v>
       </c>
       <c r="H174" s="28">
-        <v>5784.96</v>
+        <v>5771.16</v>
       </c>
       <c r="I174" s="29">
-        <v>0.6753</v>
+        <v>0.6736</v>
       </c>
       <c r="J174" s="1" t="s">
         <v>15</v>
@@ -8481,16 +8481,16 @@
         <v>79586.6</v>
       </c>
       <c r="F176" s="28">
-        <v>4475.0</v>
+        <v>4453.8</v>
       </c>
       <c r="G176" s="28">
-        <v>80550.0</v>
+        <v>80168.4</v>
       </c>
       <c r="H176" s="28">
-        <v>963.4</v>
+        <v>581.8</v>
       </c>
       <c r="I176" s="29">
-        <v>0.0121</v>
+        <v>0.0073</v>
       </c>
       <c r="J176" s="1" t="s">
         <v>26</v>
@@ -8522,16 +8522,16 @@
         <v>35446.4</v>
       </c>
       <c r="F177" s="28">
-        <v>1872.05</v>
+        <v>1872.7</v>
       </c>
       <c r="G177" s="28">
-        <v>56161.5</v>
+        <v>56181.0</v>
       </c>
       <c r="H177" s="28">
-        <v>20715.1</v>
+        <v>20734.6</v>
       </c>
       <c r="I177" s="29">
-        <v>0.5844</v>
+        <v>0.585</v>
       </c>
       <c r="J177" s="1" t="s">
         <v>26</v>
@@ -8850,16 +8850,16 @@
         <v>639.95</v>
       </c>
       <c r="F185" s="28">
-        <v>437.9</v>
+        <v>437.45</v>
       </c>
       <c r="G185" s="28">
-        <v>437.9</v>
+        <v>437.45</v>
       </c>
       <c r="H185" s="28">
-        <v>-202.05</v>
+        <v>-202.5</v>
       </c>
       <c r="I185" s="29">
-        <v>-0.3157</v>
+        <v>-0.3164</v>
       </c>
       <c r="J185" s="1" t="s">
         <v>26</v>
@@ -9178,16 +9178,16 @@
         <v>1679.0</v>
       </c>
       <c r="F193" s="28">
-        <v>1999.1</v>
+        <v>2000.5</v>
       </c>
       <c r="G193" s="28">
-        <v>1999.1</v>
+        <v>2000.5</v>
       </c>
       <c r="H193" s="28">
-        <v>320.1</v>
+        <v>321.5</v>
       </c>
       <c r="I193" s="29">
-        <v>0.1906</v>
+        <v>0.1915</v>
       </c>
       <c r="J193" s="1" t="s">
         <v>15</v>
@@ -9260,16 +9260,16 @@
         <v>84780.2</v>
       </c>
       <c r="F195" s="28">
-        <v>287.8</v>
+        <v>288.6</v>
       </c>
       <c r="G195" s="28">
-        <v>160016.8</v>
+        <v>160461.6</v>
       </c>
       <c r="H195" s="28">
-        <v>75236.6</v>
+        <v>75681.4</v>
       </c>
       <c r="I195" s="29">
-        <v>0.8874</v>
+        <v>0.8927</v>
       </c>
       <c r="J195" s="1" t="s">
         <v>26</v>
@@ -9383,16 +9383,16 @@
         <v>37387.9</v>
       </c>
       <c r="F198" s="28">
-        <v>550.0</v>
+        <v>548.45</v>
       </c>
       <c r="G198" s="28">
-        <v>41800.0</v>
+        <v>41682.2</v>
       </c>
       <c r="H198" s="28">
-        <v>4412.1</v>
+        <v>4294.3</v>
       </c>
       <c r="I198" s="29">
-        <v>0.118</v>
+        <v>0.1149</v>
       </c>
       <c r="J198" s="1" t="s">
         <v>26</v>
@@ -9506,16 +9506,16 @@
         <v>14635.0</v>
       </c>
       <c r="F201" s="28">
-        <v>309.45</v>
+        <v>309.55</v>
       </c>
       <c r="G201" s="28">
-        <v>15472.5</v>
+        <v>15477.5</v>
       </c>
       <c r="H201" s="28">
-        <v>837.5</v>
+        <v>842.5</v>
       </c>
       <c r="I201" s="29">
-        <v>0.0572</v>
+        <v>0.0576</v>
       </c>
       <c r="J201" s="1" t="s">
         <v>26</v>
@@ -9752,16 +9752,16 @@
         <v>9643.15</v>
       </c>
       <c r="F207" s="28">
-        <v>761.15</v>
+        <v>761.95</v>
       </c>
       <c r="G207" s="28">
-        <v>9894.95</v>
+        <v>9905.35</v>
       </c>
       <c r="H207" s="28">
-        <v>251.8</v>
+        <v>262.2</v>
       </c>
       <c r="I207" s="29">
-        <v>0.0261</v>
+        <v>0.0272</v>
       </c>
       <c r="J207" s="1" t="s">
         <v>26</v>
@@ -9793,16 +9793,16 @@
         <v>9346.2</v>
       </c>
       <c r="F208" s="28">
-        <v>1362.2</v>
+        <v>1362.85</v>
       </c>
       <c r="G208" s="28">
-        <v>16346.4</v>
+        <v>16354.2</v>
       </c>
       <c r="H208" s="28">
-        <v>7000.2</v>
+        <v>7008.0</v>
       </c>
       <c r="I208" s="29">
-        <v>0.749</v>
+        <v>0.7498</v>
       </c>
       <c r="J208" s="1" t="s">
         <v>26</v>
@@ -10080,16 +10080,16 @@
         <v>137415.0</v>
       </c>
       <c r="F215" s="28">
-        <v>14515.0</v>
+        <v>14519.18</v>
       </c>
       <c r="G215" s="28">
-        <v>217725.0</v>
+        <v>217787.7</v>
       </c>
       <c r="H215" s="28">
-        <v>80310.0</v>
+        <v>80372.7</v>
       </c>
       <c r="I215" s="29">
-        <v>0.5844</v>
+        <v>0.5849</v>
       </c>
       <c r="J215" s="1" t="s">
         <v>15</v>
@@ -10162,16 +10162,16 @@
         <v>18092.0</v>
       </c>
       <c r="F217" s="28">
-        <v>14525.0</v>
+        <v>14570.28</v>
       </c>
       <c r="G217" s="28">
-        <v>29050.0</v>
+        <v>29140.56</v>
       </c>
       <c r="H217" s="28">
-        <v>10958.0</v>
+        <v>11048.56</v>
       </c>
       <c r="I217" s="29">
-        <v>0.6057</v>
+        <v>0.6107</v>
       </c>
       <c r="J217" s="1" t="s">
         <v>15</v>
@@ -10367,16 +10367,16 @@
         <v>145192.0</v>
       </c>
       <c r="F222" s="28">
-        <v>667.5</v>
+        <v>667.55</v>
       </c>
       <c r="G222" s="28">
-        <v>165540.0</v>
+        <v>165552.4</v>
       </c>
       <c r="H222" s="28">
-        <v>20348.0</v>
+        <v>20360.4</v>
       </c>
       <c r="I222" s="29">
-        <v>0.1401</v>
+        <v>0.1402</v>
       </c>
       <c r="J222" s="1" t="s">
         <v>26</v>
@@ -10531,16 +10531,16 @@
         <v>82301.55</v>
       </c>
       <c r="F226" s="28">
-        <v>1394.9</v>
+        <v>1391.5</v>
       </c>
       <c r="G226" s="28">
-        <v>235738.1</v>
+        <v>235163.5</v>
       </c>
       <c r="H226" s="28">
-        <v>153436.55</v>
+        <v>152861.95</v>
       </c>
       <c r="I226" s="29">
-        <v>1.8643</v>
+        <v>1.8573</v>
       </c>
       <c r="J226" s="1" t="s">
         <v>15</v>
@@ -10613,16 +10613,16 @@
         <v>44852.2</v>
       </c>
       <c r="F228" s="28">
-        <v>4733.85</v>
+        <v>4736.5</v>
       </c>
       <c r="G228" s="28">
-        <v>52072.35</v>
+        <v>52101.5</v>
       </c>
       <c r="H228" s="28">
-        <v>7220.15</v>
+        <v>7249.3</v>
       </c>
       <c r="I228" s="29">
-        <v>0.161</v>
+        <v>0.1616</v>
       </c>
       <c r="J228" s="1" t="s">
         <v>26</v>
@@ -10736,16 +10736,16 @@
         <v>4617.6</v>
       </c>
       <c r="F231" s="28">
-        <v>463.4</v>
+        <v>464.05</v>
       </c>
       <c r="G231" s="28">
-        <v>5560.8</v>
+        <v>5568.6</v>
       </c>
       <c r="H231" s="28">
-        <v>943.2</v>
+        <v>951.0</v>
       </c>
       <c r="I231" s="29">
-        <v>0.2043</v>
+        <v>0.206</v>
       </c>
       <c r="J231" s="1" t="s">
         <v>26</v>
@@ -10818,16 +10818,16 @@
         <v>4377.95</v>
       </c>
       <c r="F233" s="28">
-        <v>90.0</v>
+        <v>90.38</v>
       </c>
       <c r="G233" s="28">
-        <v>3510.0</v>
+        <v>3524.82</v>
       </c>
       <c r="H233" s="28">
-        <v>-867.95</v>
+        <v>-853.13</v>
       </c>
       <c r="I233" s="29">
-        <v>-0.1983</v>
+        <v>-0.1949</v>
       </c>
       <c r="J233" s="1" t="s">
         <v>26</v>
@@ -10859,16 +10859,16 @@
         <v>19967.9</v>
       </c>
       <c r="F234" s="28">
-        <v>133.45</v>
+        <v>133.82</v>
       </c>
       <c r="G234" s="28">
-        <v>21352.0</v>
+        <v>21411.2</v>
       </c>
       <c r="H234" s="28">
-        <v>1384.1</v>
+        <v>1443.3</v>
       </c>
       <c r="I234" s="29">
-        <v>0.0693</v>
+        <v>0.0723</v>
       </c>
       <c r="J234" s="1" t="s">
         <v>26</v>
@@ -10900,16 +10900,16 @@
         <v>165.85</v>
       </c>
       <c r="F235" s="28">
-        <v>289.4</v>
+        <v>289.85</v>
       </c>
       <c r="G235" s="28">
-        <v>289.4</v>
+        <v>289.85</v>
       </c>
       <c r="H235" s="28">
-        <v>123.55</v>
+        <v>124.0</v>
       </c>
       <c r="I235" s="29">
-        <v>0.745</v>
+        <v>0.7477</v>
       </c>
       <c r="J235" s="1" t="s">
         <v>15</v>
@@ -10941,16 +10941,16 @@
         <v>56060.4</v>
       </c>
       <c r="F236" s="28">
-        <v>1543.6</v>
+        <v>1546.85</v>
       </c>
       <c r="G236" s="28">
-        <v>78723.6</v>
+        <v>78889.35</v>
       </c>
       <c r="H236" s="28">
-        <v>22663.2</v>
+        <v>22828.95</v>
       </c>
       <c r="I236" s="29">
-        <v>0.4043</v>
+        <v>0.4072</v>
       </c>
       <c r="J236" s="1" t="s">
         <v>26</v>
@@ -11187,16 +11187,16 @@
         <v>49689.7</v>
       </c>
       <c r="F242" s="28">
-        <v>850.9</v>
+        <v>851.45</v>
       </c>
       <c r="G242" s="28">
-        <v>46799.5</v>
+        <v>46829.75</v>
       </c>
       <c r="H242" s="28">
-        <v>-2890.2</v>
+        <v>-2859.95</v>
       </c>
       <c r="I242" s="29">
-        <v>-0.0582</v>
+        <v>-0.0576</v>
       </c>
       <c r="J242" s="1" t="s">
         <v>26</v>
@@ -11269,16 +11269,16 @@
         <v>39906.4</v>
       </c>
       <c r="F244" s="28">
-        <v>1148.0</v>
+        <v>1145.55</v>
       </c>
       <c r="G244" s="28">
-        <v>41328.0</v>
+        <v>41239.8</v>
       </c>
       <c r="H244" s="28">
-        <v>1421.6</v>
+        <v>1333.4</v>
       </c>
       <c r="I244" s="29">
-        <v>0.0356</v>
+        <v>0.0334</v>
       </c>
       <c r="J244" s="1" t="s">
         <v>26</v>
@@ -11310,16 +11310,16 @@
         <v>19914.4</v>
       </c>
       <c r="F245" s="28">
-        <v>169.5</v>
+        <v>169.22</v>
       </c>
       <c r="G245" s="28">
-        <v>18645.0</v>
+        <v>18614.2</v>
       </c>
       <c r="H245" s="28">
-        <v>-1269.4</v>
+        <v>-1300.2</v>
       </c>
       <c r="I245" s="29">
-        <v>-0.0637</v>
+        <v>-0.0653</v>
       </c>
       <c r="J245" s="1" t="s">
         <v>26</v>
@@ -11351,16 +11351,16 @@
         <v>53805.3</v>
       </c>
       <c r="F246" s="28">
-        <v>1262.2</v>
+        <v>1262.55</v>
       </c>
       <c r="G246" s="28">
-        <v>45439.2</v>
+        <v>45451.8</v>
       </c>
       <c r="H246" s="28">
-        <v>-8366.1</v>
+        <v>-8353.5</v>
       </c>
       <c r="I246" s="29">
-        <v>-0.1555</v>
+        <v>-0.1553</v>
       </c>
       <c r="J246" s="1" t="s">
         <v>26</v>
@@ -11433,16 +11433,16 @@
         <v>39588.85</v>
       </c>
       <c r="F248" s="28">
-        <v>591.95</v>
+        <v>592.2</v>
       </c>
       <c r="G248" s="28">
-        <v>44396.25</v>
+        <v>44415.0</v>
       </c>
       <c r="H248" s="28">
-        <v>4807.4</v>
+        <v>4826.15</v>
       </c>
       <c r="I248" s="29">
-        <v>0.1214</v>
+        <v>0.1219</v>
       </c>
       <c r="J248" s="1" t="s">
         <v>26</v>
@@ -11638,16 +11638,16 @@
         <v>26314.4</v>
       </c>
       <c r="F253" s="28">
-        <v>2083.1</v>
+        <v>2087.8</v>
       </c>
       <c r="G253" s="28">
-        <v>29163.4</v>
+        <v>29229.2</v>
       </c>
       <c r="H253" s="28">
-        <v>2849.0</v>
+        <v>2914.8</v>
       </c>
       <c r="I253" s="29">
-        <v>0.1083</v>
+        <v>0.1108</v>
       </c>
       <c r="J253" s="1" t="s">
         <v>26</v>
@@ -11720,16 +11720,16 @@
         <v>39331.9</v>
       </c>
       <c r="F255" s="28">
-        <v>4475.0</v>
+        <v>4453.8</v>
       </c>
       <c r="G255" s="28">
-        <v>40275.0</v>
+        <v>40084.2</v>
       </c>
       <c r="H255" s="28">
-        <v>943.1</v>
+        <v>752.3</v>
       </c>
       <c r="I255" s="29">
-        <v>0.024</v>
+        <v>0.0191</v>
       </c>
       <c r="J255" s="1" t="s">
         <v>26</v>
@@ -11761,16 +11761,16 @@
         <v>9990.4</v>
       </c>
       <c r="F256" s="28">
-        <v>770.6</v>
+        <v>771.45</v>
       </c>
       <c r="G256" s="28">
-        <v>10788.4</v>
+        <v>10800.3</v>
       </c>
       <c r="H256" s="28">
-        <v>798.0</v>
+        <v>809.9</v>
       </c>
       <c r="I256" s="29">
-        <v>0.0799</v>
+        <v>0.0811</v>
       </c>
       <c r="J256" s="1" t="s">
         <v>26</v>
@@ -12007,16 +12007,16 @@
         <v>99474.25</v>
       </c>
       <c r="F262" s="28">
-        <v>673.0</v>
+        <v>675.9</v>
       </c>
       <c r="G262" s="28">
-        <v>110372.0</v>
+        <v>110847.6</v>
       </c>
       <c r="H262" s="28">
-        <v>10897.75</v>
+        <v>11373.35</v>
       </c>
       <c r="I262" s="29">
-        <v>0.1096</v>
+        <v>0.1143</v>
       </c>
       <c r="J262" s="1" t="s">
         <v>26</v>
@@ -12089,16 +12089,16 @@
         <v>9896.8</v>
       </c>
       <c r="F264" s="28">
-        <v>287.8</v>
+        <v>288.6</v>
       </c>
       <c r="G264" s="28">
-        <v>11512.0</v>
+        <v>11544.0</v>
       </c>
       <c r="H264" s="28">
-        <v>1615.2</v>
+        <v>1647.2</v>
       </c>
       <c r="I264" s="29">
-        <v>0.1632</v>
+        <v>0.1664</v>
       </c>
       <c r="J264" s="1" t="s">
         <v>26</v>
@@ -12294,16 +12294,16 @@
         <v>99969.41</v>
       </c>
       <c r="F269" s="28">
-        <v>71.75</v>
+        <v>71.88</v>
       </c>
       <c r="G269" s="28">
-        <v>96288.5</v>
+        <v>96462.96</v>
       </c>
       <c r="H269" s="28">
-        <v>-3680.91</v>
+        <v>-3506.45</v>
       </c>
       <c r="I269" s="29">
-        <v>-0.0368</v>
+        <v>-0.0351</v>
       </c>
       <c r="J269" s="1" t="s">
         <v>26</v>
@@ -12417,16 +12417,16 @@
         <v>58877.0</v>
       </c>
       <c r="F272" s="28">
-        <v>4733.85</v>
+        <v>4736.5</v>
       </c>
       <c r="G272" s="28">
-        <v>61540.05</v>
+        <v>61574.5</v>
       </c>
       <c r="H272" s="28">
-        <v>2663.05</v>
+        <v>2697.5</v>
       </c>
       <c r="I272" s="29">
-        <v>0.0452</v>
+        <v>0.0458</v>
       </c>
       <c r="J272" s="1" t="s">
         <v>26</v>
@@ -12745,16 +12745,16 @@
         <v>3650.0</v>
       </c>
       <c r="F280" s="28">
-        <v>380.3</v>
+        <v>381.4</v>
       </c>
       <c r="G280" s="28">
-        <v>3803.0</v>
+        <v>3814.0</v>
       </c>
       <c r="H280" s="28">
-        <v>153.0</v>
+        <v>164.0</v>
       </c>
       <c r="I280" s="29">
-        <v>0.0419</v>
+        <v>0.0449</v>
       </c>
       <c r="J280" s="1" t="s">
         <v>26</v>
@@ -12786,16 +12786,16 @@
         <v>783.6</v>
       </c>
       <c r="F281" s="28">
-        <v>424.3</v>
+        <v>424.65</v>
       </c>
       <c r="G281" s="28">
-        <v>848.6</v>
+        <v>849.3</v>
       </c>
       <c r="H281" s="28">
-        <v>65.0</v>
+        <v>65.7</v>
       </c>
       <c r="I281" s="29">
-        <v>0.083</v>
+        <v>0.0838</v>
       </c>
       <c r="J281" s="1" t="s">
         <v>26</v>
@@ -12909,16 +12909,16 @@
         <v>12694.2</v>
       </c>
       <c r="F284" s="28">
-        <v>591.95</v>
+        <v>592.2</v>
       </c>
       <c r="G284" s="28">
-        <v>13022.9</v>
+        <v>13028.4</v>
       </c>
       <c r="H284" s="28">
-        <v>328.7</v>
+        <v>334.2</v>
       </c>
       <c r="I284" s="29">
-        <v>0.0259</v>
+        <v>0.0263</v>
       </c>
       <c r="J284" s="1" t="s">
         <v>26</v>
@@ -12950,16 +12950,16 @@
         <v>11628.6</v>
       </c>
       <c r="F285" s="28">
-        <v>4475.0</v>
+        <v>4453.8</v>
       </c>
       <c r="G285" s="28">
-        <v>13425.0</v>
+        <v>13361.4</v>
       </c>
       <c r="H285" s="28">
-        <v>1796.4</v>
+        <v>1732.8</v>
       </c>
       <c r="I285" s="29">
-        <v>0.1545</v>
+        <v>0.149</v>
       </c>
       <c r="J285" s="1" t="s">
         <v>26</v>
@@ -12991,16 +12991,16 @@
         <v>5808.0</v>
       </c>
       <c r="F286" s="28">
-        <v>2861.9</v>
+        <v>2863.6</v>
       </c>
       <c r="G286" s="28">
-        <v>5723.8</v>
+        <v>5727.2</v>
       </c>
       <c r="H286" s="28">
-        <v>-84.2</v>
+        <v>-80.8</v>
       </c>
       <c r="I286" s="29">
-        <v>-0.0145</v>
+        <v>-0.0139</v>
       </c>
       <c r="J286" s="1" t="s">
         <v>26</v>
@@ -13032,16 +13032,16 @@
         <v>1877.31</v>
       </c>
       <c r="F287" s="28">
-        <v>224.8</v>
+        <v>225.35</v>
       </c>
       <c r="G287" s="28">
-        <v>2023.2</v>
+        <v>2028.15</v>
       </c>
       <c r="H287" s="28">
-        <v>145.89</v>
+        <v>150.84</v>
       </c>
       <c r="I287" s="29">
-        <v>0.0777</v>
+        <v>0.0803</v>
       </c>
       <c r="J287" s="1" t="s">
         <v>26</v>
@@ -13073,16 +13073,16 @@
         <v>7787.1</v>
       </c>
       <c r="F288" s="28">
-        <v>287.8</v>
+        <v>288.6</v>
       </c>
       <c r="G288" s="28">
-        <v>9497.4</v>
+        <v>9523.8</v>
       </c>
       <c r="H288" s="28">
-        <v>1710.3</v>
+        <v>1736.7</v>
       </c>
       <c r="I288" s="29">
-        <v>0.2196</v>
+        <v>0.223</v>
       </c>
       <c r="J288" s="1" t="s">
         <v>26</v>
@@ -13114,16 +13114,16 @@
         <v>10923.0</v>
       </c>
       <c r="F289" s="28">
-        <v>550.0</v>
+        <v>548.45</v>
       </c>
       <c r="G289" s="28">
-        <v>11000.0</v>
+        <v>10969.0</v>
       </c>
       <c r="H289" s="28">
-        <v>77.0</v>
+        <v>46.0</v>
       </c>
       <c r="I289" s="29">
-        <v>0.007</v>
+        <v>0.0042</v>
       </c>
       <c r="J289" s="1" t="s">
         <v>26</v>
@@ -13319,13 +13319,13 @@
         <v>13167.3</v>
       </c>
       <c r="F294" s="28">
-        <v>667.5</v>
+        <v>667.55</v>
       </c>
       <c r="G294" s="28">
-        <v>15352.5</v>
+        <v>15353.65</v>
       </c>
       <c r="H294" s="28">
-        <v>2185.2</v>
+        <v>2186.35</v>
       </c>
       <c r="I294" s="29">
         <v>0.166</v>
@@ -13360,16 +13360,16 @@
         <v>14733.0</v>
       </c>
       <c r="F295" s="28">
-        <v>4733.85</v>
+        <v>4736.5</v>
       </c>
       <c r="G295" s="28">
-        <v>14201.55</v>
+        <v>14209.5</v>
       </c>
       <c r="H295" s="28">
-        <v>-531.45</v>
+        <v>-523.5</v>
       </c>
       <c r="I295" s="29">
-        <v>-0.0361</v>
+        <v>-0.0355</v>
       </c>
       <c r="J295" s="1" t="s">
         <v>26</v>
@@ -13442,16 +13442,16 @@
         <v>3496.92</v>
       </c>
       <c r="F297" s="28">
-        <v>133.45</v>
+        <v>133.82</v>
       </c>
       <c r="G297" s="28">
-        <v>3202.8</v>
+        <v>3211.68</v>
       </c>
       <c r="H297" s="28">
-        <v>-294.12</v>
+        <v>-285.24</v>
       </c>
       <c r="I297" s="29">
-        <v>-0.0841</v>
+        <v>-0.0816</v>
       </c>
       <c r="J297" s="1" t="s">
         <v>26</v>
@@ -17557,24 +17557,24 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="B100" s="30">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="C100" s="30">
-        <v>1395.0</v>
+        <v>2134.6</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="B101" s="30">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="C101" s="30">
-        <v>2134.6</v>
+        <v>1395.0</v>
       </c>
     </row>
   </sheetData>
@@ -17632,7 +17632,7 @@
         <v>1.3395</v>
       </c>
       <c r="F2" s="29">
-        <v>0.0588</v>
+        <v>0.0587</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>54</v>
@@ -17649,13 +17649,13 @@
         <v>113390.12</v>
       </c>
       <c r="C3" s="28">
-        <v>135168.75</v>
+        <v>135178.88</v>
       </c>
       <c r="D3" s="28">
-        <v>21778.63</v>
+        <v>21788.75</v>
       </c>
       <c r="E3" s="29">
-        <v>0.1921</v>
+        <v>0.1922</v>
       </c>
       <c r="F3" s="29">
         <v>0.0349</v>
@@ -17675,16 +17675,16 @@
         <v>71147.76</v>
       </c>
       <c r="C4" s="28">
-        <v>128934.4</v>
+        <v>129292.8</v>
       </c>
       <c r="D4" s="28">
-        <v>57786.64</v>
+        <v>58145.04</v>
       </c>
       <c r="E4" s="29">
-        <v>0.8122</v>
+        <v>0.8172</v>
       </c>
       <c r="F4" s="29">
-        <v>0.0333</v>
+        <v>0.0334</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>33</v>
@@ -17753,13 +17753,13 @@
         <v>85752.75</v>
       </c>
       <c r="C7" s="28">
-        <v>89943.15</v>
+        <v>89993.5</v>
       </c>
       <c r="D7" s="28">
-        <v>4190.4</v>
+        <v>4240.75</v>
       </c>
       <c r="E7" s="29">
-        <v>0.0489</v>
+        <v>0.0495</v>
       </c>
       <c r="F7" s="29">
         <v>0.0232</v>
@@ -17857,16 +17857,16 @@
         <v>77945.85</v>
       </c>
       <c r="C11" s="28">
-        <v>80550.0</v>
+        <v>80168.4</v>
       </c>
       <c r="D11" s="28">
-        <v>2604.15</v>
+        <v>2222.55</v>
       </c>
       <c r="E11" s="29">
-        <v>0.0334</v>
+        <v>0.0285</v>
       </c>
       <c r="F11" s="29">
-        <v>0.0208</v>
+        <v>0.0207</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>54</v>
@@ -17883,13 +17883,13 @@
         <v>53808.6</v>
       </c>
       <c r="C12" s="28">
-        <v>77690.07</v>
+        <v>77717.05</v>
       </c>
       <c r="D12" s="28">
-        <v>23881.48</v>
+        <v>23908.45</v>
       </c>
       <c r="E12" s="29">
-        <v>0.4438</v>
+        <v>0.4443</v>
       </c>
       <c r="F12" s="29">
         <v>0.0201</v>
@@ -17961,13 +17961,13 @@
         <v>67733.95</v>
       </c>
       <c r="C15" s="28">
-        <v>72513.88</v>
+        <v>72544.5</v>
       </c>
       <c r="D15" s="28">
-        <v>4779.93</v>
+        <v>4810.55</v>
       </c>
       <c r="E15" s="29">
-        <v>0.0706</v>
+        <v>0.071</v>
       </c>
       <c r="F15" s="29">
         <v>0.0187</v>
@@ -18013,13 +18013,13 @@
         <v>72381.3</v>
       </c>
       <c r="C17" s="28">
-        <v>70094.62</v>
+        <v>70116.15</v>
       </c>
       <c r="D17" s="28">
-        <v>-2286.67</v>
+        <v>-2265.15</v>
       </c>
       <c r="E17" s="29">
-        <v>-0.0316</v>
+        <v>-0.0313</v>
       </c>
       <c r="F17" s="29">
         <v>0.0181</v>
@@ -18039,16 +18039,16 @@
         <v>64643.95</v>
       </c>
       <c r="C18" s="28">
-        <v>68646.0</v>
+        <v>68941.8</v>
       </c>
       <c r="D18" s="28">
-        <v>4002.05</v>
+        <v>4297.85</v>
       </c>
       <c r="E18" s="29">
-        <v>0.0619</v>
+        <v>0.0665</v>
       </c>
       <c r="F18" s="29">
-        <v>0.0177</v>
+        <v>0.0178</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>17</v>
@@ -18221,13 +18221,13 @@
         <v>49573.2</v>
       </c>
       <c r="C25" s="28">
-        <v>52077.5</v>
+        <v>52195.0</v>
       </c>
       <c r="D25" s="28">
-        <v>2504.3</v>
+        <v>2621.8</v>
       </c>
       <c r="E25" s="29">
-        <v>0.0505</v>
+        <v>0.0529</v>
       </c>
       <c r="F25" s="29">
         <v>0.0135</v>
@@ -18247,13 +18247,13 @@
         <v>46334.02</v>
       </c>
       <c r="C26" s="28">
-        <v>51514.2</v>
+        <v>51544.8</v>
       </c>
       <c r="D26" s="28">
-        <v>5180.18</v>
+        <v>5210.78</v>
       </c>
       <c r="E26" s="29">
-        <v>0.1118</v>
+        <v>0.1125</v>
       </c>
       <c r="F26" s="29">
         <v>0.0133</v>
@@ -18325,16 +18325,16 @@
         <v>49984.7</v>
       </c>
       <c r="C29" s="28">
-        <v>48144.25</v>
+        <v>48231.48</v>
       </c>
       <c r="D29" s="28">
-        <v>-1840.45</v>
+        <v>-1753.22</v>
       </c>
       <c r="E29" s="29">
-        <v>-0.0368</v>
+        <v>-0.0351</v>
       </c>
       <c r="F29" s="29">
-        <v>0.0124</v>
+        <v>0.0125</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>62</v>
@@ -18377,13 +18377,13 @@
         <v>49132.65</v>
       </c>
       <c r="C31" s="28">
-        <v>43545.9</v>
+        <v>43557.97</v>
       </c>
       <c r="D31" s="28">
-        <v>-5586.75</v>
+        <v>-5574.67</v>
       </c>
       <c r="E31" s="29">
-        <v>-0.1137</v>
+        <v>-0.1135</v>
       </c>
       <c r="F31" s="29">
         <v>0.0113</v>
@@ -18507,13 +18507,13 @@
         <v>14547.5</v>
       </c>
       <c r="C36" s="28">
-        <v>40375.0</v>
+        <v>40382.5</v>
       </c>
       <c r="D36" s="28">
-        <v>25827.5</v>
+        <v>25835.0</v>
       </c>
       <c r="E36" s="29">
-        <v>1.7754</v>
+        <v>1.7759</v>
       </c>
       <c r="F36" s="29">
         <v>0.0104</v>
@@ -18533,13 +18533,13 @@
         <v>28030.2</v>
       </c>
       <c r="C37" s="28">
-        <v>39361.8</v>
+        <v>39444.67</v>
       </c>
       <c r="D37" s="28">
-        <v>11331.6</v>
+        <v>11414.48</v>
       </c>
       <c r="E37" s="29">
-        <v>0.4043</v>
+        <v>0.4072</v>
       </c>
       <c r="F37" s="29">
         <v>0.0102</v>
@@ -18663,13 +18663,13 @@
         <v>21235.27</v>
       </c>
       <c r="C42" s="28">
-        <v>36915.78</v>
+        <v>36954.58</v>
       </c>
       <c r="D42" s="28">
-        <v>15680.5</v>
+        <v>15719.3</v>
       </c>
       <c r="E42" s="29">
-        <v>0.7384</v>
+        <v>0.7402</v>
       </c>
       <c r="F42" s="29">
         <v>0.0095</v>
@@ -18741,16 +18741,16 @@
         <v>33603.95</v>
       </c>
       <c r="C45" s="28">
-        <v>33866.0</v>
+        <v>33793.72</v>
       </c>
       <c r="D45" s="28">
-        <v>262.05</v>
+        <v>189.78</v>
       </c>
       <c r="E45" s="29">
-        <v>0.0078</v>
+        <v>0.0056</v>
       </c>
       <c r="F45" s="29">
-        <v>0.0088</v>
+        <v>0.0087</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>62</v>
@@ -18793,16 +18793,16 @@
         <v>29401.45</v>
       </c>
       <c r="C47" s="28">
-        <v>31625.0</v>
+        <v>31535.88</v>
       </c>
       <c r="D47" s="28">
-        <v>2223.55</v>
+        <v>2134.43</v>
       </c>
       <c r="E47" s="29">
-        <v>0.0756</v>
+        <v>0.0726</v>
       </c>
       <c r="F47" s="29">
-        <v>0.0082</v>
+        <v>0.0081</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>62</v>
@@ -18871,13 +18871,13 @@
         <v>15534.15</v>
       </c>
       <c r="C50" s="28">
-        <v>29287.3</v>
+        <v>29301.27</v>
       </c>
       <c r="D50" s="28">
-        <v>13753.15</v>
+        <v>13767.13</v>
       </c>
       <c r="E50" s="29">
-        <v>0.8853</v>
+        <v>0.8862</v>
       </c>
       <c r="F50" s="29">
         <v>0.0076</v>
@@ -18958,7 +18958,7 @@
         <v>0.1003</v>
       </c>
       <c r="F53" s="29">
-        <v>0.0072</v>
+        <v>0.0071</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>17</v>
@@ -18975,13 +18975,13 @@
         <v>26249.6</v>
       </c>
       <c r="C54" s="28">
-        <v>27571.75</v>
+        <v>27651.5</v>
       </c>
       <c r="D54" s="28">
-        <v>1322.15</v>
+        <v>1401.9</v>
       </c>
       <c r="E54" s="29">
-        <v>0.0504</v>
+        <v>0.0534</v>
       </c>
       <c r="F54" s="29">
         <v>0.0071</v>
@@ -19088,7 +19088,7 @@
         <v>-0.0154</v>
       </c>
       <c r="F58" s="29">
-        <v>0.0064</v>
+        <v>0.0063</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>17</v>
@@ -19105,16 +19105,16 @@
         <v>23284.61</v>
       </c>
       <c r="C59" s="28">
-        <v>24166.0</v>
+        <v>24225.12</v>
       </c>
       <c r="D59" s="28">
-        <v>881.39</v>
+        <v>940.51</v>
       </c>
       <c r="E59" s="29">
-        <v>0.0379</v>
+        <v>0.0404</v>
       </c>
       <c r="F59" s="29">
-        <v>0.0062</v>
+        <v>0.0063</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>17</v>
@@ -19131,13 +19131,13 @@
         <v>24844.85</v>
       </c>
       <c r="C60" s="28">
-        <v>23399.75</v>
+        <v>23414.88</v>
       </c>
       <c r="D60" s="28">
-        <v>-1445.1</v>
+        <v>-1429.97</v>
       </c>
       <c r="E60" s="29">
-        <v>-0.0582</v>
+        <v>-0.0576</v>
       </c>
       <c r="F60" s="29">
         <v>0.006</v>
@@ -19365,16 +19365,16 @@
         <v>14843.12</v>
       </c>
       <c r="C69" s="28">
-        <v>17910.0</v>
+        <v>18018.0</v>
       </c>
       <c r="D69" s="28">
-        <v>3066.88</v>
+        <v>3174.88</v>
       </c>
       <c r="E69" s="29">
-        <v>0.2066</v>
+        <v>0.2139</v>
       </c>
       <c r="F69" s="29">
-        <v>0.0046</v>
+        <v>0.0047</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>17</v>
@@ -19443,13 +19443,13 @@
         <v>16696.13</v>
       </c>
       <c r="C72" s="28">
-        <v>16614.52</v>
+        <v>16660.59</v>
       </c>
       <c r="D72" s="28">
-        <v>-81.61</v>
+        <v>-35.54</v>
       </c>
       <c r="E72" s="29">
-        <v>-0.0049</v>
+        <v>-0.0021</v>
       </c>
       <c r="F72" s="29">
         <v>0.0043</v>
@@ -19599,13 +19599,13 @@
         <v>12778.72</v>
       </c>
       <c r="C78" s="28">
-        <v>14001.9</v>
+        <v>14013.45</v>
       </c>
       <c r="D78" s="28">
-        <v>1223.18</v>
+        <v>1234.73</v>
       </c>
       <c r="E78" s="29">
-        <v>0.0957</v>
+        <v>0.0966</v>
       </c>
       <c r="F78" s="29">
         <v>0.0036</v>
@@ -19703,13 +19703,13 @@
         <v>12453.65</v>
       </c>
       <c r="C82" s="28">
-        <v>13340.75</v>
+        <v>13346.12</v>
       </c>
       <c r="D82" s="28">
-        <v>887.1</v>
+        <v>892.48</v>
       </c>
       <c r="E82" s="29">
-        <v>0.0712</v>
+        <v>0.0717</v>
       </c>
       <c r="F82" s="29">
         <v>0.0034</v>
@@ -19729,13 +19729,13 @@
         <v>17016.17</v>
       </c>
       <c r="C83" s="28">
-        <v>12918.05</v>
+        <v>12904.77</v>
       </c>
       <c r="D83" s="28">
-        <v>-4098.12</v>
+        <v>-4111.4</v>
       </c>
       <c r="E83" s="29">
-        <v>-0.2408</v>
+        <v>-0.2416</v>
       </c>
       <c r="F83" s="29">
         <v>0.0033</v>
@@ -19781,16 +19781,16 @@
         <v>6277.5</v>
       </c>
       <c r="C85" s="28">
-        <v>11583.0</v>
+        <v>11416.5</v>
       </c>
       <c r="D85" s="28">
-        <v>5305.5</v>
+        <v>5139.0</v>
       </c>
       <c r="E85" s="29">
-        <v>0.8452</v>
+        <v>0.8186</v>
       </c>
       <c r="F85" s="29">
-        <v>0.003</v>
+        <v>0.0029</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>17</v>
@@ -19920,7 +19920,7 @@
         <v>-0.0044</v>
       </c>
       <c r="F90" s="29">
-        <v>0.0026</v>
+        <v>0.0025</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>17</v>
@@ -20093,13 +20093,13 @@
         <v>9957.2</v>
       </c>
       <c r="C97" s="28">
-        <v>9322.5</v>
+        <v>9307.1</v>
       </c>
       <c r="D97" s="28">
-        <v>-634.7</v>
+        <v>-650.1</v>
       </c>
       <c r="E97" s="29">
-        <v>-0.0637</v>
+        <v>-0.0653</v>
       </c>
       <c r="F97" s="29">
         <v>0.0024</v>
@@ -20171,13 +20171,13 @@
         <v>7317.5</v>
       </c>
       <c r="C100" s="28">
-        <v>7736.25</v>
+        <v>7738.75</v>
       </c>
       <c r="D100" s="28">
-        <v>418.75</v>
+        <v>421.25</v>
       </c>
       <c r="E100" s="29">
-        <v>0.0572</v>
+        <v>0.0576</v>
       </c>
       <c r="F100" s="29">
         <v>0.002</v>
@@ -20249,13 +20249,13 @@
         <v>4995.2</v>
       </c>
       <c r="C103" s="28">
-        <v>5394.2</v>
+        <v>5400.15</v>
       </c>
       <c r="D103" s="28">
-        <v>399.0</v>
+        <v>404.95</v>
       </c>
       <c r="E103" s="29">
-        <v>0.0799</v>
+        <v>0.0811</v>
       </c>
       <c r="F103" s="29">
         <v>0.0014</v>
@@ -20353,13 +20353,13 @@
         <v>2188.98</v>
       </c>
       <c r="C107" s="28">
-        <v>1755.0</v>
+        <v>1762.41</v>
       </c>
       <c r="D107" s="28">
-        <v>-433.98</v>
+        <v>-426.57</v>
       </c>
       <c r="E107" s="29">
-        <v>-0.1983</v>
+        <v>-0.1949</v>
       </c>
       <c r="F107" s="29">
         <v>5.0E-4</v>
@@ -20405,13 +20405,13 @@
         <v>222.45</v>
       </c>
       <c r="C109" s="28">
-        <v>385.8</v>
+        <v>386.55</v>
       </c>
       <c r="D109" s="28">
-        <v>163.35</v>
+        <v>164.1</v>
       </c>
       <c r="E109" s="29">
-        <v>0.7343</v>
+        <v>0.7377</v>
       </c>
       <c r="F109" s="29">
         <v>1.0E-4</v>
@@ -20499,16 +20499,16 @@
         <v>14599.99</v>
       </c>
       <c r="F2" s="28">
-        <v>3450860.42</v>
+        <v>3451770.83</v>
       </c>
       <c r="G2" s="28">
-        <v>1507881.04</v>
+        <v>1508791.45</v>
       </c>
       <c r="H2" s="29">
-        <v>0.7761</v>
+        <v>0.7765</v>
       </c>
       <c r="I2" s="29">
-        <v>0.2051</v>
+        <v>0.2052</v>
       </c>
       <c r="J2" s="29" t="s">
         <v>23</v>
@@ -20628,19 +20628,19 @@
         <v>183396.9</v>
       </c>
       <c r="E5" s="28">
-        <v>1999.1</v>
+        <v>2000.5</v>
       </c>
       <c r="F5" s="28">
-        <v>737667.9</v>
+        <v>738184.5</v>
       </c>
       <c r="G5" s="28">
-        <v>554271.0</v>
+        <v>554787.6</v>
       </c>
       <c r="H5" s="29">
-        <v>3.0222</v>
+        <v>3.0251</v>
       </c>
       <c r="I5" s="29">
-        <v>0.0438</v>
+        <v>0.0439</v>
       </c>
       <c r="J5" s="29">
         <v>0.063</v>
@@ -20716,22 +20716,22 @@
         <v>124501.8</v>
       </c>
       <c r="E7" s="28">
-        <v>1394.9</v>
+        <v>1391.5</v>
       </c>
       <c r="F7" s="28">
-        <v>403126.1</v>
+        <v>402143.5</v>
       </c>
       <c r="G7" s="28">
-        <v>278624.3</v>
+        <v>277641.7</v>
       </c>
       <c r="H7" s="29">
-        <v>2.2379</v>
+        <v>2.23</v>
       </c>
       <c r="I7" s="29">
-        <v>0.024</v>
+        <v>0.0239</v>
       </c>
       <c r="J7" s="29">
-        <v>0.0344</v>
+        <v>0.0343</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>15</v>
@@ -20760,22 +20760,22 @@
         <v>191353.6</v>
       </c>
       <c r="E8" s="28">
-        <v>654.3</v>
+        <v>652.6</v>
       </c>
       <c r="F8" s="28">
-        <v>398468.7</v>
+        <v>397433.4</v>
       </c>
       <c r="G8" s="28">
-        <v>207115.1</v>
+        <v>206079.8</v>
       </c>
       <c r="H8" s="29">
-        <v>1.0824</v>
+        <v>1.077</v>
       </c>
       <c r="I8" s="29">
-        <v>0.0237</v>
+        <v>0.0236</v>
       </c>
       <c r="J8" s="29">
-        <v>0.034</v>
+        <v>0.0339</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>15</v>
@@ -20804,16 +20804,16 @@
         <v>226780.25</v>
       </c>
       <c r="E9" s="28">
-        <v>667.5</v>
+        <v>667.55</v>
       </c>
       <c r="F9" s="28">
-        <v>270337.5</v>
+        <v>270357.75</v>
       </c>
       <c r="G9" s="28">
-        <v>43557.25</v>
+        <v>43577.5</v>
       </c>
       <c r="H9" s="29">
-        <v>0.1921</v>
+        <v>0.1922</v>
       </c>
       <c r="I9" s="29">
         <v>0.0161</v>
@@ -20848,22 +20848,22 @@
         <v>142295.53</v>
       </c>
       <c r="E10" s="28">
-        <v>287.8</v>
+        <v>288.6</v>
       </c>
       <c r="F10" s="28">
-        <v>257868.8</v>
+        <v>258585.6</v>
       </c>
       <c r="G10" s="28">
-        <v>115573.27</v>
+        <v>116290.07</v>
       </c>
       <c r="H10" s="29">
-        <v>0.8122</v>
+        <v>0.8172</v>
       </c>
       <c r="I10" s="29">
-        <v>0.0153</v>
+        <v>0.0154</v>
       </c>
       <c r="J10" s="29">
-        <v>0.022</v>
+        <v>0.0221</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>26</v>
@@ -20980,13 +20980,13 @@
         <v>22697.7</v>
       </c>
       <c r="E13" s="28">
-        <v>1849.8</v>
+        <v>1850.0</v>
       </c>
       <c r="F13" s="28">
-        <v>186849.8</v>
+        <v>186850.0</v>
       </c>
       <c r="G13" s="28">
-        <v>164152.1</v>
+        <v>164152.3</v>
       </c>
       <c r="H13" s="29">
         <v>7.2321</v>
@@ -20995,7 +20995,7 @@
         <v>0.0111</v>
       </c>
       <c r="J13" s="29">
-        <v>0.0159</v>
+        <v>0.016</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>15</v>
@@ -21112,16 +21112,16 @@
         <v>171505.5</v>
       </c>
       <c r="E16" s="28">
-        <v>4733.85</v>
+        <v>4736.5</v>
       </c>
       <c r="F16" s="28">
-        <v>179886.3</v>
+        <v>179987.0</v>
       </c>
       <c r="G16" s="28">
-        <v>8380.8</v>
+        <v>8481.5</v>
       </c>
       <c r="H16" s="29">
-        <v>0.0489</v>
+        <v>0.0495</v>
       </c>
       <c r="I16" s="29">
         <v>0.0107</v>
@@ -21288,22 +21288,22 @@
         <v>155891.7</v>
       </c>
       <c r="E20" s="28">
-        <v>4475.0</v>
+        <v>4453.8</v>
       </c>
       <c r="F20" s="28">
-        <v>161100.0</v>
+        <v>160336.8</v>
       </c>
       <c r="G20" s="28">
-        <v>5208.3</v>
+        <v>4445.1</v>
       </c>
       <c r="H20" s="29">
-        <v>0.0334</v>
+        <v>0.0285</v>
       </c>
       <c r="I20" s="29">
-        <v>0.0096</v>
+        <v>0.0095</v>
       </c>
       <c r="J20" s="29">
-        <v>0.0138</v>
+        <v>0.0137</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>26</v>
@@ -21332,16 +21332,16 @@
         <v>107617.2</v>
       </c>
       <c r="E21" s="28">
-        <v>1872.05</v>
+        <v>1872.7</v>
       </c>
       <c r="F21" s="28">
-        <v>155380.15</v>
+        <v>155434.1</v>
       </c>
       <c r="G21" s="28">
-        <v>47762.95</v>
+        <v>47816.9</v>
       </c>
       <c r="H21" s="29">
-        <v>0.4438</v>
+        <v>0.4443</v>
       </c>
       <c r="I21" s="29">
         <v>0.0092</v>
@@ -21464,16 +21464,16 @@
         <v>135467.9</v>
       </c>
       <c r="E24" s="28">
-        <v>591.95</v>
+        <v>592.2</v>
       </c>
       <c r="F24" s="28">
-        <v>145027.75</v>
+        <v>145089.0</v>
       </c>
       <c r="G24" s="28">
-        <v>9559.85</v>
+        <v>9621.1</v>
       </c>
       <c r="H24" s="29">
-        <v>0.0706</v>
+        <v>0.071</v>
       </c>
       <c r="I24" s="29">
         <v>0.0086</v>
@@ -21596,16 +21596,16 @@
         <v>144762.6</v>
       </c>
       <c r="E27" s="28">
-        <v>3419.25</v>
+        <v>3420.3</v>
       </c>
       <c r="F27" s="28">
-        <v>140189.25</v>
+        <v>140232.3</v>
       </c>
       <c r="G27" s="28">
-        <v>-4573.35</v>
+        <v>-4530.3</v>
       </c>
       <c r="H27" s="29">
-        <v>-0.0316</v>
+        <v>-0.0313</v>
       </c>
       <c r="I27" s="29">
         <v>0.0083</v>
@@ -21640,22 +21640,22 @@
         <v>129287.9</v>
       </c>
       <c r="E28" s="28">
-        <v>673.0</v>
+        <v>675.9</v>
       </c>
       <c r="F28" s="28">
-        <v>137292.0</v>
+        <v>137883.6</v>
       </c>
       <c r="G28" s="28">
-        <v>8004.1</v>
+        <v>8595.7</v>
       </c>
       <c r="H28" s="29">
-        <v>0.0619</v>
+        <v>0.0665</v>
       </c>
       <c r="I28" s="29">
         <v>0.0082</v>
       </c>
       <c r="J28" s="29">
-        <v>0.0117</v>
+        <v>0.0118</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>26</v>
@@ -22039,13 +22039,13 @@
         <v>463.4</v>
       </c>
       <c r="F37" s="28">
-        <v>113996.4</v>
+        <v>114021.1</v>
       </c>
       <c r="G37" s="28">
-        <v>19490.3</v>
+        <v>19515.0</v>
       </c>
       <c r="H37" s="29">
-        <v>0.2062</v>
+        <v>0.2065</v>
       </c>
       <c r="I37" s="29">
         <v>0.0068</v>
@@ -22124,16 +22124,16 @@
         <v>99146.4</v>
       </c>
       <c r="E39" s="28">
-        <v>2083.1</v>
+        <v>2087.8</v>
       </c>
       <c r="F39" s="28">
-        <v>104155.0</v>
+        <v>104390.0</v>
       </c>
       <c r="G39" s="28">
-        <v>5008.6</v>
+        <v>5243.6</v>
       </c>
       <c r="H39" s="29">
-        <v>0.0505</v>
+        <v>0.0529</v>
       </c>
       <c r="I39" s="29">
         <v>0.0062</v>
@@ -22168,13 +22168,13 @@
         <v>92668.05</v>
       </c>
       <c r="E40" s="28">
-        <v>2861.9</v>
+        <v>2863.6</v>
       </c>
       <c r="F40" s="28">
-        <v>103028.4</v>
+        <v>103031.8</v>
       </c>
       <c r="G40" s="28">
-        <v>10360.35</v>
+        <v>10363.75</v>
       </c>
       <c r="H40" s="29">
         <v>0.1118</v>
@@ -22432,16 +22432,16 @@
         <v>99969.41</v>
       </c>
       <c r="E46" s="28">
-        <v>71.75</v>
+        <v>71.88</v>
       </c>
       <c r="F46" s="28">
-        <v>96288.5</v>
+        <v>96462.96</v>
       </c>
       <c r="G46" s="28">
-        <v>-3680.91</v>
+        <v>-3506.45</v>
       </c>
       <c r="H46" s="29">
-        <v>-0.0368</v>
+        <v>-0.0351</v>
       </c>
       <c r="I46" s="29">
         <v>0.0057</v>
@@ -22520,16 +22520,16 @@
         <v>98265.3</v>
       </c>
       <c r="E48" s="28">
-        <v>1262.2</v>
+        <v>1262.55</v>
       </c>
       <c r="F48" s="28">
-        <v>87091.8</v>
+        <v>87115.95</v>
       </c>
       <c r="G48" s="28">
-        <v>-11173.5</v>
+        <v>-11149.35</v>
       </c>
       <c r="H48" s="29">
-        <v>-0.1137</v>
+        <v>-0.1135</v>
       </c>
       <c r="I48" s="29">
         <v>0.0052</v>
@@ -22743,13 +22743,13 @@
         <v>151.32</v>
       </c>
       <c r="F53" s="28">
-        <v>82601.52</v>
+        <v>82620.72</v>
       </c>
       <c r="G53" s="28">
-        <v>8393.25</v>
+        <v>8412.45</v>
       </c>
       <c r="H53" s="29">
-        <v>0.1131</v>
+        <v>0.1134</v>
       </c>
       <c r="I53" s="29">
         <v>0.0049</v>
@@ -22872,16 +22872,16 @@
         <v>29095.0</v>
       </c>
       <c r="E56" s="28">
-        <v>807.5</v>
+        <v>807.65</v>
       </c>
       <c r="F56" s="28">
-        <v>80750.0</v>
+        <v>80765.0</v>
       </c>
       <c r="G56" s="28">
-        <v>51655.0</v>
+        <v>51670.0</v>
       </c>
       <c r="H56" s="29">
-        <v>1.7754</v>
+        <v>1.7759</v>
       </c>
       <c r="I56" s="29">
         <v>0.0048</v>
@@ -22916,16 +22916,16 @@
         <v>56060.4</v>
       </c>
       <c r="E57" s="28">
-        <v>1543.6</v>
+        <v>1546.85</v>
       </c>
       <c r="F57" s="28">
-        <v>78723.6</v>
+        <v>78889.35</v>
       </c>
       <c r="G57" s="28">
-        <v>22663.2</v>
+        <v>22828.95</v>
       </c>
       <c r="H57" s="29">
-        <v>0.4043</v>
+        <v>0.4072</v>
       </c>
       <c r="I57" s="29">
         <v>0.0047</v>
@@ -23180,16 +23180,16 @@
         <v>42470.55</v>
       </c>
       <c r="E63" s="28">
-        <v>761.15</v>
+        <v>761.95</v>
       </c>
       <c r="F63" s="28">
-        <v>73831.55</v>
+        <v>73841.95</v>
       </c>
       <c r="G63" s="28">
-        <v>31361.0</v>
+        <v>31371.4</v>
       </c>
       <c r="H63" s="29">
-        <v>0.7384</v>
+        <v>0.7387</v>
       </c>
       <c r="I63" s="29">
         <v>0.0044</v>
@@ -23312,16 +23312,16 @@
         <v>67207.9</v>
       </c>
       <c r="E66" s="28">
-        <v>1148.0</v>
+        <v>1145.55</v>
       </c>
       <c r="F66" s="28">
-        <v>67732.0</v>
+        <v>67587.45</v>
       </c>
       <c r="G66" s="28">
-        <v>524.1</v>
+        <v>379.55</v>
       </c>
       <c r="H66" s="29">
-        <v>0.0078</v>
+        <v>0.0056</v>
       </c>
       <c r="I66" s="29">
         <v>0.004</v>
@@ -23444,19 +23444,19 @@
         <v>58802.9</v>
       </c>
       <c r="E69" s="28">
-        <v>550.0</v>
+        <v>548.45</v>
       </c>
       <c r="F69" s="28">
-        <v>63250.0</v>
+        <v>63071.75</v>
       </c>
       <c r="G69" s="28">
-        <v>4447.1</v>
+        <v>4268.85</v>
       </c>
       <c r="H69" s="29">
-        <v>0.0756</v>
+        <v>0.0726</v>
       </c>
       <c r="I69" s="29">
-        <v>0.0038</v>
+        <v>0.0037</v>
       </c>
       <c r="J69" s="29">
         <v>0.0054</v>
@@ -23576,16 +23576,16 @@
         <v>31068.3</v>
       </c>
       <c r="E72" s="28">
-        <v>1362.2</v>
+        <v>1362.85</v>
       </c>
       <c r="F72" s="28">
-        <v>58574.6</v>
+        <v>58602.55</v>
       </c>
       <c r="G72" s="28">
-        <v>27506.3</v>
+        <v>27534.25</v>
       </c>
       <c r="H72" s="29">
-        <v>0.8853</v>
+        <v>0.8862</v>
       </c>
       <c r="I72" s="29">
         <v>0.0035</v>
@@ -23752,16 +23752,16 @@
         <v>52499.2</v>
       </c>
       <c r="E76" s="28">
-        <v>380.3</v>
+        <v>381.4</v>
       </c>
       <c r="F76" s="28">
-        <v>55143.5</v>
+        <v>55154.5</v>
       </c>
       <c r="G76" s="28">
-        <v>2644.3</v>
+        <v>2655.3</v>
       </c>
       <c r="H76" s="29">
-        <v>0.0504</v>
+        <v>0.0506</v>
       </c>
       <c r="I76" s="29">
         <v>0.0033</v>
@@ -23972,16 +23972,16 @@
         <v>46569.23</v>
       </c>
       <c r="E81" s="28">
-        <v>224.8</v>
+        <v>225.35</v>
       </c>
       <c r="F81" s="28">
-        <v>48404.1</v>
+        <v>48409.05</v>
       </c>
       <c r="G81" s="28">
-        <v>1834.87</v>
+        <v>1839.82</v>
       </c>
       <c r="H81" s="29">
-        <v>0.0394</v>
+        <v>0.0395</v>
       </c>
       <c r="I81" s="29">
         <v>0.0029</v>
@@ -24060,16 +24060,16 @@
         <v>49689.7</v>
       </c>
       <c r="E83" s="28">
-        <v>850.9</v>
+        <v>851.45</v>
       </c>
       <c r="F83" s="28">
-        <v>46799.5</v>
+        <v>46829.75</v>
       </c>
       <c r="G83" s="28">
-        <v>-2890.2</v>
+        <v>-2859.95</v>
       </c>
       <c r="H83" s="29">
-        <v>-0.0582</v>
+        <v>-0.0576</v>
       </c>
       <c r="I83" s="29">
         <v>0.0028</v>
@@ -24456,16 +24456,16 @@
         <v>29686.25</v>
       </c>
       <c r="E92" s="28">
-        <v>796.0</v>
+        <v>800.8</v>
       </c>
       <c r="F92" s="28">
-        <v>35820.0</v>
+        <v>36036.0</v>
       </c>
       <c r="G92" s="28">
-        <v>6133.75</v>
+        <v>6349.75</v>
       </c>
       <c r="H92" s="29">
-        <v>0.2066</v>
+        <v>0.2139</v>
       </c>
       <c r="I92" s="29">
         <v>0.0021</v>
@@ -24547,13 +24547,13 @@
         <v>113.45</v>
       </c>
       <c r="F94" s="28">
-        <v>34824.3</v>
+        <v>34829.15</v>
       </c>
       <c r="G94" s="28">
-        <v>4987.06</v>
+        <v>4991.91</v>
       </c>
       <c r="H94" s="29">
-        <v>0.1671</v>
+        <v>0.1673</v>
       </c>
       <c r="I94" s="29">
         <v>0.0021</v>
@@ -24588,16 +24588,16 @@
         <v>33392.27</v>
       </c>
       <c r="E95" s="28">
-        <v>133.45</v>
+        <v>133.82</v>
       </c>
       <c r="F95" s="28">
-        <v>33229.05</v>
+        <v>33321.18</v>
       </c>
       <c r="G95" s="28">
-        <v>-163.22</v>
+        <v>-71.09</v>
       </c>
       <c r="H95" s="29">
-        <v>-0.0049</v>
+        <v>-0.0021</v>
       </c>
       <c r="I95" s="29">
         <v>0.002</v>
@@ -24723,13 +24723,13 @@
         <v>947.05</v>
       </c>
       <c r="F98" s="28">
-        <v>31222.9</v>
+        <v>31252.65</v>
       </c>
       <c r="G98" s="28">
-        <v>-4147.35</v>
+        <v>-4117.6</v>
       </c>
       <c r="H98" s="29">
-        <v>-0.1173</v>
+        <v>-0.1164</v>
       </c>
       <c r="I98" s="29">
         <v>0.0019</v>
@@ -24764,16 +24764,16 @@
         <v>12454.04</v>
       </c>
       <c r="E99" s="28">
-        <v>104.0</v>
+        <v>103.9</v>
       </c>
       <c r="F99" s="28">
-        <v>30992.0</v>
+        <v>30962.2</v>
       </c>
       <c r="G99" s="28">
-        <v>18537.96</v>
+        <v>18508.16</v>
       </c>
       <c r="H99" s="29">
-        <v>1.4885</v>
+        <v>1.4861</v>
       </c>
       <c r="I99" s="29">
         <v>0.0018</v>
@@ -24896,16 +24896,16 @@
         <v>25557.45</v>
       </c>
       <c r="E102" s="28">
-        <v>424.3</v>
+        <v>424.65</v>
       </c>
       <c r="F102" s="28">
-        <v>28003.8</v>
+        <v>28026.9</v>
       </c>
       <c r="G102" s="28">
-        <v>2446.35</v>
+        <v>2469.45</v>
       </c>
       <c r="H102" s="29">
-        <v>0.0957</v>
+        <v>0.0966</v>
       </c>
       <c r="I102" s="29">
         <v>0.0017</v>
@@ -25031,10 +25031,10 @@
         <v>527.0</v>
       </c>
       <c r="F105" s="28">
-        <v>26876.5</v>
+        <v>26877.0</v>
       </c>
       <c r="G105" s="28">
-        <v>1653.9</v>
+        <v>1654.4</v>
       </c>
       <c r="H105" s="29">
         <v>0.0656</v>
@@ -25072,16 +25072,16 @@
         <v>24907.3</v>
       </c>
       <c r="E106" s="28">
-        <v>620.5</v>
+        <v>620.75</v>
       </c>
       <c r="F106" s="28">
-        <v>26681.5</v>
+        <v>26692.25</v>
       </c>
       <c r="G106" s="28">
-        <v>1774.2</v>
+        <v>1784.95</v>
       </c>
       <c r="H106" s="29">
-        <v>0.0712</v>
+        <v>0.0717</v>
       </c>
       <c r="I106" s="29">
         <v>0.0016</v>
@@ -25116,13 +25116,13 @@
         <v>34032.35</v>
       </c>
       <c r="E107" s="28">
-        <v>437.9</v>
+        <v>437.45</v>
       </c>
       <c r="F107" s="28">
-        <v>25810.0</v>
+        <v>25809.55</v>
       </c>
       <c r="G107" s="28">
-        <v>-8222.35</v>
+        <v>-8222.8</v>
       </c>
       <c r="H107" s="29">
         <v>-0.2416</v>
@@ -25192,28 +25192,28 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="B109" s="27">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="C109" s="28">
-        <v>1395.0</v>
+        <v>2134.6</v>
       </c>
       <c r="D109" s="28">
-        <v>12555.0</v>
+        <v>10673.0</v>
       </c>
       <c r="E109" s="28">
-        <v>2574.0</v>
+        <v>4621.2</v>
       </c>
       <c r="F109" s="28">
-        <v>23166.0</v>
+        <v>23106.0</v>
       </c>
       <c r="G109" s="28">
-        <v>10611.0</v>
+        <v>12433.0</v>
       </c>
       <c r="H109" s="29">
-        <v>0.8452</v>
+        <v>1.1649</v>
       </c>
       <c r="I109" s="29">
         <v>0.0014</v>
@@ -25222,7 +25222,7 @@
         <v>0.002</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="L109" s="1" t="s">
         <v>16</v>
@@ -25236,37 +25236,37 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="B110" s="27">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="C110" s="28">
-        <v>2134.6</v>
+        <v>1395.0</v>
       </c>
       <c r="D110" s="28">
-        <v>10673.0</v>
+        <v>12555.0</v>
       </c>
       <c r="E110" s="28">
-        <v>4621.2</v>
+        <v>2537.0</v>
       </c>
       <c r="F110" s="28">
-        <v>23106.0</v>
+        <v>22833.0</v>
       </c>
       <c r="G110" s="28">
-        <v>12433.0</v>
+        <v>10278.0</v>
       </c>
       <c r="H110" s="29">
-        <v>1.1649</v>
+        <v>0.8186</v>
       </c>
       <c r="I110" s="29">
         <v>0.0014</v>
       </c>
       <c r="J110" s="29">
-        <v>0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="L110" s="1" t="s">
         <v>16</v>
@@ -25820,16 +25820,16 @@
         <v>19914.4</v>
       </c>
       <c r="E123" s="28">
-        <v>169.5</v>
+        <v>169.22</v>
       </c>
       <c r="F123" s="28">
-        <v>18645.0</v>
+        <v>18614.2</v>
       </c>
       <c r="G123" s="28">
-        <v>-1269.4</v>
+        <v>-1300.2</v>
       </c>
       <c r="H123" s="29">
-        <v>-0.0637</v>
+        <v>-0.0653</v>
       </c>
       <c r="I123" s="29">
         <v>0.0011</v>
@@ -25952,16 +25952,16 @@
         <v>14635.0</v>
       </c>
       <c r="E126" s="28">
-        <v>309.45</v>
+        <v>309.55</v>
       </c>
       <c r="F126" s="28">
-        <v>15472.5</v>
+        <v>15477.5</v>
       </c>
       <c r="G126" s="28">
-        <v>837.5</v>
+        <v>842.5</v>
       </c>
       <c r="H126" s="29">
-        <v>0.0572</v>
+        <v>0.0576</v>
       </c>
       <c r="I126" s="29">
         <v>9.0E-4</v>
@@ -26084,16 +26084,16 @@
         <v>9990.4</v>
       </c>
       <c r="E129" s="28">
-        <v>770.6</v>
+        <v>771.45</v>
       </c>
       <c r="F129" s="28">
-        <v>10788.4</v>
+        <v>10800.3</v>
       </c>
       <c r="G129" s="28">
-        <v>798.0</v>
+        <v>809.9</v>
       </c>
       <c r="H129" s="29">
-        <v>0.0799</v>
+        <v>0.0811</v>
       </c>
       <c r="I129" s="29">
         <v>6.0E-4</v>
@@ -26348,16 +26348,16 @@
         <v>3464.5</v>
       </c>
       <c r="E135" s="28">
-        <v>1892.0</v>
+        <v>1892.45</v>
       </c>
       <c r="F135" s="28">
-        <v>5676.0</v>
+        <v>5677.35</v>
       </c>
       <c r="G135" s="28">
-        <v>2211.5</v>
+        <v>2212.85</v>
       </c>
       <c r="H135" s="29">
-        <v>0.6383</v>
+        <v>0.6387</v>
       </c>
       <c r="I135" s="29">
         <v>3.0E-4</v>
@@ -26392,16 +26392,16 @@
         <v>4377.95</v>
       </c>
       <c r="E136" s="28">
-        <v>90.0</v>
+        <v>90.38</v>
       </c>
       <c r="F136" s="28">
-        <v>3510.0</v>
+        <v>3524.82</v>
       </c>
       <c r="G136" s="28">
-        <v>-867.95</v>
+        <v>-853.13</v>
       </c>
       <c r="H136" s="29">
-        <v>-0.1983</v>
+        <v>-0.1949</v>
       </c>
       <c r="I136" s="29">
         <v>2.0E-4</v>
@@ -26436,16 +26436,16 @@
         <v>885.9</v>
       </c>
       <c r="E137" s="28">
-        <v>314.5</v>
+        <v>314.9</v>
       </c>
       <c r="F137" s="28">
-        <v>3459.5</v>
+        <v>3463.9</v>
       </c>
       <c r="G137" s="28">
-        <v>2573.6</v>
+        <v>2578.0</v>
       </c>
       <c r="H137" s="29">
-        <v>2.9051</v>
+        <v>2.91</v>
       </c>
       <c r="I137" s="29">
         <v>2.0E-4</v>
@@ -26480,16 +26480,16 @@
         <v>415.9</v>
       </c>
       <c r="E138" s="28">
-        <v>1915.5</v>
+        <v>1915.7</v>
       </c>
       <c r="F138" s="28">
-        <v>1915.5</v>
+        <v>1915.7</v>
       </c>
       <c r="G138" s="28">
-        <v>1499.6</v>
+        <v>1499.8</v>
       </c>
       <c r="H138" s="29">
-        <v>3.6057</v>
+        <v>3.6062</v>
       </c>
       <c r="I138" s="29">
         <v>1.0E-4</v>
@@ -26524,16 +26524,16 @@
         <v>588.9</v>
       </c>
       <c r="E139" s="28">
-        <v>787.45</v>
+        <v>784.1</v>
       </c>
       <c r="F139" s="28">
-        <v>787.45</v>
+        <v>784.1</v>
       </c>
       <c r="G139" s="28">
-        <v>198.55</v>
+        <v>195.2</v>
       </c>
       <c r="H139" s="29">
-        <v>0.3372</v>
+        <v>0.3315</v>
       </c>
       <c r="I139" s="29">
         <v>0.0</v>
@@ -26568,16 +26568,16 @@
         <v>262.0</v>
       </c>
       <c r="E140" s="28">
-        <v>726.85</v>
+        <v>727.3</v>
       </c>
       <c r="F140" s="28">
-        <v>726.85</v>
+        <v>727.3</v>
       </c>
       <c r="G140" s="28">
-        <v>464.85</v>
+        <v>465.3</v>
       </c>
       <c r="H140" s="29">
-        <v>1.7742</v>
+        <v>1.776</v>
       </c>
       <c r="I140" s="29">
         <v>0.0</v>
@@ -26656,16 +26656,16 @@
         <v>53.6</v>
       </c>
       <c r="E142" s="28">
-        <v>514.3</v>
+        <v>514.55</v>
       </c>
       <c r="F142" s="28">
-        <v>514.3</v>
+        <v>514.55</v>
       </c>
       <c r="G142" s="28">
-        <v>460.7</v>
+        <v>460.95</v>
       </c>
       <c r="H142" s="29">
-        <v>8.5951</v>
+        <v>8.5998</v>
       </c>
       <c r="I142" s="29">
         <v>0.0</v>
@@ -26700,16 +26700,16 @@
         <v>222.45</v>
       </c>
       <c r="E143" s="28">
-        <v>385.8</v>
+        <v>386.55</v>
       </c>
       <c r="F143" s="28">
-        <v>385.8</v>
+        <v>386.55</v>
       </c>
       <c r="G143" s="28">
-        <v>163.35</v>
+        <v>164.1</v>
       </c>
       <c r="H143" s="29">
-        <v>0.7343</v>
+        <v>0.7377</v>
       </c>
       <c r="I143" s="29">
         <v>0.0</v>
@@ -26744,16 +26744,16 @@
         <v>394.05</v>
       </c>
       <c r="E144" s="28">
-        <v>334.7</v>
+        <v>334.4</v>
       </c>
       <c r="F144" s="28">
-        <v>334.7</v>
+        <v>334.4</v>
       </c>
       <c r="G144" s="28">
-        <v>-59.35</v>
+        <v>-59.65</v>
       </c>
       <c r="H144" s="29">
-        <v>-0.1506</v>
+        <v>-0.1514</v>
       </c>
       <c r="I144" s="29">
         <v>0.0</v>
@@ -26832,16 +26832,16 @@
         <v>165.85</v>
       </c>
       <c r="E146" s="28">
-        <v>289.4</v>
+        <v>289.85</v>
       </c>
       <c r="F146" s="28">
-        <v>289.4</v>
+        <v>289.85</v>
       </c>
       <c r="G146" s="28">
-        <v>123.55</v>
+        <v>124.0</v>
       </c>
       <c r="H146" s="29">
-        <v>0.745</v>
+        <v>0.7477</v>
       </c>
       <c r="I146" s="29">
         <v>0.0</v>
@@ -26964,16 +26964,16 @@
         <v>25.25</v>
       </c>
       <c r="E149" s="28">
-        <v>138.15</v>
+        <v>138.27</v>
       </c>
       <c r="F149" s="28">
-        <v>138.15</v>
+        <v>138.27</v>
       </c>
       <c r="G149" s="28">
-        <v>112.9</v>
+        <v>113.02</v>
       </c>
       <c r="H149" s="29">
-        <v>4.4713</v>
+        <v>4.476</v>
       </c>
       <c r="I149" s="29">
         <v>0.0</v>
@@ -27052,16 +27052,16 @@
         <v>51.86</v>
       </c>
       <c r="E151" s="28">
-        <v>96.59</v>
+        <v>96.9</v>
       </c>
       <c r="F151" s="28">
-        <v>96.59</v>
+        <v>96.9</v>
       </c>
       <c r="G151" s="28">
-        <v>44.73</v>
+        <v>45.04</v>
       </c>
       <c r="H151" s="29">
-        <v>0.8624</v>
+        <v>0.8684</v>
       </c>
       <c r="I151" s="29">
         <v>0.0</v>

--- a/data/portfolio.xlsx
+++ b/data/portfolio.xlsx
@@ -164,13 +164,13 @@
     <t>WOCKPHARMA</t>
   </si>
   <si>
-    <t>ICICI PRUDENTIAL GOLD ETF FOF - DIRECT PLAN</t>
-  </si>
-  <si>
     <t>UTI NIFTY 50 INDEX FUND - DIRECT PLAN</t>
   </si>
   <si>
     <t>MF</t>
+  </si>
+  <si>
+    <t>ICICI PRUDENTIAL GOLD ETF FOF - DIRECT PLAN</t>
   </si>
   <si>
     <t>K_HUF</t>
@@ -596,13 +596,13 @@
     <t>SJVN</t>
   </si>
   <si>
-    <t>ADITYA BIRLA SUN LIFE ARBITRAGE FUND - DIRECT PLAN</t>
-  </si>
-  <si>
     <t>EDELWEISS ARBITRAGE FUND - DIRECT PLAN</t>
   </si>
   <si>
     <t>INVESCO INDIA ARBITRAGE FUND - DIRECT PLAN</t>
+  </si>
+  <si>
+    <t>ADITYA BIRLA SUN LIFE ARBITRAGE FUND - DIRECT PLAN</t>
   </si>
   <si>
     <t>Shashi</t>
@@ -1190,16 +1190,16 @@
         <v>51.86</v>
       </c>
       <c r="F2" s="7">
-        <v>95.65</v>
+        <v>95.26</v>
       </c>
       <c r="G2" s="7">
-        <v>95.65</v>
+        <v>95.26</v>
       </c>
       <c r="H2" s="7">
-        <v>43.79</v>
+        <v>43.4</v>
       </c>
       <c r="I2" s="8">
-        <v>0.8443</v>
+        <v>0.8368</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>15</v>
@@ -1232,16 +1232,16 @@
         <v>45632.3</v>
       </c>
       <c r="F3" s="11">
-        <v>809.0</v>
+        <v>807.15</v>
       </c>
       <c r="G3" s="7">
-        <v>137530.0</v>
+        <v>137215.5</v>
       </c>
       <c r="H3" s="11">
-        <v>91897.7</v>
+        <v>91583.2</v>
       </c>
       <c r="I3" s="12">
-        <v>2.0139</v>
+        <v>2.007</v>
       </c>
       <c r="J3" s="13" t="s">
         <v>15</v>
@@ -1358,13 +1358,13 @@
         <v>0.0</v>
       </c>
       <c r="F6" s="11">
-        <v>406.05</v>
+        <v>406.2</v>
       </c>
       <c r="G6" s="7">
-        <v>4872.6</v>
+        <v>4874.4</v>
       </c>
       <c r="H6" s="11">
-        <v>4872.6</v>
+        <v>4874.4</v>
       </c>
       <c r="I6" s="12">
         <v>0.0</v>
@@ -1400,16 +1400,16 @@
         <v>111.28</v>
       </c>
       <c r="F7" s="11">
-        <v>230.88</v>
+        <v>231.05</v>
       </c>
       <c r="G7" s="7">
-        <v>230.88</v>
+        <v>231.05</v>
       </c>
       <c r="H7" s="11">
-        <v>119.6</v>
+        <v>119.77</v>
       </c>
       <c r="I7" s="12">
-        <v>1.0748</v>
+        <v>1.0763</v>
       </c>
       <c r="J7" s="13" t="s">
         <v>15</v>
@@ -1442,16 +1442,16 @@
         <v>110.1</v>
       </c>
       <c r="F8" s="11">
-        <v>546.05</v>
+        <v>518.55</v>
       </c>
       <c r="G8" s="11">
-        <v>546.05</v>
+        <v>518.55</v>
       </c>
       <c r="H8" s="11">
-        <v>435.95</v>
+        <v>408.45</v>
       </c>
       <c r="I8" s="12">
-        <v>3.9596</v>
+        <v>3.7098</v>
       </c>
       <c r="J8" s="13" t="s">
         <v>26</v>
@@ -1484,16 +1484,16 @@
         <v>29095.0</v>
       </c>
       <c r="F9" s="11">
-        <v>760.15</v>
+        <v>760.5</v>
       </c>
       <c r="G9" s="11">
-        <v>76015.0</v>
+        <v>76050.0</v>
       </c>
       <c r="H9" s="11">
-        <v>46920.0</v>
+        <v>46955.0</v>
       </c>
       <c r="I9" s="12">
-        <v>1.6126</v>
+        <v>1.6139</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>26</v>
@@ -1610,16 +1610,16 @@
         <v>222.45</v>
       </c>
       <c r="F12" s="11">
-        <v>398.1</v>
+        <v>398.15</v>
       </c>
       <c r="G12" s="7">
-        <v>398.1</v>
+        <v>398.15</v>
       </c>
       <c r="H12" s="11">
-        <v>175.65</v>
+        <v>175.7</v>
       </c>
       <c r="I12" s="12">
-        <v>0.7896</v>
+        <v>0.7898</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>26</v>
@@ -1652,16 +1652,16 @@
         <v>588.9</v>
       </c>
       <c r="F13" s="11">
-        <v>815.0</v>
+        <v>813.55</v>
       </c>
       <c r="G13" s="7">
-        <v>815.0</v>
+        <v>813.55</v>
       </c>
       <c r="H13" s="11">
-        <v>226.1</v>
+        <v>224.65</v>
       </c>
       <c r="I13" s="14">
-        <v>0.3839</v>
+        <v>0.3815</v>
       </c>
       <c r="J13" s="15" t="s">
         <v>15</v>
@@ -1694,16 +1694,16 @@
         <v>429.7</v>
       </c>
       <c r="F14" s="7">
-        <v>299.5</v>
+        <v>300.55</v>
       </c>
       <c r="G14" s="7">
-        <v>299.5</v>
+        <v>300.55</v>
       </c>
       <c r="H14" s="7">
-        <v>-130.2</v>
+        <v>-129.15</v>
       </c>
       <c r="I14" s="8">
-        <v>-0.303</v>
+        <v>-0.3006</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>26</v>
@@ -1904,16 +1904,16 @@
         <v>25.25</v>
       </c>
       <c r="F19" s="11">
-        <v>135.31</v>
+        <v>135.45</v>
       </c>
       <c r="G19" s="7">
-        <v>135.31</v>
+        <v>135.45</v>
       </c>
       <c r="H19" s="11">
-        <v>110.06</v>
+        <v>110.2</v>
       </c>
       <c r="I19" s="14">
-        <v>4.3588</v>
+        <v>4.3644</v>
       </c>
       <c r="J19" s="16" t="s">
         <v>15</v>
@@ -1988,16 +1988,16 @@
         <v>142.65</v>
       </c>
       <c r="F21" s="11">
-        <v>275.0</v>
+        <v>274.75</v>
       </c>
       <c r="G21" s="11">
-        <v>275.0</v>
+        <v>274.75</v>
       </c>
       <c r="H21" s="11">
-        <v>132.35</v>
+        <v>132.1</v>
       </c>
       <c r="I21" s="12">
-        <v>0.9278</v>
+        <v>0.926</v>
       </c>
       <c r="J21" s="13" t="s">
         <v>15</v>
@@ -2114,16 +2114,16 @@
         <v>11538.0</v>
       </c>
       <c r="F24" s="11">
-        <v>1441.0</v>
+        <v>1441.7</v>
       </c>
       <c r="G24" s="7">
-        <v>57640.0</v>
+        <v>57668.0</v>
       </c>
       <c r="H24" s="11">
-        <v>46102.0</v>
+        <v>46130.0</v>
       </c>
       <c r="I24" s="12">
-        <v>3.9957</v>
+        <v>3.9981</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>15</v>
@@ -2156,16 +2156,16 @@
         <v>3464.5</v>
       </c>
       <c r="F25" s="7">
-        <v>1870.4</v>
+        <v>1871.6</v>
       </c>
       <c r="G25" s="7">
-        <v>5611.2</v>
+        <v>5614.8</v>
       </c>
       <c r="H25" s="7">
-        <v>2146.7</v>
+        <v>2150.3</v>
       </c>
       <c r="I25" s="17">
-        <v>0.6196</v>
+        <v>0.6207</v>
       </c>
       <c r="J25" s="16" t="s">
         <v>15</v>
@@ -2198,16 +2198,16 @@
         <v>53.6</v>
       </c>
       <c r="F26" s="7">
-        <v>503.0</v>
+        <v>502.2</v>
       </c>
       <c r="G26" s="7">
-        <v>503.0</v>
+        <v>502.2</v>
       </c>
       <c r="H26" s="7">
-        <v>449.4</v>
+        <v>448.6</v>
       </c>
       <c r="I26" s="17">
-        <v>8.3843</v>
+        <v>8.3694</v>
       </c>
       <c r="J26" s="16" t="s">
         <v>15</v>
@@ -2240,16 +2240,16 @@
         <v>415.9</v>
       </c>
       <c r="F27" s="11">
-        <v>1830.35</v>
+        <v>1831.3</v>
       </c>
       <c r="G27" s="11">
-        <v>1830.35</v>
+        <v>1831.3</v>
       </c>
       <c r="H27" s="11">
-        <v>1414.45</v>
+        <v>1415.4</v>
       </c>
       <c r="I27" s="14">
-        <v>3.4009</v>
+        <v>3.4032</v>
       </c>
       <c r="J27" s="16" t="s">
         <v>15</v>
@@ -2273,31 +2273,31 @@
         <v>49</v>
       </c>
       <c r="C28" s="6">
-        <v>6232.198</v>
+        <v>520.788</v>
       </c>
       <c r="D28" s="7">
-        <v>16.04</v>
+        <v>38.4</v>
       </c>
       <c r="E28" s="7">
-        <v>99994.99</v>
+        <v>19998.99</v>
       </c>
       <c r="F28" s="11">
-        <v>46.21</v>
+        <v>86.36</v>
       </c>
       <c r="G28" s="7">
-        <v>287968.68</v>
+        <v>44976.08</v>
       </c>
       <c r="H28" s="11">
-        <v>187973.69</v>
+        <v>24977.1</v>
       </c>
       <c r="I28" s="17">
-        <v>1.8798</v>
+        <v>1.2489</v>
       </c>
       <c r="J28" s="15" t="s">
         <v>15</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>17</v>
@@ -2312,7 +2312,7 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C29" s="6">
         <v>432.33</v>
@@ -2324,22 +2324,22 @@
         <v>39998.01</v>
       </c>
       <c r="F29" s="11">
-        <v>171.62</v>
+        <v>171.42</v>
       </c>
       <c r="G29" s="7">
-        <v>74195.83</v>
+        <v>74108.11</v>
       </c>
       <c r="H29" s="11">
-        <v>34197.82</v>
+        <v>34110.1</v>
       </c>
       <c r="I29" s="12">
-        <v>0.855</v>
+        <v>0.8528</v>
       </c>
       <c r="J29" s="9" t="s">
         <v>15</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>17</v>
@@ -2354,34 +2354,34 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C30" s="6">
-        <v>520.788</v>
+        <v>6232.198</v>
       </c>
       <c r="D30" s="7">
-        <v>38.4</v>
+        <v>16.04</v>
       </c>
       <c r="E30" s="7">
-        <v>19998.99</v>
+        <v>99994.99</v>
       </c>
       <c r="F30" s="11">
-        <v>86.46</v>
+        <v>45.92</v>
       </c>
       <c r="G30" s="7">
-        <v>45029.31</v>
+        <v>286154.49</v>
       </c>
       <c r="H30" s="11">
-        <v>25030.32</v>
+        <v>186159.49</v>
       </c>
       <c r="I30" s="17">
-        <v>1.2516</v>
+        <v>1.8617</v>
       </c>
       <c r="J30" s="15" t="s">
         <v>15</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>17</v>
@@ -2576,16 +2576,16 @@
         <v>24773.85</v>
       </c>
       <c r="F35" s="11">
-        <v>403.55</v>
+        <v>403.65</v>
       </c>
       <c r="G35" s="11">
-        <v>25827.2</v>
+        <v>25833.6</v>
       </c>
       <c r="H35" s="11">
-        <v>1053.35</v>
+        <v>1059.75</v>
       </c>
       <c r="I35" s="12">
-        <v>0.0425</v>
+        <v>0.0428</v>
       </c>
       <c r="J35" s="9" t="s">
         <v>26</v>
@@ -2702,16 +2702,16 @@
         <v>19998.4</v>
       </c>
       <c r="F38" s="11">
-        <v>1089.8</v>
+        <v>1090.0</v>
       </c>
       <c r="G38" s="7">
-        <v>17436.8</v>
+        <v>17440.0</v>
       </c>
       <c r="H38" s="11">
-        <v>-2561.6</v>
+        <v>-2558.4</v>
       </c>
       <c r="I38" s="14">
-        <v>-0.1281</v>
+        <v>-0.1279</v>
       </c>
       <c r="J38" s="15" t="s">
         <v>26</v>
@@ -2744,16 +2744,16 @@
         <v>19800.0</v>
       </c>
       <c r="F39" s="11">
-        <v>1331.8</v>
+        <v>1327.1</v>
       </c>
       <c r="G39" s="7">
-        <v>19977.0</v>
+        <v>19906.5</v>
       </c>
       <c r="H39" s="11">
-        <v>177.0</v>
+        <v>106.5</v>
       </c>
       <c r="I39" s="12">
-        <v>0.0089</v>
+        <v>0.0054</v>
       </c>
       <c r="J39" s="9" t="s">
         <v>26</v>
@@ -2954,16 +2954,16 @@
         <v>811.65</v>
       </c>
       <c r="F44" s="11">
-        <v>126.62</v>
+        <v>126.7</v>
       </c>
       <c r="G44" s="7">
-        <v>633.1</v>
+        <v>633.5</v>
       </c>
       <c r="H44" s="11">
-        <v>-178.55</v>
+        <v>-178.15</v>
       </c>
       <c r="I44" s="12">
-        <v>-0.22</v>
+        <v>-0.2195</v>
       </c>
       <c r="J44" s="9" t="s">
         <v>26</v>
@@ -2996,16 +2996,16 @@
         <v>394.05</v>
       </c>
       <c r="F45" s="11">
-        <v>329.0</v>
+        <v>327.85</v>
       </c>
       <c r="G45" s="11">
-        <v>329.0</v>
+        <v>327.85</v>
       </c>
       <c r="H45" s="11">
-        <v>-65.05</v>
+        <v>-66.2</v>
       </c>
       <c r="I45" s="12">
-        <v>-0.1651</v>
+        <v>-0.168</v>
       </c>
       <c r="J45" s="9" t="s">
         <v>15</v>
@@ -3206,13 +3206,13 @@
         <v>12555.0</v>
       </c>
       <c r="F50" s="11">
-        <v>2635.0</v>
+        <v>2635.05</v>
       </c>
       <c r="G50" s="7">
-        <v>23715.0</v>
+        <v>23715.45</v>
       </c>
       <c r="H50" s="11">
-        <v>11160.0</v>
+        <v>11160.45</v>
       </c>
       <c r="I50" s="14">
         <v>0.8889</v>
@@ -3290,16 +3290,16 @@
         <v>19760.0</v>
       </c>
       <c r="F52" s="11">
-        <v>1415.9</v>
+        <v>1414.2</v>
       </c>
       <c r="G52" s="7">
-        <v>26902.1</v>
+        <v>26869.8</v>
       </c>
       <c r="H52" s="11">
-        <v>7142.1</v>
+        <v>7109.8</v>
       </c>
       <c r="I52" s="12">
-        <v>0.3614</v>
+        <v>0.3598</v>
       </c>
       <c r="J52" s="13" t="s">
         <v>26</v>
@@ -3374,16 +3374,16 @@
         <v>13793.3</v>
       </c>
       <c r="F54" s="7">
-        <v>585.5</v>
+        <v>581.05</v>
       </c>
       <c r="G54" s="7">
-        <v>13466.5</v>
+        <v>13364.15</v>
       </c>
       <c r="H54" s="7">
-        <v>-326.8</v>
+        <v>-429.15</v>
       </c>
       <c r="I54" s="8">
-        <v>-0.0237</v>
+        <v>-0.0311</v>
       </c>
       <c r="J54" s="9" t="s">
         <v>26</v>
@@ -3458,16 +3458,16 @@
         <v>45490.4</v>
       </c>
       <c r="F56" s="11">
-        <v>2020.7</v>
+        <v>2021.9</v>
       </c>
       <c r="G56" s="11">
-        <v>44455.4</v>
+        <v>44481.8</v>
       </c>
       <c r="H56" s="11">
-        <v>-1035.0</v>
+        <v>-1008.6</v>
       </c>
       <c r="I56" s="12">
-        <v>-0.0228</v>
+        <v>-0.0222</v>
       </c>
       <c r="J56" s="9" t="s">
         <v>26</v>
@@ -3542,16 +3542,16 @@
         <v>52621.05</v>
       </c>
       <c r="F58" s="11">
-        <v>1561.8</v>
+        <v>1564.1</v>
       </c>
       <c r="G58" s="11">
-        <v>81213.6</v>
+        <v>81333.2</v>
       </c>
       <c r="H58" s="11">
-        <v>28592.55</v>
+        <v>28712.15</v>
       </c>
       <c r="I58" s="17">
-        <v>0.5434</v>
+        <v>0.5456</v>
       </c>
       <c r="J58" s="15" t="s">
         <v>26</v>
@@ -3626,16 +3626,16 @@
         <v>32138.35</v>
       </c>
       <c r="F60" s="11">
-        <v>497.5</v>
+        <v>496.05</v>
       </c>
       <c r="G60" s="7">
-        <v>28855.0</v>
+        <v>28770.9</v>
       </c>
       <c r="H60" s="11">
-        <v>-3283.35</v>
+        <v>-3367.45</v>
       </c>
       <c r="I60" s="12">
-        <v>-0.1022</v>
+        <v>-0.1048</v>
       </c>
       <c r="J60" s="9" t="s">
         <v>26</v>
@@ -3668,16 +3668,16 @@
         <v>11919.9</v>
       </c>
       <c r="F61" s="11">
-        <v>4338.0</v>
+        <v>4363.55</v>
       </c>
       <c r="G61" s="7">
-        <v>13014.0</v>
+        <v>13090.65</v>
       </c>
       <c r="H61" s="11">
-        <v>1094.1</v>
+        <v>1170.75</v>
       </c>
       <c r="I61" s="8">
-        <v>0.0918</v>
+        <v>0.0982</v>
       </c>
       <c r="J61" s="9" t="s">
         <v>26</v>
@@ -3710,16 +3710,16 @@
         <v>72170.8</v>
       </c>
       <c r="F62" s="11">
-        <v>2005.15</v>
+        <v>2006.2</v>
       </c>
       <c r="G62" s="7">
-        <v>106272.95</v>
+        <v>106328.6</v>
       </c>
       <c r="H62" s="11">
-        <v>34102.15</v>
+        <v>34157.8</v>
       </c>
       <c r="I62" s="14">
-        <v>0.4725</v>
+        <v>0.4733</v>
       </c>
       <c r="J62" s="15" t="s">
         <v>26</v>
@@ -3794,16 +3794,16 @@
         <v>29686.25</v>
       </c>
       <c r="F64" s="11">
-        <v>795.0</v>
+        <v>800.35</v>
       </c>
       <c r="G64" s="11">
-        <v>35775.0</v>
+        <v>36015.75</v>
       </c>
       <c r="H64" s="11">
-        <v>6088.75</v>
+        <v>6329.5</v>
       </c>
       <c r="I64" s="12">
-        <v>0.2051</v>
+        <v>0.2132</v>
       </c>
       <c r="J64" s="9" t="s">
         <v>26</v>
@@ -4046,16 +4046,16 @@
         <v>10095.6</v>
       </c>
       <c r="F70" s="11">
-        <v>1069.2</v>
+        <v>1070.8</v>
       </c>
       <c r="G70" s="7">
-        <v>6415.2</v>
+        <v>6424.8</v>
       </c>
       <c r="H70" s="11">
-        <v>-3680.4</v>
+        <v>-3670.8</v>
       </c>
       <c r="I70" s="12">
-        <v>-0.3646</v>
+        <v>-0.3636</v>
       </c>
       <c r="J70" s="9" t="s">
         <v>26</v>
@@ -4088,16 +4088,16 @@
         <v>9840.61</v>
       </c>
       <c r="F71" s="11">
-        <v>173.95</v>
+        <v>173.88</v>
       </c>
       <c r="G71" s="7">
-        <v>10263.05</v>
+        <v>10258.92</v>
       </c>
       <c r="H71" s="11">
-        <v>422.44</v>
+        <v>418.31</v>
       </c>
       <c r="I71" s="12">
-        <v>0.0429</v>
+        <v>0.0425</v>
       </c>
       <c r="J71" s="13" t="s">
         <v>26</v>
@@ -4172,16 +4172,16 @@
         <v>29813.65</v>
       </c>
       <c r="F73" s="11">
-        <v>638.6</v>
+        <v>633.4</v>
       </c>
       <c r="G73" s="7">
-        <v>25544.0</v>
+        <v>25336.0</v>
       </c>
       <c r="H73" s="11">
-        <v>-4269.65</v>
+        <v>-4477.65</v>
       </c>
       <c r="I73" s="12">
-        <v>-0.1432</v>
+        <v>-0.1502</v>
       </c>
       <c r="J73" s="9" t="s">
         <v>26</v>
@@ -4214,16 +4214,16 @@
         <v>18015.6</v>
       </c>
       <c r="F74" s="11">
-        <v>4284.55</v>
+        <v>4286.5</v>
       </c>
       <c r="G74" s="7">
-        <v>17138.2</v>
+        <v>17146.0</v>
       </c>
       <c r="H74" s="11">
-        <v>-877.4</v>
+        <v>-869.6</v>
       </c>
       <c r="I74" s="8">
-        <v>-0.0487</v>
+        <v>-0.0483</v>
       </c>
       <c r="J74" s="9" t="s">
         <v>15</v>
@@ -4256,16 +4256,16 @@
         <v>49672.65</v>
       </c>
       <c r="F75" s="11">
-        <v>303.25</v>
+        <v>303.3</v>
       </c>
       <c r="G75" s="7">
-        <v>55191.5</v>
+        <v>55200.6</v>
       </c>
       <c r="H75" s="11">
-        <v>5518.85</v>
+        <v>5527.95</v>
       </c>
       <c r="I75" s="12">
-        <v>0.1111</v>
+        <v>0.1113</v>
       </c>
       <c r="J75" s="9" t="s">
         <v>26</v>
@@ -4676,16 +4676,16 @@
         <v>21722.1</v>
       </c>
       <c r="F85" s="11">
-        <v>1406.2</v>
+        <v>1407.2</v>
       </c>
       <c r="G85" s="7">
-        <v>43592.2</v>
+        <v>43623.2</v>
       </c>
       <c r="H85" s="11">
-        <v>21870.1</v>
+        <v>21901.1</v>
       </c>
       <c r="I85" s="12">
-        <v>1.0068</v>
+        <v>1.0082</v>
       </c>
       <c r="J85" s="9" t="s">
         <v>26</v>
@@ -4760,16 +4760,16 @@
         <v>19116.7</v>
       </c>
       <c r="F87" s="11">
-        <v>3138.4</v>
+        <v>3142.0</v>
       </c>
       <c r="G87" s="7">
-        <v>21968.8</v>
+        <v>21994.0</v>
       </c>
       <c r="H87" s="11">
-        <v>2852.1</v>
+        <v>2877.3</v>
       </c>
       <c r="I87" s="12">
-        <v>0.1492</v>
+        <v>0.1505</v>
       </c>
       <c r="J87" s="9" t="s">
         <v>26</v>
@@ -4844,16 +4844,16 @@
         <v>10241.0</v>
       </c>
       <c r="F89" s="11">
-        <v>148.9</v>
+        <v>148.8</v>
       </c>
       <c r="G89" s="7">
-        <v>8934.0</v>
+        <v>8928.0</v>
       </c>
       <c r="H89" s="11">
-        <v>-1307.0</v>
+        <v>-1313.0</v>
       </c>
       <c r="I89" s="17">
-        <v>-0.1276</v>
+        <v>-0.1282</v>
       </c>
       <c r="J89" s="15" t="s">
         <v>26</v>
@@ -4928,16 +4928,16 @@
         <v>8884.2</v>
       </c>
       <c r="F91" s="11">
-        <v>128.6</v>
+        <v>130.69</v>
       </c>
       <c r="G91" s="11">
-        <v>8359.0</v>
+        <v>8494.85</v>
       </c>
       <c r="H91" s="11">
-        <v>-525.2</v>
+        <v>-389.35</v>
       </c>
       <c r="I91" s="12">
-        <v>-0.0591</v>
+        <v>-0.0438</v>
       </c>
       <c r="J91" s="13" t="s">
         <v>26</v>
@@ -5306,16 +5306,16 @@
         <v>52375.25</v>
       </c>
       <c r="F100" s="11">
-        <v>612.0</v>
+        <v>612.25</v>
       </c>
       <c r="G100" s="7">
-        <v>50796.0</v>
+        <v>50816.75</v>
       </c>
       <c r="H100" s="11">
-        <v>-1579.25</v>
+        <v>-1558.5</v>
       </c>
       <c r="I100" s="8">
-        <v>-0.0302</v>
+        <v>-0.0298</v>
       </c>
       <c r="J100" s="9" t="s">
         <v>26</v>
@@ -5390,16 +5390,16 @@
         <v>9927.45</v>
       </c>
       <c r="F102" s="11">
-        <v>136.97</v>
+        <v>137.05</v>
       </c>
       <c r="G102" s="7">
-        <v>8903.05</v>
+        <v>8908.25</v>
       </c>
       <c r="H102" s="11">
-        <v>-1024.4</v>
+        <v>-1019.2</v>
       </c>
       <c r="I102" s="12">
-        <v>-0.1032</v>
+        <v>-0.1027</v>
       </c>
       <c r="J102" s="9" t="s">
         <v>26</v>
@@ -5516,16 +5516,16 @@
         <v>20755.8</v>
       </c>
       <c r="F105" s="11">
-        <v>792.1</v>
+        <v>792.5</v>
       </c>
       <c r="G105" s="11">
-        <v>14257.8</v>
+        <v>14265.0</v>
       </c>
       <c r="H105" s="11">
-        <v>-6498.0</v>
+        <v>-6490.8</v>
       </c>
       <c r="I105" s="12">
-        <v>-0.3131</v>
+        <v>-0.3127</v>
       </c>
       <c r="J105" s="9" t="s">
         <v>26</v>
@@ -5600,16 +5600,16 @@
         <v>9202.7</v>
       </c>
       <c r="F107" s="11">
-        <v>377.05</v>
+        <v>373.8</v>
       </c>
       <c r="G107" s="7">
-        <v>9803.3</v>
+        <v>9718.8</v>
       </c>
       <c r="H107" s="11">
-        <v>600.6</v>
+        <v>516.1</v>
       </c>
       <c r="I107" s="14">
-        <v>0.0653</v>
+        <v>0.0561</v>
       </c>
       <c r="J107" s="16" t="s">
         <v>26</v>
@@ -5642,16 +5642,16 @@
         <v>7303.1</v>
       </c>
       <c r="F108" s="11">
-        <v>1089.8</v>
+        <v>1090.0</v>
       </c>
       <c r="G108" s="11">
-        <v>7628.6</v>
+        <v>7630.0</v>
       </c>
       <c r="H108" s="11">
-        <v>325.5</v>
+        <v>326.9</v>
       </c>
       <c r="I108" s="12">
-        <v>0.0446</v>
+        <v>0.0448</v>
       </c>
       <c r="J108" s="9" t="s">
         <v>26</v>
@@ -5768,16 +5768,16 @@
         <v>9925.04</v>
       </c>
       <c r="F111" s="11">
-        <v>111.83</v>
+        <v>111.85</v>
       </c>
       <c r="G111" s="7">
-        <v>10847.51</v>
+        <v>10849.45</v>
       </c>
       <c r="H111" s="11">
-        <v>922.47</v>
+        <v>924.41</v>
       </c>
       <c r="I111" s="12">
-        <v>0.0929</v>
+        <v>0.0931</v>
       </c>
       <c r="J111" s="9" t="s">
         <v>26</v>
@@ -5810,16 +5810,16 @@
         <v>9529.0</v>
       </c>
       <c r="F112" s="11">
-        <v>2020.7</v>
+        <v>2021.9</v>
       </c>
       <c r="G112" s="11">
-        <v>10103.5</v>
+        <v>10109.5</v>
       </c>
       <c r="H112" s="11">
-        <v>574.5</v>
+        <v>580.5</v>
       </c>
       <c r="I112" s="12">
-        <v>0.0603</v>
+        <v>0.0609</v>
       </c>
       <c r="J112" s="9" t="s">
         <v>26</v>
@@ -5852,16 +5852,16 @@
         <v>13424.7</v>
       </c>
       <c r="F113" s="11">
-        <v>4338.0</v>
+        <v>4363.55</v>
       </c>
       <c r="G113" s="11">
-        <v>13014.0</v>
+        <v>13090.65</v>
       </c>
       <c r="H113" s="11">
-        <v>-410.7</v>
+        <v>-334.05</v>
       </c>
       <c r="I113" s="12">
-        <v>-0.0306</v>
+        <v>-0.0249</v>
       </c>
       <c r="J113" s="13" t="s">
         <v>26</v>
@@ -5936,16 +5936,16 @@
         <v>10492.0</v>
       </c>
       <c r="F115" s="11">
-        <v>568.7</v>
+        <v>569.25</v>
       </c>
       <c r="G115" s="11">
-        <v>10805.3</v>
+        <v>10815.75</v>
       </c>
       <c r="H115" s="11">
-        <v>313.3</v>
+        <v>323.75</v>
       </c>
       <c r="I115" s="12">
-        <v>0.0299</v>
+        <v>0.0309</v>
       </c>
       <c r="J115" s="9" t="s">
         <v>26</v>
@@ -6050,28 +6050,28 @@
         <v>132</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>49</v>
+        <v>137</v>
       </c>
       <c r="C118" s="6">
-        <v>3874.587</v>
+        <v>3973.047</v>
       </c>
       <c r="D118" s="7">
-        <v>12.9</v>
+        <v>12.58</v>
       </c>
       <c r="E118" s="11">
         <v>50000.0</v>
       </c>
       <c r="F118" s="11">
-        <v>46.21</v>
+        <v>44.75</v>
       </c>
       <c r="G118" s="11">
-        <v>179031.49</v>
+        <v>177800.21</v>
       </c>
       <c r="H118" s="11">
-        <v>129031.5</v>
+        <v>127800.21</v>
       </c>
       <c r="I118" s="12">
-        <v>2.5806</v>
+        <v>2.556</v>
       </c>
       <c r="J118" s="9" t="s">
         <v>15</v>
@@ -6092,28 +6092,28 @@
         <v>132</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>137</v>
+        <v>51</v>
       </c>
       <c r="C119" s="6">
-        <v>3973.047</v>
+        <v>3874.587</v>
       </c>
       <c r="D119" s="7">
-        <v>12.58</v>
+        <v>12.9</v>
       </c>
       <c r="E119" s="11">
         <v>50000.0</v>
       </c>
       <c r="F119" s="11">
-        <v>45.12</v>
+        <v>45.92</v>
       </c>
       <c r="G119" s="11">
-        <v>179266.66</v>
+        <v>177903.6</v>
       </c>
       <c r="H119" s="11">
-        <v>129266.66</v>
+        <v>127903.6</v>
       </c>
       <c r="I119" s="12">
-        <v>2.5853</v>
+        <v>2.5581</v>
       </c>
       <c r="J119" s="9" t="s">
         <v>15</v>
@@ -6188,16 +6188,16 @@
         <v>691.7</v>
       </c>
       <c r="F121" s="11">
-        <v>809.0</v>
+        <v>807.15</v>
       </c>
       <c r="G121" s="7">
-        <v>809.0</v>
+        <v>807.15</v>
       </c>
       <c r="H121" s="11">
-        <v>117.3</v>
+        <v>115.45</v>
       </c>
       <c r="I121" s="12">
-        <v>0.1696</v>
+        <v>0.1669</v>
       </c>
       <c r="J121" s="9" t="s">
         <v>15</v>
@@ -6272,13 +6272,13 @@
         <v>0.0</v>
       </c>
       <c r="F123" s="11">
-        <v>406.05</v>
+        <v>406.2</v>
       </c>
       <c r="G123" s="7">
-        <v>40605.0</v>
+        <v>40620.0</v>
       </c>
       <c r="H123" s="11">
-        <v>40605.0</v>
+        <v>40620.0</v>
       </c>
       <c r="I123" s="12">
         <v>0.0</v>
@@ -6356,16 +6356,16 @@
         <v>1059.2</v>
       </c>
       <c r="F125" s="11">
-        <v>1415.9</v>
+        <v>1414.2</v>
       </c>
       <c r="G125" s="7">
-        <v>1415.9</v>
+        <v>1414.2</v>
       </c>
       <c r="H125" s="11">
-        <v>356.7</v>
+        <v>355.0</v>
       </c>
       <c r="I125" s="14">
-        <v>0.3368</v>
+        <v>0.3352</v>
       </c>
       <c r="J125" s="15" t="s">
         <v>26</v>
@@ -6440,16 +6440,16 @@
         <v>538.0</v>
       </c>
       <c r="F127" s="11">
-        <v>497.5</v>
+        <v>496.05</v>
       </c>
       <c r="G127" s="7">
-        <v>497.5</v>
+        <v>496.05</v>
       </c>
       <c r="H127" s="11">
-        <v>-40.5</v>
+        <v>-41.95</v>
       </c>
       <c r="I127" s="14">
-        <v>-0.0753</v>
+        <v>-0.078</v>
       </c>
       <c r="J127" s="16" t="s">
         <v>26</v>
@@ -6524,16 +6524,16 @@
         <v>461.55</v>
       </c>
       <c r="F129" s="11">
-        <v>299.5</v>
+        <v>300.55</v>
       </c>
       <c r="G129" s="11">
-        <v>299.5</v>
+        <v>300.55</v>
       </c>
       <c r="H129" s="11">
-        <v>-162.05</v>
+        <v>-161.0</v>
       </c>
       <c r="I129" s="12">
-        <v>-0.3511</v>
+        <v>-0.3488</v>
       </c>
       <c r="J129" s="9" t="s">
         <v>26</v>
@@ -6566,16 +6566,16 @@
         <v>1789.9</v>
       </c>
       <c r="F130" s="11">
-        <v>1069.2</v>
+        <v>1070.8</v>
       </c>
       <c r="G130" s="7">
-        <v>1069.2</v>
+        <v>1070.8</v>
       </c>
       <c r="H130" s="11">
-        <v>-720.7</v>
+        <v>-719.1</v>
       </c>
       <c r="I130" s="12">
-        <v>-0.4026</v>
+        <v>-0.4018</v>
       </c>
       <c r="J130" s="9" t="s">
         <v>26</v>
@@ -6608,16 +6608,16 @@
         <v>262.0</v>
       </c>
       <c r="F131" s="11">
-        <v>676.5</v>
+        <v>676.3</v>
       </c>
       <c r="G131" s="7">
-        <v>676.5</v>
+        <v>676.3</v>
       </c>
       <c r="H131" s="11">
-        <v>414.5</v>
+        <v>414.3</v>
       </c>
       <c r="I131" s="12">
-        <v>1.5821</v>
+        <v>1.5813</v>
       </c>
       <c r="J131" s="9" t="s">
         <v>15</v>
@@ -6986,16 +6986,16 @@
         <v>9077.0</v>
       </c>
       <c r="F140" s="11">
-        <v>14220.0</v>
+        <v>14342.0</v>
       </c>
       <c r="G140" s="7">
-        <v>14220.0</v>
+        <v>14342.0</v>
       </c>
       <c r="H140" s="11">
-        <v>5143.0</v>
+        <v>5265.0</v>
       </c>
       <c r="I140" s="12">
-        <v>0.5666</v>
+        <v>0.58</v>
       </c>
       <c r="J140" s="9" t="s">
         <v>15</v>
@@ -7028,16 +7028,16 @@
         <v>9071.0</v>
       </c>
       <c r="F141" s="11">
-        <v>14301.01</v>
+        <v>14331.0</v>
       </c>
       <c r="G141" s="7">
-        <v>14301.01</v>
+        <v>14331.0</v>
       </c>
       <c r="H141" s="11">
-        <v>5230.01</v>
+        <v>5260.0</v>
       </c>
       <c r="I141" s="12">
-        <v>0.5766</v>
+        <v>0.5799</v>
       </c>
       <c r="J141" s="9" t="s">
         <v>15</v>
@@ -7112,16 +7112,16 @@
         <v>885.9</v>
       </c>
       <c r="F143" s="11">
-        <v>346.2</v>
+        <v>346.75</v>
       </c>
       <c r="G143" s="7">
-        <v>3808.2</v>
+        <v>3814.25</v>
       </c>
       <c r="H143" s="11">
-        <v>2922.3</v>
+        <v>2928.35</v>
       </c>
       <c r="I143" s="14">
-        <v>3.2987</v>
+        <v>3.3055</v>
       </c>
       <c r="J143" s="16" t="s">
         <v>15</v>
@@ -7154,16 +7154,16 @@
         <v>30662.25</v>
       </c>
       <c r="F144" s="11">
-        <v>1441.0</v>
+        <v>1441.7</v>
       </c>
       <c r="G144" s="11">
-        <v>115280.0</v>
+        <v>115336.0</v>
       </c>
       <c r="H144" s="11">
-        <v>84617.75</v>
+        <v>84673.75</v>
       </c>
       <c r="I144" s="12">
-        <v>2.7597</v>
+        <v>2.7615</v>
       </c>
       <c r="J144" s="9" t="s">
         <v>15</v>
@@ -7196,16 +7196,16 @@
         <v>2702.0</v>
       </c>
       <c r="F145" s="11">
-        <v>792.1</v>
+        <v>792.5</v>
       </c>
       <c r="G145" s="7">
-        <v>1584.2</v>
+        <v>1585.0</v>
       </c>
       <c r="H145" s="11">
-        <v>-1117.8</v>
+        <v>-1117.0</v>
       </c>
       <c r="I145" s="14">
-        <v>-0.4137</v>
+        <v>-0.4134</v>
       </c>
       <c r="J145" s="15" t="s">
         <v>26</v>
@@ -7322,16 +7322,16 @@
         <v>5607.5</v>
       </c>
       <c r="F148" s="11">
-        <v>809.0</v>
+        <v>807.15</v>
       </c>
       <c r="G148" s="11">
-        <v>9708.0</v>
+        <v>9685.8</v>
       </c>
       <c r="H148" s="11">
-        <v>4100.5</v>
+        <v>4078.3</v>
       </c>
       <c r="I148" s="14">
-        <v>0.7313</v>
+        <v>0.7273</v>
       </c>
       <c r="J148" s="16" t="s">
         <v>15</v>
@@ -7448,16 +7448,16 @@
         <v>24660.0</v>
       </c>
       <c r="F151" s="11">
-        <v>1331.8</v>
+        <v>1327.1</v>
       </c>
       <c r="G151" s="7">
-        <v>23972.4</v>
+        <v>23887.8</v>
       </c>
       <c r="H151" s="11">
-        <v>-687.6</v>
+        <v>-772.2</v>
       </c>
       <c r="I151" s="14">
-        <v>-0.0279</v>
+        <v>-0.0313</v>
       </c>
       <c r="J151" s="16" t="s">
         <v>26</v>
@@ -7532,16 +7532,16 @@
         <v>10673.0</v>
       </c>
       <c r="F153" s="11">
-        <v>4284.0</v>
+        <v>4290.55</v>
       </c>
       <c r="G153" s="7">
-        <v>21420.0</v>
+        <v>21452.75</v>
       </c>
       <c r="H153" s="11">
-        <v>10747.0</v>
+        <v>10779.75</v>
       </c>
       <c r="I153" s="8">
-        <v>1.0069</v>
+        <v>1.01</v>
       </c>
       <c r="J153" s="9" t="s">
         <v>15</v>
@@ -7658,16 +7658,16 @@
         <v>25112.5</v>
       </c>
       <c r="F156" s="11">
-        <v>546.05</v>
+        <v>518.55</v>
       </c>
       <c r="G156" s="7">
-        <v>27302.5</v>
+        <v>25927.5</v>
       </c>
       <c r="H156" s="11">
-        <v>2190.0</v>
+        <v>815.0</v>
       </c>
       <c r="I156" s="12">
-        <v>0.0872</v>
+        <v>0.0325</v>
       </c>
       <c r="J156" s="9" t="s">
         <v>26</v>
@@ -7784,16 +7784,16 @@
         <v>10003.56</v>
       </c>
       <c r="F159" s="7">
-        <v>64.0</v>
+        <v>63.81</v>
       </c>
       <c r="G159" s="7">
-        <v>9472.0</v>
+        <v>9443.88</v>
       </c>
       <c r="H159" s="25">
-        <v>-531.56</v>
+        <v>-559.68</v>
       </c>
       <c r="I159" s="26">
-        <v>-0.0531</v>
+        <v>-0.0559</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>26</v>
@@ -8071,16 +8071,16 @@
         <v>11114.0</v>
       </c>
       <c r="F166" s="7">
-        <v>585.5</v>
+        <v>581.05</v>
       </c>
       <c r="G166" s="7">
-        <v>11710.0</v>
+        <v>11621.0</v>
       </c>
       <c r="H166" s="25">
-        <v>596.0</v>
+        <v>507.0</v>
       </c>
       <c r="I166" s="26">
-        <v>0.0536</v>
+        <v>0.0456</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>26</v>
@@ -8153,16 +8153,16 @@
         <v>17812.6</v>
       </c>
       <c r="F168" s="7">
-        <v>2020.7</v>
+        <v>2021.9</v>
       </c>
       <c r="G168" s="7">
-        <v>18186.3</v>
+        <v>18197.1</v>
       </c>
       <c r="H168" s="25">
-        <v>373.7</v>
+        <v>384.5</v>
       </c>
       <c r="I168" s="26">
-        <v>0.021</v>
+        <v>0.0216</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>26</v>
@@ -8194,16 +8194,16 @@
         <v>9690.8</v>
       </c>
       <c r="F169" s="7">
-        <v>1561.8</v>
+        <v>1564.1</v>
       </c>
       <c r="G169" s="7">
-        <v>10932.6</v>
+        <v>10948.7</v>
       </c>
       <c r="H169" s="25">
-        <v>1241.8</v>
+        <v>1257.9</v>
       </c>
       <c r="I169" s="26">
-        <v>0.1281</v>
+        <v>0.1298</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>26</v>
@@ -8440,16 +8440,16 @@
         <v>43190.9</v>
       </c>
       <c r="F175" s="28">
-        <v>497.5</v>
+        <v>496.05</v>
       </c>
       <c r="G175" s="28">
-        <v>39800.0</v>
+        <v>39684.0</v>
       </c>
       <c r="H175" s="28">
-        <v>-3390.9</v>
+        <v>-3506.9</v>
       </c>
       <c r="I175" s="29">
-        <v>-0.0785</v>
+        <v>-0.0812</v>
       </c>
       <c r="J175" s="1" t="s">
         <v>26</v>
@@ -8481,16 +8481,16 @@
         <v>79586.6</v>
       </c>
       <c r="F176" s="28">
-        <v>4338.0</v>
+        <v>4363.55</v>
       </c>
       <c r="G176" s="28">
-        <v>78084.0</v>
+        <v>78543.9</v>
       </c>
       <c r="H176" s="28">
-        <v>-1502.6</v>
+        <v>-1042.7</v>
       </c>
       <c r="I176" s="29">
-        <v>-0.0189</v>
+        <v>-0.0131</v>
       </c>
       <c r="J176" s="1" t="s">
         <v>26</v>
@@ -8522,16 +8522,16 @@
         <v>35446.4</v>
       </c>
       <c r="F177" s="28">
-        <v>2005.15</v>
+        <v>2006.2</v>
       </c>
       <c r="G177" s="28">
-        <v>60154.5</v>
+        <v>60186.0</v>
       </c>
       <c r="H177" s="28">
-        <v>24708.1</v>
+        <v>24739.6</v>
       </c>
       <c r="I177" s="29">
-        <v>0.6971</v>
+        <v>0.6979</v>
       </c>
       <c r="J177" s="1" t="s">
         <v>26</v>
@@ -8850,16 +8850,16 @@
         <v>639.95</v>
       </c>
       <c r="F185" s="28">
-        <v>429.05</v>
+        <v>429.15</v>
       </c>
       <c r="G185" s="28">
-        <v>429.05</v>
+        <v>429.15</v>
       </c>
       <c r="H185" s="28">
-        <v>-210.9</v>
+        <v>-210.8</v>
       </c>
       <c r="I185" s="29">
-        <v>-0.3296</v>
+        <v>-0.3294</v>
       </c>
       <c r="J185" s="1" t="s">
         <v>26</v>
@@ -9014,16 +9014,16 @@
         <v>9848.4</v>
       </c>
       <c r="F189" s="28">
-        <v>173.95</v>
+        <v>173.88</v>
       </c>
       <c r="G189" s="28">
-        <v>10089.1</v>
+        <v>10085.04</v>
       </c>
       <c r="H189" s="28">
-        <v>240.7</v>
+        <v>236.64</v>
       </c>
       <c r="I189" s="29">
-        <v>0.0244</v>
+        <v>0.024</v>
       </c>
       <c r="J189" s="1" t="s">
         <v>26</v>
@@ -9137,16 +9137,16 @@
         <v>48196.25</v>
       </c>
       <c r="F192" s="28">
-        <v>4284.55</v>
+        <v>4286.5</v>
       </c>
       <c r="G192" s="28">
-        <v>55699.15</v>
+        <v>55724.5</v>
       </c>
       <c r="H192" s="28">
-        <v>7502.9</v>
+        <v>7528.25</v>
       </c>
       <c r="I192" s="29">
-        <v>0.1557</v>
+        <v>0.1562</v>
       </c>
       <c r="J192" s="1" t="s">
         <v>15</v>
@@ -9219,16 +9219,16 @@
         <v>54922.25</v>
       </c>
       <c r="F194" s="28">
-        <v>303.25</v>
+        <v>303.3</v>
       </c>
       <c r="G194" s="28">
-        <v>57314.25</v>
+        <v>57323.7</v>
       </c>
       <c r="H194" s="28">
-        <v>2392.0</v>
+        <v>2401.45</v>
       </c>
       <c r="I194" s="29">
-        <v>0.0436</v>
+        <v>0.0437</v>
       </c>
       <c r="J194" s="1" t="s">
         <v>26</v>
@@ -9383,16 +9383,16 @@
         <v>37387.9</v>
       </c>
       <c r="F198" s="28">
-        <v>568.7</v>
+        <v>569.25</v>
       </c>
       <c r="G198" s="28">
-        <v>43221.2</v>
+        <v>43263.0</v>
       </c>
       <c r="H198" s="28">
-        <v>5833.3</v>
+        <v>5875.1</v>
       </c>
       <c r="I198" s="29">
-        <v>0.156</v>
+        <v>0.1571</v>
       </c>
       <c r="J198" s="1" t="s">
         <v>26</v>
@@ -9506,16 +9506,16 @@
         <v>14635.0</v>
       </c>
       <c r="F201" s="28">
-        <v>302.9</v>
+        <v>303.0</v>
       </c>
       <c r="G201" s="28">
-        <v>15145.0</v>
+        <v>15150.0</v>
       </c>
       <c r="H201" s="28">
-        <v>510.0</v>
+        <v>515.0</v>
       </c>
       <c r="I201" s="29">
-        <v>0.0348</v>
+        <v>0.0352</v>
       </c>
       <c r="J201" s="1" t="s">
         <v>26</v>
@@ -9752,16 +9752,16 @@
         <v>9643.15</v>
       </c>
       <c r="F207" s="28">
-        <v>780.9</v>
+        <v>779.25</v>
       </c>
       <c r="G207" s="28">
-        <v>10151.7</v>
+        <v>10130.25</v>
       </c>
       <c r="H207" s="28">
-        <v>508.55</v>
+        <v>487.1</v>
       </c>
       <c r="I207" s="29">
-        <v>0.0527</v>
+        <v>0.0505</v>
       </c>
       <c r="J207" s="1" t="s">
         <v>26</v>
@@ -9793,16 +9793,16 @@
         <v>9346.2</v>
       </c>
       <c r="F208" s="28">
-        <v>1406.2</v>
+        <v>1407.2</v>
       </c>
       <c r="G208" s="28">
-        <v>16874.4</v>
+        <v>16886.4</v>
       </c>
       <c r="H208" s="28">
-        <v>7528.2</v>
+        <v>7540.2</v>
       </c>
       <c r="I208" s="29">
-        <v>0.8055</v>
+        <v>0.8068</v>
       </c>
       <c r="J208" s="1" t="s">
         <v>26</v>
@@ -9916,16 +9916,16 @@
         <v>71808.6</v>
       </c>
       <c r="F211" s="28">
-        <v>3138.4</v>
+        <v>3142.0</v>
       </c>
       <c r="G211" s="28">
-        <v>156920.0</v>
+        <v>157100.0</v>
       </c>
       <c r="H211" s="28">
-        <v>85111.4</v>
+        <v>85291.4</v>
       </c>
       <c r="I211" s="29">
-        <v>1.1853</v>
+        <v>1.1878</v>
       </c>
       <c r="J211" s="1" t="s">
         <v>26</v>
@@ -10080,16 +10080,16 @@
         <v>137415.0</v>
       </c>
       <c r="F215" s="28">
-        <v>14310.0</v>
+        <v>14397.7</v>
       </c>
       <c r="G215" s="28">
-        <v>214650.0</v>
+        <v>215965.5</v>
       </c>
       <c r="H215" s="28">
-        <v>77235.0</v>
+        <v>78550.5</v>
       </c>
       <c r="I215" s="29">
-        <v>0.5621</v>
+        <v>0.5716</v>
       </c>
       <c r="J215" s="1" t="s">
         <v>15</v>
@@ -10121,16 +10121,16 @@
         <v>52975.0</v>
       </c>
       <c r="F216" s="28">
-        <v>14323.24</v>
+        <v>14416.24</v>
       </c>
       <c r="G216" s="28">
-        <v>85939.44</v>
+        <v>86497.44</v>
       </c>
       <c r="H216" s="28">
-        <v>32964.44</v>
+        <v>33522.44</v>
       </c>
       <c r="I216" s="29">
-        <v>0.6223</v>
+        <v>0.6328</v>
       </c>
       <c r="J216" s="1" t="s">
         <v>15</v>
@@ -10203,16 +10203,16 @@
         <v>242767.0</v>
       </c>
       <c r="F218" s="28">
-        <v>14325.0</v>
+        <v>14308.63</v>
       </c>
       <c r="G218" s="28">
-        <v>272175.0</v>
+        <v>271863.97</v>
       </c>
       <c r="H218" s="28">
-        <v>29408.0</v>
+        <v>29096.97</v>
       </c>
       <c r="I218" s="29">
-        <v>0.1211</v>
+        <v>0.1199</v>
       </c>
       <c r="J218" s="1" t="s">
         <v>15</v>
@@ -10367,16 +10367,16 @@
         <v>145192.0</v>
       </c>
       <c r="F222" s="28">
-        <v>670.0</v>
+        <v>670.75</v>
       </c>
       <c r="G222" s="28">
-        <v>166160.0</v>
+        <v>166346.0</v>
       </c>
       <c r="H222" s="28">
-        <v>20968.0</v>
+        <v>21154.0</v>
       </c>
       <c r="I222" s="29">
-        <v>0.1444</v>
+        <v>0.1457</v>
       </c>
       <c r="J222" s="1" t="s">
         <v>26</v>
@@ -10531,16 +10531,16 @@
         <v>82301.55</v>
       </c>
       <c r="F226" s="28">
-        <v>1441.0</v>
+        <v>1441.7</v>
       </c>
       <c r="G226" s="28">
-        <v>243529.0</v>
+        <v>243647.3</v>
       </c>
       <c r="H226" s="28">
-        <v>161227.45</v>
+        <v>161345.75</v>
       </c>
       <c r="I226" s="29">
-        <v>1.959</v>
+        <v>1.9604</v>
       </c>
       <c r="J226" s="1" t="s">
         <v>15</v>
@@ -10695,16 +10695,16 @@
         <v>49616.7</v>
       </c>
       <c r="F230" s="28">
-        <v>612.0</v>
+        <v>612.25</v>
       </c>
       <c r="G230" s="28">
-        <v>56304.0</v>
+        <v>56327.0</v>
       </c>
       <c r="H230" s="28">
-        <v>6687.3</v>
+        <v>6710.3</v>
       </c>
       <c r="I230" s="29">
-        <v>0.1348</v>
+        <v>0.1352</v>
       </c>
       <c r="J230" s="1" t="s">
         <v>26</v>
@@ -10859,16 +10859,16 @@
         <v>19967.9</v>
       </c>
       <c r="F234" s="28">
-        <v>136.97</v>
+        <v>137.05</v>
       </c>
       <c r="G234" s="28">
-        <v>21915.2</v>
+        <v>21928.0</v>
       </c>
       <c r="H234" s="28">
-        <v>1947.3</v>
+        <v>1960.1</v>
       </c>
       <c r="I234" s="29">
-        <v>0.0975</v>
+        <v>0.0982</v>
       </c>
       <c r="J234" s="1" t="s">
         <v>26</v>
@@ -10900,16 +10900,16 @@
         <v>165.85</v>
       </c>
       <c r="F235" s="28">
-        <v>282.0</v>
+        <v>281.05</v>
       </c>
       <c r="G235" s="28">
-        <v>282.0</v>
+        <v>281.05</v>
       </c>
       <c r="H235" s="28">
-        <v>116.15</v>
+        <v>115.2</v>
       </c>
       <c r="I235" s="29">
-        <v>0.7003</v>
+        <v>0.6946</v>
       </c>
       <c r="J235" s="1" t="s">
         <v>15</v>
@@ -10941,16 +10941,16 @@
         <v>56060.4</v>
       </c>
       <c r="F236" s="28">
-        <v>1601.9</v>
+        <v>1602.5</v>
       </c>
       <c r="G236" s="28">
-        <v>81696.9</v>
+        <v>81727.5</v>
       </c>
       <c r="H236" s="28">
-        <v>25636.5</v>
+        <v>25667.1</v>
       </c>
       <c r="I236" s="29">
-        <v>0.4573</v>
+        <v>0.4578</v>
       </c>
       <c r="J236" s="1" t="s">
         <v>26</v>
@@ -11023,16 +11023,16 @@
         <v>4275.0</v>
       </c>
       <c r="F238" s="28">
-        <v>792.1</v>
+        <v>792.5</v>
       </c>
       <c r="G238" s="28">
-        <v>2376.3</v>
+        <v>2377.5</v>
       </c>
       <c r="H238" s="28">
-        <v>-1898.7</v>
+        <v>-1897.5</v>
       </c>
       <c r="I238" s="29">
-        <v>-0.4441</v>
+        <v>-0.4439</v>
       </c>
       <c r="J238" s="1" t="s">
         <v>26</v>
@@ -11105,22 +11105,22 @@
         <v>530870.0</v>
       </c>
       <c r="F240" s="28">
-        <v>14.42</v>
+        <v>14.43</v>
       </c>
       <c r="G240" s="28">
-        <v>580458.37</v>
+        <v>580860.91</v>
       </c>
       <c r="H240" s="28">
-        <v>49588.37</v>
+        <v>49990.91</v>
       </c>
       <c r="I240" s="29">
-        <v>0.0934</v>
+        <v>0.0942</v>
       </c>
       <c r="J240" s="1" t="s">
         <v>15</v>
       </c>
       <c r="K240" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L240" s="1" t="s">
         <v>17</v>
@@ -11269,16 +11269,16 @@
         <v>39906.4</v>
       </c>
       <c r="F244" s="28">
-        <v>1089.8</v>
+        <v>1090.0</v>
       </c>
       <c r="G244" s="28">
-        <v>39232.8</v>
+        <v>39240.0</v>
       </c>
       <c r="H244" s="28">
-        <v>-673.6</v>
+        <v>-666.4</v>
       </c>
       <c r="I244" s="29">
-        <v>-0.0169</v>
+        <v>-0.0167</v>
       </c>
       <c r="J244" s="1" t="s">
         <v>26</v>
@@ -11310,16 +11310,16 @@
         <v>19914.4</v>
       </c>
       <c r="F245" s="28">
-        <v>163.5</v>
+        <v>162.88</v>
       </c>
       <c r="G245" s="28">
-        <v>17985.0</v>
+        <v>17916.8</v>
       </c>
       <c r="H245" s="28">
-        <v>-1929.4</v>
+        <v>-1997.6</v>
       </c>
       <c r="I245" s="29">
-        <v>-0.0969</v>
+        <v>-0.1003</v>
       </c>
       <c r="J245" s="1" t="s">
         <v>26</v>
@@ -11351,16 +11351,16 @@
         <v>53805.3</v>
       </c>
       <c r="F246" s="28">
-        <v>1331.8</v>
+        <v>1327.1</v>
       </c>
       <c r="G246" s="28">
-        <v>47944.8</v>
+        <v>47775.6</v>
       </c>
       <c r="H246" s="28">
-        <v>-5860.5</v>
+        <v>-6029.7</v>
       </c>
       <c r="I246" s="29">
-        <v>-0.1089</v>
+        <v>-0.1121</v>
       </c>
       <c r="J246" s="1" t="s">
         <v>26</v>
@@ -11597,16 +11597,16 @@
         <v>19912.2</v>
       </c>
       <c r="F252" s="28">
-        <v>111.83</v>
+        <v>111.85</v>
       </c>
       <c r="G252" s="28">
-        <v>23484.3</v>
+        <v>23488.5</v>
       </c>
       <c r="H252" s="28">
-        <v>3572.1</v>
+        <v>3576.3</v>
       </c>
       <c r="I252" s="29">
-        <v>0.1794</v>
+        <v>0.1796</v>
       </c>
       <c r="J252" s="1" t="s">
         <v>26</v>
@@ -11638,16 +11638,16 @@
         <v>26314.4</v>
       </c>
       <c r="F253" s="28">
-        <v>2020.7</v>
+        <v>2021.9</v>
       </c>
       <c r="G253" s="28">
-        <v>28289.8</v>
+        <v>28306.6</v>
       </c>
       <c r="H253" s="28">
-        <v>1975.4</v>
+        <v>1992.2</v>
       </c>
       <c r="I253" s="29">
-        <v>0.0751</v>
+        <v>0.0757</v>
       </c>
       <c r="J253" s="1" t="s">
         <v>26</v>
@@ -11720,16 +11720,16 @@
         <v>39331.9</v>
       </c>
       <c r="F255" s="28">
-        <v>4338.0</v>
+        <v>4363.55</v>
       </c>
       <c r="G255" s="28">
-        <v>39042.0</v>
+        <v>39271.95</v>
       </c>
       <c r="H255" s="28">
-        <v>-289.9</v>
+        <v>-59.95</v>
       </c>
       <c r="I255" s="29">
-        <v>-0.0074</v>
+        <v>-0.0015</v>
       </c>
       <c r="J255" s="1" t="s">
         <v>26</v>
@@ -11761,16 +11761,16 @@
         <v>9990.4</v>
       </c>
       <c r="F256" s="28">
-        <v>770.0</v>
+        <v>769.15</v>
       </c>
       <c r="G256" s="28">
-        <v>10780.0</v>
+        <v>10768.1</v>
       </c>
       <c r="H256" s="28">
-        <v>789.6</v>
+        <v>777.7</v>
       </c>
       <c r="I256" s="29">
-        <v>0.079</v>
+        <v>0.0778</v>
       </c>
       <c r="J256" s="1" t="s">
         <v>26</v>
@@ -12007,16 +12007,16 @@
         <v>99474.25</v>
       </c>
       <c r="F262" s="28">
-        <v>638.6</v>
+        <v>633.4</v>
       </c>
       <c r="G262" s="28">
-        <v>104730.4</v>
+        <v>103877.6</v>
       </c>
       <c r="H262" s="28">
-        <v>5256.15</v>
+        <v>4403.35</v>
       </c>
       <c r="I262" s="29">
-        <v>0.0528</v>
+        <v>0.0443</v>
       </c>
       <c r="J262" s="1" t="s">
         <v>26</v>
@@ -12048,16 +12048,16 @@
         <v>9958.75</v>
       </c>
       <c r="F263" s="28">
-        <v>303.25</v>
+        <v>303.3</v>
       </c>
       <c r="G263" s="28">
-        <v>9400.75</v>
+        <v>9402.3</v>
       </c>
       <c r="H263" s="28">
-        <v>-558.0</v>
+        <v>-556.45</v>
       </c>
       <c r="I263" s="29">
-        <v>-0.056</v>
+        <v>-0.0559</v>
       </c>
       <c r="J263" s="1" t="s">
         <v>26</v>
@@ -12212,16 +12212,16 @@
         <v>9662.0</v>
       </c>
       <c r="F267" s="28">
-        <v>1971.95</v>
+        <v>1960.15</v>
       </c>
       <c r="G267" s="28">
-        <v>9859.75</v>
+        <v>9800.75</v>
       </c>
       <c r="H267" s="28">
-        <v>197.75</v>
+        <v>138.75</v>
       </c>
       <c r="I267" s="29">
-        <v>0.0205</v>
+        <v>0.0144</v>
       </c>
       <c r="J267" s="1" t="s">
         <v>26</v>
@@ -12294,16 +12294,16 @@
         <v>99969.41</v>
       </c>
       <c r="F269" s="28">
-        <v>70.2</v>
+        <v>70.09</v>
       </c>
       <c r="G269" s="28">
-        <v>94208.4</v>
+        <v>94060.78</v>
       </c>
       <c r="H269" s="28">
-        <v>-5761.01</v>
+        <v>-5908.63</v>
       </c>
       <c r="I269" s="29">
-        <v>-0.0576</v>
+        <v>-0.0591</v>
       </c>
       <c r="J269" s="1" t="s">
         <v>26</v>
@@ -12458,16 +12458,16 @@
         <v>59668.55</v>
       </c>
       <c r="F273" s="28">
-        <v>612.0</v>
+        <v>612.25</v>
       </c>
       <c r="G273" s="28">
-        <v>63648.0</v>
+        <v>63674.0</v>
       </c>
       <c r="H273" s="28">
-        <v>3979.45</v>
+        <v>4005.45</v>
       </c>
       <c r="I273" s="29">
-        <v>0.0667</v>
+        <v>0.0671</v>
       </c>
       <c r="J273" s="1" t="s">
         <v>26</v>
@@ -12531,37 +12531,37 @@
         <v>193</v>
       </c>
       <c r="C275" s="27">
-        <v>3272.077</v>
+        <v>11266.534</v>
       </c>
       <c r="D275" s="28">
-        <v>30.56</v>
+        <v>22.19</v>
       </c>
       <c r="E275" s="28">
-        <v>99995.0</v>
+        <v>249987.49</v>
       </c>
       <c r="F275" s="28">
-        <v>30.58</v>
+        <v>22.22</v>
       </c>
       <c r="G275" s="28">
-        <v>100072.88</v>
+        <v>250314.22</v>
       </c>
       <c r="H275" s="28">
-        <v>77.88</v>
+        <v>326.73</v>
       </c>
       <c r="I275" s="29">
-        <v>8.0E-4</v>
+        <v>0.0013</v>
       </c>
       <c r="J275" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K275" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L275" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M275" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="276">
@@ -12569,40 +12569,40 @@
         <v>185</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="C276" s="27">
-        <v>11266.534</v>
+        <v>17353.013</v>
       </c>
       <c r="D276" s="28">
-        <v>22.19</v>
+        <v>14.41</v>
       </c>
       <c r="E276" s="28">
-        <v>249987.49</v>
+        <v>249987.51</v>
       </c>
       <c r="F276" s="28">
-        <v>22.21</v>
+        <v>14.43</v>
       </c>
       <c r="G276" s="28">
-        <v>250198.17</v>
+        <v>250403.98</v>
       </c>
       <c r="H276" s="28">
-        <v>210.68</v>
+        <v>416.47</v>
       </c>
       <c r="I276" s="29">
-        <v>8.0E-4</v>
+        <v>0.0017</v>
       </c>
       <c r="J276" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K276" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L276" s="1" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="M276" s="1" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="277">
@@ -12610,40 +12610,40 @@
         <v>185</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="C277" s="27">
-        <v>17353.013</v>
+        <v>2713.804</v>
       </c>
       <c r="D277" s="28">
-        <v>14.41</v>
+        <v>36.85</v>
       </c>
       <c r="E277" s="28">
-        <v>249987.51</v>
+        <v>99994.99</v>
       </c>
       <c r="F277" s="28">
-        <v>14.42</v>
+        <v>36.89</v>
       </c>
       <c r="G277" s="28">
-        <v>250230.45</v>
+        <v>100124.98</v>
       </c>
       <c r="H277" s="28">
-        <v>242.94</v>
+        <v>129.99</v>
       </c>
       <c r="I277" s="29">
-        <v>0.001</v>
+        <v>0.0013</v>
       </c>
       <c r="J277" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K277" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L277" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="M277" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="278">
@@ -12654,37 +12654,37 @@
         <v>195</v>
       </c>
       <c r="C278" s="27">
-        <v>2713.804</v>
+        <v>3272.077</v>
       </c>
       <c r="D278" s="28">
-        <v>36.85</v>
+        <v>30.56</v>
       </c>
       <c r="E278" s="28">
-        <v>99994.99</v>
+        <v>99995.0</v>
       </c>
       <c r="F278" s="28">
-        <v>36.88</v>
+        <v>30.6</v>
       </c>
       <c r="G278" s="28">
-        <v>100087.53</v>
+        <v>100123.27</v>
       </c>
       <c r="H278" s="28">
-        <v>92.54</v>
+        <v>128.27</v>
       </c>
       <c r="I278" s="29">
-        <v>9.0E-4</v>
+        <v>0.0013</v>
       </c>
       <c r="J278" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K278" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L278" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M278" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="279">
@@ -12704,16 +12704,16 @@
         <v>567.98</v>
       </c>
       <c r="F279" s="28">
-        <v>405.05</v>
+        <v>405.25</v>
       </c>
       <c r="G279" s="28">
-        <v>810.1</v>
+        <v>810.5</v>
       </c>
       <c r="H279" s="28">
-        <v>242.12</v>
+        <v>242.52</v>
       </c>
       <c r="I279" s="29">
-        <v>0.4263</v>
+        <v>0.427</v>
       </c>
       <c r="J279" s="1" t="s">
         <v>26</v>
@@ -12745,16 +12745,16 @@
         <v>3650.0</v>
       </c>
       <c r="F280" s="28">
-        <v>377.05</v>
+        <v>374.85</v>
       </c>
       <c r="G280" s="28">
-        <v>3770.5</v>
+        <v>3748.5</v>
       </c>
       <c r="H280" s="28">
-        <v>120.5</v>
+        <v>98.5</v>
       </c>
       <c r="I280" s="29">
-        <v>0.033</v>
+        <v>0.027</v>
       </c>
       <c r="J280" s="1" t="s">
         <v>26</v>
@@ -12786,16 +12786,16 @@
         <v>783.6</v>
       </c>
       <c r="F281" s="28">
-        <v>403.55</v>
+        <v>403.65</v>
       </c>
       <c r="G281" s="28">
-        <v>807.1</v>
+        <v>807.3</v>
       </c>
       <c r="H281" s="28">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="I281" s="29">
-        <v>0.03</v>
+        <v>0.0302</v>
       </c>
       <c r="J281" s="1" t="s">
         <v>26</v>
@@ -12827,16 +12827,16 @@
         <v>7244.8</v>
       </c>
       <c r="F282" s="28">
-        <v>538.3</v>
+        <v>538.65</v>
       </c>
       <c r="G282" s="28">
-        <v>8612.8</v>
+        <v>8618.4</v>
       </c>
       <c r="H282" s="28">
-        <v>1368.0</v>
+        <v>1373.6</v>
       </c>
       <c r="I282" s="29">
-        <v>0.1888</v>
+        <v>0.1896</v>
       </c>
       <c r="J282" s="1" t="s">
         <v>26</v>
@@ -12950,16 +12950,16 @@
         <v>11628.6</v>
       </c>
       <c r="F285" s="28">
-        <v>4338.0</v>
+        <v>4363.55</v>
       </c>
       <c r="G285" s="28">
-        <v>13014.0</v>
+        <v>13090.65</v>
       </c>
       <c r="H285" s="28">
-        <v>1385.4</v>
+        <v>1462.05</v>
       </c>
       <c r="I285" s="29">
-        <v>0.1191</v>
+        <v>0.1257</v>
       </c>
       <c r="J285" s="1" t="s">
         <v>26</v>
@@ -13114,16 +13114,16 @@
         <v>10923.0</v>
       </c>
       <c r="F289" s="28">
-        <v>568.7</v>
+        <v>569.25</v>
       </c>
       <c r="G289" s="28">
-        <v>11374.0</v>
+        <v>11385.0</v>
       </c>
       <c r="H289" s="28">
-        <v>451.0</v>
+        <v>462.0</v>
       </c>
       <c r="I289" s="29">
-        <v>0.0413</v>
+        <v>0.0423</v>
       </c>
       <c r="J289" s="1" t="s">
         <v>26</v>
@@ -13196,16 +13196,16 @@
         <v>12124.6</v>
       </c>
       <c r="F291" s="28">
-        <v>3138.4</v>
+        <v>3142.0</v>
       </c>
       <c r="G291" s="28">
-        <v>15692.0</v>
+        <v>15710.0</v>
       </c>
       <c r="H291" s="28">
-        <v>3567.4</v>
+        <v>3585.4</v>
       </c>
       <c r="I291" s="29">
-        <v>0.2942</v>
+        <v>0.2957</v>
       </c>
       <c r="J291" s="1" t="s">
         <v>26</v>
@@ -13401,16 +13401,16 @@
         <v>4591.2</v>
       </c>
       <c r="F296" s="28">
-        <v>612.0</v>
+        <v>612.25</v>
       </c>
       <c r="G296" s="28">
-        <v>4896.0</v>
+        <v>4898.0</v>
       </c>
       <c r="H296" s="28">
-        <v>304.8</v>
+        <v>306.8</v>
       </c>
       <c r="I296" s="29">
-        <v>0.0664</v>
+        <v>0.0668</v>
       </c>
       <c r="J296" s="1" t="s">
         <v>26</v>
@@ -13442,16 +13442,16 @@
         <v>3496.92</v>
       </c>
       <c r="F297" s="28">
-        <v>136.97</v>
+        <v>137.05</v>
       </c>
       <c r="G297" s="28">
-        <v>3287.28</v>
+        <v>3289.2</v>
       </c>
       <c r="H297" s="28">
-        <v>-209.64</v>
+        <v>-207.72</v>
       </c>
       <c r="I297" s="29">
-        <v>-0.0599</v>
+        <v>-0.0594</v>
       </c>
       <c r="J297" s="1" t="s">
         <v>26</v>
@@ -16264,7 +16264,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>15</v>
@@ -16287,7 +16287,7 @@
         <v>15</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>17</v>
@@ -16298,13 +16298,13 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>17</v>
@@ -16315,13 +16315,13 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>17</v>
@@ -16392,19 +16392,19 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>198</v>
@@ -16412,19 +16412,19 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>198</v>
@@ -16432,19 +16432,19 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>198</v>
@@ -17458,68 +17458,68 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="B91" s="30">
-        <v>20.0</v>
+        <v>298.0</v>
       </c>
       <c r="C91" s="30">
-        <v>1040.96</v>
+        <v>41.79</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="B92" s="30">
-        <v>298.0</v>
+        <v>20.0</v>
       </c>
       <c r="C92" s="30">
-        <v>41.79</v>
+        <v>1040.96</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>25</v>
+        <v>188</v>
       </c>
       <c r="B93" s="30">
-        <v>51.0</v>
+        <v>32.0</v>
       </c>
       <c r="C93" s="30">
-        <v>494.56</v>
+        <v>934.45</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="B94" s="30">
-        <v>32.0</v>
+        <v>15.0</v>
       </c>
       <c r="C94" s="30">
-        <v>934.45</v>
+        <v>1526.68</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="s">
-        <v>159</v>
+        <v>58</v>
       </c>
       <c r="B95" s="30">
-        <v>15.0</v>
+        <v>66.0</v>
       </c>
       <c r="C95" s="30">
-        <v>1526.68</v>
+        <v>387.23</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="B96" s="30">
-        <v>66.0</v>
+        <v>51.0</v>
       </c>
       <c r="C96" s="30">
-        <v>387.23</v>
+        <v>494.56</v>
       </c>
     </row>
     <row r="97">
@@ -17623,16 +17623,16 @@
         <v>97204.68</v>
       </c>
       <c r="C2" s="28">
-        <v>200702.27</v>
+        <v>200801.38</v>
       </c>
       <c r="D2" s="28">
-        <v>103497.59</v>
+        <v>103596.69</v>
       </c>
       <c r="E2" s="29">
-        <v>1.0647</v>
+        <v>1.0658</v>
       </c>
       <c r="F2" s="29">
-        <v>0.0523</v>
+        <v>0.0524</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>54</v>
@@ -17701,13 +17701,13 @@
         <v>51524.95</v>
       </c>
       <c r="C5" s="28">
-        <v>97290.4</v>
+        <v>97402.0</v>
       </c>
       <c r="D5" s="28">
-        <v>45765.45</v>
+        <v>45877.05</v>
       </c>
       <c r="E5" s="29">
-        <v>0.8882</v>
+        <v>0.8904</v>
       </c>
       <c r="F5" s="29">
         <v>0.0254</v>
@@ -17727,13 +17727,13 @@
         <v>79870.22</v>
       </c>
       <c r="C6" s="28">
-        <v>91241.85</v>
+        <v>91301.18</v>
       </c>
       <c r="D6" s="28">
-        <v>11371.63</v>
+        <v>11430.95</v>
       </c>
       <c r="E6" s="29">
-        <v>0.1424</v>
+        <v>0.1431</v>
       </c>
       <c r="F6" s="29">
         <v>0.0238</v>
@@ -17779,13 +17779,13 @@
         <v>83125.85</v>
       </c>
       <c r="C8" s="28">
-        <v>87822.0</v>
+        <v>87857.88</v>
       </c>
       <c r="D8" s="28">
-        <v>4696.15</v>
+        <v>4732.03</v>
       </c>
       <c r="E8" s="29">
-        <v>0.0565</v>
+        <v>0.0569</v>
       </c>
       <c r="F8" s="29">
         <v>0.0229</v>
@@ -17857,13 +17857,13 @@
         <v>53808.6</v>
       </c>
       <c r="C11" s="28">
-        <v>83213.73</v>
+        <v>83257.3</v>
       </c>
       <c r="D11" s="28">
-        <v>29405.13</v>
+        <v>29448.7</v>
       </c>
       <c r="E11" s="29">
-        <v>0.5465</v>
+        <v>0.5473</v>
       </c>
       <c r="F11" s="29">
         <v>0.0217</v>
@@ -17909,16 +17909,16 @@
         <v>77945.85</v>
       </c>
       <c r="C13" s="28">
-        <v>78084.0</v>
+        <v>78543.9</v>
       </c>
       <c r="D13" s="28">
-        <v>138.15</v>
+        <v>598.05</v>
       </c>
       <c r="E13" s="29">
-        <v>0.0018</v>
+        <v>0.0077</v>
       </c>
       <c r="F13" s="29">
-        <v>0.0204</v>
+        <v>0.0205</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>54</v>
@@ -18039,16 +18039,16 @@
         <v>64643.95</v>
       </c>
       <c r="C18" s="28">
-        <v>65137.2</v>
+        <v>64606.8</v>
       </c>
       <c r="D18" s="28">
-        <v>493.25</v>
+        <v>-37.15</v>
       </c>
       <c r="E18" s="29">
-        <v>0.0076</v>
+        <v>-6.0E-4</v>
       </c>
       <c r="F18" s="29">
-        <v>0.017</v>
+        <v>0.0169</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>17</v>
@@ -18091,13 +18091,13 @@
         <v>57276.82</v>
       </c>
       <c r="C20" s="28">
-        <v>60953.25</v>
+        <v>60963.3</v>
       </c>
       <c r="D20" s="28">
-        <v>3676.43</v>
+        <v>3686.48</v>
       </c>
       <c r="E20" s="29">
-        <v>0.0642</v>
+        <v>0.0644</v>
       </c>
       <c r="F20" s="29">
         <v>0.0159</v>
@@ -18247,13 +18247,13 @@
         <v>49573.2</v>
       </c>
       <c r="C26" s="28">
-        <v>50517.5</v>
+        <v>50547.5</v>
       </c>
       <c r="D26" s="28">
-        <v>944.3</v>
+        <v>974.3</v>
       </c>
       <c r="E26" s="29">
-        <v>0.019</v>
+        <v>0.0197</v>
       </c>
       <c r="F26" s="29">
         <v>0.0132</v>
@@ -18325,13 +18325,13 @@
         <v>49984.7</v>
       </c>
       <c r="C29" s="28">
-        <v>47104.2</v>
+        <v>47030.39</v>
       </c>
       <c r="D29" s="28">
-        <v>-2880.5</v>
+        <v>-2954.31</v>
       </c>
       <c r="E29" s="29">
-        <v>-0.0576</v>
+        <v>-0.0591</v>
       </c>
       <c r="F29" s="29">
         <v>0.0123</v>
@@ -18351,13 +18351,13 @@
         <v>31155.92</v>
       </c>
       <c r="C30" s="28">
-        <v>46073.1</v>
+        <v>46140.95</v>
       </c>
       <c r="D30" s="28">
-        <v>14917.18</v>
+        <v>14985.03</v>
       </c>
       <c r="E30" s="29">
-        <v>0.4788</v>
+        <v>0.481</v>
       </c>
       <c r="F30" s="29">
         <v>0.012</v>
@@ -18377,16 +18377,16 @@
         <v>49132.65</v>
       </c>
       <c r="C31" s="28">
-        <v>45947.1</v>
+        <v>45784.95</v>
       </c>
       <c r="D31" s="28">
-        <v>-3185.55</v>
+        <v>-3347.7</v>
       </c>
       <c r="E31" s="29">
-        <v>-0.0648</v>
+        <v>-0.0681</v>
       </c>
       <c r="F31" s="29">
-        <v>0.012</v>
+        <v>0.0119</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>17</v>
@@ -18455,13 +18455,13 @@
         <v>28030.2</v>
       </c>
       <c r="C34" s="28">
-        <v>40848.45</v>
+        <v>40863.75</v>
       </c>
       <c r="D34" s="28">
-        <v>12818.25</v>
+        <v>12833.55</v>
       </c>
       <c r="E34" s="29">
-        <v>0.4573</v>
+        <v>0.4578</v>
       </c>
       <c r="F34" s="29">
         <v>0.0107</v>
@@ -18533,13 +18533,13 @@
         <v>34377.15</v>
       </c>
       <c r="C37" s="28">
-        <v>40424.97</v>
+        <v>40183.08</v>
       </c>
       <c r="D37" s="28">
-        <v>6047.83</v>
+        <v>5805.93</v>
       </c>
       <c r="E37" s="29">
-        <v>0.1759</v>
+        <v>0.1689</v>
       </c>
       <c r="F37" s="29">
         <v>0.0105</v>
@@ -18559,13 +18559,13 @@
         <v>14547.5</v>
       </c>
       <c r="C38" s="28">
-        <v>38007.5</v>
+        <v>38025.0</v>
       </c>
       <c r="D38" s="28">
-        <v>23460.0</v>
+        <v>23477.5</v>
       </c>
       <c r="E38" s="29">
-        <v>1.6126</v>
+        <v>1.6139</v>
       </c>
       <c r="F38" s="29">
         <v>0.0099</v>
@@ -18611,13 +18611,13 @@
         <v>21235.27</v>
       </c>
       <c r="C40" s="28">
-        <v>37873.65</v>
+        <v>37793.62</v>
       </c>
       <c r="D40" s="28">
-        <v>16638.38</v>
+        <v>16558.35</v>
       </c>
       <c r="E40" s="29">
-        <v>0.7835</v>
+        <v>0.7798</v>
       </c>
       <c r="F40" s="29">
         <v>0.0099</v>
@@ -18741,13 +18741,13 @@
         <v>37933.62</v>
       </c>
       <c r="C45" s="28">
-        <v>34576.25</v>
+        <v>34475.47</v>
       </c>
       <c r="D45" s="28">
-        <v>-3357.37</v>
+        <v>-3458.15</v>
       </c>
       <c r="E45" s="29">
-        <v>-0.0885</v>
+        <v>-0.0912</v>
       </c>
       <c r="F45" s="29">
         <v>0.009</v>
@@ -18767,13 +18767,13 @@
         <v>29401.45</v>
       </c>
       <c r="C46" s="28">
-        <v>32700.25</v>
+        <v>32731.88</v>
       </c>
       <c r="D46" s="28">
-        <v>3298.8</v>
+        <v>3330.43</v>
       </c>
       <c r="E46" s="29">
-        <v>0.1122</v>
+        <v>0.1133</v>
       </c>
       <c r="F46" s="29">
         <v>0.0085</v>
@@ -18793,13 +18793,13 @@
         <v>33603.95</v>
       </c>
       <c r="C47" s="28">
-        <v>32149.1</v>
+        <v>32155.0</v>
       </c>
       <c r="D47" s="28">
-        <v>-1454.85</v>
+        <v>-1448.95</v>
       </c>
       <c r="E47" s="29">
-        <v>-0.0433</v>
+        <v>-0.0431</v>
       </c>
       <c r="F47" s="29">
         <v>0.0084</v>
@@ -18819,13 +18819,13 @@
         <v>15534.15</v>
       </c>
       <c r="C48" s="28">
-        <v>30233.3</v>
+        <v>30254.8</v>
       </c>
       <c r="D48" s="28">
-        <v>14699.15</v>
+        <v>14720.65</v>
       </c>
       <c r="E48" s="29">
-        <v>0.9462</v>
+        <v>0.9476</v>
       </c>
       <c r="F48" s="29">
         <v>0.0079</v>
@@ -18923,13 +18923,13 @@
         <v>26249.6</v>
       </c>
       <c r="C52" s="28">
-        <v>27336.12</v>
+        <v>27176.62</v>
       </c>
       <c r="D52" s="28">
-        <v>1086.53</v>
+        <v>927.03</v>
       </c>
       <c r="E52" s="29">
-        <v>0.0414</v>
+        <v>0.0353</v>
       </c>
       <c r="F52" s="29">
         <v>0.0071</v>
@@ -19218,7 +19218,7 @@
         <v>0.117</v>
       </c>
       <c r="F63" s="29">
-        <v>0.0053</v>
+        <v>0.0054</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>17</v>
@@ -19339,13 +19339,13 @@
         <v>14843.12</v>
       </c>
       <c r="C68" s="28">
-        <v>17887.5</v>
+        <v>18007.88</v>
       </c>
       <c r="D68" s="28">
-        <v>3044.38</v>
+        <v>3164.75</v>
       </c>
       <c r="E68" s="29">
-        <v>0.2051</v>
+        <v>0.2132</v>
       </c>
       <c r="F68" s="29">
         <v>0.0047</v>
@@ -19443,13 +19443,13 @@
         <v>14918.62</v>
       </c>
       <c r="C72" s="28">
-        <v>17165.9</v>
+        <v>17168.97</v>
       </c>
       <c r="D72" s="28">
-        <v>2247.28</v>
+        <v>2250.35</v>
       </c>
       <c r="E72" s="29">
-        <v>0.1506</v>
+        <v>0.1508</v>
       </c>
       <c r="F72" s="29">
         <v>0.0045</v>
@@ -19469,16 +19469,16 @@
         <v>16696.13</v>
       </c>
       <c r="C73" s="28">
-        <v>17052.76</v>
+        <v>17062.73</v>
       </c>
       <c r="D73" s="28">
-        <v>356.63</v>
+        <v>366.59</v>
       </c>
       <c r="E73" s="29">
-        <v>0.0214</v>
+        <v>0.022</v>
       </c>
       <c r="F73" s="29">
-        <v>0.0044</v>
+        <v>0.0045</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>17</v>
@@ -19573,13 +19573,13 @@
         <v>10409.6</v>
       </c>
       <c r="C77" s="28">
-        <v>14159.0</v>
+        <v>14142.0</v>
       </c>
       <c r="D77" s="28">
-        <v>3749.4</v>
+        <v>3732.4</v>
       </c>
       <c r="E77" s="29">
-        <v>0.3602</v>
+        <v>0.3586</v>
       </c>
       <c r="F77" s="29">
         <v>0.0037</v>
@@ -19593,22 +19593,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>25</v>
+        <v>188</v>
       </c>
       <c r="B78" s="28">
-        <v>12611.3</v>
+        <v>14951.2</v>
       </c>
       <c r="C78" s="28">
-        <v>13924.27</v>
+        <v>13460.0</v>
       </c>
       <c r="D78" s="28">
-        <v>1312.98</v>
+        <v>-1491.2</v>
       </c>
       <c r="E78" s="29">
-        <v>0.1041</v>
+        <v>-0.0997</v>
       </c>
       <c r="F78" s="29">
-        <v>0.0036</v>
+        <v>0.0035</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>17</v>
@@ -19619,19 +19619,19 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="B79" s="28">
-        <v>14951.2</v>
+        <v>11450.1</v>
       </c>
       <c r="C79" s="28">
-        <v>13460.0</v>
+        <v>13365.75</v>
       </c>
       <c r="D79" s="28">
-        <v>-1491.2</v>
+        <v>1915.65</v>
       </c>
       <c r="E79" s="29">
-        <v>-0.0997</v>
+        <v>0.1673</v>
       </c>
       <c r="F79" s="29">
         <v>0.0035</v>
@@ -19645,19 +19645,19 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>159</v>
+        <v>58</v>
       </c>
       <c r="B80" s="28">
-        <v>11450.1</v>
+        <v>12778.72</v>
       </c>
       <c r="C80" s="28">
-        <v>13365.75</v>
+        <v>13320.45</v>
       </c>
       <c r="D80" s="28">
-        <v>1915.65</v>
+        <v>541.73</v>
       </c>
       <c r="E80" s="29">
-        <v>0.1673</v>
+        <v>0.0424</v>
       </c>
       <c r="F80" s="29">
         <v>0.0035</v>
@@ -19671,22 +19671,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="B81" s="28">
-        <v>12778.72</v>
+        <v>12611.3</v>
       </c>
       <c r="C81" s="28">
-        <v>13317.15</v>
+        <v>13223.02</v>
       </c>
       <c r="D81" s="28">
-        <v>538.43</v>
+        <v>611.73</v>
       </c>
       <c r="E81" s="29">
-        <v>0.0421</v>
+        <v>0.0485</v>
       </c>
       <c r="F81" s="29">
-        <v>0.0035</v>
+        <v>0.0034</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>17</v>
@@ -19729,13 +19729,13 @@
         <v>17016.17</v>
       </c>
       <c r="C83" s="28">
-        <v>12656.98</v>
+        <v>12659.92</v>
       </c>
       <c r="D83" s="28">
-        <v>-4359.2</v>
+        <v>-4356.25</v>
       </c>
       <c r="E83" s="29">
-        <v>-0.2562</v>
+        <v>-0.256</v>
       </c>
       <c r="F83" s="29">
         <v>0.0033</v>
@@ -19755,13 +19755,13 @@
         <v>12453.65</v>
       </c>
       <c r="C84" s="28">
-        <v>12588.25</v>
+        <v>12492.57</v>
       </c>
       <c r="D84" s="28">
-        <v>134.6</v>
+        <v>38.93</v>
       </c>
       <c r="E84" s="29">
-        <v>0.0108</v>
+        <v>0.0031</v>
       </c>
       <c r="F84" s="29">
         <v>0.0033</v>
@@ -19781,10 +19781,10 @@
         <v>6277.5</v>
       </c>
       <c r="C85" s="28">
-        <v>11857.5</v>
+        <v>11857.73</v>
       </c>
       <c r="D85" s="28">
-        <v>5580.0</v>
+        <v>5580.23</v>
       </c>
       <c r="E85" s="29">
         <v>0.8889</v>
@@ -20041,13 +20041,13 @@
         <v>13866.4</v>
       </c>
       <c r="C95" s="28">
-        <v>9109.15</v>
+        <v>9113.75</v>
       </c>
       <c r="D95" s="28">
-        <v>-4757.25</v>
+        <v>-4752.65</v>
       </c>
       <c r="E95" s="29">
-        <v>-0.3431</v>
+        <v>-0.3427</v>
       </c>
       <c r="F95" s="29">
         <v>0.0024</v>
@@ -20093,13 +20093,13 @@
         <v>9957.2</v>
       </c>
       <c r="C97" s="28">
-        <v>8992.5</v>
+        <v>8958.4</v>
       </c>
       <c r="D97" s="28">
-        <v>-964.7</v>
+        <v>-998.8</v>
       </c>
       <c r="E97" s="29">
-        <v>-0.0969</v>
+        <v>-0.1003</v>
       </c>
       <c r="F97" s="29">
         <v>0.0023</v>
@@ -20171,13 +20171,13 @@
         <v>7317.5</v>
       </c>
       <c r="C100" s="28">
-        <v>7572.5</v>
+        <v>7575.0</v>
       </c>
       <c r="D100" s="28">
-        <v>255.0</v>
+        <v>257.5</v>
       </c>
       <c r="E100" s="29">
-        <v>0.0348</v>
+        <v>0.0352</v>
       </c>
       <c r="F100" s="29">
         <v>0.002</v>
@@ -20249,13 +20249,13 @@
         <v>4995.2</v>
       </c>
       <c r="C103" s="28">
-        <v>5390.0</v>
+        <v>5384.05</v>
       </c>
       <c r="D103" s="28">
-        <v>394.8</v>
+        <v>388.85</v>
       </c>
       <c r="E103" s="29">
-        <v>0.079</v>
+        <v>0.0778</v>
       </c>
       <c r="F103" s="29">
         <v>0.0014</v>
@@ -20301,13 +20301,13 @@
         <v>5001.78</v>
       </c>
       <c r="C105" s="28">
-        <v>4736.0</v>
+        <v>4721.94</v>
       </c>
       <c r="D105" s="28">
-        <v>-265.78</v>
+        <v>-279.84</v>
       </c>
       <c r="E105" s="29">
-        <v>-0.0531</v>
+        <v>-0.0559</v>
       </c>
       <c r="F105" s="29">
         <v>0.0012</v>
@@ -20327,13 +20327,13 @@
         <v>4442.1</v>
       </c>
       <c r="C106" s="28">
-        <v>4179.5</v>
+        <v>4247.43</v>
       </c>
       <c r="D106" s="28">
-        <v>-262.6</v>
+        <v>-194.68</v>
       </c>
       <c r="E106" s="29">
-        <v>-0.0591</v>
+        <v>-0.0438</v>
       </c>
       <c r="F106" s="29">
         <v>0.0011</v>
@@ -20379,13 +20379,13 @@
         <v>405.83</v>
       </c>
       <c r="C108" s="28">
-        <v>316.55</v>
+        <v>316.75</v>
       </c>
       <c r="D108" s="28">
-        <v>-89.28</v>
+        <v>-89.08</v>
       </c>
       <c r="E108" s="29">
-        <v>-0.22</v>
+        <v>-0.2195</v>
       </c>
       <c r="F108" s="29">
         <v>1.0E-4</v>
@@ -20405,13 +20405,13 @@
         <v>222.45</v>
       </c>
       <c r="C109" s="28">
-        <v>398.1</v>
+        <v>398.15</v>
       </c>
       <c r="D109" s="28">
-        <v>175.65</v>
+        <v>175.7</v>
       </c>
       <c r="E109" s="29">
-        <v>0.7896</v>
+        <v>0.7898</v>
       </c>
       <c r="F109" s="29">
         <v>1.0E-4</v>
@@ -20496,19 +20496,19 @@
         <v>1942979.39</v>
       </c>
       <c r="E2" s="28">
-        <v>14325.0</v>
+        <v>14308.63</v>
       </c>
       <c r="F2" s="28">
-        <v>3440121.03</v>
+        <v>3437426.96</v>
       </c>
       <c r="G2" s="28">
-        <v>1497141.65</v>
+        <v>1494447.57</v>
       </c>
       <c r="H2" s="29">
-        <v>0.7705</v>
+        <v>0.7692</v>
       </c>
       <c r="I2" s="29">
-        <v>0.2056</v>
+        <v>0.2055</v>
       </c>
       <c r="J2" s="29" t="s">
         <v>23</v>
@@ -20584,19 +20584,19 @@
         <v>780857.5</v>
       </c>
       <c r="E4" s="28">
-        <v>14.42</v>
+        <v>14.43</v>
       </c>
       <c r="F4" s="28">
-        <v>830688.82</v>
+        <v>831264.88</v>
       </c>
       <c r="G4" s="28">
-        <v>49831.32</v>
+        <v>50407.38</v>
       </c>
       <c r="H4" s="29">
-        <v>0.0638</v>
+        <v>0.0646</v>
       </c>
       <c r="I4" s="29">
-        <v>0.0496</v>
+        <v>0.0497</v>
       </c>
       <c r="J4" s="29" t="s">
         <v>23</v>
@@ -20605,7 +20605,7 @@
         <v>15</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>17</v>
@@ -20672,16 +20672,16 @@
         <v>124501.8</v>
       </c>
       <c r="E6" s="28">
-        <v>1441.0</v>
+        <v>1441.7</v>
       </c>
       <c r="F6" s="28">
-        <v>416449.0</v>
+        <v>416651.3</v>
       </c>
       <c r="G6" s="28">
-        <v>291947.2</v>
+        <v>292149.5</v>
       </c>
       <c r="H6" s="29">
-        <v>2.3449</v>
+        <v>2.3465</v>
       </c>
       <c r="I6" s="29">
         <v>0.0249</v>
@@ -20716,13 +20716,13 @@
         <v>194409.37</v>
       </c>
       <c r="E7" s="28">
-        <v>405.05</v>
+        <v>405.25</v>
       </c>
       <c r="F7" s="28">
-        <v>401602.35</v>
+        <v>401602.75</v>
       </c>
       <c r="G7" s="28">
-        <v>207192.98</v>
+        <v>207193.38</v>
       </c>
       <c r="H7" s="29">
         <v>1.0658</v>
@@ -20731,7 +20731,7 @@
         <v>0.024</v>
       </c>
       <c r="J7" s="29">
-        <v>0.0344</v>
+        <v>0.0345</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>26</v>
@@ -20807,13 +20807,13 @@
         <v>670.75</v>
       </c>
       <c r="F9" s="28">
-        <v>271467.75</v>
+        <v>271653.75</v>
       </c>
       <c r="G9" s="28">
-        <v>44687.5</v>
+        <v>44873.5</v>
       </c>
       <c r="H9" s="29">
-        <v>0.1971</v>
+        <v>0.1979</v>
       </c>
       <c r="I9" s="29">
         <v>0.0162</v>
@@ -20880,7 +20880,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B11" s="27">
         <v>11266.534</v>
@@ -20892,16 +20892,16 @@
         <v>249987.49</v>
       </c>
       <c r="E11" s="28">
-        <v>22.21</v>
+        <v>22.22</v>
       </c>
       <c r="F11" s="28">
-        <v>250198.17</v>
+        <v>250314.22</v>
       </c>
       <c r="G11" s="28">
-        <v>210.68</v>
+        <v>326.73</v>
       </c>
       <c r="H11" s="29">
-        <v>8.0E-4</v>
+        <v>0.0013</v>
       </c>
       <c r="I11" s="29">
         <v>0.015</v>
@@ -20913,13 +20913,13 @@
         <v>22</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
@@ -20936,16 +20936,16 @@
         <v>103049.9</v>
       </c>
       <c r="E12" s="28">
-        <v>3138.4</v>
+        <v>3142.0</v>
       </c>
       <c r="F12" s="28">
-        <v>194580.8</v>
+        <v>194804.0</v>
       </c>
       <c r="G12" s="28">
-        <v>91530.9</v>
+        <v>91754.1</v>
       </c>
       <c r="H12" s="29">
-        <v>0.8882</v>
+        <v>0.8904</v>
       </c>
       <c r="I12" s="29">
         <v>0.0116</v>
@@ -21024,13 +21024,13 @@
         <v>159740.45</v>
       </c>
       <c r="E14" s="28">
-        <v>538.3</v>
+        <v>538.65</v>
       </c>
       <c r="F14" s="28">
-        <v>182483.7</v>
+        <v>182489.3</v>
       </c>
       <c r="G14" s="28">
-        <v>22743.25</v>
+        <v>22748.85</v>
       </c>
       <c r="H14" s="29">
         <v>0.1424</v>
@@ -21112,16 +21112,16 @@
         <v>166251.7</v>
       </c>
       <c r="E16" s="28">
-        <v>612.0</v>
+        <v>612.25</v>
       </c>
       <c r="F16" s="28">
-        <v>175644.0</v>
+        <v>175715.75</v>
       </c>
       <c r="G16" s="28">
-        <v>9392.3</v>
+        <v>9464.05</v>
       </c>
       <c r="H16" s="29">
-        <v>0.0565</v>
+        <v>0.0569</v>
       </c>
       <c r="I16" s="29">
         <v>0.0105</v>
@@ -21288,19 +21288,19 @@
         <v>107617.2</v>
       </c>
       <c r="E20" s="28">
-        <v>2005.15</v>
+        <v>2006.2</v>
       </c>
       <c r="F20" s="28">
-        <v>166427.45</v>
+        <v>166514.6</v>
       </c>
       <c r="G20" s="28">
-        <v>58810.25</v>
+        <v>58897.4</v>
       </c>
       <c r="H20" s="29">
-        <v>0.5465</v>
+        <v>0.5473</v>
       </c>
       <c r="I20" s="29">
-        <v>0.0099</v>
+        <v>0.01</v>
       </c>
       <c r="J20" s="29">
         <v>0.0143</v>
@@ -21376,22 +21376,22 @@
         <v>155891.7</v>
       </c>
       <c r="E22" s="28">
-        <v>4338.0</v>
+        <v>4363.55</v>
       </c>
       <c r="F22" s="28">
-        <v>156168.0</v>
+        <v>157087.8</v>
       </c>
       <c r="G22" s="28">
-        <v>276.3</v>
+        <v>1196.1</v>
       </c>
       <c r="H22" s="29">
-        <v>0.0018</v>
+        <v>0.0077</v>
       </c>
       <c r="I22" s="29">
-        <v>0.0093</v>
+        <v>0.0094</v>
       </c>
       <c r="J22" s="29">
-        <v>0.0134</v>
+        <v>0.0135</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>26</v>
@@ -21464,16 +21464,16 @@
         <v>51931.5</v>
       </c>
       <c r="E24" s="28">
-        <v>809.0</v>
+        <v>807.15</v>
       </c>
       <c r="F24" s="28">
-        <v>148047.0</v>
+        <v>147708.45</v>
       </c>
       <c r="G24" s="28">
-        <v>96115.5</v>
+        <v>95776.95</v>
       </c>
       <c r="H24" s="29">
-        <v>1.8508</v>
+        <v>1.8443</v>
       </c>
       <c r="I24" s="29">
         <v>0.0088</v>
@@ -21684,22 +21684,22 @@
         <v>129287.9</v>
       </c>
       <c r="E29" s="28">
-        <v>638.6</v>
+        <v>633.4</v>
       </c>
       <c r="F29" s="28">
-        <v>130274.4</v>
+        <v>129213.6</v>
       </c>
       <c r="G29" s="28">
-        <v>986.5</v>
+        <v>-74.3</v>
       </c>
       <c r="H29" s="29">
-        <v>0.0076</v>
+        <v>-6.0E-4</v>
       </c>
       <c r="I29" s="29">
-        <v>0.0078</v>
+        <v>0.0077</v>
       </c>
       <c r="J29" s="29">
-        <v>0.0112</v>
+        <v>0.0111</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>26</v>
@@ -21816,16 +21816,16 @@
         <v>114553.65</v>
       </c>
       <c r="E32" s="28">
-        <v>303.25</v>
+        <v>303.3</v>
       </c>
       <c r="F32" s="28">
-        <v>121906.5</v>
+        <v>121926.6</v>
       </c>
       <c r="G32" s="28">
-        <v>7352.85</v>
+        <v>7372.95</v>
       </c>
       <c r="H32" s="29">
-        <v>0.0642</v>
+        <v>0.0644</v>
       </c>
       <c r="I32" s="29">
         <v>0.0073</v>
@@ -21892,7 +21892,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B34" s="27">
         <v>953.1179999999999</v>
@@ -21904,16 +21904,16 @@
         <v>59997.0</v>
       </c>
       <c r="E34" s="28">
-        <v>86.46</v>
+        <v>171.42</v>
       </c>
       <c r="F34" s="28">
-        <v>119225.14</v>
+        <v>119084.19</v>
       </c>
       <c r="G34" s="28">
-        <v>59228.14</v>
+        <v>59087.2</v>
       </c>
       <c r="H34" s="29">
-        <v>0.9872</v>
+        <v>0.9848</v>
       </c>
       <c r="I34" s="29">
         <v>0.0071</v>
@@ -21925,7 +21925,7 @@
         <v>15</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>17</v>
@@ -22168,16 +22168,16 @@
         <v>99146.4</v>
       </c>
       <c r="E40" s="28">
-        <v>2020.7</v>
+        <v>2021.9</v>
       </c>
       <c r="F40" s="28">
-        <v>101035.0</v>
+        <v>101095.0</v>
       </c>
       <c r="G40" s="28">
-        <v>1888.6</v>
+        <v>1948.6</v>
       </c>
       <c r="H40" s="29">
-        <v>0.019</v>
+        <v>0.0197</v>
       </c>
       <c r="I40" s="29">
         <v>0.006</v>
@@ -22244,7 +22244,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B42" s="27">
         <v>2713.804</v>
@@ -22256,16 +22256,16 @@
         <v>99994.99</v>
       </c>
       <c r="E42" s="28">
-        <v>36.88</v>
+        <v>36.89</v>
       </c>
       <c r="F42" s="28">
-        <v>100087.53</v>
+        <v>100124.98</v>
       </c>
       <c r="G42" s="28">
-        <v>92.54</v>
+        <v>129.99</v>
       </c>
       <c r="H42" s="29">
-        <v>9.0E-4</v>
+        <v>0.0013</v>
       </c>
       <c r="I42" s="29">
         <v>0.006</v>
@@ -22277,18 +22277,18 @@
         <v>22</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B43" s="27">
         <v>3272.077</v>
@@ -22300,16 +22300,16 @@
         <v>99995.0</v>
       </c>
       <c r="E43" s="28">
-        <v>30.58</v>
+        <v>30.6</v>
       </c>
       <c r="F43" s="28">
-        <v>100072.88</v>
+        <v>100123.27</v>
       </c>
       <c r="G43" s="28">
-        <v>77.88</v>
+        <v>128.27</v>
       </c>
       <c r="H43" s="29">
-        <v>8.0E-4</v>
+        <v>0.0013</v>
       </c>
       <c r="I43" s="29">
         <v>0.006</v>
@@ -22321,13 +22321,13 @@
         <v>22</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44">
@@ -22432,16 +22432,16 @@
         <v>99969.41</v>
       </c>
       <c r="E46" s="28">
-        <v>70.2</v>
+        <v>70.09</v>
       </c>
       <c r="F46" s="28">
-        <v>94208.4</v>
+        <v>94060.78</v>
       </c>
       <c r="G46" s="28">
-        <v>-5761.01</v>
+        <v>-5908.63</v>
       </c>
       <c r="H46" s="29">
-        <v>-0.0576</v>
+        <v>-0.0591</v>
       </c>
       <c r="I46" s="29">
         <v>0.0056</v>
@@ -22476,16 +22476,16 @@
         <v>62311.85</v>
       </c>
       <c r="E47" s="28">
-        <v>1561.8</v>
+        <v>1564.1</v>
       </c>
       <c r="F47" s="28">
-        <v>92146.2</v>
+        <v>92281.9</v>
       </c>
       <c r="G47" s="28">
-        <v>29834.35</v>
+        <v>29970.05</v>
       </c>
       <c r="H47" s="29">
-        <v>0.4788</v>
+        <v>0.481</v>
       </c>
       <c r="I47" s="29">
         <v>0.0055</v>
@@ -22520,16 +22520,16 @@
         <v>98265.3</v>
       </c>
       <c r="E48" s="28">
-        <v>1331.8</v>
+        <v>1327.1</v>
       </c>
       <c r="F48" s="28">
-        <v>91894.2</v>
+        <v>91569.9</v>
       </c>
       <c r="G48" s="28">
-        <v>-6371.1</v>
+        <v>-6695.4</v>
       </c>
       <c r="H48" s="29">
-        <v>-0.0648</v>
+        <v>-0.0681</v>
       </c>
       <c r="I48" s="29">
         <v>0.0055</v>
@@ -22567,13 +22567,13 @@
         <v>173.88</v>
       </c>
       <c r="F49" s="28">
-        <v>90773.55</v>
+        <v>90765.36</v>
       </c>
       <c r="G49" s="28">
-        <v>11457.02</v>
+        <v>11448.83</v>
       </c>
       <c r="H49" s="29">
-        <v>0.1444</v>
+        <v>0.1443</v>
       </c>
       <c r="I49" s="29">
         <v>0.0054</v>
@@ -22696,16 +22696,16 @@
         <v>56060.4</v>
       </c>
       <c r="E52" s="28">
-        <v>1601.9</v>
+        <v>1602.5</v>
       </c>
       <c r="F52" s="28">
-        <v>81696.9</v>
+        <v>81727.5</v>
       </c>
       <c r="G52" s="28">
-        <v>25636.5</v>
+        <v>25667.1</v>
       </c>
       <c r="H52" s="29">
-        <v>0.4573</v>
+        <v>0.4578</v>
       </c>
       <c r="I52" s="29">
         <v>0.0049</v>
@@ -22743,13 +22743,13 @@
         <v>147.7</v>
       </c>
       <c r="F53" s="28">
-        <v>80716.2</v>
+        <v>80710.2</v>
       </c>
       <c r="G53" s="28">
-        <v>6507.93</v>
+        <v>6501.93</v>
       </c>
       <c r="H53" s="29">
-        <v>0.0877</v>
+        <v>0.0876</v>
       </c>
       <c r="I53" s="29">
         <v>0.0048</v>
@@ -22828,16 +22828,16 @@
         <v>68754.3</v>
       </c>
       <c r="E55" s="28">
-        <v>1971.95</v>
+        <v>1960.15</v>
       </c>
       <c r="F55" s="28">
-        <v>80347.75</v>
+        <v>80288.75</v>
       </c>
       <c r="G55" s="28">
-        <v>11593.45</v>
+        <v>11534.45</v>
       </c>
       <c r="H55" s="29">
-        <v>0.1686</v>
+        <v>0.1678</v>
       </c>
       <c r="I55" s="29">
         <v>0.0048</v>
@@ -22916,16 +22916,16 @@
         <v>29095.0</v>
       </c>
       <c r="E57" s="28">
-        <v>760.15</v>
+        <v>760.5</v>
       </c>
       <c r="F57" s="28">
-        <v>76015.0</v>
+        <v>76050.0</v>
       </c>
       <c r="G57" s="28">
-        <v>46920.0</v>
+        <v>46955.0</v>
       </c>
       <c r="H57" s="29">
-        <v>1.6126</v>
+        <v>1.6139</v>
       </c>
       <c r="I57" s="29">
         <v>0.0045</v>
@@ -23004,16 +23004,16 @@
         <v>42470.55</v>
       </c>
       <c r="E59" s="28">
-        <v>780.9</v>
+        <v>779.25</v>
       </c>
       <c r="F59" s="28">
-        <v>75608.7</v>
+        <v>75587.25</v>
       </c>
       <c r="G59" s="28">
-        <v>33138.15</v>
+        <v>33116.7</v>
       </c>
       <c r="H59" s="29">
-        <v>0.7803</v>
+        <v>0.7798</v>
       </c>
       <c r="I59" s="29">
         <v>0.0045</v>
@@ -23092,22 +23092,22 @@
         <v>66211.85</v>
       </c>
       <c r="E61" s="28">
-        <v>4284.55</v>
+        <v>4286.5</v>
       </c>
       <c r="F61" s="28">
-        <v>72837.35</v>
+        <v>72870.5</v>
       </c>
       <c r="G61" s="28">
-        <v>6625.5</v>
+        <v>6658.65</v>
       </c>
       <c r="H61" s="29">
-        <v>0.1001</v>
+        <v>0.1006</v>
       </c>
       <c r="I61" s="29">
         <v>0.0044</v>
       </c>
       <c r="J61" s="29">
-        <v>0.0062</v>
+        <v>0.0063</v>
       </c>
       <c r="K61" s="1" t="s">
         <v>15</v>
@@ -23268,16 +23268,16 @@
         <v>75867.25</v>
       </c>
       <c r="E65" s="28">
-        <v>497.5</v>
+        <v>496.05</v>
       </c>
       <c r="F65" s="28">
-        <v>69152.5</v>
+        <v>68950.95</v>
       </c>
       <c r="G65" s="28">
-        <v>-6714.75</v>
+        <v>-6916.3</v>
       </c>
       <c r="H65" s="29">
-        <v>-0.0885</v>
+        <v>-0.0912</v>
       </c>
       <c r="I65" s="29">
         <v>0.0041</v>
@@ -23312,16 +23312,16 @@
         <v>58802.9</v>
       </c>
       <c r="E66" s="28">
-        <v>568.7</v>
+        <v>569.25</v>
       </c>
       <c r="F66" s="28">
-        <v>65400.5</v>
+        <v>65463.75</v>
       </c>
       <c r="G66" s="28">
-        <v>6597.6</v>
+        <v>6660.85</v>
       </c>
       <c r="H66" s="29">
-        <v>0.1122</v>
+        <v>0.1133</v>
       </c>
       <c r="I66" s="29">
         <v>0.0039</v>
@@ -23356,16 +23356,16 @@
         <v>67207.9</v>
       </c>
       <c r="E67" s="28">
-        <v>1089.8</v>
+        <v>1090.0</v>
       </c>
       <c r="F67" s="28">
-        <v>64298.2</v>
+        <v>64310.0</v>
       </c>
       <c r="G67" s="28">
-        <v>-2909.7</v>
+        <v>-2897.9</v>
       </c>
       <c r="H67" s="29">
-        <v>-0.0433</v>
+        <v>-0.0431</v>
       </c>
       <c r="I67" s="29">
         <v>0.0038</v>
@@ -23488,16 +23488,16 @@
         <v>31068.3</v>
       </c>
       <c r="E70" s="28">
-        <v>1406.2</v>
+        <v>1407.2</v>
       </c>
       <c r="F70" s="28">
-        <v>60466.6</v>
+        <v>60509.6</v>
       </c>
       <c r="G70" s="28">
-        <v>29398.3</v>
+        <v>29441.3</v>
       </c>
       <c r="H70" s="29">
-        <v>0.9462</v>
+        <v>0.9476</v>
       </c>
       <c r="I70" s="29">
         <v>0.0036</v>
@@ -23664,16 +23664,16 @@
         <v>52499.2</v>
       </c>
       <c r="E74" s="28">
-        <v>377.05</v>
+        <v>374.85</v>
       </c>
       <c r="F74" s="28">
-        <v>54318.0</v>
+        <v>54211.5</v>
       </c>
       <c r="G74" s="28">
-        <v>1818.8</v>
+        <v>1712.3</v>
       </c>
       <c r="H74" s="29">
-        <v>0.0346</v>
+        <v>0.0326</v>
       </c>
       <c r="I74" s="29">
         <v>0.0032</v>
@@ -24104,13 +24104,13 @@
         <v>0.0</v>
       </c>
       <c r="E84" s="28">
-        <v>406.05</v>
+        <v>406.2</v>
       </c>
       <c r="F84" s="28">
-        <v>45477.6</v>
+        <v>45494.4</v>
       </c>
       <c r="G84" s="28">
-        <v>45477.6</v>
+        <v>45494.4</v>
       </c>
       <c r="H84" s="29">
         <v>0.0</v>
@@ -24412,19 +24412,19 @@
         <v>29686.25</v>
       </c>
       <c r="E91" s="28">
-        <v>795.0</v>
+        <v>800.35</v>
       </c>
       <c r="F91" s="28">
-        <v>35775.0</v>
+        <v>36015.75</v>
       </c>
       <c r="G91" s="28">
-        <v>6088.75</v>
+        <v>6329.5</v>
       </c>
       <c r="H91" s="29">
-        <v>0.2051</v>
+        <v>0.2132</v>
       </c>
       <c r="I91" s="29">
-        <v>0.0021</v>
+        <v>0.0022</v>
       </c>
       <c r="J91" s="29">
         <v>0.0031</v>
@@ -24459,13 +24459,13 @@
         <v>1069.2</v>
       </c>
       <c r="F92" s="28">
-        <v>35283.6</v>
+        <v>35294.8</v>
       </c>
       <c r="G92" s="28">
-        <v>-86.65</v>
+        <v>-75.45</v>
       </c>
       <c r="H92" s="29">
-        <v>-0.0024</v>
+        <v>-0.0021</v>
       </c>
       <c r="I92" s="29">
         <v>0.0021</v>
@@ -24588,16 +24588,16 @@
         <v>29837.24</v>
       </c>
       <c r="E95" s="28">
-        <v>111.83</v>
+        <v>111.85</v>
       </c>
       <c r="F95" s="28">
-        <v>34331.81</v>
+        <v>34337.95</v>
       </c>
       <c r="G95" s="28">
-        <v>4494.57</v>
+        <v>4500.71</v>
       </c>
       <c r="H95" s="29">
-        <v>0.1506</v>
+        <v>0.1508</v>
       </c>
       <c r="I95" s="29">
         <v>0.0021</v>
@@ -24632,16 +24632,16 @@
         <v>33392.27</v>
       </c>
       <c r="E96" s="28">
-        <v>136.97</v>
+        <v>137.05</v>
       </c>
       <c r="F96" s="28">
-        <v>34105.53</v>
+        <v>34125.45</v>
       </c>
       <c r="G96" s="28">
-        <v>713.26</v>
+        <v>733.18</v>
       </c>
       <c r="H96" s="29">
-        <v>0.0214</v>
+        <v>0.022</v>
       </c>
       <c r="I96" s="29">
         <v>0.002</v>
@@ -24796,28 +24796,28 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="B100" s="27">
-        <v>20.0</v>
+        <v>298.0</v>
       </c>
       <c r="C100" s="28">
-        <v>1040.96</v>
+        <v>41.79</v>
       </c>
       <c r="D100" s="28">
-        <v>20819.2</v>
+        <v>12454.04</v>
       </c>
       <c r="E100" s="28">
-        <v>1415.9</v>
+        <v>95.0</v>
       </c>
       <c r="F100" s="28">
-        <v>28318.0</v>
+        <v>28310.0</v>
       </c>
       <c r="G100" s="28">
-        <v>7498.8</v>
+        <v>15855.96</v>
       </c>
       <c r="H100" s="29">
-        <v>0.3602</v>
+        <v>1.2732</v>
       </c>
       <c r="I100" s="29">
         <v>0.0017</v>
@@ -24826,42 +24826,42 @@
         <v>0.0024</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="L100" s="1" t="s">
         <v>16</v>
       </c>
       <c r="M100" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="B101" s="27">
-        <v>298.0</v>
+        <v>20.0</v>
       </c>
       <c r="C101" s="28">
-        <v>41.79</v>
+        <v>1040.96</v>
       </c>
       <c r="D101" s="28">
-        <v>12454.04</v>
+        <v>20819.2</v>
       </c>
       <c r="E101" s="28">
-        <v>95.0</v>
+        <v>1414.2</v>
       </c>
       <c r="F101" s="28">
-        <v>28310.0</v>
+        <v>28284.0</v>
       </c>
       <c r="G101" s="28">
-        <v>15855.96</v>
+        <v>7464.8</v>
       </c>
       <c r="H101" s="29">
-        <v>1.2732</v>
+        <v>0.3586</v>
       </c>
       <c r="I101" s="29">
         <v>0.0017</v>
@@ -24870,48 +24870,48 @@
         <v>0.0024</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="L101" s="1" t="s">
         <v>16</v>
       </c>
       <c r="M101" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
-        <v>25</v>
+        <v>188</v>
       </c>
       <c r="B102" s="27">
-        <v>51.0</v>
+        <v>32.0</v>
       </c>
       <c r="C102" s="28">
-        <v>494.56</v>
+        <v>934.45</v>
       </c>
       <c r="D102" s="28">
-        <v>25222.6</v>
+        <v>29902.4</v>
       </c>
       <c r="E102" s="28">
-        <v>546.05</v>
+        <v>841.25</v>
       </c>
       <c r="F102" s="28">
-        <v>27848.55</v>
+        <v>26920.0</v>
       </c>
       <c r="G102" s="28">
-        <v>2625.95</v>
+        <v>-2982.4</v>
       </c>
       <c r="H102" s="29">
-        <v>0.1041</v>
+        <v>-0.0997</v>
       </c>
       <c r="I102" s="29">
-        <v>0.0017</v>
+        <v>0.0016</v>
       </c>
       <c r="J102" s="29">
-        <v>0.0024</v>
+        <v>0.0023</v>
       </c>
       <c r="K102" s="1" t="s">
         <v>26</v>
@@ -24928,28 +24928,28 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="B103" s="27">
-        <v>32.0</v>
+        <v>15.0</v>
       </c>
       <c r="C103" s="28">
-        <v>934.45</v>
+        <v>1526.68</v>
       </c>
       <c r="D103" s="28">
-        <v>29902.4</v>
+        <v>22900.2</v>
       </c>
       <c r="E103" s="28">
-        <v>841.25</v>
+        <v>1782.1</v>
       </c>
       <c r="F103" s="28">
-        <v>26920.0</v>
+        <v>26731.5</v>
       </c>
       <c r="G103" s="28">
-        <v>-2982.4</v>
+        <v>3831.3</v>
       </c>
       <c r="H103" s="29">
-        <v>-0.0997</v>
+        <v>0.1673</v>
       </c>
       <c r="I103" s="29">
         <v>0.0016</v>
@@ -24972,28 +24972,28 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="s">
-        <v>159</v>
+        <v>58</v>
       </c>
       <c r="B104" s="27">
-        <v>15.0</v>
+        <v>66.0</v>
       </c>
       <c r="C104" s="28">
-        <v>1526.68</v>
+        <v>387.23</v>
       </c>
       <c r="D104" s="28">
-        <v>22900.2</v>
+        <v>25557.45</v>
       </c>
       <c r="E104" s="28">
-        <v>1782.1</v>
+        <v>403.65</v>
       </c>
       <c r="F104" s="28">
-        <v>26731.5</v>
+        <v>26640.9</v>
       </c>
       <c r="G104" s="28">
-        <v>3831.3</v>
+        <v>1083.45</v>
       </c>
       <c r="H104" s="29">
-        <v>0.1673</v>
+        <v>0.0424</v>
       </c>
       <c r="I104" s="29">
         <v>0.0016</v>
@@ -25016,28 +25016,28 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="B105" s="27">
-        <v>66.0</v>
+        <v>51.0</v>
       </c>
       <c r="C105" s="28">
-        <v>387.23</v>
+        <v>494.56</v>
       </c>
       <c r="D105" s="28">
-        <v>25557.45</v>
+        <v>25222.6</v>
       </c>
       <c r="E105" s="28">
-        <v>403.55</v>
+        <v>518.55</v>
       </c>
       <c r="F105" s="28">
-        <v>26634.3</v>
+        <v>26446.05</v>
       </c>
       <c r="G105" s="28">
-        <v>1076.85</v>
+        <v>1223.45</v>
       </c>
       <c r="H105" s="29">
-        <v>0.0421</v>
+        <v>0.0485</v>
       </c>
       <c r="I105" s="29">
         <v>0.0016</v>
@@ -25116,13 +25116,13 @@
         <v>34032.35</v>
       </c>
       <c r="E107" s="28">
-        <v>429.05</v>
+        <v>429.15</v>
       </c>
       <c r="F107" s="28">
-        <v>25313.95</v>
+        <v>25314.05</v>
       </c>
       <c r="G107" s="28">
-        <v>-8718.4</v>
+        <v>-8718.3</v>
       </c>
       <c r="H107" s="29">
         <v>-0.2562</v>
@@ -25160,22 +25160,22 @@
         <v>24907.3</v>
       </c>
       <c r="E108" s="28">
-        <v>585.5</v>
+        <v>581.05</v>
       </c>
       <c r="F108" s="28">
-        <v>25176.5</v>
+        <v>24985.15</v>
       </c>
       <c r="G108" s="28">
-        <v>269.2</v>
+        <v>77.85</v>
       </c>
       <c r="H108" s="29">
-        <v>0.0108</v>
+        <v>0.0031</v>
       </c>
       <c r="I108" s="29">
         <v>0.0015</v>
       </c>
       <c r="J108" s="29">
-        <v>0.0022</v>
+        <v>0.0021</v>
       </c>
       <c r="K108" s="1" t="s">
         <v>26</v>
@@ -25204,13 +25204,13 @@
         <v>12555.0</v>
       </c>
       <c r="E109" s="28">
-        <v>2635.0</v>
+        <v>2635.05</v>
       </c>
       <c r="F109" s="28">
-        <v>23715.0</v>
+        <v>23715.45</v>
       </c>
       <c r="G109" s="28">
-        <v>11160.0</v>
+        <v>11160.45</v>
       </c>
       <c r="H109" s="29">
         <v>0.8889</v>
@@ -25424,16 +25424,16 @@
         <v>10673.0</v>
       </c>
       <c r="E114" s="28">
-        <v>4284.0</v>
+        <v>4290.55</v>
       </c>
       <c r="F114" s="28">
-        <v>21420.0</v>
+        <v>21452.75</v>
       </c>
       <c r="G114" s="28">
-        <v>10747.0</v>
+        <v>10779.75</v>
       </c>
       <c r="H114" s="29">
-        <v>1.0069</v>
+        <v>1.01</v>
       </c>
       <c r="I114" s="29">
         <v>0.0013</v>
@@ -25515,10 +25515,10 @@
         <v>300.55</v>
       </c>
       <c r="F116" s="28">
-        <v>20735.85</v>
+        <v>20737.95</v>
       </c>
       <c r="G116" s="28">
-        <v>-11211.4</v>
+        <v>-11209.3</v>
       </c>
       <c r="H116" s="29">
         <v>-0.3509</v>
@@ -25732,16 +25732,16 @@
         <v>27732.8</v>
       </c>
       <c r="E121" s="28">
-        <v>792.1</v>
+        <v>792.5</v>
       </c>
       <c r="F121" s="28">
-        <v>18218.3</v>
+        <v>18227.5</v>
       </c>
       <c r="G121" s="28">
-        <v>-9514.5</v>
+        <v>-9505.3</v>
       </c>
       <c r="H121" s="29">
-        <v>-0.3431</v>
+        <v>-0.3427</v>
       </c>
       <c r="I121" s="29">
         <v>0.0011</v>
@@ -25820,16 +25820,16 @@
         <v>19914.4</v>
       </c>
       <c r="E123" s="28">
-        <v>163.5</v>
+        <v>162.88</v>
       </c>
       <c r="F123" s="28">
-        <v>17985.0</v>
+        <v>17916.8</v>
       </c>
       <c r="G123" s="28">
-        <v>-1929.4</v>
+        <v>-1997.6</v>
       </c>
       <c r="H123" s="29">
-        <v>-0.0969</v>
+        <v>-0.1003</v>
       </c>
       <c r="I123" s="29">
         <v>0.0011</v>
@@ -25952,16 +25952,16 @@
         <v>14635.0</v>
       </c>
       <c r="E126" s="28">
-        <v>302.9</v>
+        <v>303.0</v>
       </c>
       <c r="F126" s="28">
-        <v>15145.0</v>
+        <v>15150.0</v>
       </c>
       <c r="G126" s="28">
-        <v>510.0</v>
+        <v>515.0</v>
       </c>
       <c r="H126" s="29">
-        <v>0.0348</v>
+        <v>0.0352</v>
       </c>
       <c r="I126" s="29">
         <v>9.0E-4</v>
@@ -26084,16 +26084,16 @@
         <v>9990.4</v>
       </c>
       <c r="E129" s="28">
-        <v>770.0</v>
+        <v>769.15</v>
       </c>
       <c r="F129" s="28">
-        <v>10780.0</v>
+        <v>10768.1</v>
       </c>
       <c r="G129" s="28">
-        <v>789.6</v>
+        <v>777.7</v>
       </c>
       <c r="H129" s="29">
-        <v>0.079</v>
+        <v>0.0778</v>
       </c>
       <c r="I129" s="29">
         <v>6.0E-4</v>
@@ -26216,16 +26216,16 @@
         <v>10003.56</v>
       </c>
       <c r="E132" s="28">
-        <v>64.0</v>
+        <v>63.81</v>
       </c>
       <c r="F132" s="28">
-        <v>9472.0</v>
+        <v>9443.88</v>
       </c>
       <c r="G132" s="28">
-        <v>-531.56</v>
+        <v>-559.68</v>
       </c>
       <c r="H132" s="29">
-        <v>-0.0531</v>
+        <v>-0.0559</v>
       </c>
       <c r="I132" s="29">
         <v>6.0E-4</v>
@@ -26304,16 +26304,16 @@
         <v>8884.2</v>
       </c>
       <c r="E134" s="28">
-        <v>128.6</v>
+        <v>130.69</v>
       </c>
       <c r="F134" s="28">
-        <v>8359.0</v>
+        <v>8494.85</v>
       </c>
       <c r="G134" s="28">
-        <v>-525.2</v>
+        <v>-389.35</v>
       </c>
       <c r="H134" s="29">
-        <v>-0.0591</v>
+        <v>-0.0438</v>
       </c>
       <c r="I134" s="29">
         <v>5.0E-4</v>
@@ -26348,16 +26348,16 @@
         <v>3464.5</v>
       </c>
       <c r="E135" s="28">
-        <v>1870.4</v>
+        <v>1871.6</v>
       </c>
       <c r="F135" s="28">
-        <v>5611.2</v>
+        <v>5614.8</v>
       </c>
       <c r="G135" s="28">
-        <v>2146.7</v>
+        <v>2150.3</v>
       </c>
       <c r="H135" s="29">
-        <v>0.6196</v>
+        <v>0.6207</v>
       </c>
       <c r="I135" s="29">
         <v>3.0E-4</v>
@@ -26392,16 +26392,16 @@
         <v>885.9</v>
       </c>
       <c r="E136" s="28">
-        <v>346.2</v>
+        <v>346.75</v>
       </c>
       <c r="F136" s="28">
-        <v>3808.2</v>
+        <v>3814.25</v>
       </c>
       <c r="G136" s="28">
-        <v>2922.3</v>
+        <v>2928.35</v>
       </c>
       <c r="H136" s="29">
-        <v>3.2987</v>
+        <v>3.3055</v>
       </c>
       <c r="I136" s="29">
         <v>2.0E-4</v>
@@ -26480,16 +26480,16 @@
         <v>415.9</v>
       </c>
       <c r="E138" s="28">
-        <v>1830.35</v>
+        <v>1831.3</v>
       </c>
       <c r="F138" s="28">
-        <v>1830.35</v>
+        <v>1831.3</v>
       </c>
       <c r="G138" s="28">
-        <v>1414.45</v>
+        <v>1415.4</v>
       </c>
       <c r="H138" s="29">
-        <v>3.4009</v>
+        <v>3.4032</v>
       </c>
       <c r="I138" s="29">
         <v>1.0E-4</v>
@@ -26524,16 +26524,16 @@
         <v>588.9</v>
       </c>
       <c r="E139" s="28">
-        <v>815.0</v>
+        <v>813.55</v>
       </c>
       <c r="F139" s="28">
-        <v>815.0</v>
+        <v>813.55</v>
       </c>
       <c r="G139" s="28">
-        <v>226.1</v>
+        <v>224.65</v>
       </c>
       <c r="H139" s="29">
-        <v>0.3839</v>
+        <v>0.3815</v>
       </c>
       <c r="I139" s="29">
         <v>0.0</v>
@@ -26568,16 +26568,16 @@
         <v>262.0</v>
       </c>
       <c r="E140" s="28">
-        <v>676.5</v>
+        <v>676.3</v>
       </c>
       <c r="F140" s="28">
-        <v>676.5</v>
+        <v>676.3</v>
       </c>
       <c r="G140" s="28">
-        <v>414.5</v>
+        <v>414.3</v>
       </c>
       <c r="H140" s="29">
-        <v>1.5821</v>
+        <v>1.5813</v>
       </c>
       <c r="I140" s="29">
         <v>0.0</v>
@@ -26612,16 +26612,16 @@
         <v>811.65</v>
       </c>
       <c r="E141" s="28">
-        <v>126.62</v>
+        <v>126.7</v>
       </c>
       <c r="F141" s="28">
-        <v>633.1</v>
+        <v>633.5</v>
       </c>
       <c r="G141" s="28">
-        <v>-178.55</v>
+        <v>-178.15</v>
       </c>
       <c r="H141" s="29">
-        <v>-0.22</v>
+        <v>-0.2195</v>
       </c>
       <c r="I141" s="29">
         <v>0.0</v>
@@ -26656,16 +26656,16 @@
         <v>53.6</v>
       </c>
       <c r="E142" s="28">
-        <v>503.0</v>
+        <v>502.2</v>
       </c>
       <c r="F142" s="28">
-        <v>503.0</v>
+        <v>502.2</v>
       </c>
       <c r="G142" s="28">
-        <v>449.4</v>
+        <v>448.6</v>
       </c>
       <c r="H142" s="29">
-        <v>8.3843</v>
+        <v>8.3694</v>
       </c>
       <c r="I142" s="29">
         <v>0.0</v>
@@ -26700,16 +26700,16 @@
         <v>222.45</v>
       </c>
       <c r="E143" s="28">
-        <v>398.1</v>
+        <v>398.15</v>
       </c>
       <c r="F143" s="28">
-        <v>398.1</v>
+        <v>398.15</v>
       </c>
       <c r="G143" s="28">
-        <v>175.65</v>
+        <v>175.7</v>
       </c>
       <c r="H143" s="29">
-        <v>0.7896</v>
+        <v>0.7898</v>
       </c>
       <c r="I143" s="29">
         <v>0.0</v>
@@ -26744,16 +26744,16 @@
         <v>394.05</v>
       </c>
       <c r="E144" s="28">
-        <v>329.0</v>
+        <v>327.85</v>
       </c>
       <c r="F144" s="28">
-        <v>329.0</v>
+        <v>327.85</v>
       </c>
       <c r="G144" s="28">
-        <v>-65.05</v>
+        <v>-66.2</v>
       </c>
       <c r="H144" s="29">
-        <v>-0.1651</v>
+        <v>-0.168</v>
       </c>
       <c r="I144" s="29">
         <v>0.0</v>
@@ -26832,16 +26832,16 @@
         <v>165.85</v>
       </c>
       <c r="E146" s="28">
-        <v>282.0</v>
+        <v>281.05</v>
       </c>
       <c r="F146" s="28">
-        <v>282.0</v>
+        <v>281.05</v>
       </c>
       <c r="G146" s="28">
-        <v>116.15</v>
+        <v>115.2</v>
       </c>
       <c r="H146" s="29">
-        <v>0.7003</v>
+        <v>0.6946</v>
       </c>
       <c r="I146" s="29">
         <v>0.0</v>
@@ -26876,16 +26876,16 @@
         <v>142.65</v>
       </c>
       <c r="E147" s="28">
-        <v>275.0</v>
+        <v>274.75</v>
       </c>
       <c r="F147" s="28">
-        <v>275.0</v>
+        <v>274.75</v>
       </c>
       <c r="G147" s="28">
-        <v>132.35</v>
+        <v>132.1</v>
       </c>
       <c r="H147" s="29">
-        <v>0.9278</v>
+        <v>0.926</v>
       </c>
       <c r="I147" s="29">
         <v>0.0</v>
@@ -26920,16 +26920,16 @@
         <v>111.28</v>
       </c>
       <c r="E148" s="28">
-        <v>230.88</v>
+        <v>231.05</v>
       </c>
       <c r="F148" s="28">
-        <v>230.88</v>
+        <v>231.05</v>
       </c>
       <c r="G148" s="28">
-        <v>119.6</v>
+        <v>119.77</v>
       </c>
       <c r="H148" s="29">
-        <v>1.0748</v>
+        <v>1.0763</v>
       </c>
       <c r="I148" s="29">
         <v>0.0</v>
@@ -26964,16 +26964,16 @@
         <v>25.25</v>
       </c>
       <c r="E149" s="28">
-        <v>135.31</v>
+        <v>135.45</v>
       </c>
       <c r="F149" s="28">
-        <v>135.31</v>
+        <v>135.45</v>
       </c>
       <c r="G149" s="28">
-        <v>110.06</v>
+        <v>110.2</v>
       </c>
       <c r="H149" s="29">
-        <v>4.3588</v>
+        <v>4.3644</v>
       </c>
       <c r="I149" s="29">
         <v>0.0</v>
@@ -27052,16 +27052,16 @@
         <v>51.86</v>
       </c>
       <c r="E151" s="28">
-        <v>95.65</v>
+        <v>95.26</v>
       </c>
       <c r="F151" s="28">
-        <v>95.65</v>
+        <v>95.26</v>
       </c>
       <c r="G151" s="28">
-        <v>43.79</v>
+        <v>43.4</v>
       </c>
       <c r="H151" s="29">
-        <v>0.8443</v>
+        <v>0.8368</v>
       </c>
       <c r="I151" s="29">
         <v>0.0</v>

--- a/data/portfolio.xlsx
+++ b/data/portfolio.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3845" uniqueCount="228">
   <si>
-    <t>Account Name</t>
+    <t>t</t>
   </si>
   <si>
     <t>Symbol</t>

--- a/data/portfolio.xlsx
+++ b/data/portfolio.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3915" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3907" uniqueCount="231">
   <si>
     <t>Account Name</t>
   </si>
@@ -719,7 +719,7 @@
     <numFmt numFmtId="165" formatCode="[Green]#,##,##0;[Red]-#,##,##0"/>
     <numFmt numFmtId="166" formatCode="[Green]0%;[Red]-0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -762,6 +762,16 @@
       <sz val="11.0"/>
       <color rgb="FFF35631"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -848,7 +858,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -948,10 +958,13 @@
     <xf borderId="0" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="7" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -15355,7 +15368,7 @@
         <v>17</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
     </row>
     <row r="76">
@@ -15932,8 +15945,8 @@
       <c r="D109" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E109" s="10" t="s">
-        <v>17</v>
+      <c r="E109" s="33" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="110">
@@ -16766,11 +16779,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="33" t="s">
+      <c r="A159" s="34" t="s">
         <v>21</v>
       </c>
       <c r="B159" s="10" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C159" s="10" t="s">
         <v>16</v>
@@ -16781,16 +16794,13 @@
       <c r="E159" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F159" s="33" t="s">
-        <v>199</v>
-      </c>
     </row>
     <row r="160">
-      <c r="A160" s="33" t="s">
+      <c r="A160" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="B160" s="33" t="s">
-        <v>22</v>
+      <c r="B160" s="34" t="s">
+        <v>25</v>
       </c>
       <c r="C160" s="10" t="s">
         <v>16</v>
@@ -16798,19 +16808,16 @@
       <c r="D160" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E160" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F160" s="33" t="s">
-        <v>199</v>
+      <c r="E160" s="33" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="33" t="s">
+      <c r="A161" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="B161" s="33" t="s">
-        <v>22</v>
+      <c r="B161" s="34" t="s">
+        <v>25</v>
       </c>
       <c r="C161" s="10" t="s">
         <v>16</v>
@@ -16821,18 +16828,15 @@
       <c r="E161" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F161" s="33" t="s">
-        <v>199</v>
-      </c>
     </row>
     <row r="162">
-      <c r="A162" s="33" t="s">
+      <c r="A162" s="34" t="s">
         <v>141</v>
       </c>
-      <c r="B162" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C162" s="33" t="s">
+      <c r="B162" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C162" s="34" t="s">
         <v>16</v>
       </c>
       <c r="D162" s="10" t="s">
@@ -16841,18 +16845,15 @@
       <c r="E162" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F162" s="33" t="s">
-        <v>199</v>
-      </c>
     </row>
     <row r="163">
-      <c r="A163" s="33" t="s">
+      <c r="A163" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="B163" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C163" s="33" t="s">
+      <c r="B163" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C163" s="34" t="s">
         <v>16</v>
       </c>
       <c r="D163" s="10" t="s">
@@ -16861,18 +16862,15 @@
       <c r="E163" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F163" s="33" t="s">
-        <v>199</v>
-      </c>
     </row>
     <row r="164">
-      <c r="A164" s="33" t="s">
+      <c r="A164" s="34" t="s">
         <v>194</v>
       </c>
-      <c r="B164" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C164" s="33" t="s">
+      <c r="B164" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C164" s="34" t="s">
         <v>50</v>
       </c>
       <c r="D164" s="10" t="s">
@@ -16881,48 +16879,39 @@
       <c r="E164" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F164" s="33" t="s">
-        <v>199</v>
-      </c>
     </row>
     <row r="165">
-      <c r="A165" s="33" t="s">
+      <c r="A165" s="34" t="s">
         <v>196</v>
       </c>
       <c r="B165" s="33" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C165" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D165" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="E165" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="F165" s="33" t="s">
-        <v>199</v>
+      <c r="D165" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="E165" s="34" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="33" t="s">
+      <c r="A166" s="34" t="s">
         <v>195</v>
       </c>
       <c r="B166" s="33" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C166" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D166" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="E166" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="F166" s="33" t="s">
-        <v>199</v>
+      <c r="D166" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="E166" s="34" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -18065,28 +18054,28 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="35" t="s">
         <v>227</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="35" t="s">
         <v>228</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="34" t="s">
+      <c r="H1" s="35" t="s">
         <v>12</v>
       </c>
     </row>
@@ -20902,8 +20891,8 @@
       <c r="A110" s="4"/>
       <c r="B110" s="29"/>
       <c r="C110" s="29"/>
-      <c r="D110" s="35"/>
-      <c r="E110" s="36"/>
+      <c r="D110" s="36"/>
+      <c r="E110" s="37"/>
       <c r="F110" s="30"/>
       <c r="G110" s="4"/>
       <c r="H110" s="4"/>
@@ -20941,46 +20930,46 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="G1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="37" t="s">
+      <c r="H1" s="38" t="s">
         <v>227</v>
       </c>
-      <c r="I1" s="37" t="s">
+      <c r="I1" s="38" t="s">
         <v>228</v>
       </c>
-      <c r="J1" s="37" t="s">
+      <c r="J1" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="37" t="s">
+      <c r="L1" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="37" t="s">
+      <c r="M1" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="37" t="s">
+      <c r="N1" s="38" t="s">
         <v>12</v>
       </c>
     </row>
